--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="317">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,9 @@
     <t>['31', '51', '90+3']</t>
   </si>
   <si>
+    <t>['14']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -803,9 +806,6 @@
   </si>
   <si>
     <t>['16', '26', '57', '65', '71']</t>
-  </si>
-  <si>
-    <t>['14']</t>
   </si>
   <si>
     <t>['35', '51']</t>
@@ -1326,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1582,7 +1582,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1994,7 +1994,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2200,7 +2200,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2406,7 +2406,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2612,7 +2612,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3024,7 +3024,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3230,7 +3230,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3642,7 +3642,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3723,7 +3723,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3848,7 +3848,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4054,7 +4054,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4260,7 +4260,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16">
         <v>0.5600000000000001</v>
@@ -4672,7 +4672,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5290,7 +5290,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5702,7 +5702,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6114,7 +6114,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6320,7 +6320,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6526,7 +6526,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6732,7 +6732,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6938,7 +6938,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7144,7 +7144,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7225,7 +7225,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ29">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR29">
         <v>1.7</v>
@@ -7350,7 +7350,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7556,7 +7556,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7634,7 +7634,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ31">
         <v>2.3</v>
@@ -7762,7 +7762,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7968,7 +7968,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8380,7 +8380,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8998,7 +8998,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9410,7 +9410,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9616,7 +9616,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9822,7 +9822,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10234,7 +10234,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10440,7 +10440,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10646,7 +10646,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11058,7 +11058,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11342,7 +11342,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ49">
         <v>0.8</v>
@@ -11470,7 +11470,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11676,7 +11676,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11882,7 +11882,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11963,7 +11963,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ52">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -12294,7 +12294,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12500,7 +12500,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12706,7 +12706,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12912,7 +12912,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13324,7 +13324,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13530,7 +13530,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13736,7 +13736,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14148,7 +14148,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14354,7 +14354,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14560,7 +14560,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14766,7 +14766,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15178,7 +15178,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15590,7 +15590,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15668,7 +15668,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ70">
         <v>2.11</v>
@@ -15796,7 +15796,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16002,7 +16002,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -17937,7 +17937,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ81">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR81">
         <v>1.64</v>
@@ -18758,7 +18758,7 @@
         <v>0.5</v>
       </c>
       <c r="AP85">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ85">
         <v>0.33</v>
@@ -21645,7 +21645,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ99">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -23084,7 +23084,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ106">
         <v>1.33</v>
@@ -25066,7 +25066,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25353,7 +25353,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ117">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR117">
         <v>1.29</v>
@@ -27538,7 +27538,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -28237,7 +28237,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ131">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR131">
         <v>1.54</v>
@@ -28646,7 +28646,7 @@
         <v>0.71</v>
       </c>
       <c r="AP133">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ133">
         <v>0.5</v>
@@ -31040,7 +31040,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31945,7 +31945,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ149">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR149">
         <v>2.17</v>
@@ -32766,7 +32766,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ153">
         <v>0.7</v>
@@ -34623,7 +34623,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ162">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR162">
         <v>1.42</v>
@@ -34826,7 +34826,7 @@
         <v>0.63</v>
       </c>
       <c r="AP163">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ163">
         <v>0.89</v>
@@ -36759,6 +36759,212 @@
       </c>
       <c r="BP172">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7491990</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45688.6875</v>
+      </c>
+      <c r="F173">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>84</v>
+      </c>
+      <c r="H173" t="s">
+        <v>75</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>1</v>
+      </c>
+      <c r="O173" t="s">
+        <v>214</v>
+      </c>
+      <c r="P173" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q173">
+        <v>3</v>
+      </c>
+      <c r="R173">
+        <v>2.2</v>
+      </c>
+      <c r="S173">
+        <v>3.4</v>
+      </c>
+      <c r="T173">
+        <v>1.36</v>
+      </c>
+      <c r="U173">
+        <v>3</v>
+      </c>
+      <c r="V173">
+        <v>2.63</v>
+      </c>
+      <c r="W173">
+        <v>1.44</v>
+      </c>
+      <c r="X173">
+        <v>7</v>
+      </c>
+      <c r="Y173">
+        <v>1.1</v>
+      </c>
+      <c r="Z173">
+        <v>2.32</v>
+      </c>
+      <c r="AA173">
+        <v>3.54</v>
+      </c>
+      <c r="AB173">
+        <v>2.94</v>
+      </c>
+      <c r="AC173">
+        <v>1.04</v>
+      </c>
+      <c r="AD173">
+        <v>13</v>
+      </c>
+      <c r="AE173">
+        <v>1.28</v>
+      </c>
+      <c r="AF173">
+        <v>3.75</v>
+      </c>
+      <c r="AG173">
+        <v>1.74</v>
+      </c>
+      <c r="AH173">
+        <v>2.1</v>
+      </c>
+      <c r="AI173">
+        <v>1.62</v>
+      </c>
+      <c r="AJ173">
+        <v>2.2</v>
+      </c>
+      <c r="AK173">
+        <v>1.45</v>
+      </c>
+      <c r="AL173">
+        <v>1.25</v>
+      </c>
+      <c r="AM173">
+        <v>1.6</v>
+      </c>
+      <c r="AN173">
+        <v>1.11</v>
+      </c>
+      <c r="AO173">
+        <v>1.56</v>
+      </c>
+      <c r="AP173">
+        <v>1.3</v>
+      </c>
+      <c r="AQ173">
+        <v>1.4</v>
+      </c>
+      <c r="AR173">
+        <v>1.38</v>
+      </c>
+      <c r="AS173">
+        <v>1.16</v>
+      </c>
+      <c r="AT173">
+        <v>2.54</v>
+      </c>
+      <c r="AU173">
+        <v>6</v>
+      </c>
+      <c r="AV173">
+        <v>3</v>
+      </c>
+      <c r="AW173">
+        <v>8</v>
+      </c>
+      <c r="AX173">
+        <v>10</v>
+      </c>
+      <c r="AY173">
+        <v>14</v>
+      </c>
+      <c r="AZ173">
+        <v>17</v>
+      </c>
+      <c r="BA173">
+        <v>3</v>
+      </c>
+      <c r="BB173">
+        <v>8</v>
+      </c>
+      <c r="BC173">
+        <v>11</v>
+      </c>
+      <c r="BD173">
+        <v>1.89</v>
+      </c>
+      <c r="BE173">
+        <v>6.4</v>
+      </c>
+      <c r="BF173">
+        <v>2.1</v>
+      </c>
+      <c r="BG173">
+        <v>1.3</v>
+      </c>
+      <c r="BH173">
+        <v>3.15</v>
+      </c>
+      <c r="BI173">
+        <v>1.52</v>
+      </c>
+      <c r="BJ173">
+        <v>2.33</v>
+      </c>
+      <c r="BK173">
+        <v>1.88</v>
+      </c>
+      <c r="BL173">
+        <v>1.92</v>
+      </c>
+      <c r="BM173">
+        <v>2.32</v>
+      </c>
+      <c r="BN173">
+        <v>1.53</v>
+      </c>
+      <c r="BO173">
+        <v>3</v>
+      </c>
+      <c r="BP173">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="326">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -661,6 +661,18 @@
     <t>['14']</t>
   </si>
   <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['19', '45+3', '46', '54']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -965,6 +977,21 @@
   </si>
   <si>
     <t>['26', '71']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['25', '81']</t>
+  </si>
+  <si>
+    <t>['62', '90+1', '90+3']</t>
+  </si>
+  <si>
+    <t>['33', '63']</t>
+  </si>
+  <si>
+    <t>['50']</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1582,7 +1609,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1994,7 +2021,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2075,7 +2102,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ4">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2200,7 +2227,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2406,7 +2433,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2612,7 +2639,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3024,7 +3051,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3230,7 +3257,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3308,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ10">
         <v>0.7</v>
@@ -3514,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ11">
         <v>1.2</v>
@@ -3642,7 +3669,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3720,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ12">
         <v>1.4</v>
@@ -3848,7 +3875,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3929,7 +3956,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ13">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4054,7 +4081,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4132,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ14">
         <v>0.78</v>
@@ -4260,7 +4287,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4338,10 +4365,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ15">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4547,7 +4574,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ16">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4672,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4753,7 +4780,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ17">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4956,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ18">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5162,10 +5189,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ19">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5290,7 +5317,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5702,7 +5729,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6114,7 +6141,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6320,7 +6347,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6526,7 +6553,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6732,7 +6759,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6938,7 +6965,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7144,7 +7171,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7350,7 +7377,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7428,10 +7455,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ30">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7556,7 +7583,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7762,7 +7789,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7840,7 +7867,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ32">
         <v>0.78</v>
@@ -7968,7 +7995,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8046,10 +8073,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ33">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR33">
         <v>1.57</v>
@@ -8252,10 +8279,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ34">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR34">
         <v>1.86</v>
@@ -8380,7 +8407,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8461,7 +8488,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ35">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR35">
         <v>2.58</v>
@@ -8664,10 +8691,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ36">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR36">
         <v>2.62</v>
@@ -8870,10 +8897,10 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR37">
         <v>1.27</v>
@@ -8998,7 +9025,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9410,7 +9437,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9616,7 +9643,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9822,7 +9849,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10109,7 +10136,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR43">
         <v>1.14</v>
@@ -10234,7 +10261,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10312,7 +10339,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ44">
         <v>2.11</v>
@@ -10440,7 +10467,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10646,7 +10673,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10933,7 +10960,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ47">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR47">
         <v>2.02</v>
@@ -11058,7 +11085,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11139,7 +11166,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ48">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR48">
         <v>2.42</v>
@@ -11345,7 +11372,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ49">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>0.41</v>
@@ -11470,7 +11497,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11548,10 +11575,10 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ50">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11676,7 +11703,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11754,10 +11781,10 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ51">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR51">
         <v>1.37</v>
@@ -11882,7 +11909,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11960,7 +11987,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ52">
         <v>1.4</v>
@@ -12166,10 +12193,10 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ53">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12294,7 +12321,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12372,7 +12399,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ54">
         <v>2.3</v>
@@ -12500,7 +12527,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12578,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ55">
         <v>0.78</v>
@@ -12706,7 +12733,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12912,7 +12939,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13324,7 +13351,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13405,7 +13432,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ59">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR59">
         <v>1.71</v>
@@ -13530,7 +13557,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13611,7 +13638,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ60">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR60">
         <v>1.26</v>
@@ -13736,7 +13763,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14020,7 +14047,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ62">
         <v>1.33</v>
@@ -14148,7 +14175,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14354,7 +14381,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14560,7 +14587,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14641,7 +14668,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ65">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR65">
         <v>1.22</v>
@@ -14766,7 +14793,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14847,7 +14874,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ66">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15050,10 +15077,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ67">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR67">
         <v>1.52</v>
@@ -15178,7 +15205,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15259,7 +15286,7 @@
         <v>2</v>
       </c>
       <c r="AQ68">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15462,10 +15489,10 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ69">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR69">
         <v>2.2</v>
@@ -15590,7 +15617,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15796,7 +15823,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15874,7 +15901,7 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ71">
         <v>2.3</v>
@@ -16080,7 +16107,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ72">
         <v>1.7</v>
@@ -16286,7 +16313,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ73">
         <v>0.78</v>
@@ -16698,7 +16725,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -16826,7 +16853,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16904,7 +16931,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ76">
         <v>0.1</v>
@@ -17032,7 +17059,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17525,7 +17552,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ79">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR79">
         <v>1.14</v>
@@ -17731,7 +17758,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ80">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR80">
         <v>1.88</v>
@@ -18346,10 +18373,10 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ83">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.3</v>
@@ -18474,7 +18501,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18552,7 +18579,7 @@
         <v>2.6</v>
       </c>
       <c r="AP84">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ84">
         <v>2.3</v>
@@ -18761,7 +18788,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ85">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR85">
         <v>0.97</v>
@@ -18886,7 +18913,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -18967,7 +18994,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ86">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR86">
         <v>1.34</v>
@@ -19092,7 +19119,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19170,7 +19197,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ87">
         <v>2.11</v>
@@ -19379,7 +19406,7 @@
         <v>2</v>
       </c>
       <c r="AQ88">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR88">
         <v>1.44</v>
@@ -19710,7 +19737,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19788,7 +19815,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ90">
         <v>1.7</v>
@@ -19916,7 +19943,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19994,10 +20021,10 @@
         <v>1.75</v>
       </c>
       <c r="AP91">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ91">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20200,10 +20227,10 @@
         <v>0.25</v>
       </c>
       <c r="AP92">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ92">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR92">
         <v>1.83</v>
@@ -20328,7 +20355,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20612,7 +20639,7 @@
         <v>0</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ94">
         <v>0.1</v>
@@ -20821,7 +20848,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ95">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR95">
         <v>1.86</v>
@@ -20946,7 +20973,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21027,7 +21054,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ96">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -21436,7 +21463,7 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ98">
         <v>1.7</v>
@@ -21564,7 +21591,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21976,7 +22003,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22054,10 +22081,10 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ101">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR101">
         <v>1.26</v>
@@ -22182,7 +22209,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22260,7 +22287,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ102">
         <v>2.11</v>
@@ -22388,7 +22415,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22469,7 +22496,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ103">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -22800,7 +22827,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22881,7 +22908,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR105">
         <v>1.47</v>
@@ -23006,7 +23033,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23212,7 +23239,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23624,7 +23651,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23702,7 +23729,7 @@
         <v>1.67</v>
       </c>
       <c r="AP109">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ109">
         <v>1.7</v>
@@ -23830,7 +23857,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23908,7 +23935,7 @@
         <v>0.83</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ110">
         <v>0.5</v>
@@ -24036,7 +24063,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24117,7 +24144,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ111">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR111">
         <v>1.13</v>
@@ -24242,7 +24269,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24320,7 +24347,7 @@
         <v>1.67</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ112">
         <v>1.7</v>
@@ -24448,7 +24475,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24526,10 +24553,10 @@
         <v>0.2</v>
       </c>
       <c r="AP113">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ113">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR113">
         <v>1.55</v>
@@ -24654,7 +24681,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24732,7 +24759,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ114">
         <v>0.7</v>
@@ -25066,7 +25093,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25147,7 +25174,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ116">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR116">
         <v>1.64</v>
@@ -25272,7 +25299,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25559,7 +25586,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ118">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>1.77</v>
@@ -25684,7 +25711,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25765,7 +25792,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ119">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR119">
         <v>1.52</v>
@@ -25890,7 +25917,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25968,7 +25995,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ120">
         <v>0.1</v>
@@ -26096,7 +26123,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26302,7 +26329,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26508,7 +26535,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26589,7 +26616,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ123">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26714,7 +26741,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26792,7 +26819,7 @@
         <v>1.86</v>
       </c>
       <c r="AP124">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ124">
         <v>1.7</v>
@@ -26920,7 +26947,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -26998,7 +27025,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ125">
         <v>1.33</v>
@@ -27126,7 +27153,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27332,7 +27359,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27538,7 +27565,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27616,10 +27643,10 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ128">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR128">
         <v>2.15</v>
@@ -27744,7 +27771,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27825,7 +27852,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ129">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -27950,7 +27977,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28028,7 +28055,7 @@
         <v>0.86</v>
       </c>
       <c r="AP130">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ130">
         <v>1.2</v>
@@ -28156,7 +28183,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28234,7 +28261,7 @@
         <v>1.83</v>
       </c>
       <c r="AP131">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ131">
         <v>1.4</v>
@@ -28362,7 +28389,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28443,7 +28470,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ132">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR132">
         <v>1.76</v>
@@ -28568,7 +28595,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28855,7 +28882,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ134">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR134">
         <v>2.13</v>
@@ -29058,7 +29085,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ135">
         <v>0.7</v>
@@ -29186,7 +29213,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29267,7 +29294,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ136">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR136">
         <v>1.28</v>
@@ -29392,7 +29419,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29679,7 +29706,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ138">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR138">
         <v>1.83</v>
@@ -29882,7 +29909,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ139">
         <v>0.5</v>
@@ -30010,7 +30037,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30091,7 +30118,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ140">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR140">
         <v>1.59</v>
@@ -30422,7 +30449,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30500,7 +30527,7 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ142">
         <v>1.7</v>
@@ -30834,7 +30861,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31040,7 +31067,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31246,7 +31273,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31327,7 +31354,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ146">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR146">
         <v>1.19</v>
@@ -31530,10 +31557,10 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ147">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR147">
         <v>1.77</v>
@@ -31739,7 +31766,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ148">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR148">
         <v>1.3</v>
@@ -32148,7 +32175,7 @@
         <v>1.13</v>
       </c>
       <c r="AP150">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ150">
         <v>1.2</v>
@@ -32276,7 +32303,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32354,10 +32381,10 @@
         <v>1.63</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ151">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR151">
         <v>1.96</v>
@@ -32560,7 +32587,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ152">
         <v>0.78</v>
@@ -32688,7 +32715,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32894,7 +32921,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -32972,10 +32999,10 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ154">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33178,10 +33205,10 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ155">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR155">
         <v>1.87</v>
@@ -33306,7 +33333,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33512,7 +33539,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33590,10 +33617,10 @@
         <v>1.44</v>
       </c>
       <c r="AP157">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ157">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR157">
         <v>1.22</v>
@@ -33718,7 +33745,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -33796,7 +33823,7 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ158">
         <v>1.2</v>
@@ -34002,10 +34029,10 @@
         <v>0.89</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ159">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR159">
         <v>1.95</v>
@@ -34130,7 +34157,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34208,10 +34235,10 @@
         <v>2</v>
       </c>
       <c r="AP160">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ160">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR160">
         <v>2.29</v>
@@ -34336,7 +34363,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34417,7 +34444,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ161">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR161">
         <v>2.2</v>
@@ -34542,7 +34569,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34620,7 +34647,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ162">
         <v>1.4</v>
@@ -34748,7 +34775,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34829,7 +34856,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ163">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR163">
         <v>1.3</v>
@@ -34954,7 +34981,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35035,7 +35062,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ164">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR164">
         <v>1.34</v>
@@ -35572,7 +35599,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q167">
         <v>2.1</v>
@@ -35778,7 +35805,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -35984,7 +36011,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q169">
         <v>7</v>
@@ -36396,7 +36423,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36680,7 +36707,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP172">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ172">
         <v>0.5</v>
@@ -36907,16 +36934,16 @@
         <v>3</v>
       </c>
       <c r="AW173">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX173">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY173">
+        <v>13</v>
+      </c>
+      <c r="AZ173">
         <v>14</v>
-      </c>
-      <c r="AZ173">
-        <v>17</v>
       </c>
       <c r="BA173">
         <v>3</v>
@@ -36965,6 +36992,1448 @@
       </c>
       <c r="BP173">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7491993</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45689.47916666666</v>
+      </c>
+      <c r="F174">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>78</v>
+      </c>
+      <c r="H174" t="s">
+        <v>74</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>1</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>2</v>
+      </c>
+      <c r="O174" t="s">
+        <v>215</v>
+      </c>
+      <c r="P174" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q174">
+        <v>3.1</v>
+      </c>
+      <c r="R174">
+        <v>2.05</v>
+      </c>
+      <c r="S174">
+        <v>3.75</v>
+      </c>
+      <c r="T174">
+        <v>1.5</v>
+      </c>
+      <c r="U174">
+        <v>2.5</v>
+      </c>
+      <c r="V174">
+        <v>3.4</v>
+      </c>
+      <c r="W174">
+        <v>1.3</v>
+      </c>
+      <c r="X174">
+        <v>10</v>
+      </c>
+      <c r="Y174">
+        <v>1.06</v>
+      </c>
+      <c r="Z174">
+        <v>2.4</v>
+      </c>
+      <c r="AA174">
+        <v>3.26</v>
+      </c>
+      <c r="AB174">
+        <v>3.21</v>
+      </c>
+      <c r="AC174">
+        <v>1.08</v>
+      </c>
+      <c r="AD174">
+        <v>8.5</v>
+      </c>
+      <c r="AE174">
+        <v>1.4</v>
+      </c>
+      <c r="AF174">
+        <v>3</v>
+      </c>
+      <c r="AG174">
+        <v>1.95</v>
+      </c>
+      <c r="AH174">
+        <v>1.75</v>
+      </c>
+      <c r="AI174">
+        <v>1.95</v>
+      </c>
+      <c r="AJ174">
+        <v>1.8</v>
+      </c>
+      <c r="AK174">
+        <v>1.33</v>
+      </c>
+      <c r="AL174">
+        <v>1.34</v>
+      </c>
+      <c r="AM174">
+        <v>1.6</v>
+      </c>
+      <c r="AN174">
+        <v>0.89</v>
+      </c>
+      <c r="AO174">
+        <v>0.89</v>
+      </c>
+      <c r="AP174">
+        <v>0.9</v>
+      </c>
+      <c r="AQ174">
+        <v>0.9</v>
+      </c>
+      <c r="AR174">
+        <v>1.36</v>
+      </c>
+      <c r="AS174">
+        <v>1.05</v>
+      </c>
+      <c r="AT174">
+        <v>2.41</v>
+      </c>
+      <c r="AU174">
+        <v>3</v>
+      </c>
+      <c r="AV174">
+        <v>0</v>
+      </c>
+      <c r="AW174">
+        <v>4</v>
+      </c>
+      <c r="AX174">
+        <v>2</v>
+      </c>
+      <c r="AY174">
+        <v>9</v>
+      </c>
+      <c r="AZ174">
+        <v>3</v>
+      </c>
+      <c r="BA174">
+        <v>3</v>
+      </c>
+      <c r="BB174">
+        <v>1</v>
+      </c>
+      <c r="BC174">
+        <v>4</v>
+      </c>
+      <c r="BD174">
+        <v>1.73</v>
+      </c>
+      <c r="BE174">
+        <v>6.5</v>
+      </c>
+      <c r="BF174">
+        <v>2.33</v>
+      </c>
+      <c r="BG174">
+        <v>1.32</v>
+      </c>
+      <c r="BH174">
+        <v>3.05</v>
+      </c>
+      <c r="BI174">
+        <v>1.55</v>
+      </c>
+      <c r="BJ174">
+        <v>2.25</v>
+      </c>
+      <c r="BK174">
+        <v>1.9</v>
+      </c>
+      <c r="BL174">
+        <v>1.79</v>
+      </c>
+      <c r="BM174">
+        <v>2.4</v>
+      </c>
+      <c r="BN174">
+        <v>1.49</v>
+      </c>
+      <c r="BO174">
+        <v>3.15</v>
+      </c>
+      <c r="BP174">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7491992</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45689.47916666666</v>
+      </c>
+      <c r="F175">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>83</v>
+      </c>
+      <c r="H175" t="s">
+        <v>73</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175">
+        <v>1</v>
+      </c>
+      <c r="N175">
+        <v>1</v>
+      </c>
+      <c r="O175" t="s">
+        <v>96</v>
+      </c>
+      <c r="P175" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q175">
+        <v>3.25</v>
+      </c>
+      <c r="R175">
+        <v>2.2</v>
+      </c>
+      <c r="S175">
+        <v>3.1</v>
+      </c>
+      <c r="T175">
+        <v>1.36</v>
+      </c>
+      <c r="U175">
+        <v>3</v>
+      </c>
+      <c r="V175">
+        <v>2.63</v>
+      </c>
+      <c r="W175">
+        <v>1.44</v>
+      </c>
+      <c r="X175">
+        <v>7</v>
+      </c>
+      <c r="Y175">
+        <v>1.1</v>
+      </c>
+      <c r="Z175">
+        <v>2.82</v>
+      </c>
+      <c r="AA175">
+        <v>3.47</v>
+      </c>
+      <c r="AB175">
+        <v>2.55</v>
+      </c>
+      <c r="AC175">
+        <v>1.04</v>
+      </c>
+      <c r="AD175">
+        <v>13</v>
+      </c>
+      <c r="AE175">
+        <v>1.25</v>
+      </c>
+      <c r="AF175">
+        <v>4</v>
+      </c>
+      <c r="AG175">
+        <v>1.81</v>
+      </c>
+      <c r="AH175">
+        <v>2.01</v>
+      </c>
+      <c r="AI175">
+        <v>1.62</v>
+      </c>
+      <c r="AJ175">
+        <v>2.2</v>
+      </c>
+      <c r="AK175">
+        <v>1.52</v>
+      </c>
+      <c r="AL175">
+        <v>1.29</v>
+      </c>
+      <c r="AM175">
+        <v>1.46</v>
+      </c>
+      <c r="AN175">
+        <v>1</v>
+      </c>
+      <c r="AO175">
+        <v>0.8</v>
+      </c>
+      <c r="AP175">
+        <v>0.9</v>
+      </c>
+      <c r="AQ175">
+        <v>1</v>
+      </c>
+      <c r="AR175">
+        <v>1.23</v>
+      </c>
+      <c r="AS175">
+        <v>1.17</v>
+      </c>
+      <c r="AT175">
+        <v>2.4</v>
+      </c>
+      <c r="AU175">
+        <v>5</v>
+      </c>
+      <c r="AV175">
+        <v>6</v>
+      </c>
+      <c r="AW175">
+        <v>18</v>
+      </c>
+      <c r="AX175">
+        <v>8</v>
+      </c>
+      <c r="AY175">
+        <v>28</v>
+      </c>
+      <c r="AZ175">
+        <v>19</v>
+      </c>
+      <c r="BA175">
+        <v>9</v>
+      </c>
+      <c r="BB175">
+        <v>7</v>
+      </c>
+      <c r="BC175">
+        <v>16</v>
+      </c>
+      <c r="BD175">
+        <v>1.97</v>
+      </c>
+      <c r="BE175">
+        <v>6.4</v>
+      </c>
+      <c r="BF175">
+        <v>2.05</v>
+      </c>
+      <c r="BG175">
+        <v>1.3</v>
+      </c>
+      <c r="BH175">
+        <v>3.05</v>
+      </c>
+      <c r="BI175">
+        <v>1.55</v>
+      </c>
+      <c r="BJ175">
+        <v>2.28</v>
+      </c>
+      <c r="BK175">
+        <v>1.9</v>
+      </c>
+      <c r="BL175">
+        <v>1.79</v>
+      </c>
+      <c r="BM175">
+        <v>2.4</v>
+      </c>
+      <c r="BN175">
+        <v>1.49</v>
+      </c>
+      <c r="BO175">
+        <v>3.15</v>
+      </c>
+      <c r="BP175">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7491986</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45689.47916666666</v>
+      </c>
+      <c r="F176">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>80</v>
+      </c>
+      <c r="H176" t="s">
+        <v>70</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>2</v>
+      </c>
+      <c r="N176">
+        <v>3</v>
+      </c>
+      <c r="O176" t="s">
+        <v>216</v>
+      </c>
+      <c r="P176" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q176">
+        <v>2</v>
+      </c>
+      <c r="R176">
+        <v>2.6</v>
+      </c>
+      <c r="S176">
+        <v>5</v>
+      </c>
+      <c r="T176">
+        <v>1.25</v>
+      </c>
+      <c r="U176">
+        <v>3.75</v>
+      </c>
+      <c r="V176">
+        <v>2.1</v>
+      </c>
+      <c r="W176">
+        <v>1.67</v>
+      </c>
+      <c r="X176">
+        <v>4.5</v>
+      </c>
+      <c r="Y176">
+        <v>1.18</v>
+      </c>
+      <c r="Z176">
+        <v>1.5</v>
+      </c>
+      <c r="AA176">
+        <v>5.1</v>
+      </c>
+      <c r="AB176">
+        <v>5.8</v>
+      </c>
+      <c r="AC176">
+        <v>1.01</v>
+      </c>
+      <c r="AD176">
+        <v>17</v>
+      </c>
+      <c r="AE176">
+        <v>1.13</v>
+      </c>
+      <c r="AF176">
+        <v>6</v>
+      </c>
+      <c r="AG176">
+        <v>1.4</v>
+      </c>
+      <c r="AH176">
+        <v>2.82</v>
+      </c>
+      <c r="AI176">
+        <v>1.53</v>
+      </c>
+      <c r="AJ176">
+        <v>2.38</v>
+      </c>
+      <c r="AK176">
+        <v>1.15</v>
+      </c>
+      <c r="AL176">
+        <v>1.18</v>
+      </c>
+      <c r="AM176">
+        <v>2.55</v>
+      </c>
+      <c r="AN176">
+        <v>2</v>
+      </c>
+      <c r="AO176">
+        <v>0.89</v>
+      </c>
+      <c r="AP176">
+        <v>1.82</v>
+      </c>
+      <c r="AQ176">
+        <v>1.1</v>
+      </c>
+      <c r="AR176">
+        <v>1.91</v>
+      </c>
+      <c r="AS176">
+        <v>1.32</v>
+      </c>
+      <c r="AT176">
+        <v>3.23</v>
+      </c>
+      <c r="AU176">
+        <v>4</v>
+      </c>
+      <c r="AV176">
+        <v>7</v>
+      </c>
+      <c r="AW176">
+        <v>8</v>
+      </c>
+      <c r="AX176">
+        <v>6</v>
+      </c>
+      <c r="AY176">
+        <v>15</v>
+      </c>
+      <c r="AZ176">
+        <v>15</v>
+      </c>
+      <c r="BA176">
+        <v>2</v>
+      </c>
+      <c r="BB176">
+        <v>0</v>
+      </c>
+      <c r="BC176">
+        <v>2</v>
+      </c>
+      <c r="BD176">
+        <v>1.32</v>
+      </c>
+      <c r="BE176">
+        <v>7.5</v>
+      </c>
+      <c r="BF176">
+        <v>3.65</v>
+      </c>
+      <c r="BG176">
+        <v>1.26</v>
+      </c>
+      <c r="BH176">
+        <v>3.4</v>
+      </c>
+      <c r="BI176">
+        <v>1.47</v>
+      </c>
+      <c r="BJ176">
+        <v>2.48</v>
+      </c>
+      <c r="BK176">
+        <v>1.75</v>
+      </c>
+      <c r="BL176">
+        <v>1.95</v>
+      </c>
+      <c r="BM176">
+        <v>2.17</v>
+      </c>
+      <c r="BN176">
+        <v>1.6</v>
+      </c>
+      <c r="BO176">
+        <v>2.7</v>
+      </c>
+      <c r="BP176">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7491987</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45689.47916666666</v>
+      </c>
+      <c r="F177">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>87</v>
+      </c>
+      <c r="H177" t="s">
+        <v>81</v>
+      </c>
+      <c r="I177">
+        <v>2</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>2</v>
+      </c>
+      <c r="L177">
+        <v>4</v>
+      </c>
+      <c r="M177">
+        <v>3</v>
+      </c>
+      <c r="N177">
+        <v>7</v>
+      </c>
+      <c r="O177" t="s">
+        <v>217</v>
+      </c>
+      <c r="P177" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q177">
+        <v>1.25</v>
+      </c>
+      <c r="R177">
+        <v>4.33</v>
+      </c>
+      <c r="S177">
+        <v>19</v>
+      </c>
+      <c r="T177">
+        <v>1.11</v>
+      </c>
+      <c r="U177">
+        <v>6.5</v>
+      </c>
+      <c r="V177">
+        <v>1.57</v>
+      </c>
+      <c r="W177">
+        <v>2.25</v>
+      </c>
+      <c r="X177">
+        <v>2.75</v>
+      </c>
+      <c r="Y177">
+        <v>1.4</v>
+      </c>
+      <c r="Z177">
+        <v>1.04</v>
+      </c>
+      <c r="AA177">
+        <v>25</v>
+      </c>
+      <c r="AB177">
+        <v>34</v>
+      </c>
+      <c r="AC177">
+        <v>1.01</v>
+      </c>
+      <c r="AD177">
+        <v>14</v>
+      </c>
+      <c r="AE177">
+        <v>1.04</v>
+      </c>
+      <c r="AF177">
+        <v>12</v>
+      </c>
+      <c r="AG177">
+        <v>1.16</v>
+      </c>
+      <c r="AH177">
+        <v>4.82</v>
+      </c>
+      <c r="AI177">
+        <v>2.2</v>
+      </c>
+      <c r="AJ177">
+        <v>1.62</v>
+      </c>
+      <c r="AK177">
+        <v>1.01</v>
+      </c>
+      <c r="AL177">
+        <v>1.02</v>
+      </c>
+      <c r="AM177">
+        <v>10.5</v>
+      </c>
+      <c r="AN177">
+        <v>2.78</v>
+      </c>
+      <c r="AO177">
+        <v>0.33</v>
+      </c>
+      <c r="AP177">
+        <v>2.8</v>
+      </c>
+      <c r="AQ177">
+        <v>0.3</v>
+      </c>
+      <c r="AR177">
+        <v>2.37</v>
+      </c>
+      <c r="AS177">
+        <v>1.14</v>
+      </c>
+      <c r="AT177">
+        <v>3.51</v>
+      </c>
+      <c r="AU177">
+        <v>13</v>
+      </c>
+      <c r="AV177">
+        <v>7</v>
+      </c>
+      <c r="AW177">
+        <v>17</v>
+      </c>
+      <c r="AX177">
+        <v>4</v>
+      </c>
+      <c r="AY177">
+        <v>36</v>
+      </c>
+      <c r="AZ177">
+        <v>11</v>
+      </c>
+      <c r="BA177">
+        <v>12</v>
+      </c>
+      <c r="BB177">
+        <v>1</v>
+      </c>
+      <c r="BC177">
+        <v>13</v>
+      </c>
+      <c r="BD177">
+        <v>1.03</v>
+      </c>
+      <c r="BE177">
+        <v>19</v>
+      </c>
+      <c r="BF177">
+        <v>15</v>
+      </c>
+      <c r="BG177">
+        <v>1.18</v>
+      </c>
+      <c r="BH177">
+        <v>4.2</v>
+      </c>
+      <c r="BI177">
+        <v>1.3</v>
+      </c>
+      <c r="BJ177">
+        <v>3.05</v>
+      </c>
+      <c r="BK177">
+        <v>1.52</v>
+      </c>
+      <c r="BL177">
+        <v>2.33</v>
+      </c>
+      <c r="BM177">
+        <v>1.81</v>
+      </c>
+      <c r="BN177">
+        <v>1.88</v>
+      </c>
+      <c r="BO177">
+        <v>2.2</v>
+      </c>
+      <c r="BP177">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7491989</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45689.47916666666</v>
+      </c>
+      <c r="F178">
+        <v>20</v>
+      </c>
+      <c r="G178" t="s">
+        <v>86</v>
+      </c>
+      <c r="H178" t="s">
+        <v>76</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <v>2</v>
+      </c>
+      <c r="N178">
+        <v>3</v>
+      </c>
+      <c r="O178" t="s">
+        <v>151</v>
+      </c>
+      <c r="P178" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q178">
+        <v>4.33</v>
+      </c>
+      <c r="R178">
+        <v>2.4</v>
+      </c>
+      <c r="S178">
+        <v>2.3</v>
+      </c>
+      <c r="T178">
+        <v>1.29</v>
+      </c>
+      <c r="U178">
+        <v>3.5</v>
+      </c>
+      <c r="V178">
+        <v>2.25</v>
+      </c>
+      <c r="W178">
+        <v>1.57</v>
+      </c>
+      <c r="X178">
+        <v>5.5</v>
+      </c>
+      <c r="Y178">
+        <v>1.14</v>
+      </c>
+      <c r="Z178">
+        <v>4.2</v>
+      </c>
+      <c r="AA178">
+        <v>4.1</v>
+      </c>
+      <c r="AB178">
+        <v>1.82</v>
+      </c>
+      <c r="AC178">
+        <v>1.02</v>
+      </c>
+      <c r="AD178">
+        <v>19</v>
+      </c>
+      <c r="AE178">
+        <v>1.18</v>
+      </c>
+      <c r="AF178">
+        <v>5</v>
+      </c>
+      <c r="AG178">
+        <v>1.52</v>
+      </c>
+      <c r="AH178">
+        <v>2.43</v>
+      </c>
+      <c r="AI178">
+        <v>1.57</v>
+      </c>
+      <c r="AJ178">
+        <v>2.25</v>
+      </c>
+      <c r="AK178">
+        <v>1.98</v>
+      </c>
+      <c r="AL178">
+        <v>1.24</v>
+      </c>
+      <c r="AM178">
+        <v>1.23</v>
+      </c>
+      <c r="AN178">
+        <v>0.78</v>
+      </c>
+      <c r="AO178">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP178">
+        <v>0.7</v>
+      </c>
+      <c r="AQ178">
+        <v>0.8</v>
+      </c>
+      <c r="AR178">
+        <v>1.36</v>
+      </c>
+      <c r="AS178">
+        <v>1.29</v>
+      </c>
+      <c r="AT178">
+        <v>2.65</v>
+      </c>
+      <c r="AU178">
+        <v>6</v>
+      </c>
+      <c r="AV178">
+        <v>6</v>
+      </c>
+      <c r="AW178">
+        <v>6</v>
+      </c>
+      <c r="AX178">
+        <v>11</v>
+      </c>
+      <c r="AY178">
+        <v>13</v>
+      </c>
+      <c r="AZ178">
+        <v>20</v>
+      </c>
+      <c r="BA178">
+        <v>4</v>
+      </c>
+      <c r="BB178">
+        <v>5</v>
+      </c>
+      <c r="BC178">
+        <v>9</v>
+      </c>
+      <c r="BD178">
+        <v>2.45</v>
+      </c>
+      <c r="BE178">
+        <v>6.75</v>
+      </c>
+      <c r="BF178">
+        <v>1.66</v>
+      </c>
+      <c r="BG178">
+        <v>1.23</v>
+      </c>
+      <c r="BH178">
+        <v>3.65</v>
+      </c>
+      <c r="BI178">
+        <v>1.41</v>
+      </c>
+      <c r="BJ178">
+        <v>2.65</v>
+      </c>
+      <c r="BK178">
+        <v>1.67</v>
+      </c>
+      <c r="BL178">
+        <v>2.05</v>
+      </c>
+      <c r="BM178">
+        <v>2.06</v>
+      </c>
+      <c r="BN178">
+        <v>1.66</v>
+      </c>
+      <c r="BO178">
+        <v>2.6</v>
+      </c>
+      <c r="BP178">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7491991</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45689.60416666666</v>
+      </c>
+      <c r="F179">
+        <v>20</v>
+      </c>
+      <c r="G179" t="s">
+        <v>79</v>
+      </c>
+      <c r="H179" t="s">
+        <v>71</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179" t="s">
+        <v>96</v>
+      </c>
+      <c r="P179" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q179">
+        <v>3.6</v>
+      </c>
+      <c r="R179">
+        <v>2.25</v>
+      </c>
+      <c r="S179">
+        <v>2.88</v>
+      </c>
+      <c r="T179">
+        <v>1.36</v>
+      </c>
+      <c r="U179">
+        <v>3</v>
+      </c>
+      <c r="V179">
+        <v>2.63</v>
+      </c>
+      <c r="W179">
+        <v>1.44</v>
+      </c>
+      <c r="X179">
+        <v>7</v>
+      </c>
+      <c r="Y179">
+        <v>1.1</v>
+      </c>
+      <c r="Z179">
+        <v>3.12</v>
+      </c>
+      <c r="AA179">
+        <v>3.62</v>
+      </c>
+      <c r="AB179">
+        <v>2.28</v>
+      </c>
+      <c r="AC179">
+        <v>1.05</v>
+      </c>
+      <c r="AD179">
+        <v>12</v>
+      </c>
+      <c r="AE179">
+        <v>1.26</v>
+      </c>
+      <c r="AF179">
+        <v>4</v>
+      </c>
+      <c r="AG179">
+        <v>1.81</v>
+      </c>
+      <c r="AH179">
+        <v>2.01</v>
+      </c>
+      <c r="AI179">
+        <v>1.62</v>
+      </c>
+      <c r="AJ179">
+        <v>2.2</v>
+      </c>
+      <c r="AK179">
+        <v>1.61</v>
+      </c>
+      <c r="AL179">
+        <v>1.3</v>
+      </c>
+      <c r="AM179">
+        <v>1.37</v>
+      </c>
+      <c r="AN179">
+        <v>1.67</v>
+      </c>
+      <c r="AO179">
+        <v>1.4</v>
+      </c>
+      <c r="AP179">
+        <v>1.6</v>
+      </c>
+      <c r="AQ179">
+        <v>1.36</v>
+      </c>
+      <c r="AR179">
+        <v>1.41</v>
+      </c>
+      <c r="AS179">
+        <v>1.12</v>
+      </c>
+      <c r="AT179">
+        <v>2.53</v>
+      </c>
+      <c r="AU179">
+        <v>7</v>
+      </c>
+      <c r="AV179">
+        <v>3</v>
+      </c>
+      <c r="AW179">
+        <v>15</v>
+      </c>
+      <c r="AX179">
+        <v>4</v>
+      </c>
+      <c r="AY179">
+        <v>29</v>
+      </c>
+      <c r="AZ179">
+        <v>8</v>
+      </c>
+      <c r="BA179">
+        <v>4</v>
+      </c>
+      <c r="BB179">
+        <v>5</v>
+      </c>
+      <c r="BC179">
+        <v>9</v>
+      </c>
+      <c r="BD179">
+        <v>1.95</v>
+      </c>
+      <c r="BE179">
+        <v>6.4</v>
+      </c>
+      <c r="BF179">
+        <v>2.05</v>
+      </c>
+      <c r="BG179">
+        <v>1.28</v>
+      </c>
+      <c r="BH179">
+        <v>3.3</v>
+      </c>
+      <c r="BI179">
+        <v>1.47</v>
+      </c>
+      <c r="BJ179">
+        <v>2.43</v>
+      </c>
+      <c r="BK179">
+        <v>1.79</v>
+      </c>
+      <c r="BL179">
+        <v>1.9</v>
+      </c>
+      <c r="BM179">
+        <v>2.23</v>
+      </c>
+      <c r="BN179">
+        <v>1.56</v>
+      </c>
+      <c r="BO179">
+        <v>2.9</v>
+      </c>
+      <c r="BP179">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7491988</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45690.47916666666</v>
+      </c>
+      <c r="F180">
+        <v>20</v>
+      </c>
+      <c r="G180" t="s">
+        <v>82</v>
+      </c>
+      <c r="H180" t="s">
+        <v>77</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>1</v>
+      </c>
+      <c r="M180">
+        <v>1</v>
+      </c>
+      <c r="N180">
+        <v>2</v>
+      </c>
+      <c r="O180" t="s">
+        <v>218</v>
+      </c>
+      <c r="P180" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q180">
+        <v>2.5</v>
+      </c>
+      <c r="R180">
+        <v>2.4</v>
+      </c>
+      <c r="S180">
+        <v>4</v>
+      </c>
+      <c r="T180">
+        <v>1.29</v>
+      </c>
+      <c r="U180">
+        <v>3.5</v>
+      </c>
+      <c r="V180">
+        <v>2.38</v>
+      </c>
+      <c r="W180">
+        <v>1.53</v>
+      </c>
+      <c r="X180">
+        <v>5.5</v>
+      </c>
+      <c r="Y180">
+        <v>1.14</v>
+      </c>
+      <c r="Z180">
+        <v>1.87</v>
+      </c>
+      <c r="AA180">
+        <v>3.99</v>
+      </c>
+      <c r="AB180">
+        <v>4</v>
+      </c>
+      <c r="AC180">
+        <v>1.02</v>
+      </c>
+      <c r="AD180">
+        <v>17</v>
+      </c>
+      <c r="AE180">
+        <v>1.18</v>
+      </c>
+      <c r="AF180">
+        <v>5</v>
+      </c>
+      <c r="AG180">
+        <v>1.65</v>
+      </c>
+      <c r="AH180">
+        <v>2.15</v>
+      </c>
+      <c r="AI180">
+        <v>1.53</v>
+      </c>
+      <c r="AJ180">
+        <v>2.38</v>
+      </c>
+      <c r="AK180">
+        <v>1.26</v>
+      </c>
+      <c r="AL180">
+        <v>1.25</v>
+      </c>
+      <c r="AM180">
+        <v>1.88</v>
+      </c>
+      <c r="AN180">
+        <v>2.22</v>
+      </c>
+      <c r="AO180">
+        <v>1.78</v>
+      </c>
+      <c r="AP180">
+        <v>2.1</v>
+      </c>
+      <c r="AQ180">
+        <v>1.7</v>
+      </c>
+      <c r="AR180">
+        <v>1.83</v>
+      </c>
+      <c r="AS180">
+        <v>1.34</v>
+      </c>
+      <c r="AT180">
+        <v>3.17</v>
+      </c>
+      <c r="AU180">
+        <v>5</v>
+      </c>
+      <c r="AV180">
+        <v>3</v>
+      </c>
+      <c r="AW180">
+        <v>12</v>
+      </c>
+      <c r="AX180">
+        <v>9</v>
+      </c>
+      <c r="AY180">
+        <v>21</v>
+      </c>
+      <c r="AZ180">
+        <v>16</v>
+      </c>
+      <c r="BA180">
+        <v>9</v>
+      </c>
+      <c r="BB180">
+        <v>1</v>
+      </c>
+      <c r="BC180">
+        <v>10</v>
+      </c>
+      <c r="BD180">
+        <v>1.49</v>
+      </c>
+      <c r="BE180">
+        <v>6.75</v>
+      </c>
+      <c r="BF180">
+        <v>2.9</v>
+      </c>
+      <c r="BG180">
+        <v>1.28</v>
+      </c>
+      <c r="BH180">
+        <v>3.3</v>
+      </c>
+      <c r="BI180">
+        <v>1.49</v>
+      </c>
+      <c r="BJ180">
+        <v>2.4</v>
+      </c>
+      <c r="BK180">
+        <v>1.78</v>
+      </c>
+      <c r="BL180">
+        <v>1.91</v>
+      </c>
+      <c r="BM180">
+        <v>2.23</v>
+      </c>
+      <c r="BN180">
+        <v>1.57</v>
+      </c>
+      <c r="BO180">
+        <v>2.8</v>
+      </c>
+      <c r="BP180">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="327">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -671,6 +671,9 @@
   </si>
   <si>
     <t>['81']</t>
+  </si>
+  <si>
+    <t>['15', '19', '51']</t>
   </si>
   <si>
     <t>['12', '38', '90+11']</t>
@@ -1353,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP180"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1612,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2021,7 +2024,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2227,7 +2230,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2433,7 +2436,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2639,7 +2642,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3051,7 +3054,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3257,7 +3260,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3669,7 +3672,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3875,7 +3878,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4081,7 +4084,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4162,7 +4165,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ14">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4287,7 +4290,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4699,7 +4702,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4777,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ17">
         <v>1.36</v>
@@ -5317,7 +5320,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5729,7 +5732,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6141,7 +6144,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6347,7 +6350,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6553,7 +6556,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6759,7 +6762,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6965,7 +6968,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7171,7 +7174,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7377,7 +7380,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7583,7 +7586,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7789,7 +7792,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7870,7 +7873,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ32">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR32">
         <v>1.36</v>
@@ -7995,7 +7998,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8407,7 +8410,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8485,7 +8488,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ35">
         <v>1.7</v>
@@ -9025,7 +9028,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9437,7 +9440,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9643,7 +9646,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9849,7 +9852,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10261,7 +10264,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10467,7 +10470,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10673,7 +10676,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11085,7 +11088,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11163,7 +11166,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ48">
         <v>0.3</v>
@@ -11497,7 +11500,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11703,7 +11706,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11909,7 +11912,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12321,7 +12324,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12527,7 +12530,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12608,7 +12611,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ55">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR55">
         <v>2.29</v>
@@ -12733,7 +12736,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12939,7 +12942,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13017,7 +13020,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ57">
         <v>1.7</v>
@@ -13351,7 +13354,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13557,7 +13560,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13763,7 +13766,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14175,7 +14178,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14381,7 +14384,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14587,7 +14590,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14793,7 +14796,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15205,7 +15208,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15617,7 +15620,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15823,7 +15826,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16316,7 +16319,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ73">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR73">
         <v>1.3</v>
@@ -16519,7 +16522,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ74">
         <v>1.33</v>
@@ -16853,7 +16856,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17059,7 +17062,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18501,7 +18504,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18913,7 +18916,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19119,7 +19122,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19612,7 +19615,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ89">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19737,7 +19740,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19943,7 +19946,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20355,7 +20358,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20433,7 +20436,7 @@
         <v>1.2</v>
       </c>
       <c r="AP93">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ93">
         <v>0.7</v>
@@ -20973,7 +20976,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21591,7 +21594,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22003,7 +22006,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22209,7 +22212,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22415,7 +22418,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22827,7 +22830,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23033,7 +23036,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23239,7 +23242,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23526,7 +23529,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ108">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR108">
         <v>1.45</v>
@@ -23651,7 +23654,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23857,7 +23860,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24063,7 +24066,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24269,7 +24272,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24475,7 +24478,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24681,7 +24684,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24965,7 +24968,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ115">
         <v>1.2</v>
@@ -25093,7 +25096,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25299,7 +25302,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25711,7 +25714,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25917,7 +25920,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26123,7 +26126,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26329,7 +26332,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26535,7 +26538,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26741,7 +26744,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26947,7 +26950,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27153,7 +27156,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27234,7 +27237,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ126">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR126">
         <v>1.74</v>
@@ -27359,7 +27362,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27565,7 +27568,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27771,7 +27774,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27977,7 +27980,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28183,7 +28186,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28389,7 +28392,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28595,7 +28598,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28879,7 +28882,7 @@
         <v>1.14</v>
       </c>
       <c r="AP134">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ134">
         <v>1</v>
@@ -29213,7 +29216,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29419,7 +29422,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -30037,7 +30040,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30449,7 +30452,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30861,7 +30864,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31067,7 +31070,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31273,7 +31276,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31969,7 +31972,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ149">
         <v>1.4</v>
@@ -32303,7 +32306,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32590,7 +32593,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ152">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR152">
         <v>2.19</v>
@@ -32715,7 +32718,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32921,7 +32924,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33333,7 +33336,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33414,7 +33417,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ156">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR156">
         <v>1.22</v>
@@ -33539,7 +33542,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33745,7 +33748,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34157,7 +34160,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34363,7 +34366,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34441,7 +34444,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ161">
         <v>1.1</v>
@@ -34569,7 +34572,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34775,7 +34778,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34981,7 +34984,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35599,7 +35602,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q167">
         <v>2.1</v>
@@ -35805,7 +35808,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q168">
         <v>4</v>
@@ -36011,7 +36014,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q169">
         <v>7</v>
@@ -36423,7 +36426,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -37041,7 +37044,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37453,7 +37456,7 @@
         <v>216</v>
       </c>
       <c r="P176" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q176">
         <v>2</v>
@@ -37659,7 +37662,7 @@
         <v>217</v>
       </c>
       <c r="P177" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q177">
         <v>1.25</v>
@@ -37865,7 +37868,7 @@
         <v>151</v>
       </c>
       <c r="P178" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q178">
         <v>4.33</v>
@@ -38170,16 +38173,16 @@
         <v>3</v>
       </c>
       <c r="AW179">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AX179">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY179">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AZ179">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA179">
         <v>4</v>
@@ -38277,7 +38280,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38434,6 +38437,212 @@
       </c>
       <c r="BP180">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7491985</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45690.5625</v>
+      </c>
+      <c r="F181">
+        <v>20</v>
+      </c>
+      <c r="G181" t="s">
+        <v>85</v>
+      </c>
+      <c r="H181" t="s">
+        <v>72</v>
+      </c>
+      <c r="I181">
+        <v>2</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>2</v>
+      </c>
+      <c r="L181">
+        <v>3</v>
+      </c>
+      <c r="M181">
+        <v>1</v>
+      </c>
+      <c r="N181">
+        <v>4</v>
+      </c>
+      <c r="O181" t="s">
+        <v>219</v>
+      </c>
+      <c r="P181" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q181">
+        <v>1.62</v>
+      </c>
+      <c r="R181">
+        <v>3</v>
+      </c>
+      <c r="S181">
+        <v>8.5</v>
+      </c>
+      <c r="T181">
+        <v>1.2</v>
+      </c>
+      <c r="U181">
+        <v>4.33</v>
+      </c>
+      <c r="V181">
+        <v>2</v>
+      </c>
+      <c r="W181">
+        <v>1.73</v>
+      </c>
+      <c r="X181">
+        <v>4.33</v>
+      </c>
+      <c r="Y181">
+        <v>1.2</v>
+      </c>
+      <c r="Z181">
+        <v>1.26</v>
+      </c>
+      <c r="AA181">
+        <v>7.1</v>
+      </c>
+      <c r="AB181">
+        <v>10</v>
+      </c>
+      <c r="AC181">
+        <v>1.02</v>
+      </c>
+      <c r="AD181">
+        <v>23</v>
+      </c>
+      <c r="AE181">
+        <v>1.1</v>
+      </c>
+      <c r="AF181">
+        <v>7</v>
+      </c>
+      <c r="AG181">
+        <v>1.35</v>
+      </c>
+      <c r="AH181">
+        <v>3.04</v>
+      </c>
+      <c r="AI181">
+        <v>1.8</v>
+      </c>
+      <c r="AJ181">
+        <v>1.95</v>
+      </c>
+      <c r="AK181">
+        <v>1.06</v>
+      </c>
+      <c r="AL181">
+        <v>1.11</v>
+      </c>
+      <c r="AM181">
+        <v>3.9</v>
+      </c>
+      <c r="AN181">
+        <v>2.3</v>
+      </c>
+      <c r="AO181">
+        <v>0.78</v>
+      </c>
+      <c r="AP181">
+        <v>2.36</v>
+      </c>
+      <c r="AQ181">
+        <v>0.7</v>
+      </c>
+      <c r="AR181">
+        <v>2.14</v>
+      </c>
+      <c r="AS181">
+        <v>1.13</v>
+      </c>
+      <c r="AT181">
+        <v>3.27</v>
+      </c>
+      <c r="AU181">
+        <v>6</v>
+      </c>
+      <c r="AV181">
+        <v>8</v>
+      </c>
+      <c r="AW181">
+        <v>4</v>
+      </c>
+      <c r="AX181">
+        <v>9</v>
+      </c>
+      <c r="AY181">
+        <v>11</v>
+      </c>
+      <c r="AZ181">
+        <v>17</v>
+      </c>
+      <c r="BA181">
+        <v>3</v>
+      </c>
+      <c r="BB181">
+        <v>3</v>
+      </c>
+      <c r="BC181">
+        <v>6</v>
+      </c>
+      <c r="BD181">
+        <v>1.13</v>
+      </c>
+      <c r="BE181">
+        <v>10</v>
+      </c>
+      <c r="BF181">
+        <v>6.1</v>
+      </c>
+      <c r="BG181">
+        <v>1.21</v>
+      </c>
+      <c r="BH181">
+        <v>3.8</v>
+      </c>
+      <c r="BI181">
+        <v>1.38</v>
+      </c>
+      <c r="BJ181">
+        <v>2.7</v>
+      </c>
+      <c r="BK181">
+        <v>1.64</v>
+      </c>
+      <c r="BL181">
+        <v>2.1</v>
+      </c>
+      <c r="BM181">
+        <v>1.98</v>
+      </c>
+      <c r="BN181">
+        <v>1.72</v>
+      </c>
+      <c r="BO181">
+        <v>2.48</v>
+      </c>
+      <c r="BP181">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -640,13 +640,13 @@
     <t>['45+1', '90+2']</t>
   </si>
   <si>
+    <t>['68']</t>
+  </si>
+  <si>
     <t>['28', '51']</t>
   </si>
   <si>
     <t>['41', '84']</t>
-  </si>
-  <si>
-    <t>['68']</t>
   </si>
   <si>
     <t>['34', '55', '86']</t>
@@ -661,13 +661,13 @@
     <t>['14']</t>
   </si>
   <si>
-    <t>['17']</t>
-  </si>
-  <si>
     <t>['49']</t>
   </si>
   <si>
     <t>['19', '45+3', '46', '54']</t>
+  </si>
+  <si>
+    <t>['17']</t>
   </si>
   <si>
     <t>['81']</t>
@@ -970,19 +970,16 @@
     <t>['13', '80']</t>
   </si>
   <si>
+    <t>['15', '54']</t>
+  </si>
+  <si>
     <t>['64', '72']</t>
   </si>
   <si>
     <t>['18', '36']</t>
   </si>
   <si>
-    <t>['15', '54']</t>
-  </si>
-  <si>
     <t>['26', '71']</t>
-  </si>
-  <si>
-    <t>['83']</t>
   </si>
   <si>
     <t>['25', '81']</t>
@@ -992,6 +989,9 @@
   </si>
   <si>
     <t>['33', '63']</t>
+  </si>
+  <si>
+    <t>['83']</t>
   </si>
   <si>
     <t>['50']</t>
@@ -25508,7 +25508,7 @@
         <v>171</v>
       </c>
       <c r="P118" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -30658,7 +30658,7 @@
         <v>96</v>
       </c>
       <c r="P143" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -35560,7 +35560,7 @@
         <v>166</v>
       </c>
       <c r="B167">
-        <v>7491977</v>
+        <v>7491979</v>
       </c>
       <c r="C167" t="s">
         <v>68</v>
@@ -35575,28 +35575,28 @@
         <v>19</v>
       </c>
       <c r="G167" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H167" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K167">
         <v>1</v>
       </c>
       <c r="L167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M167">
         <v>2</v>
       </c>
       <c r="N167">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O167" t="s">
         <v>208</v>
@@ -35605,160 +35605,160 @@
         <v>318</v>
       </c>
       <c r="Q167">
+        <v>7</v>
+      </c>
+      <c r="R167">
+        <v>2.75</v>
+      </c>
+      <c r="S167">
+        <v>1.73</v>
+      </c>
+      <c r="T167">
+        <v>1.22</v>
+      </c>
+      <c r="U167">
+        <v>4</v>
+      </c>
+      <c r="V167">
         <v>2.1</v>
       </c>
-      <c r="R167">
-        <v>2.5</v>
-      </c>
-      <c r="S167">
+      <c r="W167">
+        <v>1.67</v>
+      </c>
+      <c r="X167">
+        <v>4.5</v>
+      </c>
+      <c r="Y167">
+        <v>1.18</v>
+      </c>
+      <c r="Z167">
+        <v>7.5</v>
+      </c>
+      <c r="AA167">
         <v>5</v>
       </c>
-      <c r="T167">
-        <v>1.25</v>
-      </c>
-      <c r="U167">
-        <v>3.75</v>
-      </c>
-      <c r="V167">
-        <v>2.2</v>
-      </c>
-      <c r="W167">
-        <v>1.62</v>
-      </c>
-      <c r="X167">
+      <c r="AB167">
+        <v>1.36</v>
+      </c>
+      <c r="AC167">
+        <v>0</v>
+      </c>
+      <c r="AD167">
+        <v>0</v>
+      </c>
+      <c r="AE167">
+        <v>1.12</v>
+      </c>
+      <c r="AF167">
+        <v>6.5</v>
+      </c>
+      <c r="AG167">
+        <v>1.4</v>
+      </c>
+      <c r="AH167">
+        <v>2.9</v>
+      </c>
+      <c r="AI167">
+        <v>1.7</v>
+      </c>
+      <c r="AJ167">
+        <v>2.05</v>
+      </c>
+      <c r="AK167">
+        <v>3.1</v>
+      </c>
+      <c r="AL167">
+        <v>1.15</v>
+      </c>
+      <c r="AM167">
+        <v>1.09</v>
+      </c>
+      <c r="AN167">
+        <v>2.38</v>
+      </c>
+      <c r="AO167">
+        <v>2.22</v>
+      </c>
+      <c r="AP167">
+        <v>2.11</v>
+      </c>
+      <c r="AQ167">
+        <v>2.3</v>
+      </c>
+      <c r="AR167">
+        <v>1.56</v>
+      </c>
+      <c r="AS167">
+        <v>2.01</v>
+      </c>
+      <c r="AT167">
+        <v>3.57</v>
+      </c>
+      <c r="AU167">
+        <v>3</v>
+      </c>
+      <c r="AV167">
+        <v>4</v>
+      </c>
+      <c r="AW167">
         <v>5</v>
       </c>
-      <c r="Y167">
-        <v>1.17</v>
-      </c>
-      <c r="Z167">
-        <v>1.62</v>
-      </c>
-      <c r="AA167">
-        <v>4.33</v>
-      </c>
-      <c r="AB167">
-        <v>5</v>
-      </c>
-      <c r="AC167">
-        <v>1.02</v>
-      </c>
-      <c r="AD167">
-        <v>19</v>
-      </c>
-      <c r="AE167">
-        <v>1.18</v>
-      </c>
-      <c r="AF167">
-        <v>5</v>
-      </c>
-      <c r="AG167">
-        <v>1.53</v>
-      </c>
-      <c r="AH167">
-        <v>2.45</v>
-      </c>
-      <c r="AI167">
-        <v>1.57</v>
-      </c>
-      <c r="AJ167">
-        <v>2.25</v>
-      </c>
-      <c r="AK167">
-        <v>1.18</v>
-      </c>
-      <c r="AL167">
-        <v>1.2</v>
-      </c>
-      <c r="AM167">
-        <v>2.25</v>
-      </c>
-      <c r="AN167">
-        <v>2.22</v>
-      </c>
-      <c r="AO167">
-        <v>1.78</v>
-      </c>
-      <c r="AP167">
-        <v>2.1</v>
-      </c>
-      <c r="AQ167">
-        <v>1.7</v>
-      </c>
-      <c r="AR167">
-        <v>1.59</v>
-      </c>
-      <c r="AS167">
-        <v>1.25</v>
-      </c>
-      <c r="AT167">
-        <v>2.84</v>
-      </c>
-      <c r="AU167">
-        <v>5</v>
-      </c>
-      <c r="AV167">
-        <v>5</v>
-      </c>
-      <c r="AW167">
+      <c r="AX167">
         <v>4</v>
-      </c>
-      <c r="AX167">
-        <v>9</v>
       </c>
       <c r="AY167">
         <v>11</v>
       </c>
       <c r="AZ167">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA167">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC167">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD167">
-        <v>1.26</v>
+        <v>9.5</v>
       </c>
       <c r="BE167">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="BF167">
-        <v>4.6</v>
+        <v>1.06</v>
       </c>
       <c r="BG167">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BH167">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="BI167">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="BJ167">
-        <v>2.57</v>
+        <v>2.19</v>
       </c>
       <c r="BK167">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="BL167">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="BM167">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="BN167">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="BO167">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="BP167">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="168" spans="1:68">
@@ -35766,7 +35766,7 @@
         <v>167</v>
       </c>
       <c r="B168">
-        <v>7491976</v>
+        <v>7491977</v>
       </c>
       <c r="C168" t="s">
         <v>68</v>
@@ -35781,19 +35781,19 @@
         <v>19</v>
       </c>
       <c r="G168" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H168" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I168">
         <v>1</v>
       </c>
       <c r="J168">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K168">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L168">
         <v>2</v>
@@ -35811,40 +35811,40 @@
         <v>319</v>
       </c>
       <c r="Q168">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R168">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S168">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="T168">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U168">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V168">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="W168">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="X168">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Y168">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z168">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA168">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AB168">
-        <v>1.95</v>
+        <v>5</v>
       </c>
       <c r="AC168">
         <v>1.02</v>
@@ -35859,94 +35859,94 @@
         <v>5</v>
       </c>
       <c r="AG168">
+        <v>1.53</v>
+      </c>
+      <c r="AH168">
+        <v>2.45</v>
+      </c>
+      <c r="AI168">
         <v>1.57</v>
       </c>
-      <c r="AH168">
-        <v>2.35</v>
-      </c>
-      <c r="AI168">
-        <v>1.53</v>
-      </c>
       <c r="AJ168">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AK168">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AL168">
+        <v>1.2</v>
+      </c>
+      <c r="AM168">
+        <v>2.25</v>
+      </c>
+      <c r="AN168">
+        <v>2.22</v>
+      </c>
+      <c r="AO168">
+        <v>1.78</v>
+      </c>
+      <c r="AP168">
+        <v>2.1</v>
+      </c>
+      <c r="AQ168">
+        <v>1.7</v>
+      </c>
+      <c r="AR168">
+        <v>1.59</v>
+      </c>
+      <c r="AS168">
         <v>1.25</v>
       </c>
-      <c r="AM168">
-        <v>1.28</v>
-      </c>
-      <c r="AN168">
-        <v>2.13</v>
-      </c>
-      <c r="AO168">
-        <v>2.25</v>
-      </c>
-      <c r="AP168">
-        <v>2</v>
-      </c>
-      <c r="AQ168">
-        <v>2.11</v>
-      </c>
-      <c r="AR168">
-        <v>1.49</v>
-      </c>
-      <c r="AS168">
-        <v>1.46</v>
-      </c>
       <c r="AT168">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AU168">
+        <v>5</v>
+      </c>
+      <c r="AV168">
+        <v>5</v>
+      </c>
+      <c r="AW168">
         <v>4</v>
       </c>
-      <c r="AV168">
-        <v>8</v>
-      </c>
-      <c r="AW168">
-        <v>2</v>
-      </c>
       <c r="AX168">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY168">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ168">
         <v>14</v>
       </c>
       <c r="BA168">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB168">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC168">
         <v>10</v>
       </c>
       <c r="BD168">
-        <v>3.4</v>
+        <v>1.26</v>
       </c>
       <c r="BE168">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF168">
-        <v>1.43</v>
+        <v>4.6</v>
       </c>
       <c r="BG168">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BH168">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="BI168">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BJ168">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="BK168">
         <v>1.82</v>
@@ -35955,16 +35955,16 @@
         <v>1.98</v>
       </c>
       <c r="BM168">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="BN168">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BO168">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="BP168">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="169" spans="1:68">
@@ -35972,7 +35972,7 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>7491979</v>
+        <v>7491976</v>
       </c>
       <c r="C169" t="s">
         <v>68</v>
@@ -35987,28 +35987,28 @@
         <v>19</v>
       </c>
       <c r="G169" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H169" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K169">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M169">
         <v>2</v>
       </c>
       <c r="N169">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O169" t="s">
         <v>210</v>
@@ -36017,160 +36017,160 @@
         <v>320</v>
       </c>
       <c r="Q169">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R169">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="S169">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="T169">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="U169">
+        <v>3.5</v>
+      </c>
+      <c r="V169">
+        <v>2.38</v>
+      </c>
+      <c r="W169">
+        <v>1.53</v>
+      </c>
+      <c r="X169">
+        <v>5.5</v>
+      </c>
+      <c r="Y169">
+        <v>1.14</v>
+      </c>
+      <c r="Z169">
+        <v>3.6</v>
+      </c>
+      <c r="AA169">
+        <v>3.8</v>
+      </c>
+      <c r="AB169">
+        <v>1.95</v>
+      </c>
+      <c r="AC169">
+        <v>1.02</v>
+      </c>
+      <c r="AD169">
+        <v>19</v>
+      </c>
+      <c r="AE169">
+        <v>1.18</v>
+      </c>
+      <c r="AF169">
+        <v>5</v>
+      </c>
+      <c r="AG169">
+        <v>1.57</v>
+      </c>
+      <c r="AH169">
+        <v>2.35</v>
+      </c>
+      <c r="AI169">
+        <v>1.53</v>
+      </c>
+      <c r="AJ169">
+        <v>2.38</v>
+      </c>
+      <c r="AK169">
+        <v>1.83</v>
+      </c>
+      <c r="AL169">
+        <v>1.25</v>
+      </c>
+      <c r="AM169">
+        <v>1.28</v>
+      </c>
+      <c r="AN169">
+        <v>2.13</v>
+      </c>
+      <c r="AO169">
+        <v>2.25</v>
+      </c>
+      <c r="AP169">
+        <v>2</v>
+      </c>
+      <c r="AQ169">
+        <v>2.11</v>
+      </c>
+      <c r="AR169">
+        <v>1.49</v>
+      </c>
+      <c r="AS169">
+        <v>1.46</v>
+      </c>
+      <c r="AT169">
+        <v>2.95</v>
+      </c>
+      <c r="AU169">
         <v>4</v>
       </c>
-      <c r="V169">
-        <v>2.1</v>
-      </c>
-      <c r="W169">
-        <v>1.67</v>
-      </c>
-      <c r="X169">
-        <v>4.5</v>
-      </c>
-      <c r="Y169">
-        <v>1.18</v>
-      </c>
-      <c r="Z169">
-        <v>7.5</v>
-      </c>
-      <c r="AA169">
-        <v>5</v>
-      </c>
-      <c r="AB169">
-        <v>1.36</v>
-      </c>
-      <c r="AC169">
-        <v>0</v>
-      </c>
-      <c r="AD169">
-        <v>0</v>
-      </c>
-      <c r="AE169">
-        <v>1.12</v>
-      </c>
-      <c r="AF169">
-        <v>6.5</v>
-      </c>
-      <c r="AG169">
-        <v>1.4</v>
-      </c>
-      <c r="AH169">
-        <v>2.9</v>
-      </c>
-      <c r="AI169">
-        <v>1.7</v>
-      </c>
-      <c r="AJ169">
-        <v>2.05</v>
-      </c>
-      <c r="AK169">
-        <v>3.1</v>
-      </c>
-      <c r="AL169">
-        <v>1.15</v>
-      </c>
-      <c r="AM169">
-        <v>1.09</v>
-      </c>
-      <c r="AN169">
-        <v>2.38</v>
-      </c>
-      <c r="AO169">
-        <v>2.22</v>
-      </c>
-      <c r="AP169">
-        <v>2.11</v>
-      </c>
-      <c r="AQ169">
-        <v>2.3</v>
-      </c>
-      <c r="AR169">
-        <v>1.56</v>
-      </c>
-      <c r="AS169">
-        <v>2.01</v>
-      </c>
-      <c r="AT169">
-        <v>3.57</v>
-      </c>
-      <c r="AU169">
-        <v>3</v>
-      </c>
       <c r="AV169">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW169">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX169">
         <v>4</v>
       </c>
       <c r="AY169">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ169">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA169">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BB169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC169">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD169">
-        <v>9.5</v>
+        <v>3.4</v>
       </c>
       <c r="BE169">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="BF169">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="BG169">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BH169">
-        <v>2.97</v>
+        <v>3.22</v>
       </c>
       <c r="BI169">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BJ169">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="BK169">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="BL169">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="BM169">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="BN169">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="BO169">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="BP169">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="170" spans="1:68">
@@ -37002,7 +37002,7 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>7491993</v>
+        <v>7491986</v>
       </c>
       <c r="C174" t="s">
         <v>68</v>
@@ -37017,16 +37017,16 @@
         <v>20</v>
       </c>
       <c r="G174" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H174" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K174">
         <v>1</v>
@@ -37035,10 +37035,10 @@
         <v>1</v>
       </c>
       <c r="M174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O174" t="s">
         <v>215</v>
@@ -37047,160 +37047,160 @@
         <v>322</v>
       </c>
       <c r="Q174">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="R174">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S174">
+        <v>5</v>
+      </c>
+      <c r="T174">
+        <v>1.25</v>
+      </c>
+      <c r="U174">
         <v>3.75</v>
       </c>
-      <c r="T174">
+      <c r="V174">
+        <v>2.1</v>
+      </c>
+      <c r="W174">
+        <v>1.67</v>
+      </c>
+      <c r="X174">
+        <v>4.5</v>
+      </c>
+      <c r="Y174">
+        <v>1.18</v>
+      </c>
+      <c r="Z174">
         <v>1.5</v>
       </c>
-      <c r="U174">
-        <v>2.5</v>
-      </c>
-      <c r="V174">
-        <v>3.4</v>
-      </c>
-      <c r="W174">
-        <v>1.3</v>
-      </c>
-      <c r="X174">
-        <v>10</v>
-      </c>
-      <c r="Y174">
-        <v>1.06</v>
-      </c>
-      <c r="Z174">
-        <v>2.4</v>
-      </c>
       <c r="AA174">
-        <v>3.26</v>
+        <v>5.1</v>
       </c>
       <c r="AB174">
-        <v>3.21</v>
+        <v>5.8</v>
       </c>
       <c r="AC174">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AD174">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="AE174">
+        <v>1.13</v>
+      </c>
+      <c r="AF174">
+        <v>6</v>
+      </c>
+      <c r="AG174">
         <v>1.4</v>
       </c>
-      <c r="AF174">
-        <v>3</v>
-      </c>
-      <c r="AG174">
-        <v>1.95</v>
-      </c>
       <c r="AH174">
-        <v>1.75</v>
+        <v>2.82</v>
       </c>
       <c r="AI174">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AJ174">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AK174">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AL174">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AM174">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="AN174">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="AO174">
         <v>0.89</v>
       </c>
       <c r="AP174">
-        <v>0.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ174">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AR174">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AS174">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AT174">
-        <v>2.41</v>
+        <v>3.23</v>
       </c>
       <c r="AU174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV174">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AW174">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX174">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY174">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ174">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BA174">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC174">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD174">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="BE174">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF174">
-        <v>2.33</v>
+        <v>3.65</v>
       </c>
       <c r="BG174">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="BH174">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BI174">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="BJ174">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="BK174">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="BL174">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="BM174">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="BN174">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="BO174">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="BP174">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="175" spans="1:68">
@@ -37208,7 +37208,7 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>7491992</v>
+        <v>7491987</v>
       </c>
       <c r="C175" t="s">
         <v>68</v>
@@ -37223,190 +37223,190 @@
         <v>20</v>
       </c>
       <c r="G175" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H175" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I175">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L175">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M175">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N175">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O175" t="s">
-        <v>96</v>
+        <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="Q175">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="R175">
+        <v>4.33</v>
+      </c>
+      <c r="S175">
+        <v>19</v>
+      </c>
+      <c r="T175">
+        <v>1.11</v>
+      </c>
+      <c r="U175">
+        <v>6.5</v>
+      </c>
+      <c r="V175">
+        <v>1.57</v>
+      </c>
+      <c r="W175">
+        <v>2.25</v>
+      </c>
+      <c r="X175">
+        <v>2.75</v>
+      </c>
+      <c r="Y175">
+        <v>1.4</v>
+      </c>
+      <c r="Z175">
+        <v>1.04</v>
+      </c>
+      <c r="AA175">
+        <v>25</v>
+      </c>
+      <c r="AB175">
+        <v>34</v>
+      </c>
+      <c r="AC175">
+        <v>1.01</v>
+      </c>
+      <c r="AD175">
+        <v>14</v>
+      </c>
+      <c r="AE175">
+        <v>1.04</v>
+      </c>
+      <c r="AF175">
+        <v>12</v>
+      </c>
+      <c r="AG175">
+        <v>1.16</v>
+      </c>
+      <c r="AH175">
+        <v>4.82</v>
+      </c>
+      <c r="AI175">
         <v>2.2</v>
       </c>
-      <c r="S175">
-        <v>3.1</v>
-      </c>
-      <c r="T175">
-        <v>1.36</v>
-      </c>
-      <c r="U175">
-        <v>3</v>
-      </c>
-      <c r="V175">
-        <v>2.63</v>
-      </c>
-      <c r="W175">
-        <v>1.44</v>
-      </c>
-      <c r="X175">
+      <c r="AJ175">
+        <v>1.62</v>
+      </c>
+      <c r="AK175">
+        <v>1.01</v>
+      </c>
+      <c r="AL175">
+        <v>1.02</v>
+      </c>
+      <c r="AM175">
+        <v>10.5</v>
+      </c>
+      <c r="AN175">
+        <v>2.78</v>
+      </c>
+      <c r="AO175">
+        <v>0.33</v>
+      </c>
+      <c r="AP175">
+        <v>2.8</v>
+      </c>
+      <c r="AQ175">
+        <v>0.3</v>
+      </c>
+      <c r="AR175">
+        <v>2.37</v>
+      </c>
+      <c r="AS175">
+        <v>1.14</v>
+      </c>
+      <c r="AT175">
+        <v>3.51</v>
+      </c>
+      <c r="AU175">
+        <v>13</v>
+      </c>
+      <c r="AV175">
         <v>7</v>
       </c>
-      <c r="Y175">
-        <v>1.1</v>
-      </c>
-      <c r="Z175">
-        <v>2.82</v>
-      </c>
-      <c r="AA175">
-        <v>3.47</v>
-      </c>
-      <c r="AB175">
-        <v>2.55</v>
-      </c>
-      <c r="AC175">
-        <v>1.04</v>
-      </c>
-      <c r="AD175">
+      <c r="AW175">
+        <v>17</v>
+      </c>
+      <c r="AX175">
+        <v>4</v>
+      </c>
+      <c r="AY175">
+        <v>36</v>
+      </c>
+      <c r="AZ175">
+        <v>11</v>
+      </c>
+      <c r="BA175">
+        <v>12</v>
+      </c>
+      <c r="BB175">
+        <v>1</v>
+      </c>
+      <c r="BC175">
         <v>13</v>
       </c>
-      <c r="AE175">
-        <v>1.25</v>
-      </c>
-      <c r="AF175">
-        <v>4</v>
-      </c>
-      <c r="AG175">
+      <c r="BD175">
+        <v>1.03</v>
+      </c>
+      <c r="BE175">
+        <v>19</v>
+      </c>
+      <c r="BF175">
+        <v>15</v>
+      </c>
+      <c r="BG175">
+        <v>1.18</v>
+      </c>
+      <c r="BH175">
+        <v>4.2</v>
+      </c>
+      <c r="BI175">
+        <v>1.3</v>
+      </c>
+      <c r="BJ175">
+        <v>3.05</v>
+      </c>
+      <c r="BK175">
+        <v>1.52</v>
+      </c>
+      <c r="BL175">
+        <v>2.33</v>
+      </c>
+      <c r="BM175">
         <v>1.81</v>
       </c>
-      <c r="AH175">
-        <v>2.01</v>
-      </c>
-      <c r="AI175">
-        <v>1.62</v>
-      </c>
-      <c r="AJ175">
+      <c r="BN175">
+        <v>1.88</v>
+      </c>
+      <c r="BO175">
         <v>2.2</v>
       </c>
-      <c r="AK175">
-        <v>1.52</v>
-      </c>
-      <c r="AL175">
-        <v>1.29</v>
-      </c>
-      <c r="AM175">
-        <v>1.46</v>
-      </c>
-      <c r="AN175">
-        <v>1</v>
-      </c>
-      <c r="AO175">
-        <v>0.8</v>
-      </c>
-      <c r="AP175">
-        <v>0.9</v>
-      </c>
-      <c r="AQ175">
-        <v>1</v>
-      </c>
-      <c r="AR175">
-        <v>1.23</v>
-      </c>
-      <c r="AS175">
-        <v>1.17</v>
-      </c>
-      <c r="AT175">
-        <v>2.4</v>
-      </c>
-      <c r="AU175">
-        <v>5</v>
-      </c>
-      <c r="AV175">
-        <v>6</v>
-      </c>
-      <c r="AW175">
-        <v>18</v>
-      </c>
-      <c r="AX175">
-        <v>8</v>
-      </c>
-      <c r="AY175">
-        <v>28</v>
-      </c>
-      <c r="AZ175">
-        <v>19</v>
-      </c>
-      <c r="BA175">
-        <v>9</v>
-      </c>
-      <c r="BB175">
-        <v>7</v>
-      </c>
-      <c r="BC175">
-        <v>16</v>
-      </c>
-      <c r="BD175">
-        <v>1.97</v>
-      </c>
-      <c r="BE175">
-        <v>6.4</v>
-      </c>
-      <c r="BF175">
-        <v>2.05</v>
-      </c>
-      <c r="BG175">
-        <v>1.3</v>
-      </c>
-      <c r="BH175">
-        <v>3.05</v>
-      </c>
-      <c r="BI175">
-        <v>1.55</v>
-      </c>
-      <c r="BJ175">
-        <v>2.28</v>
-      </c>
-      <c r="BK175">
-        <v>1.9</v>
-      </c>
-      <c r="BL175">
-        <v>1.79</v>
-      </c>
-      <c r="BM175">
-        <v>2.4</v>
-      </c>
-      <c r="BN175">
-        <v>1.49</v>
-      </c>
-      <c r="BO175">
-        <v>3.15</v>
-      </c>
       <c r="BP175">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="176" spans="1:68">
@@ -37414,7 +37414,7 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>7491986</v>
+        <v>7491989</v>
       </c>
       <c r="C176" t="s">
         <v>68</v>
@@ -37429,10 +37429,10 @@
         <v>20</v>
       </c>
       <c r="G176" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H176" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -37453,166 +37453,166 @@
         <v>3</v>
       </c>
       <c r="O176" t="s">
-        <v>216</v>
+        <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q176">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="R176">
+        <v>2.4</v>
+      </c>
+      <c r="S176">
+        <v>2.3</v>
+      </c>
+      <c r="T176">
+        <v>1.29</v>
+      </c>
+      <c r="U176">
+        <v>3.5</v>
+      </c>
+      <c r="V176">
+        <v>2.25</v>
+      </c>
+      <c r="W176">
+        <v>1.57</v>
+      </c>
+      <c r="X176">
+        <v>5.5</v>
+      </c>
+      <c r="Y176">
+        <v>1.14</v>
+      </c>
+      <c r="Z176">
+        <v>4.2</v>
+      </c>
+      <c r="AA176">
+        <v>4.1</v>
+      </c>
+      <c r="AB176">
+        <v>1.82</v>
+      </c>
+      <c r="AC176">
+        <v>1.02</v>
+      </c>
+      <c r="AD176">
+        <v>19</v>
+      </c>
+      <c r="AE176">
+        <v>1.18</v>
+      </c>
+      <c r="AF176">
+        <v>5</v>
+      </c>
+      <c r="AG176">
+        <v>1.52</v>
+      </c>
+      <c r="AH176">
+        <v>2.43</v>
+      </c>
+      <c r="AI176">
+        <v>1.57</v>
+      </c>
+      <c r="AJ176">
+        <v>2.25</v>
+      </c>
+      <c r="AK176">
+        <v>1.98</v>
+      </c>
+      <c r="AL176">
+        <v>1.24</v>
+      </c>
+      <c r="AM176">
+        <v>1.23</v>
+      </c>
+      <c r="AN176">
+        <v>0.78</v>
+      </c>
+      <c r="AO176">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP176">
+        <v>0.7</v>
+      </c>
+      <c r="AQ176">
+        <v>0.8</v>
+      </c>
+      <c r="AR176">
+        <v>1.36</v>
+      </c>
+      <c r="AS176">
+        <v>1.29</v>
+      </c>
+      <c r="AT176">
+        <v>2.65</v>
+      </c>
+      <c r="AU176">
+        <v>6</v>
+      </c>
+      <c r="AV176">
+        <v>6</v>
+      </c>
+      <c r="AW176">
+        <v>6</v>
+      </c>
+      <c r="AX176">
+        <v>11</v>
+      </c>
+      <c r="AY176">
+        <v>13</v>
+      </c>
+      <c r="AZ176">
+        <v>20</v>
+      </c>
+      <c r="BA176">
+        <v>4</v>
+      </c>
+      <c r="BB176">
+        <v>5</v>
+      </c>
+      <c r="BC176">
+        <v>9</v>
+      </c>
+      <c r="BD176">
+        <v>2.45</v>
+      </c>
+      <c r="BE176">
+        <v>6.75</v>
+      </c>
+      <c r="BF176">
+        <v>1.66</v>
+      </c>
+      <c r="BG176">
+        <v>1.23</v>
+      </c>
+      <c r="BH176">
+        <v>3.65</v>
+      </c>
+      <c r="BI176">
+        <v>1.41</v>
+      </c>
+      <c r="BJ176">
+        <v>2.65</v>
+      </c>
+      <c r="BK176">
+        <v>1.67</v>
+      </c>
+      <c r="BL176">
+        <v>2.05</v>
+      </c>
+      <c r="BM176">
+        <v>2.06</v>
+      </c>
+      <c r="BN176">
+        <v>1.66</v>
+      </c>
+      <c r="BO176">
         <v>2.6</v>
       </c>
-      <c r="S176">
-        <v>5</v>
-      </c>
-      <c r="T176">
-        <v>1.25</v>
-      </c>
-      <c r="U176">
-        <v>3.75</v>
-      </c>
-      <c r="V176">
-        <v>2.1</v>
-      </c>
-      <c r="W176">
-        <v>1.67</v>
-      </c>
-      <c r="X176">
-        <v>4.5</v>
-      </c>
-      <c r="Y176">
-        <v>1.18</v>
-      </c>
-      <c r="Z176">
-        <v>1.5</v>
-      </c>
-      <c r="AA176">
-        <v>5.1</v>
-      </c>
-      <c r="AB176">
-        <v>5.8</v>
-      </c>
-      <c r="AC176">
-        <v>1.01</v>
-      </c>
-      <c r="AD176">
-        <v>17</v>
-      </c>
-      <c r="AE176">
-        <v>1.13</v>
-      </c>
-      <c r="AF176">
-        <v>6</v>
-      </c>
-      <c r="AG176">
-        <v>1.4</v>
-      </c>
-      <c r="AH176">
-        <v>2.82</v>
-      </c>
-      <c r="AI176">
-        <v>1.53</v>
-      </c>
-      <c r="AJ176">
-        <v>2.38</v>
-      </c>
-      <c r="AK176">
-        <v>1.15</v>
-      </c>
-      <c r="AL176">
-        <v>1.18</v>
-      </c>
-      <c r="AM176">
-        <v>2.55</v>
-      </c>
-      <c r="AN176">
-        <v>2</v>
-      </c>
-      <c r="AO176">
-        <v>0.89</v>
-      </c>
-      <c r="AP176">
-        <v>1.82</v>
-      </c>
-      <c r="AQ176">
-        <v>1.1</v>
-      </c>
-      <c r="AR176">
-        <v>1.91</v>
-      </c>
-      <c r="AS176">
-        <v>1.32</v>
-      </c>
-      <c r="AT176">
-        <v>3.23</v>
-      </c>
-      <c r="AU176">
-        <v>4</v>
-      </c>
-      <c r="AV176">
-        <v>7</v>
-      </c>
-      <c r="AW176">
-        <v>8</v>
-      </c>
-      <c r="AX176">
-        <v>6</v>
-      </c>
-      <c r="AY176">
-        <v>15</v>
-      </c>
-      <c r="AZ176">
-        <v>15</v>
-      </c>
-      <c r="BA176">
-        <v>2</v>
-      </c>
-      <c r="BB176">
-        <v>0</v>
-      </c>
-      <c r="BC176">
-        <v>2</v>
-      </c>
-      <c r="BD176">
-        <v>1.32</v>
-      </c>
-      <c r="BE176">
-        <v>7.5</v>
-      </c>
-      <c r="BF176">
-        <v>3.65</v>
-      </c>
-      <c r="BG176">
-        <v>1.26</v>
-      </c>
-      <c r="BH176">
-        <v>3.4</v>
-      </c>
-      <c r="BI176">
-        <v>1.47</v>
-      </c>
-      <c r="BJ176">
-        <v>2.48</v>
-      </c>
-      <c r="BK176">
-        <v>1.75</v>
-      </c>
-      <c r="BL176">
-        <v>1.95</v>
-      </c>
-      <c r="BM176">
-        <v>2.17</v>
-      </c>
-      <c r="BN176">
-        <v>1.6</v>
-      </c>
-      <c r="BO176">
-        <v>2.7</v>
-      </c>
       <c r="BP176">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="177" spans="1:68">
@@ -37620,7 +37620,7 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>7491987</v>
+        <v>7491992</v>
       </c>
       <c r="C177" t="s">
         <v>68</v>
@@ -37635,190 +37635,190 @@
         <v>20</v>
       </c>
       <c r="G177" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H177" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I177">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <v>1</v>
+      </c>
+      <c r="N177">
+        <v>1</v>
+      </c>
+      <c r="O177" t="s">
+        <v>96</v>
+      </c>
+      <c r="P177" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q177">
+        <v>3.25</v>
+      </c>
+      <c r="R177">
+        <v>2.2</v>
+      </c>
+      <c r="S177">
+        <v>3.1</v>
+      </c>
+      <c r="T177">
+        <v>1.36</v>
+      </c>
+      <c r="U177">
+        <v>3</v>
+      </c>
+      <c r="V177">
+        <v>2.63</v>
+      </c>
+      <c r="W177">
+        <v>1.44</v>
+      </c>
+      <c r="X177">
+        <v>7</v>
+      </c>
+      <c r="Y177">
+        <v>1.1</v>
+      </c>
+      <c r="Z177">
+        <v>2.82</v>
+      </c>
+      <c r="AA177">
+        <v>3.47</v>
+      </c>
+      <c r="AB177">
+        <v>2.55</v>
+      </c>
+      <c r="AC177">
+        <v>1.04</v>
+      </c>
+      <c r="AD177">
+        <v>13</v>
+      </c>
+      <c r="AE177">
+        <v>1.25</v>
+      </c>
+      <c r="AF177">
         <v>4</v>
       </c>
-      <c r="M177">
-        <v>3</v>
-      </c>
-      <c r="N177">
+      <c r="AG177">
+        <v>1.81</v>
+      </c>
+      <c r="AH177">
+        <v>2.01</v>
+      </c>
+      <c r="AI177">
+        <v>1.62</v>
+      </c>
+      <c r="AJ177">
+        <v>2.2</v>
+      </c>
+      <c r="AK177">
+        <v>1.52</v>
+      </c>
+      <c r="AL177">
+        <v>1.29</v>
+      </c>
+      <c r="AM177">
+        <v>1.46</v>
+      </c>
+      <c r="AN177">
+        <v>1</v>
+      </c>
+      <c r="AO177">
+        <v>0.8</v>
+      </c>
+      <c r="AP177">
+        <v>0.9</v>
+      </c>
+      <c r="AQ177">
+        <v>1</v>
+      </c>
+      <c r="AR177">
+        <v>1.23</v>
+      </c>
+      <c r="AS177">
+        <v>1.17</v>
+      </c>
+      <c r="AT177">
+        <v>2.4</v>
+      </c>
+      <c r="AU177">
+        <v>5</v>
+      </c>
+      <c r="AV177">
+        <v>6</v>
+      </c>
+      <c r="AW177">
+        <v>18</v>
+      </c>
+      <c r="AX177">
+        <v>8</v>
+      </c>
+      <c r="AY177">
+        <v>28</v>
+      </c>
+      <c r="AZ177">
+        <v>19</v>
+      </c>
+      <c r="BA177">
+        <v>9</v>
+      </c>
+      <c r="BB177">
         <v>7</v>
       </c>
-      <c r="O177" t="s">
-        <v>217</v>
-      </c>
-      <c r="P177" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q177">
-        <v>1.25</v>
-      </c>
-      <c r="R177">
-        <v>4.33</v>
-      </c>
-      <c r="S177">
-        <v>19</v>
-      </c>
-      <c r="T177">
-        <v>1.11</v>
-      </c>
-      <c r="U177">
-        <v>6.5</v>
-      </c>
-      <c r="V177">
-        <v>1.57</v>
-      </c>
-      <c r="W177">
-        <v>2.25</v>
-      </c>
-      <c r="X177">
-        <v>2.75</v>
-      </c>
-      <c r="Y177">
-        <v>1.4</v>
-      </c>
-      <c r="Z177">
-        <v>1.04</v>
-      </c>
-      <c r="AA177">
-        <v>25</v>
-      </c>
-      <c r="AB177">
-        <v>34</v>
-      </c>
-      <c r="AC177">
-        <v>1.01</v>
-      </c>
-      <c r="AD177">
-        <v>14</v>
-      </c>
-      <c r="AE177">
-        <v>1.04</v>
-      </c>
-      <c r="AF177">
-        <v>12</v>
-      </c>
-      <c r="AG177">
-        <v>1.16</v>
-      </c>
-      <c r="AH177">
-        <v>4.82</v>
-      </c>
-      <c r="AI177">
-        <v>2.2</v>
-      </c>
-      <c r="AJ177">
-        <v>1.62</v>
-      </c>
-      <c r="AK177">
-        <v>1.01</v>
-      </c>
-      <c r="AL177">
-        <v>1.02</v>
-      </c>
-      <c r="AM177">
-        <v>10.5</v>
-      </c>
-      <c r="AN177">
-        <v>2.78</v>
-      </c>
-      <c r="AO177">
-        <v>0.33</v>
-      </c>
-      <c r="AP177">
-        <v>2.8</v>
-      </c>
-      <c r="AQ177">
-        <v>0.3</v>
-      </c>
-      <c r="AR177">
-        <v>2.37</v>
-      </c>
-      <c r="AS177">
-        <v>1.14</v>
-      </c>
-      <c r="AT177">
-        <v>3.51</v>
-      </c>
-      <c r="AU177">
-        <v>13</v>
-      </c>
-      <c r="AV177">
-        <v>7</v>
-      </c>
-      <c r="AW177">
-        <v>17</v>
-      </c>
-      <c r="AX177">
-        <v>4</v>
-      </c>
-      <c r="AY177">
-        <v>36</v>
-      </c>
-      <c r="AZ177">
-        <v>11</v>
-      </c>
-      <c r="BA177">
-        <v>12</v>
-      </c>
-      <c r="BB177">
-        <v>1</v>
-      </c>
       <c r="BC177">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BD177">
-        <v>1.03</v>
+        <v>1.97</v>
       </c>
       <c r="BE177">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="BF177">
-        <v>15</v>
+        <v>2.05</v>
       </c>
       <c r="BG177">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="BH177">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI177">
+        <v>1.55</v>
+      </c>
+      <c r="BJ177">
+        <v>2.28</v>
+      </c>
+      <c r="BK177">
+        <v>1.9</v>
+      </c>
+      <c r="BL177">
+        <v>1.79</v>
+      </c>
+      <c r="BM177">
+        <v>2.4</v>
+      </c>
+      <c r="BN177">
+        <v>1.49</v>
+      </c>
+      <c r="BO177">
+        <v>3.15</v>
+      </c>
+      <c r="BP177">
         <v>1.3</v>
-      </c>
-      <c r="BJ177">
-        <v>3.05</v>
-      </c>
-      <c r="BK177">
-        <v>1.52</v>
-      </c>
-      <c r="BL177">
-        <v>2.33</v>
-      </c>
-      <c r="BM177">
-        <v>1.81</v>
-      </c>
-      <c r="BN177">
-        <v>1.88</v>
-      </c>
-      <c r="BO177">
-        <v>2.2</v>
-      </c>
-      <c r="BP177">
-        <v>1.57</v>
       </c>
     </row>
     <row r="178" spans="1:68">
@@ -37826,7 +37826,7 @@
         <v>177</v>
       </c>
       <c r="B178">
-        <v>7491989</v>
+        <v>7491993</v>
       </c>
       <c r="C178" t="s">
         <v>68</v>
@@ -37841,16 +37841,16 @@
         <v>20</v>
       </c>
       <c r="G178" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H178" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K178">
         <v>1</v>
@@ -37859,172 +37859,172 @@
         <v>1</v>
       </c>
       <c r="M178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O178" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="P178" t="s">
         <v>325</v>
       </c>
       <c r="Q178">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R178">
+        <v>2.05</v>
+      </c>
+      <c r="S178">
+        <v>3.75</v>
+      </c>
+      <c r="T178">
+        <v>1.5</v>
+      </c>
+      <c r="U178">
+        <v>2.5</v>
+      </c>
+      <c r="V178">
+        <v>3.4</v>
+      </c>
+      <c r="W178">
+        <v>1.3</v>
+      </c>
+      <c r="X178">
+        <v>10</v>
+      </c>
+      <c r="Y178">
+        <v>1.06</v>
+      </c>
+      <c r="Z178">
         <v>2.4</v>
       </c>
-      <c r="S178">
-        <v>2.3</v>
-      </c>
-      <c r="T178">
-        <v>1.29</v>
-      </c>
-      <c r="U178">
-        <v>3.5</v>
-      </c>
-      <c r="V178">
-        <v>2.25</v>
-      </c>
-      <c r="W178">
-        <v>1.57</v>
-      </c>
-      <c r="X178">
-        <v>5.5</v>
-      </c>
-      <c r="Y178">
-        <v>1.14</v>
-      </c>
-      <c r="Z178">
-        <v>4.2</v>
-      </c>
       <c r="AA178">
-        <v>4.1</v>
+        <v>3.26</v>
       </c>
       <c r="AB178">
-        <v>1.82</v>
+        <v>3.21</v>
       </c>
       <c r="AC178">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AD178">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="AE178">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AF178">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG178">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AH178">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AI178">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AJ178">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK178">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="AL178">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AM178">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AN178">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AO178">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="AP178">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AQ178">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AR178">
         <v>1.36</v>
       </c>
       <c r="AS178">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AT178">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="AU178">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV178">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AW178">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX178">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AY178">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ178">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="BA178">
+        <v>3</v>
+      </c>
+      <c r="BB178">
+        <v>1</v>
+      </c>
+      <c r="BC178">
         <v>4</v>
       </c>
-      <c r="BB178">
-        <v>5</v>
-      </c>
-      <c r="BC178">
-        <v>9</v>
-      </c>
       <c r="BD178">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="BE178">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="BF178">
-        <v>1.66</v>
+        <v>2.33</v>
       </c>
       <c r="BG178">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="BH178">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="BI178">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="BJ178">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="BK178">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="BL178">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="BM178">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="BN178">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="BO178">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="BP178">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="179" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="328">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -674,6 +674,9 @@
   </si>
   <si>
     <t>['15', '19', '51']</t>
+  </si>
+  <si>
+    <t>['56', '82', '90+7']</t>
   </si>
   <si>
     <t>['12', '38', '90+11']</t>
@@ -1356,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1612,7 +1615,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2024,7 +2027,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2230,7 +2233,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2436,7 +2439,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2517,7 +2520,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ6">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2642,7 +2645,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3054,7 +3057,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3260,7 +3263,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3672,7 +3675,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3878,7 +3881,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4084,7 +4087,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4290,7 +4293,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4702,7 +4705,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5192,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5320,7 +5323,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5732,7 +5735,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6144,7 +6147,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6350,7 +6353,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6556,7 +6559,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6762,7 +6765,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6968,7 +6971,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7049,7 +7052,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ28">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR28">
         <v>1.23</v>
@@ -7174,7 +7177,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7380,7 +7383,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7586,7 +7589,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7792,7 +7795,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7998,7 +8001,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8410,7 +8413,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9028,7 +9031,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9440,7 +9443,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9646,7 +9649,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9852,7 +9855,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10264,7 +10267,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10342,7 +10345,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ44">
         <v>2.11</v>
@@ -10470,7 +10473,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10676,7 +10679,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10757,7 +10760,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ46">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR46">
         <v>1.82</v>
@@ -11088,7 +11091,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11500,7 +11503,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11706,7 +11709,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11912,7 +11915,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12324,7 +12327,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12530,7 +12533,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12736,7 +12739,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12942,7 +12945,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13354,7 +13357,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13560,7 +13563,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13766,7 +13769,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14050,7 +14053,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ62">
         <v>1.33</v>
@@ -14178,7 +14181,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14384,7 +14387,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14465,7 +14468,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ64">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR64">
         <v>1.11</v>
@@ -14590,7 +14593,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14796,7 +14799,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15208,7 +15211,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15620,7 +15623,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15826,7 +15829,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16728,7 +16731,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -16856,7 +16859,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17062,7 +17065,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18173,7 +18176,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ82">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18504,7 +18507,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18916,7 +18919,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19122,7 +19125,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19740,7 +19743,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19946,7 +19949,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20230,7 +20233,7 @@
         <v>0.25</v>
       </c>
       <c r="AP92">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ92">
         <v>0.9</v>
@@ -20358,7 +20361,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20976,7 +20979,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21469,7 +21472,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ98">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR98">
         <v>1.59</v>
@@ -21594,7 +21597,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22006,7 +22009,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22212,7 +22215,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22418,7 +22421,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22830,7 +22833,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23036,7 +23039,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23242,7 +23245,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23654,7 +23657,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23860,7 +23863,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24066,7 +24069,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24272,7 +24275,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24353,7 +24356,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ112">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR112">
         <v>1.23</v>
@@ -24478,7 +24481,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24684,7 +24687,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24762,7 +24765,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ114">
         <v>0.7</v>
@@ -25096,7 +25099,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25302,7 +25305,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25714,7 +25717,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25920,7 +25923,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26126,7 +26129,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26332,7 +26335,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26538,7 +26541,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26744,7 +26747,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26825,7 +26828,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ124">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -26950,7 +26953,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27156,7 +27159,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27362,7 +27365,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27568,7 +27571,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27646,7 +27649,7 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ128">
         <v>1.36</v>
@@ -27774,7 +27777,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27980,7 +27983,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28186,7 +28189,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28392,7 +28395,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28598,7 +28601,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -29216,7 +29219,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29422,7 +29425,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -30040,7 +30043,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30452,7 +30455,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30864,7 +30867,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -30945,7 +30948,7 @@
         <v>2</v>
       </c>
       <c r="AQ144">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -31070,7 +31073,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31276,7 +31279,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -32306,7 +32309,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32590,7 +32593,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ152">
         <v>0.7</v>
@@ -32718,7 +32721,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32924,7 +32927,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33336,7 +33339,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33542,7 +33545,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33748,7 +33751,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34160,7 +34163,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34238,7 +34241,7 @@
         <v>2</v>
       </c>
       <c r="AP160">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ160">
         <v>1.7</v>
@@ -34366,7 +34369,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34572,7 +34575,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34778,7 +34781,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34984,7 +34987,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35602,7 +35605,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35808,7 +35811,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -35889,7 +35892,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ168">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR168">
         <v>1.59</v>
@@ -36014,7 +36017,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36426,7 +36429,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -37044,7 +37047,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37250,7 +37253,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37328,7 +37331,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ175">
         <v>0.3</v>
@@ -37456,7 +37459,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37868,7 +37871,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38280,7 +38283,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38486,7 +38489,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38643,6 +38646,212 @@
       </c>
       <c r="BP181">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7491994</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45695.6875</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>87</v>
+      </c>
+      <c r="H182" t="s">
+        <v>84</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>3</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>3</v>
+      </c>
+      <c r="O182" t="s">
+        <v>220</v>
+      </c>
+      <c r="P182" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q182">
+        <v>1.4</v>
+      </c>
+      <c r="R182">
+        <v>3.6</v>
+      </c>
+      <c r="S182">
+        <v>12</v>
+      </c>
+      <c r="T182">
+        <v>1.14</v>
+      </c>
+      <c r="U182">
+        <v>5.5</v>
+      </c>
+      <c r="V182">
+        <v>1.73</v>
+      </c>
+      <c r="W182">
+        <v>2</v>
+      </c>
+      <c r="X182">
+        <v>3.25</v>
+      </c>
+      <c r="Y182">
+        <v>1.33</v>
+      </c>
+      <c r="Z182">
+        <v>1.11</v>
+      </c>
+      <c r="AA182">
+        <v>13</v>
+      </c>
+      <c r="AB182">
+        <v>19</v>
+      </c>
+      <c r="AC182">
+        <v>0</v>
+      </c>
+      <c r="AD182">
+        <v>0</v>
+      </c>
+      <c r="AE182">
+        <v>1.05</v>
+      </c>
+      <c r="AF182">
+        <v>10</v>
+      </c>
+      <c r="AG182">
+        <v>1.25</v>
+      </c>
+      <c r="AH182">
+        <v>3.75</v>
+      </c>
+      <c r="AI182">
+        <v>1.91</v>
+      </c>
+      <c r="AJ182">
+        <v>1.91</v>
+      </c>
+      <c r="AK182">
+        <v>1.02</v>
+      </c>
+      <c r="AL182">
+        <v>1.05</v>
+      </c>
+      <c r="AM182">
+        <v>6.5</v>
+      </c>
+      <c r="AN182">
+        <v>2.8</v>
+      </c>
+      <c r="AO182">
+        <v>1.7</v>
+      </c>
+      <c r="AP182">
+        <v>2.82</v>
+      </c>
+      <c r="AQ182">
+        <v>1.55</v>
+      </c>
+      <c r="AR182">
+        <v>2.47</v>
+      </c>
+      <c r="AS182">
+        <v>1.28</v>
+      </c>
+      <c r="AT182">
+        <v>3.75</v>
+      </c>
+      <c r="AU182">
+        <v>13</v>
+      </c>
+      <c r="AV182">
+        <v>0</v>
+      </c>
+      <c r="AW182">
+        <v>9</v>
+      </c>
+      <c r="AX182">
+        <v>3</v>
+      </c>
+      <c r="AY182">
+        <v>23</v>
+      </c>
+      <c r="AZ182">
+        <v>3</v>
+      </c>
+      <c r="BA182">
+        <v>5</v>
+      </c>
+      <c r="BB182">
+        <v>2</v>
+      </c>
+      <c r="BC182">
+        <v>7</v>
+      </c>
+      <c r="BD182">
+        <v>1.07</v>
+      </c>
+      <c r="BE182">
+        <v>12.5</v>
+      </c>
+      <c r="BF182">
+        <v>8.5</v>
+      </c>
+      <c r="BG182">
+        <v>1.25</v>
+      </c>
+      <c r="BH182">
+        <v>3.45</v>
+      </c>
+      <c r="BI182">
+        <v>1.44</v>
+      </c>
+      <c r="BJ182">
+        <v>2.55</v>
+      </c>
+      <c r="BK182">
+        <v>1.72</v>
+      </c>
+      <c r="BL182">
+        <v>1.98</v>
+      </c>
+      <c r="BM182">
+        <v>2.08</v>
+      </c>
+      <c r="BN182">
+        <v>1.65</v>
+      </c>
+      <c r="BO182">
+        <v>2.65</v>
+      </c>
+      <c r="BP182">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="331">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -679,6 +679,12 @@
     <t>['56', '82', '90+7']</t>
   </si>
   <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['26']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -907,9 +913,6 @@
     <t>['14', '40']</t>
   </si>
   <si>
-    <t>['30']</t>
-  </si>
-  <si>
     <t>['24', '54']</t>
   </si>
   <si>
@@ -998,6 +1001,12 @@
   </si>
   <si>
     <t>['50']</t>
+  </si>
+  <si>
+    <t>['50', '61']</t>
+  </si>
+  <si>
+    <t>['24', '61', '73', '87']</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP182"/>
+  <dimension ref="A1:BP188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1615,7 +1624,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1693,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ2">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2027,7 +2036,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2105,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>0.3</v>
@@ -2233,7 +2242,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2311,10 +2320,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ5">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2439,7 +2448,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2645,7 +2654,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2723,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2929,10 +2938,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ8">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3057,7 +3066,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3135,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ9">
         <v>2.3</v>
@@ -3263,7 +3272,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3344,7 +3353,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ10">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3675,7 +3684,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3881,7 +3890,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4087,7 +4096,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4293,7 +4302,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4705,7 +4714,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4992,7 +5001,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ18">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5323,7 +5332,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5401,10 +5410,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ20">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR20">
         <v>1.89</v>
@@ -5610,7 +5619,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR21">
         <v>1.16</v>
@@ -5735,7 +5744,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5813,10 +5822,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>2.26</v>
@@ -6019,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ23">
         <v>0.1</v>
@@ -6147,7 +6156,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6225,10 +6234,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR24">
         <v>1.03</v>
@@ -6353,7 +6362,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6431,10 +6440,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR25">
         <v>1.46</v>
@@ -6559,7 +6568,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6765,7 +6774,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6971,7 +6980,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7049,7 +7058,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ28">
         <v>1.55</v>
@@ -7177,7 +7186,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7383,7 +7392,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7589,7 +7598,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7795,7 +7804,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8001,7 +8010,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8413,7 +8422,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9031,7 +9040,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9109,7 +9118,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ38">
         <v>0.1</v>
@@ -9315,10 +9324,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ39">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9443,7 +9452,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9521,10 +9530,10 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ40">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9649,7 +9658,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9727,10 +9736,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ41">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR41">
         <v>1.28</v>
@@ -9855,7 +9864,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -9933,7 +9942,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ42">
         <v>1.2</v>
@@ -10142,7 +10151,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR43">
         <v>1.14</v>
@@ -10267,7 +10276,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10348,7 +10357,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ44">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10473,7 +10482,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10554,7 +10563,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ45">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR45">
         <v>1</v>
@@ -10679,7 +10688,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10757,7 +10766,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ46">
         <v>1.55</v>
@@ -11091,7 +11100,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11503,7 +11512,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11709,7 +11718,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11915,7 +11924,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12327,7 +12336,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12533,7 +12542,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12739,7 +12748,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12817,7 +12826,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ56">
         <v>1.2</v>
@@ -12945,7 +12954,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13026,7 +13035,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ57">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR57">
         <v>2.44</v>
@@ -13229,7 +13238,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
         <v>0.1</v>
@@ -13357,7 +13366,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13435,10 +13444,10 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ59">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR59">
         <v>1.71</v>
@@ -13563,7 +13572,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13641,7 +13650,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ60">
         <v>1.36</v>
@@ -13769,7 +13778,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13847,10 +13856,10 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ61">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR61">
         <v>1.33</v>
@@ -14056,7 +14065,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ62">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR62">
         <v>1.47</v>
@@ -14181,7 +14190,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14262,7 +14271,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ63">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR63">
         <v>1.07</v>
@@ -14387,7 +14396,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14465,7 +14474,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ64">
         <v>1.55</v>
@@ -14593,7 +14602,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14671,7 +14680,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65">
         <v>1.1</v>
@@ -14799,7 +14808,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15211,7 +15220,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15623,7 +15632,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15704,7 +15713,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ70">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR70">
         <v>0.6899999999999999</v>
@@ -15829,7 +15838,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16116,7 +16125,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ72">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16528,7 +16537,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ74">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR74">
         <v>2.41</v>
@@ -16734,7 +16743,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ75">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR75">
         <v>1.82</v>
@@ -16859,7 +16868,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17065,7 +17074,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17143,7 +17152,7 @@
         <v>0.75</v>
       </c>
       <c r="AP77">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
         <v>1.2</v>
@@ -17352,7 +17361,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ78">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -17555,10 +17564,10 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ79">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR79">
         <v>1.14</v>
@@ -17761,7 +17770,7 @@
         <v>2.5</v>
       </c>
       <c r="AP80">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ80">
         <v>1.36</v>
@@ -17967,7 +17976,7 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ81">
         <v>1.4</v>
@@ -18173,7 +18182,7 @@
         <v>2.5</v>
       </c>
       <c r="AP82">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ82">
         <v>1.55</v>
@@ -18507,7 +18516,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18919,7 +18928,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -18997,7 +19006,7 @@
         <v>0.25</v>
       </c>
       <c r="AP86">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ86">
         <v>0.8</v>
@@ -19125,7 +19134,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19206,7 +19215,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ87">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -19743,7 +19752,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19824,7 +19833,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ90">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR90">
         <v>2.13</v>
@@ -19949,7 +19958,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20236,7 +20245,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR92">
         <v>1.83</v>
@@ -20361,7 +20370,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20442,7 +20451,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ93">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR93">
         <v>2.3</v>
@@ -20851,7 +20860,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ95">
         <v>1</v>
@@ -20979,7 +20988,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21057,7 +21066,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
         <v>1.36</v>
@@ -21263,10 +21272,10 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ97">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR97">
         <v>1.25</v>
@@ -21597,7 +21606,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21881,7 +21890,7 @@
         <v>1.2</v>
       </c>
       <c r="AP100">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ100">
         <v>1.2</v>
@@ -22009,7 +22018,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22215,7 +22224,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22296,7 +22305,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ102">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR102">
         <v>1.35</v>
@@ -22421,7 +22430,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22499,7 +22508,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ103">
         <v>1.1</v>
@@ -22833,7 +22842,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23039,7 +23048,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23120,7 +23129,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ106">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR106">
         <v>1.1</v>
@@ -23245,7 +23254,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23323,7 +23332,7 @@
         <v>2.67</v>
       </c>
       <c r="AP107">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ107">
         <v>2.3</v>
@@ -23529,7 +23538,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108">
         <v>0.7</v>
@@ -23657,7 +23666,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23738,7 +23747,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ109">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -23863,7 +23872,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23944,7 +23953,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ110">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR110">
         <v>2.1</v>
@@ -24069,7 +24078,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24275,7 +24284,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24481,7 +24490,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24562,7 +24571,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ113">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR113">
         <v>1.55</v>
@@ -24687,7 +24696,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24768,7 +24777,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ114">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR114">
         <v>2.04</v>
@@ -25099,7 +25108,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25177,7 +25186,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ116">
         <v>0.8</v>
@@ -25305,7 +25314,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25383,7 +25392,7 @@
         <v>2.2</v>
       </c>
       <c r="AP117">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ117">
         <v>1.4</v>
@@ -25589,7 +25598,7 @@
         <v>1.17</v>
       </c>
       <c r="AP118">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ118">
         <v>1</v>
@@ -25717,7 +25726,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25795,7 +25804,7 @@
         <v>2.17</v>
       </c>
       <c r="AP119">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ119">
         <v>1.7</v>
@@ -25923,7 +25932,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26129,7 +26138,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26207,7 +26216,7 @@
         <v>2.43</v>
       </c>
       <c r="AP121">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ121">
         <v>2.3</v>
@@ -26335,7 +26344,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26416,7 +26425,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ122">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26541,7 +26550,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>297</v>
+        <v>221</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26619,7 +26628,7 @@
         <v>0.33</v>
       </c>
       <c r="AP123">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ123">
         <v>0.3</v>
@@ -26747,7 +26756,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26953,7 +26962,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27034,7 +27043,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ125">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR125">
         <v>1.33</v>
@@ -27159,7 +27168,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27237,7 +27246,7 @@
         <v>0.5</v>
       </c>
       <c r="AP126">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ126">
         <v>0.7</v>
@@ -27365,7 +27374,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27446,7 +27455,7 @@
         <v>2</v>
       </c>
       <c r="AQ127">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR127">
         <v>1.42</v>
@@ -27571,7 +27580,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27777,7 +27786,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27858,7 +27867,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ129">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -27983,7 +27992,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28189,7 +28198,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28395,7 +28404,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28473,7 +28482,7 @@
         <v>0.83</v>
       </c>
       <c r="AP132">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ132">
         <v>1.1</v>
@@ -28601,7 +28610,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28682,7 +28691,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ133">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR133">
         <v>1.24</v>
@@ -29094,7 +29103,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ135">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR135">
         <v>1.23</v>
@@ -29219,7 +29228,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29297,7 +29306,7 @@
         <v>0.33</v>
       </c>
       <c r="AP136">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ136">
         <v>0.8</v>
@@ -29425,7 +29434,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29503,10 +29512,10 @@
         <v>2.14</v>
       </c>
       <c r="AP137">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ137">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR137">
         <v>1.63</v>
@@ -29709,7 +29718,7 @@
         <v>1.86</v>
       </c>
       <c r="AP138">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ138">
         <v>1.7</v>
@@ -29918,7 +29927,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ139">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR139">
         <v>1.27</v>
@@ -30043,7 +30052,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30121,7 +30130,7 @@
         <v>0.29</v>
       </c>
       <c r="AP140">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ140">
         <v>0.3</v>
@@ -30327,7 +30336,7 @@
         <v>0.13</v>
       </c>
       <c r="AP141">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ141">
         <v>0.1</v>
@@ -30455,7 +30464,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30536,7 +30545,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ142">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR142">
         <v>1.26</v>
@@ -30739,7 +30748,7 @@
         <v>2.13</v>
       </c>
       <c r="AP143">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ143">
         <v>2.3</v>
@@ -30867,7 +30876,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31073,7 +31082,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31154,7 +31163,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ145">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31279,7 +31288,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31769,7 +31778,7 @@
         <v>1.14</v>
       </c>
       <c r="AP148">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ148">
         <v>1.1</v>
@@ -32309,7 +32318,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32721,7 +32730,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32802,7 +32811,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ153">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR153">
         <v>1.26</v>
@@ -32927,7 +32936,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33008,7 +33017,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ154">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33339,7 +33348,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33545,7 +33554,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33751,7 +33760,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34163,7 +34172,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34369,7 +34378,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34575,7 +34584,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34781,7 +34790,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34862,7 +34871,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ163">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR163">
         <v>1.3</v>
@@ -34987,7 +34996,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35065,7 +35074,7 @@
         <v>0.25</v>
       </c>
       <c r="AP164">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ164">
         <v>0.3</v>
@@ -35271,10 +35280,10 @@
         <v>1.5</v>
       </c>
       <c r="AP165">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ165">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR165">
         <v>1.46</v>
@@ -35480,7 +35489,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ166">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR166">
         <v>1.56</v>
@@ -35605,7 +35614,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35683,7 +35692,7 @@
         <v>2.22</v>
       </c>
       <c r="AP167">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ167">
         <v>2.3</v>
@@ -35811,7 +35820,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -35889,7 +35898,7 @@
         <v>1.78</v>
       </c>
       <c r="AP168">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ168">
         <v>1.55</v>
@@ -36017,7 +36026,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36098,7 +36107,7 @@
         <v>2</v>
       </c>
       <c r="AQ169">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR169">
         <v>1.49</v>
@@ -36301,7 +36310,7 @@
         <v>0.11</v>
       </c>
       <c r="AP170">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ170">
         <v>0.1</v>
@@ -36429,7 +36438,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36507,10 +36516,10 @@
         <v>1.78</v>
       </c>
       <c r="AP171">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ171">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR171">
         <v>1.74</v>
@@ -36716,7 +36725,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ172">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR172">
         <v>1.31</v>
@@ -37047,7 +37056,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37253,7 +37262,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37459,7 +37468,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37871,7 +37880,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -37952,7 +37961,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ178">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR178">
         <v>1.36</v>
@@ -38283,7 +38292,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38489,7 +38498,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38852,6 +38861,1242 @@
       </c>
       <c r="BP182">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7491999</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F183">
+        <v>21</v>
+      </c>
+      <c r="G183" t="s">
+        <v>77</v>
+      </c>
+      <c r="H183" t="s">
+        <v>85</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+      <c r="N183">
+        <v>0</v>
+      </c>
+      <c r="O183" t="s">
+        <v>96</v>
+      </c>
+      <c r="P183" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q183">
+        <v>4.33</v>
+      </c>
+      <c r="R183">
+        <v>2.38</v>
+      </c>
+      <c r="S183">
+        <v>2.38</v>
+      </c>
+      <c r="T183">
+        <v>1.3</v>
+      </c>
+      <c r="U183">
+        <v>3.4</v>
+      </c>
+      <c r="V183">
+        <v>2.5</v>
+      </c>
+      <c r="W183">
+        <v>1.5</v>
+      </c>
+      <c r="X183">
+        <v>6</v>
+      </c>
+      <c r="Y183">
+        <v>1.13</v>
+      </c>
+      <c r="Z183">
+        <v>4.2</v>
+      </c>
+      <c r="AA183">
+        <v>4.1</v>
+      </c>
+      <c r="AB183">
+        <v>1.82</v>
+      </c>
+      <c r="AC183">
+        <v>1.03</v>
+      </c>
+      <c r="AD183">
+        <v>15</v>
+      </c>
+      <c r="AE183">
+        <v>1.2</v>
+      </c>
+      <c r="AF183">
+        <v>4.5</v>
+      </c>
+      <c r="AG183">
+        <v>1.65</v>
+      </c>
+      <c r="AH183">
+        <v>2.15</v>
+      </c>
+      <c r="AI183">
+        <v>1.57</v>
+      </c>
+      <c r="AJ183">
+        <v>2.25</v>
+      </c>
+      <c r="AK183">
+        <v>1.93</v>
+      </c>
+      <c r="AL183">
+        <v>1.25</v>
+      </c>
+      <c r="AM183">
+        <v>1.24</v>
+      </c>
+      <c r="AN183">
+        <v>1.2</v>
+      </c>
+      <c r="AO183">
+        <v>2.11</v>
+      </c>
+      <c r="AP183">
+        <v>1.18</v>
+      </c>
+      <c r="AQ183">
+        <v>2</v>
+      </c>
+      <c r="AR183">
+        <v>1.45</v>
+      </c>
+      <c r="AS183">
+        <v>1.47</v>
+      </c>
+      <c r="AT183">
+        <v>2.92</v>
+      </c>
+      <c r="AU183">
+        <v>9</v>
+      </c>
+      <c r="AV183">
+        <v>2</v>
+      </c>
+      <c r="AW183">
+        <v>5</v>
+      </c>
+      <c r="AX183">
+        <v>14</v>
+      </c>
+      <c r="AY183">
+        <v>16</v>
+      </c>
+      <c r="AZ183">
+        <v>18</v>
+      </c>
+      <c r="BA183">
+        <v>3</v>
+      </c>
+      <c r="BB183">
+        <v>9</v>
+      </c>
+      <c r="BC183">
+        <v>12</v>
+      </c>
+      <c r="BD183">
+        <v>2.75</v>
+      </c>
+      <c r="BE183">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF183">
+        <v>1.64</v>
+      </c>
+      <c r="BG183">
+        <v>1.23</v>
+      </c>
+      <c r="BH183">
+        <v>3.42</v>
+      </c>
+      <c r="BI183">
+        <v>1.46</v>
+      </c>
+      <c r="BJ183">
+        <v>2.45</v>
+      </c>
+      <c r="BK183">
+        <v>1.82</v>
+      </c>
+      <c r="BL183">
+        <v>1.88</v>
+      </c>
+      <c r="BM183">
+        <v>2.32</v>
+      </c>
+      <c r="BN183">
+        <v>1.51</v>
+      </c>
+      <c r="BO183">
+        <v>3.08</v>
+      </c>
+      <c r="BP183">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7491996</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184" t="s">
+        <v>76</v>
+      </c>
+      <c r="H184" t="s">
+        <v>80</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>1</v>
+      </c>
+      <c r="M184">
+        <v>2</v>
+      </c>
+      <c r="N184">
+        <v>3</v>
+      </c>
+      <c r="O184" t="s">
+        <v>218</v>
+      </c>
+      <c r="P184" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q184">
+        <v>2.5</v>
+      </c>
+      <c r="R184">
+        <v>2.4</v>
+      </c>
+      <c r="S184">
+        <v>3.75</v>
+      </c>
+      <c r="T184">
+        <v>1.29</v>
+      </c>
+      <c r="U184">
+        <v>3.5</v>
+      </c>
+      <c r="V184">
+        <v>2.25</v>
+      </c>
+      <c r="W184">
+        <v>1.57</v>
+      </c>
+      <c r="X184">
+        <v>5.5</v>
+      </c>
+      <c r="Y184">
+        <v>1.14</v>
+      </c>
+      <c r="Z184">
+        <v>2.16</v>
+      </c>
+      <c r="AA184">
+        <v>3.84</v>
+      </c>
+      <c r="AB184">
+        <v>3.23</v>
+      </c>
+      <c r="AC184">
+        <v>1.02</v>
+      </c>
+      <c r="AD184">
+        <v>19</v>
+      </c>
+      <c r="AE184">
+        <v>1.18</v>
+      </c>
+      <c r="AF184">
+        <v>5</v>
+      </c>
+      <c r="AG184">
+        <v>1.53</v>
+      </c>
+      <c r="AH184">
+        <v>2.45</v>
+      </c>
+      <c r="AI184">
+        <v>1.5</v>
+      </c>
+      <c r="AJ184">
+        <v>2.5</v>
+      </c>
+      <c r="AK184">
+        <v>1.36</v>
+      </c>
+      <c r="AL184">
+        <v>1.27</v>
+      </c>
+      <c r="AM184">
+        <v>1.66</v>
+      </c>
+      <c r="AN184">
+        <v>2.1</v>
+      </c>
+      <c r="AO184">
+        <v>1.33</v>
+      </c>
+      <c r="AP184">
+        <v>1.91</v>
+      </c>
+      <c r="AQ184">
+        <v>1.5</v>
+      </c>
+      <c r="AR184">
+        <v>1.55</v>
+      </c>
+      <c r="AS184">
+        <v>1.26</v>
+      </c>
+      <c r="AT184">
+        <v>2.81</v>
+      </c>
+      <c r="AU184">
+        <v>6</v>
+      </c>
+      <c r="AV184">
+        <v>3</v>
+      </c>
+      <c r="AW184">
+        <v>10</v>
+      </c>
+      <c r="AX184">
+        <v>2</v>
+      </c>
+      <c r="AY184">
+        <v>20</v>
+      </c>
+      <c r="AZ184">
+        <v>6</v>
+      </c>
+      <c r="BA184">
+        <v>9</v>
+      </c>
+      <c r="BB184">
+        <v>4</v>
+      </c>
+      <c r="BC184">
+        <v>13</v>
+      </c>
+      <c r="BD184">
+        <v>1.76</v>
+      </c>
+      <c r="BE184">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF184">
+        <v>2.47</v>
+      </c>
+      <c r="BG184">
+        <v>1.19</v>
+      </c>
+      <c r="BH184">
+        <v>3.8</v>
+      </c>
+      <c r="BI184">
+        <v>1.39</v>
+      </c>
+      <c r="BJ184">
+        <v>2.67</v>
+      </c>
+      <c r="BK184">
+        <v>1.71</v>
+      </c>
+      <c r="BL184">
+        <v>2.02</v>
+      </c>
+      <c r="BM184">
+        <v>2.14</v>
+      </c>
+      <c r="BN184">
+        <v>1.6</v>
+      </c>
+      <c r="BO184">
+        <v>2.81</v>
+      </c>
+      <c r="BP184">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7491997</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F185">
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>72</v>
+      </c>
+      <c r="H185" t="s">
+        <v>79</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <v>4</v>
+      </c>
+      <c r="N185">
+        <v>4</v>
+      </c>
+      <c r="O185" t="s">
+        <v>96</v>
+      </c>
+      <c r="P185" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q185">
+        <v>2.75</v>
+      </c>
+      <c r="R185">
+        <v>2.2</v>
+      </c>
+      <c r="S185">
+        <v>3.75</v>
+      </c>
+      <c r="T185">
+        <v>1.36</v>
+      </c>
+      <c r="U185">
+        <v>3</v>
+      </c>
+      <c r="V185">
+        <v>2.75</v>
+      </c>
+      <c r="W185">
+        <v>1.4</v>
+      </c>
+      <c r="X185">
+        <v>7</v>
+      </c>
+      <c r="Y185">
+        <v>1.1</v>
+      </c>
+      <c r="Z185">
+        <v>2.14</v>
+      </c>
+      <c r="AA185">
+        <v>3.6</v>
+      </c>
+      <c r="AB185">
+        <v>3.45</v>
+      </c>
+      <c r="AC185">
+        <v>1.04</v>
+      </c>
+      <c r="AD185">
+        <v>13</v>
+      </c>
+      <c r="AE185">
+        <v>1.28</v>
+      </c>
+      <c r="AF185">
+        <v>3.75</v>
+      </c>
+      <c r="AG185">
+        <v>1.81</v>
+      </c>
+      <c r="AH185">
+        <v>2.01</v>
+      </c>
+      <c r="AI185">
+        <v>1.67</v>
+      </c>
+      <c r="AJ185">
+        <v>2.1</v>
+      </c>
+      <c r="AK185">
+        <v>1.33</v>
+      </c>
+      <c r="AL185">
+        <v>1.28</v>
+      </c>
+      <c r="AM185">
+        <v>1.68</v>
+      </c>
+      <c r="AN185">
+        <v>1.1</v>
+      </c>
+      <c r="AO185">
+        <v>0.5</v>
+      </c>
+      <c r="AP185">
+        <v>1</v>
+      </c>
+      <c r="AQ185">
+        <v>0.73</v>
+      </c>
+      <c r="AR185">
+        <v>1.84</v>
+      </c>
+      <c r="AS185">
+        <v>1.21</v>
+      </c>
+      <c r="AT185">
+        <v>3.05</v>
+      </c>
+      <c r="AU185">
+        <v>5</v>
+      </c>
+      <c r="AV185">
+        <v>8</v>
+      </c>
+      <c r="AW185">
+        <v>12</v>
+      </c>
+      <c r="AX185">
+        <v>15</v>
+      </c>
+      <c r="AY185">
+        <v>22</v>
+      </c>
+      <c r="AZ185">
+        <v>29</v>
+      </c>
+      <c r="BA185">
+        <v>8</v>
+      </c>
+      <c r="BB185">
+        <v>4</v>
+      </c>
+      <c r="BC185">
+        <v>12</v>
+      </c>
+      <c r="BD185">
+        <v>1.7</v>
+      </c>
+      <c r="BE185">
+        <v>9</v>
+      </c>
+      <c r="BF185">
+        <v>2.58</v>
+      </c>
+      <c r="BG185">
+        <v>1.19</v>
+      </c>
+      <c r="BH185">
+        <v>3.82</v>
+      </c>
+      <c r="BI185">
+        <v>1.39</v>
+      </c>
+      <c r="BJ185">
+        <v>2.67</v>
+      </c>
+      <c r="BK185">
+        <v>1.7</v>
+      </c>
+      <c r="BL185">
+        <v>2.03</v>
+      </c>
+      <c r="BM185">
+        <v>2.14</v>
+      </c>
+      <c r="BN185">
+        <v>1.6</v>
+      </c>
+      <c r="BO185">
+        <v>2.78</v>
+      </c>
+      <c r="BP185">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7491998</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F186">
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>73</v>
+      </c>
+      <c r="H186" t="s">
+        <v>86</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>1</v>
+      </c>
+      <c r="O186" t="s">
+        <v>221</v>
+      </c>
+      <c r="P186" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q186">
+        <v>2.3</v>
+      </c>
+      <c r="R186">
+        <v>2.3</v>
+      </c>
+      <c r="S186">
+        <v>4.75</v>
+      </c>
+      <c r="T186">
+        <v>1.33</v>
+      </c>
+      <c r="U186">
+        <v>3.25</v>
+      </c>
+      <c r="V186">
+        <v>2.63</v>
+      </c>
+      <c r="W186">
+        <v>1.44</v>
+      </c>
+      <c r="X186">
+        <v>6.5</v>
+      </c>
+      <c r="Y186">
+        <v>1.11</v>
+      </c>
+      <c r="Z186">
+        <v>1.84</v>
+      </c>
+      <c r="AA186">
+        <v>3.89</v>
+      </c>
+      <c r="AB186">
+        <v>4.3</v>
+      </c>
+      <c r="AC186">
+        <v>1.04</v>
+      </c>
+      <c r="AD186">
+        <v>13</v>
+      </c>
+      <c r="AE186">
+        <v>1.25</v>
+      </c>
+      <c r="AF186">
+        <v>4</v>
+      </c>
+      <c r="AG186">
+        <v>1.61</v>
+      </c>
+      <c r="AH186">
+        <v>2.15</v>
+      </c>
+      <c r="AI186">
+        <v>1.7</v>
+      </c>
+      <c r="AJ186">
+        <v>2.05</v>
+      </c>
+      <c r="AK186">
+        <v>1.23</v>
+      </c>
+      <c r="AL186">
+        <v>1.26</v>
+      </c>
+      <c r="AM186">
+        <v>1.93</v>
+      </c>
+      <c r="AN186">
+        <v>2.11</v>
+      </c>
+      <c r="AO186">
+        <v>0.7</v>
+      </c>
+      <c r="AP186">
+        <v>2.2</v>
+      </c>
+      <c r="AQ186">
+        <v>0.64</v>
+      </c>
+      <c r="AR186">
+        <v>1.5</v>
+      </c>
+      <c r="AS186">
+        <v>1.22</v>
+      </c>
+      <c r="AT186">
+        <v>2.72</v>
+      </c>
+      <c r="AU186">
+        <v>4</v>
+      </c>
+      <c r="AV186">
+        <v>6</v>
+      </c>
+      <c r="AW186">
+        <v>6</v>
+      </c>
+      <c r="AX186">
+        <v>6</v>
+      </c>
+      <c r="AY186">
+        <v>10</v>
+      </c>
+      <c r="AZ186">
+        <v>15</v>
+      </c>
+      <c r="BA186">
+        <v>6</v>
+      </c>
+      <c r="BB186">
+        <v>3</v>
+      </c>
+      <c r="BC186">
+        <v>9</v>
+      </c>
+      <c r="BD186">
+        <v>1.49</v>
+      </c>
+      <c r="BE186">
+        <v>9</v>
+      </c>
+      <c r="BF186">
+        <v>3.28</v>
+      </c>
+      <c r="BG186">
+        <v>1.27</v>
+      </c>
+      <c r="BH186">
+        <v>3.14</v>
+      </c>
+      <c r="BI186">
+        <v>1.52</v>
+      </c>
+      <c r="BJ186">
+        <v>2.3</v>
+      </c>
+      <c r="BK186">
+        <v>1.92</v>
+      </c>
+      <c r="BL186">
+        <v>1.79</v>
+      </c>
+      <c r="BM186">
+        <v>2.48</v>
+      </c>
+      <c r="BN186">
+        <v>1.45</v>
+      </c>
+      <c r="BO186">
+        <v>3.34</v>
+      </c>
+      <c r="BP186">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7492000</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F187">
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>75</v>
+      </c>
+      <c r="H187" t="s">
+        <v>74</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187" t="s">
+        <v>96</v>
+      </c>
+      <c r="P187" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q187">
+        <v>2.4</v>
+      </c>
+      <c r="R187">
+        <v>2.2</v>
+      </c>
+      <c r="S187">
+        <v>4.75</v>
+      </c>
+      <c r="T187">
+        <v>1.4</v>
+      </c>
+      <c r="U187">
+        <v>2.75</v>
+      </c>
+      <c r="V187">
+        <v>2.75</v>
+      </c>
+      <c r="W187">
+        <v>1.4</v>
+      </c>
+      <c r="X187">
+        <v>8</v>
+      </c>
+      <c r="Y187">
+        <v>1.08</v>
+      </c>
+      <c r="Z187">
+        <v>1.83</v>
+      </c>
+      <c r="AA187">
+        <v>3.72</v>
+      </c>
+      <c r="AB187">
+        <v>4.5</v>
+      </c>
+      <c r="AC187">
+        <v>1.05</v>
+      </c>
+      <c r="AD187">
+        <v>11</v>
+      </c>
+      <c r="AE187">
+        <v>1.3</v>
+      </c>
+      <c r="AF187">
+        <v>3.6</v>
+      </c>
+      <c r="AG187">
+        <v>1.87</v>
+      </c>
+      <c r="AH187">
+        <v>1.83</v>
+      </c>
+      <c r="AI187">
+        <v>1.8</v>
+      </c>
+      <c r="AJ187">
+        <v>1.95</v>
+      </c>
+      <c r="AK187">
+        <v>1.22</v>
+      </c>
+      <c r="AL187">
+        <v>1.28</v>
+      </c>
+      <c r="AM187">
+        <v>1.93</v>
+      </c>
+      <c r="AN187">
+        <v>1.7</v>
+      </c>
+      <c r="AO187">
+        <v>0.9</v>
+      </c>
+      <c r="AP187">
+        <v>1.64</v>
+      </c>
+      <c r="AQ187">
+        <v>0.91</v>
+      </c>
+      <c r="AR187">
+        <v>1.47</v>
+      </c>
+      <c r="AS187">
+        <v>0.99</v>
+      </c>
+      <c r="AT187">
+        <v>2.46</v>
+      </c>
+      <c r="AU187">
+        <v>5</v>
+      </c>
+      <c r="AV187">
+        <v>3</v>
+      </c>
+      <c r="AW187">
+        <v>4</v>
+      </c>
+      <c r="AX187">
+        <v>6</v>
+      </c>
+      <c r="AY187">
+        <v>10</v>
+      </c>
+      <c r="AZ187">
+        <v>10</v>
+      </c>
+      <c r="BA187">
+        <v>1</v>
+      </c>
+      <c r="BB187">
+        <v>3</v>
+      </c>
+      <c r="BC187">
+        <v>4</v>
+      </c>
+      <c r="BD187">
+        <v>1.44</v>
+      </c>
+      <c r="BE187">
+        <v>9.6</v>
+      </c>
+      <c r="BF187">
+        <v>3.44</v>
+      </c>
+      <c r="BG187">
+        <v>1.18</v>
+      </c>
+      <c r="BH187">
+        <v>3.84</v>
+      </c>
+      <c r="BI187">
+        <v>1.38</v>
+      </c>
+      <c r="BJ187">
+        <v>2.71</v>
+      </c>
+      <c r="BK187">
+        <v>1.69</v>
+      </c>
+      <c r="BL187">
+        <v>2.04</v>
+      </c>
+      <c r="BM187">
+        <v>2.11</v>
+      </c>
+      <c r="BN187">
+        <v>1.62</v>
+      </c>
+      <c r="BO187">
+        <v>2.74</v>
+      </c>
+      <c r="BP187">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7492001</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45696.60416666666</v>
+      </c>
+      <c r="F188">
+        <v>21</v>
+      </c>
+      <c r="G188" t="s">
+        <v>70</v>
+      </c>
+      <c r="H188" t="s">
+        <v>82</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188">
+        <v>1</v>
+      </c>
+      <c r="K188">
+        <v>2</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>1</v>
+      </c>
+      <c r="N188">
+        <v>2</v>
+      </c>
+      <c r="O188" t="s">
+        <v>222</v>
+      </c>
+      <c r="P188" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q188">
+        <v>3</v>
+      </c>
+      <c r="R188">
+        <v>2.4</v>
+      </c>
+      <c r="S188">
+        <v>3</v>
+      </c>
+      <c r="T188">
+        <v>1.29</v>
+      </c>
+      <c r="U188">
+        <v>3.5</v>
+      </c>
+      <c r="V188">
+        <v>2.25</v>
+      </c>
+      <c r="W188">
+        <v>1.57</v>
+      </c>
+      <c r="X188">
+        <v>5.5</v>
+      </c>
+      <c r="Y188">
+        <v>1.14</v>
+      </c>
+      <c r="Z188">
+        <v>2.83</v>
+      </c>
+      <c r="AA188">
+        <v>3.69</v>
+      </c>
+      <c r="AB188">
+        <v>2.43</v>
+      </c>
+      <c r="AC188">
+        <v>1.02</v>
+      </c>
+      <c r="AD188">
+        <v>17</v>
+      </c>
+      <c r="AE188">
+        <v>1.18</v>
+      </c>
+      <c r="AF188">
+        <v>5</v>
+      </c>
+      <c r="AG188">
+        <v>1.53</v>
+      </c>
+      <c r="AH188">
+        <v>2.45</v>
+      </c>
+      <c r="AI188">
+        <v>1.44</v>
+      </c>
+      <c r="AJ188">
+        <v>2.63</v>
+      </c>
+      <c r="AK188">
+        <v>1.57</v>
+      </c>
+      <c r="AL188">
+        <v>1.27</v>
+      </c>
+      <c r="AM188">
+        <v>1.43</v>
+      </c>
+      <c r="AN188">
+        <v>1.9</v>
+      </c>
+      <c r="AO188">
+        <v>1.7</v>
+      </c>
+      <c r="AP188">
+        <v>1.82</v>
+      </c>
+      <c r="AQ188">
+        <v>1.64</v>
+      </c>
+      <c r="AR188">
+        <v>1.5</v>
+      </c>
+      <c r="AS188">
+        <v>1.44</v>
+      </c>
+      <c r="AT188">
+        <v>2.94</v>
+      </c>
+      <c r="AU188">
+        <v>4</v>
+      </c>
+      <c r="AV188">
+        <v>8</v>
+      </c>
+      <c r="AW188">
+        <v>5</v>
+      </c>
+      <c r="AX188">
+        <v>8</v>
+      </c>
+      <c r="AY188">
+        <v>10</v>
+      </c>
+      <c r="AZ188">
+        <v>17</v>
+      </c>
+      <c r="BA188">
+        <v>6</v>
+      </c>
+      <c r="BB188">
+        <v>1</v>
+      </c>
+      <c r="BC188">
+        <v>7</v>
+      </c>
+      <c r="BD188">
+        <v>2.02</v>
+      </c>
+      <c r="BE188">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF188">
+        <v>2.09</v>
+      </c>
+      <c r="BG188">
+        <v>1.15</v>
+      </c>
+      <c r="BH188">
+        <v>4.2</v>
+      </c>
+      <c r="BI188">
+        <v>1.32</v>
+      </c>
+      <c r="BJ188">
+        <v>2.88</v>
+      </c>
+      <c r="BK188">
+        <v>1.59</v>
+      </c>
+      <c r="BL188">
+        <v>2.16</v>
+      </c>
+      <c r="BM188">
+        <v>2</v>
+      </c>
+      <c r="BN188">
+        <v>1.72</v>
+      </c>
+      <c r="BO188">
+        <v>2.57</v>
+      </c>
+      <c r="BP188">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="333">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,9 @@
     <t>['26']</t>
   </si>
   <si>
+    <t>['3', '50']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1007,6 +1010,9 @@
   </si>
   <si>
     <t>['24', '61', '73', '87']</t>
+  </si>
+  <si>
+    <t>['37', '39']</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP188"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1624,7 +1630,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1908,10 +1914,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ3">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2036,7 +2042,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2242,7 +2248,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2448,7 +2454,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2654,7 +2660,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3066,7 +3072,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3272,7 +3278,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3559,7 +3565,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ11">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3684,7 +3690,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3890,7 +3896,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3968,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ13">
         <v>1.7</v>
@@ -4096,7 +4102,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4302,7 +4308,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4714,7 +4720,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5332,7 +5338,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5616,7 +5622,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ21">
         <v>0.73</v>
@@ -5744,7 +5750,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6031,7 +6037,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ23">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR23">
         <v>1.5</v>
@@ -6156,7 +6162,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6362,7 +6368,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6568,7 +6574,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6646,7 +6652,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ26">
         <v>2.3</v>
@@ -6774,7 +6780,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6855,7 +6861,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ27">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR27">
         <v>1.22</v>
@@ -6980,7 +6986,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7186,7 +7192,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7392,7 +7398,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7598,7 +7604,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7804,7 +7810,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8010,7 +8016,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8422,7 +8428,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9040,7 +9046,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9121,7 +9127,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ38">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR38">
         <v>1.73</v>
@@ -9452,7 +9458,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9658,7 +9664,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9864,7 +9870,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -9945,7 +9951,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ42">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR42">
         <v>1.82</v>
@@ -10148,7 +10154,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ43">
         <v>0.91</v>
@@ -10276,7 +10282,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10482,7 +10488,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10560,7 +10566,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ45">
         <v>1.64</v>
@@ -10688,7 +10694,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11100,7 +11106,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11512,7 +11518,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11718,7 +11724,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11924,7 +11930,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12336,7 +12342,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12542,7 +12548,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12748,7 +12754,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12829,7 +12835,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ56">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR56">
         <v>1.91</v>
@@ -12954,7 +12960,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13241,7 +13247,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13366,7 +13372,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13572,7 +13578,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13778,7 +13784,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14190,7 +14196,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14268,7 +14274,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ63">
         <v>0.73</v>
@@ -14396,7 +14402,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14602,7 +14608,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14808,7 +14814,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15220,7 +15226,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15298,7 +15304,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15632,7 +15638,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15838,7 +15844,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16868,7 +16874,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16949,7 +16955,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ76">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17074,7 +17080,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17155,7 +17161,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR77">
         <v>1.67</v>
@@ -17358,7 +17364,7 @@
         <v>1.5</v>
       </c>
       <c r="AP78">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ78">
         <v>0.64</v>
@@ -18516,7 +18522,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18928,7 +18934,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19134,7 +19140,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19418,7 +19424,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ88">
         <v>1.1</v>
@@ -19752,7 +19758,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19958,7 +19964,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20370,7 +20376,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20657,7 +20663,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ94">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR94">
         <v>2.18</v>
@@ -20988,7 +20994,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21606,7 +21612,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21684,7 +21690,7 @@
         <v>2</v>
       </c>
       <c r="AP99">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ99">
         <v>1.4</v>
@@ -21893,7 +21899,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ100">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -22018,7 +22024,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22224,7 +22230,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22430,7 +22436,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22717,7 +22723,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ104">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR104">
         <v>1.72</v>
@@ -22842,7 +22848,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22920,7 +22926,7 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ105">
         <v>1.7</v>
@@ -23048,7 +23054,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23254,7 +23260,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23666,7 +23672,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23872,7 +23878,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24078,7 +24084,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24156,7 +24162,7 @@
         <v>1.67</v>
       </c>
       <c r="AP111">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ111">
         <v>1.36</v>
@@ -24284,7 +24290,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24490,7 +24496,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24696,7 +24702,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24983,7 +24989,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ115">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR115">
         <v>2.31</v>
@@ -25108,7 +25114,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25314,7 +25320,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25726,7 +25732,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25932,7 +25938,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26013,7 +26019,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ120">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR120">
         <v>1.27</v>
@@ -26138,7 +26144,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26344,7 +26350,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26756,7 +26762,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26962,7 +26968,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27168,7 +27174,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27374,7 +27380,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27452,7 +27458,7 @@
         <v>1.86</v>
       </c>
       <c r="AP127">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ127">
         <v>1.64</v>
@@ -27580,7 +27586,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27786,7 +27792,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27864,7 +27870,7 @@
         <v>0.33</v>
       </c>
       <c r="AP129">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ129">
         <v>0.91</v>
@@ -27992,7 +27998,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28073,7 +28079,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ130">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR130">
         <v>1.98</v>
@@ -28198,7 +28204,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28404,7 +28410,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28610,7 +28616,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -29228,7 +29234,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29434,7 +29440,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -30052,7 +30058,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30339,7 +30345,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ141">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR141">
         <v>1.48</v>
@@ -30464,7 +30470,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30876,7 +30882,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -30954,7 +30960,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ144">
         <v>1.55</v>
@@ -31082,7 +31088,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31288,7 +31294,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31366,7 +31372,7 @@
         <v>0.71</v>
       </c>
       <c r="AP146">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ146">
         <v>0.8</v>
@@ -32193,7 +32199,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ150">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR150">
         <v>1.25</v>
@@ -32318,7 +32324,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32730,7 +32736,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32936,7 +32942,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33348,7 +33354,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33426,7 +33432,7 @@
         <v>0.5</v>
       </c>
       <c r="AP156">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ156">
         <v>0.7</v>
@@ -33554,7 +33560,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33760,7 +33766,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -33841,7 +33847,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ158">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR158">
         <v>1.38</v>
@@ -34172,7 +34178,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34378,7 +34384,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34584,7 +34590,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34790,7 +34796,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34996,7 +35002,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35614,7 +35620,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35820,7 +35826,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36026,7 +36032,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36104,7 +36110,7 @@
         <v>2.25</v>
       </c>
       <c r="AP169">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ169">
         <v>2</v>
@@ -36313,7 +36319,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ170">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AR170">
         <v>1.47</v>
@@ -36438,7 +36444,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -37056,7 +37062,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37262,7 +37268,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37468,7 +37474,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37880,7 +37886,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38292,7 +38298,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38498,7 +38504,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -39116,7 +39122,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39322,7 +39328,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39940,7 +39946,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40097,6 +40103,418 @@
       </c>
       <c r="BP188">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7492002</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45697.47916666666</v>
+      </c>
+      <c r="F189">
+        <v>21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>81</v>
+      </c>
+      <c r="H189" t="s">
+        <v>83</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>2</v>
+      </c>
+      <c r="K189">
+        <v>3</v>
+      </c>
+      <c r="L189">
+        <v>2</v>
+      </c>
+      <c r="M189">
+        <v>2</v>
+      </c>
+      <c r="N189">
+        <v>4</v>
+      </c>
+      <c r="O189" t="s">
+        <v>223</v>
+      </c>
+      <c r="P189" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q189">
+        <v>2.88</v>
+      </c>
+      <c r="R189">
+        <v>2.3</v>
+      </c>
+      <c r="S189">
+        <v>3.4</v>
+      </c>
+      <c r="T189">
+        <v>1.33</v>
+      </c>
+      <c r="U189">
+        <v>3.25</v>
+      </c>
+      <c r="V189">
+        <v>2.5</v>
+      </c>
+      <c r="W189">
+        <v>1.5</v>
+      </c>
+      <c r="X189">
+        <v>6.5</v>
+      </c>
+      <c r="Y189">
+        <v>1.11</v>
+      </c>
+      <c r="Z189">
+        <v>2.36</v>
+      </c>
+      <c r="AA189">
+        <v>3.6</v>
+      </c>
+      <c r="AB189">
+        <v>3.01</v>
+      </c>
+      <c r="AC189">
+        <v>1.04</v>
+      </c>
+      <c r="AD189">
+        <v>13</v>
+      </c>
+      <c r="AE189">
+        <v>1.22</v>
+      </c>
+      <c r="AF189">
+        <v>4.33</v>
+      </c>
+      <c r="AG189">
+        <v>1.7</v>
+      </c>
+      <c r="AH189">
+        <v>2.05</v>
+      </c>
+      <c r="AI189">
+        <v>1.57</v>
+      </c>
+      <c r="AJ189">
+        <v>2.25</v>
+      </c>
+      <c r="AK189">
+        <v>1.39</v>
+      </c>
+      <c r="AL189">
+        <v>1.29</v>
+      </c>
+      <c r="AM189">
+        <v>1.58</v>
+      </c>
+      <c r="AN189">
+        <v>0.9</v>
+      </c>
+      <c r="AO189">
+        <v>0.1</v>
+      </c>
+      <c r="AP189">
+        <v>0.91</v>
+      </c>
+      <c r="AQ189">
+        <v>0.18</v>
+      </c>
+      <c r="AR189">
+        <v>1.24</v>
+      </c>
+      <c r="AS189">
+        <v>1.15</v>
+      </c>
+      <c r="AT189">
+        <v>2.39</v>
+      </c>
+      <c r="AU189">
+        <v>4</v>
+      </c>
+      <c r="AV189">
+        <v>6</v>
+      </c>
+      <c r="AW189">
+        <v>7</v>
+      </c>
+      <c r="AX189">
+        <v>15</v>
+      </c>
+      <c r="AY189">
+        <v>12</v>
+      </c>
+      <c r="AZ189">
+        <v>24</v>
+      </c>
+      <c r="BA189">
+        <v>3</v>
+      </c>
+      <c r="BB189">
+        <v>5</v>
+      </c>
+      <c r="BC189">
+        <v>8</v>
+      </c>
+      <c r="BD189">
+        <v>2.06</v>
+      </c>
+      <c r="BE189">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF189">
+        <v>2.05</v>
+      </c>
+      <c r="BG189">
+        <v>1.16</v>
+      </c>
+      <c r="BH189">
+        <v>4.15</v>
+      </c>
+      <c r="BI189">
+        <v>1.33</v>
+      </c>
+      <c r="BJ189">
+        <v>2.83</v>
+      </c>
+      <c r="BK189">
+        <v>1.7</v>
+      </c>
+      <c r="BL189">
+        <v>2.05</v>
+      </c>
+      <c r="BM189">
+        <v>2.03</v>
+      </c>
+      <c r="BN189">
+        <v>1.7</v>
+      </c>
+      <c r="BO189">
+        <v>2.64</v>
+      </c>
+      <c r="BP189">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7491995</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45697.5625</v>
+      </c>
+      <c r="F190">
+        <v>21</v>
+      </c>
+      <c r="G190" t="s">
+        <v>71</v>
+      </c>
+      <c r="H190" t="s">
+        <v>78</v>
+      </c>
+      <c r="I190">
+        <v>2</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>2</v>
+      </c>
+      <c r="L190">
+        <v>2</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>2</v>
+      </c>
+      <c r="O190" t="s">
+        <v>92</v>
+      </c>
+      <c r="P190" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q190">
+        <v>2.2</v>
+      </c>
+      <c r="R190">
+        <v>2.3</v>
+      </c>
+      <c r="S190">
+        <v>5.5</v>
+      </c>
+      <c r="T190">
+        <v>1.33</v>
+      </c>
+      <c r="U190">
+        <v>3.25</v>
+      </c>
+      <c r="V190">
+        <v>2.63</v>
+      </c>
+      <c r="W190">
+        <v>1.44</v>
+      </c>
+      <c r="X190">
+        <v>6.5</v>
+      </c>
+      <c r="Y190">
+        <v>1.11</v>
+      </c>
+      <c r="Z190">
+        <v>1.57</v>
+      </c>
+      <c r="AA190">
+        <v>4.5</v>
+      </c>
+      <c r="AB190">
+        <v>5.7</v>
+      </c>
+      <c r="AC190">
+        <v>1.03</v>
+      </c>
+      <c r="AD190">
+        <v>15</v>
+      </c>
+      <c r="AE190">
+        <v>1.24</v>
+      </c>
+      <c r="AF190">
+        <v>4.2</v>
+      </c>
+      <c r="AG190">
+        <v>1.68</v>
+      </c>
+      <c r="AH190">
+        <v>2.11</v>
+      </c>
+      <c r="AI190">
+        <v>1.75</v>
+      </c>
+      <c r="AJ190">
+        <v>2</v>
+      </c>
+      <c r="AK190">
+        <v>1.16</v>
+      </c>
+      <c r="AL190">
+        <v>1.21</v>
+      </c>
+      <c r="AM190">
+        <v>2.35</v>
+      </c>
+      <c r="AN190">
+        <v>2</v>
+      </c>
+      <c r="AO190">
+        <v>1.2</v>
+      </c>
+      <c r="AP190">
+        <v>2.1</v>
+      </c>
+      <c r="AQ190">
+        <v>1.09</v>
+      </c>
+      <c r="AR190">
+        <v>1.45</v>
+      </c>
+      <c r="AS190">
+        <v>1.15</v>
+      </c>
+      <c r="AT190">
+        <v>2.6</v>
+      </c>
+      <c r="AU190">
+        <v>7</v>
+      </c>
+      <c r="AV190">
+        <v>5</v>
+      </c>
+      <c r="AW190">
+        <v>5</v>
+      </c>
+      <c r="AX190">
+        <v>3</v>
+      </c>
+      <c r="AY190">
+        <v>12</v>
+      </c>
+      <c r="AZ190">
+        <v>8</v>
+      </c>
+      <c r="BA190">
+        <v>5</v>
+      </c>
+      <c r="BB190">
+        <v>4</v>
+      </c>
+      <c r="BC190">
+        <v>9</v>
+      </c>
+      <c r="BD190">
+        <v>1.46</v>
+      </c>
+      <c r="BE190">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF190">
+        <v>3.4</v>
+      </c>
+      <c r="BG190">
+        <v>1.26</v>
+      </c>
+      <c r="BH190">
+        <v>3.22</v>
+      </c>
+      <c r="BI190">
+        <v>1.5</v>
+      </c>
+      <c r="BJ190">
+        <v>2.35</v>
+      </c>
+      <c r="BK190">
+        <v>1.8</v>
+      </c>
+      <c r="BL190">
+        <v>1.91</v>
+      </c>
+      <c r="BM190">
+        <v>2.42</v>
+      </c>
+      <c r="BN190">
+        <v>1.47</v>
+      </c>
+      <c r="BO190">
+        <v>3.2</v>
+      </c>
+      <c r="BP190">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="333">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1374,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ6">
         <v>1.55</v>
@@ -4801,7 +4801,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -6858,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ27">
         <v>1.09</v>
@@ -7270,7 +7270,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ29">
         <v>1.4</v>
@@ -8921,7 +8921,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ37">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
         <v>1.27</v>
@@ -10978,7 +10978,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ47">
         <v>1.1</v>
@@ -12217,7 +12217,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ53">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -13659,7 +13659,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ60">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR60">
         <v>1.26</v>
@@ -14892,7 +14892,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ66">
         <v>0.8</v>
@@ -17779,7 +17779,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ80">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR80">
         <v>1.88</v>
@@ -19630,7 +19630,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ89">
         <v>0.7</v>
@@ -21075,7 +21075,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -22720,7 +22720,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ104">
         <v>0.18</v>
@@ -24165,7 +24165,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ111">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR111">
         <v>1.13</v>
@@ -26428,7 +26428,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ122">
         <v>2</v>
@@ -27667,7 +27667,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ128">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR128">
         <v>2.15</v>
@@ -31166,7 +31166,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ145">
         <v>1.5</v>
@@ -32405,7 +32405,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ151">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR151">
         <v>1.96</v>
@@ -33641,7 +33641,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ157">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR157">
         <v>1.22</v>
@@ -35492,7 +35492,7 @@
         <v>0.78</v>
       </c>
       <c r="AP166">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ166">
         <v>0.64</v>
@@ -38173,7 +38173,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ179">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR179">
         <v>1.41</v>
@@ -40515,6 +40515,212 @@
       </c>
       <c r="BP190">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7492008</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45702.6875</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>74</v>
+      </c>
+      <c r="H191" t="s">
+        <v>71</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>0</v>
+      </c>
+      <c r="O191" t="s">
+        <v>96</v>
+      </c>
+      <c r="P191" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q191">
+        <v>3.75</v>
+      </c>
+      <c r="R191">
+        <v>2.25</v>
+      </c>
+      <c r="S191">
+        <v>2.75</v>
+      </c>
+      <c r="T191">
+        <v>1.36</v>
+      </c>
+      <c r="U191">
+        <v>3</v>
+      </c>
+      <c r="V191">
+        <v>2.63</v>
+      </c>
+      <c r="W191">
+        <v>1.44</v>
+      </c>
+      <c r="X191">
+        <v>7</v>
+      </c>
+      <c r="Y191">
+        <v>1.1</v>
+      </c>
+      <c r="Z191">
+        <v>3.37</v>
+      </c>
+      <c r="AA191">
+        <v>3.64</v>
+      </c>
+      <c r="AB191">
+        <v>2.16</v>
+      </c>
+      <c r="AC191">
+        <v>1.04</v>
+      </c>
+      <c r="AD191">
+        <v>13</v>
+      </c>
+      <c r="AE191">
+        <v>1.25</v>
+      </c>
+      <c r="AF191">
+        <v>4</v>
+      </c>
+      <c r="AG191">
+        <v>1.81</v>
+      </c>
+      <c r="AH191">
+        <v>2.01</v>
+      </c>
+      <c r="AI191">
+        <v>1.67</v>
+      </c>
+      <c r="AJ191">
+        <v>2.1</v>
+      </c>
+      <c r="AK191">
+        <v>1.68</v>
+      </c>
+      <c r="AL191">
+        <v>1.28</v>
+      </c>
+      <c r="AM191">
+        <v>1.33</v>
+      </c>
+      <c r="AN191">
+        <v>1.7</v>
+      </c>
+      <c r="AO191">
+        <v>1.36</v>
+      </c>
+      <c r="AP191">
+        <v>1.64</v>
+      </c>
+      <c r="AQ191">
+        <v>1.33</v>
+      </c>
+      <c r="AR191">
+        <v>1.56</v>
+      </c>
+      <c r="AS191">
+        <v>1.1</v>
+      </c>
+      <c r="AT191">
+        <v>2.66</v>
+      </c>
+      <c r="AU191">
+        <v>3</v>
+      </c>
+      <c r="AV191">
+        <v>5</v>
+      </c>
+      <c r="AW191">
+        <v>9</v>
+      </c>
+      <c r="AX191">
+        <v>10</v>
+      </c>
+      <c r="AY191">
+        <v>15</v>
+      </c>
+      <c r="AZ191">
+        <v>19</v>
+      </c>
+      <c r="BA191">
+        <v>8</v>
+      </c>
+      <c r="BB191">
+        <v>9</v>
+      </c>
+      <c r="BC191">
+        <v>17</v>
+      </c>
+      <c r="BD191">
+        <v>1.98</v>
+      </c>
+      <c r="BE191">
+        <v>6.4</v>
+      </c>
+      <c r="BF191">
+        <v>1.98</v>
+      </c>
+      <c r="BG191">
+        <v>1.28</v>
+      </c>
+      <c r="BH191">
+        <v>3.2</v>
+      </c>
+      <c r="BI191">
+        <v>1.49</v>
+      </c>
+      <c r="BJ191">
+        <v>2.4</v>
+      </c>
+      <c r="BK191">
+        <v>1.8</v>
+      </c>
+      <c r="BL191">
+        <v>1.88</v>
+      </c>
+      <c r="BM191">
+        <v>2.28</v>
+      </c>
+      <c r="BN191">
+        <v>1.55</v>
+      </c>
+      <c r="BO191">
+        <v>2.9</v>
+      </c>
+      <c r="BP191">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -688,6 +688,12 @@
     <t>['3', '50']</t>
   </si>
   <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['33', '35']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1013,6 +1019,15 @@
   </si>
   <si>
     <t>['37', '39']</t>
+  </si>
+  <si>
+    <t>['77', '87']</t>
+  </si>
+  <si>
+    <t>['10', '26']</t>
+  </si>
+  <si>
+    <t>['88']</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1630,7 +1645,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2042,7 +2057,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2248,7 +2263,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2454,7 +2469,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2660,7 +2675,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3072,7 +3087,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3153,7 +3168,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ9">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3278,7 +3293,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3356,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ10">
         <v>0.64</v>
@@ -3562,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ11">
         <v>1.09</v>
@@ -3690,7 +3705,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3768,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12">
         <v>1.4</v>
@@ -3896,7 +3911,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3977,7 +3992,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ13">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4102,7 +4117,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4308,7 +4323,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4386,10 +4401,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ15">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4595,7 +4610,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ16">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4720,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4798,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ17">
         <v>1.33</v>
@@ -5213,7 +5228,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5338,7 +5353,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5750,7 +5765,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6162,7 +6177,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6368,7 +6383,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6574,7 +6589,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6655,7 +6670,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ26">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR26">
         <v>1.4</v>
@@ -6780,7 +6795,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6986,7 +7001,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7192,7 +7207,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7398,7 +7413,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7479,7 +7494,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7604,7 +7619,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7685,7 +7700,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ31">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR31">
         <v>0.65</v>
@@ -7810,7 +7825,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7888,7 +7903,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ32">
         <v>0.7</v>
@@ -8016,7 +8031,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8094,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ33">
         <v>0.3</v>
@@ -8303,7 +8318,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ34">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR34">
         <v>1.86</v>
@@ -8428,7 +8443,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8506,10 +8521,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ35">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR35">
         <v>2.58</v>
@@ -8712,10 +8727,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR36">
         <v>2.62</v>
@@ -8918,7 +8933,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -9046,7 +9061,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9458,7 +9473,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9664,7 +9679,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9870,7 +9885,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10282,7 +10297,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10488,7 +10503,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10694,7 +10709,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10981,7 +10996,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ47">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR47">
         <v>2.02</v>
@@ -11106,7 +11121,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11184,7 +11199,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ48">
         <v>0.3</v>
@@ -11393,7 +11408,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR49">
         <v>0.41</v>
@@ -11518,7 +11533,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11596,10 +11611,10 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ50">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11724,7 +11739,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11802,10 +11817,10 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ51">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR51">
         <v>1.37</v>
@@ -11930,7 +11945,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12008,7 +12023,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ52">
         <v>1.4</v>
@@ -12342,7 +12357,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12423,7 +12438,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ54">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR54">
         <v>1.7</v>
@@ -12548,7 +12563,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12626,7 +12641,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ55">
         <v>0.7</v>
@@ -12754,7 +12769,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12960,7 +12975,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13038,7 +13053,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ57">
         <v>1.64</v>
@@ -13372,7 +13387,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13578,7 +13593,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13784,7 +13799,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14196,7 +14211,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14402,7 +14417,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14608,7 +14623,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14689,7 +14704,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR65">
         <v>1.22</v>
@@ -14814,7 +14829,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14895,7 +14910,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ66">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15098,10 +15113,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ67">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR67">
         <v>1.52</v>
@@ -15226,7 +15241,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15307,7 +15322,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15510,7 +15525,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ69">
         <v>0.3</v>
@@ -15638,7 +15653,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15844,7 +15859,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15922,10 +15937,10 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ71">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR71">
         <v>1.42</v>
@@ -16128,7 +16143,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ72">
         <v>1.64</v>
@@ -16540,7 +16555,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ74">
         <v>1.5</v>
@@ -16874,7 +16889,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17080,7 +17095,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18394,10 +18409,10 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR83">
         <v>1.3</v>
@@ -18522,7 +18537,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18600,10 +18615,10 @@
         <v>2.6</v>
       </c>
       <c r="AP84">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ84">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -18934,7 +18949,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19015,7 +19030,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ86">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR86">
         <v>1.34</v>
@@ -19140,7 +19155,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19218,7 +19233,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ87">
         <v>2</v>
@@ -19427,7 +19442,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ88">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR88">
         <v>1.44</v>
@@ -19758,7 +19773,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19836,7 +19851,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ90">
         <v>1.64</v>
@@ -19964,7 +19979,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20045,7 +20060,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ91">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20376,7 +20391,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20454,7 +20469,7 @@
         <v>1.2</v>
       </c>
       <c r="AP93">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ93">
         <v>0.64</v>
@@ -20660,7 +20675,7 @@
         <v>0</v>
       </c>
       <c r="AP94">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ94">
         <v>0.18</v>
@@ -20869,7 +20884,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR95">
         <v>1.86</v>
@@ -20994,7 +21009,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21612,7 +21627,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22024,7 +22039,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22102,7 +22117,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ101">
         <v>0.3</v>
@@ -22230,7 +22245,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22308,7 +22323,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ102">
         <v>2</v>
@@ -22436,7 +22451,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22517,7 +22532,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ103">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -22848,7 +22863,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22929,7 +22944,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ105">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR105">
         <v>1.47</v>
@@ -23054,7 +23069,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23260,7 +23275,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23341,7 +23356,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ107">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR107">
         <v>1.93</v>
@@ -23672,7 +23687,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23878,7 +23893,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23956,7 +23971,7 @@
         <v>0.83</v>
       </c>
       <c r="AP110">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ110">
         <v>0.73</v>
@@ -24084,7 +24099,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24290,7 +24305,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24368,7 +24383,7 @@
         <v>1.67</v>
       </c>
       <c r="AP112">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ112">
         <v>1.55</v>
@@ -24496,7 +24511,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24702,7 +24717,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24986,7 +25001,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ115">
         <v>1.09</v>
@@ -25114,7 +25129,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25195,7 +25210,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ116">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR116">
         <v>1.64</v>
@@ -25320,7 +25335,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25607,7 +25622,7 @@
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR118">
         <v>1.77</v>
@@ -25732,7 +25747,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25813,7 +25828,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ119">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR119">
         <v>1.52</v>
@@ -25938,7 +25953,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26016,7 +26031,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ120">
         <v>0.18</v>
@@ -26144,7 +26159,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26225,7 +26240,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ121">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR121">
         <v>1.51</v>
@@ -26350,7 +26365,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26762,7 +26777,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26840,7 +26855,7 @@
         <v>1.86</v>
       </c>
       <c r="AP124">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ124">
         <v>1.55</v>
@@ -26968,7 +26983,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27174,7 +27189,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27380,7 +27395,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27586,7 +27601,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27792,7 +27807,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27998,7 +28013,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28076,7 +28091,7 @@
         <v>0.86</v>
       </c>
       <c r="AP130">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ130">
         <v>1.09</v>
@@ -28204,7 +28219,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28410,7 +28425,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28491,7 +28506,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR132">
         <v>1.76</v>
@@ -28616,7 +28631,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28900,10 +28915,10 @@
         <v>1.14</v>
       </c>
       <c r="AP134">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR134">
         <v>2.13</v>
@@ -29106,7 +29121,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ135">
         <v>0.64</v>
@@ -29234,7 +29249,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29315,7 +29330,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ136">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR136">
         <v>1.28</v>
@@ -29440,7 +29455,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29727,7 +29742,7 @@
         <v>1</v>
       </c>
       <c r="AQ138">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR138">
         <v>1.83</v>
@@ -30058,7 +30073,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30470,7 +30485,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30548,7 +30563,7 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ142">
         <v>1.64</v>
@@ -30757,7 +30772,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ143">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR143">
         <v>1.59</v>
@@ -30882,7 +30897,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31088,7 +31103,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31294,7 +31309,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31375,7 +31390,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ146">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR146">
         <v>1.19</v>
@@ -31581,7 +31596,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR147">
         <v>1.77</v>
@@ -31787,7 +31802,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ148">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR148">
         <v>1.3</v>
@@ -31990,7 +32005,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ149">
         <v>1.4</v>
@@ -32196,7 +32211,7 @@
         <v>1.13</v>
       </c>
       <c r="AP150">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ150">
         <v>1.09</v>
@@ -32324,7 +32339,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32402,7 +32417,7 @@
         <v>1.63</v>
       </c>
       <c r="AP151">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ151">
         <v>1.33</v>
@@ -32736,7 +32751,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32942,7 +32957,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33020,7 +33035,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ154">
         <v>0.91</v>
@@ -33229,7 +33244,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ155">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR155">
         <v>1.87</v>
@@ -33354,7 +33369,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33560,7 +33575,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33638,7 +33653,7 @@
         <v>1.44</v>
       </c>
       <c r="AP157">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ157">
         <v>1.33</v>
@@ -33766,7 +33781,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34050,10 +34065,10 @@
         <v>0.89</v>
       </c>
       <c r="AP159">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ159">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR159">
         <v>1.95</v>
@@ -34178,7 +34193,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34259,7 +34274,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ160">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR160">
         <v>2.29</v>
@@ -34384,7 +34399,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34462,10 +34477,10 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ161">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR161">
         <v>2.2</v>
@@ -34590,7 +34605,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34668,7 +34683,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ162">
         <v>1.4</v>
@@ -34796,7 +34811,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -35002,7 +35017,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35620,7 +35635,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35701,7 +35716,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ167">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR167">
         <v>1.56</v>
@@ -35826,7 +35841,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36032,7 +36047,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36444,7 +36459,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36728,7 +36743,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP172">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ172">
         <v>0.73</v>
@@ -37062,7 +37077,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37140,10 +37155,10 @@
         <v>0.89</v>
       </c>
       <c r="AP174">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ174">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR174">
         <v>1.91</v>
@@ -37268,7 +37283,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37474,7 +37489,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37555,7 +37570,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ176">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR176">
         <v>1.36</v>
@@ -37758,10 +37773,10 @@
         <v>0.8</v>
       </c>
       <c r="AP177">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ177">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR177">
         <v>1.23</v>
@@ -37886,7 +37901,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -37964,7 +37979,7 @@
         <v>0.89</v>
       </c>
       <c r="AP178">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ178">
         <v>0.91</v>
@@ -38170,7 +38185,7 @@
         <v>1.4</v>
       </c>
       <c r="AP179">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ179">
         <v>1.33</v>
@@ -38298,7 +38313,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38379,7 +38394,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ180">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR180">
         <v>1.83</v>
@@ -38504,7 +38519,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38582,7 +38597,7 @@
         <v>0.78</v>
       </c>
       <c r="AP181">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ181">
         <v>0.7</v>
@@ -39122,7 +39137,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39328,7 +39343,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39946,7 +39961,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40152,7 +40167,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40721,6 +40736,1036 @@
       </c>
       <c r="BP191">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7492004</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45703.47916666666</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>80</v>
+      </c>
+      <c r="H192" t="s">
+        <v>77</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>2</v>
+      </c>
+      <c r="N192">
+        <v>3</v>
+      </c>
+      <c r="O192" t="s">
+        <v>126</v>
+      </c>
+      <c r="P192" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q192">
+        <v>2.3</v>
+      </c>
+      <c r="R192">
+        <v>2.4</v>
+      </c>
+      <c r="S192">
+        <v>4.33</v>
+      </c>
+      <c r="T192">
+        <v>1.29</v>
+      </c>
+      <c r="U192">
+        <v>3.5</v>
+      </c>
+      <c r="V192">
+        <v>2.25</v>
+      </c>
+      <c r="W192">
+        <v>1.57</v>
+      </c>
+      <c r="X192">
+        <v>5.5</v>
+      </c>
+      <c r="Y192">
+        <v>1.14</v>
+      </c>
+      <c r="Z192">
+        <v>1.76</v>
+      </c>
+      <c r="AA192">
+        <v>4.2</v>
+      </c>
+      <c r="AB192">
+        <v>4.33</v>
+      </c>
+      <c r="AC192">
+        <v>1.02</v>
+      </c>
+      <c r="AD192">
+        <v>19</v>
+      </c>
+      <c r="AE192">
+        <v>1.18</v>
+      </c>
+      <c r="AF192">
+        <v>5</v>
+      </c>
+      <c r="AG192">
+        <v>1.5</v>
+      </c>
+      <c r="AH192">
+        <v>2.48</v>
+      </c>
+      <c r="AI192">
+        <v>1.53</v>
+      </c>
+      <c r="AJ192">
+        <v>2.38</v>
+      </c>
+      <c r="AK192">
+        <v>1.22</v>
+      </c>
+      <c r="AL192">
+        <v>1.23</v>
+      </c>
+      <c r="AM192">
+        <v>2.05</v>
+      </c>
+      <c r="AN192">
+        <v>1.82</v>
+      </c>
+      <c r="AO192">
+        <v>1.7</v>
+      </c>
+      <c r="AP192">
+        <v>1.67</v>
+      </c>
+      <c r="AQ192">
+        <v>1.82</v>
+      </c>
+      <c r="AR192">
+        <v>1.88</v>
+      </c>
+      <c r="AS192">
+        <v>1.32</v>
+      </c>
+      <c r="AT192">
+        <v>3.2</v>
+      </c>
+      <c r="AU192">
+        <v>5</v>
+      </c>
+      <c r="AV192">
+        <v>4</v>
+      </c>
+      <c r="AW192">
+        <v>6</v>
+      </c>
+      <c r="AX192">
+        <v>4</v>
+      </c>
+      <c r="AY192">
+        <v>12</v>
+      </c>
+      <c r="AZ192">
+        <v>11</v>
+      </c>
+      <c r="BA192">
+        <v>7</v>
+      </c>
+      <c r="BB192">
+        <v>5</v>
+      </c>
+      <c r="BC192">
+        <v>12</v>
+      </c>
+      <c r="BD192">
+        <v>1.45</v>
+      </c>
+      <c r="BE192">
+        <v>6.75</v>
+      </c>
+      <c r="BF192">
+        <v>3.05</v>
+      </c>
+      <c r="BG192">
+        <v>1.29</v>
+      </c>
+      <c r="BH192">
+        <v>3.2</v>
+      </c>
+      <c r="BI192">
+        <v>1.49</v>
+      </c>
+      <c r="BJ192">
+        <v>2.4</v>
+      </c>
+      <c r="BK192">
+        <v>1.8</v>
+      </c>
+      <c r="BL192">
+        <v>1.88</v>
+      </c>
+      <c r="BM192">
+        <v>2.23</v>
+      </c>
+      <c r="BN192">
+        <v>1.56</v>
+      </c>
+      <c r="BO192">
+        <v>2.9</v>
+      </c>
+      <c r="BP192">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7492009</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45703.47916666666</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H193" t="s">
+        <v>70</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>2</v>
+      </c>
+      <c r="K193">
+        <v>2</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
+      <c r="M193">
+        <v>2</v>
+      </c>
+      <c r="N193">
+        <v>3</v>
+      </c>
+      <c r="O193" t="s">
+        <v>224</v>
+      </c>
+      <c r="P193" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q193">
+        <v>2.88</v>
+      </c>
+      <c r="R193">
+        <v>2.2</v>
+      </c>
+      <c r="S193">
+        <v>3.5</v>
+      </c>
+      <c r="T193">
+        <v>1.36</v>
+      </c>
+      <c r="U193">
+        <v>3</v>
+      </c>
+      <c r="V193">
+        <v>2.63</v>
+      </c>
+      <c r="W193">
+        <v>1.44</v>
+      </c>
+      <c r="X193">
+        <v>7</v>
+      </c>
+      <c r="Y193">
+        <v>1.1</v>
+      </c>
+      <c r="Z193">
+        <v>2.42</v>
+      </c>
+      <c r="AA193">
+        <v>3.52</v>
+      </c>
+      <c r="AB193">
+        <v>2.96</v>
+      </c>
+      <c r="AC193">
+        <v>1.04</v>
+      </c>
+      <c r="AD193">
+        <v>13</v>
+      </c>
+      <c r="AE193">
+        <v>1.25</v>
+      </c>
+      <c r="AF193">
+        <v>4</v>
+      </c>
+      <c r="AG193">
+        <v>1.81</v>
+      </c>
+      <c r="AH193">
+        <v>2.01</v>
+      </c>
+      <c r="AI193">
+        <v>1.67</v>
+      </c>
+      <c r="AJ193">
+        <v>2.1</v>
+      </c>
+      <c r="AK193">
+        <v>1.39</v>
+      </c>
+      <c r="AL193">
+        <v>1.3</v>
+      </c>
+      <c r="AM193">
+        <v>1.57</v>
+      </c>
+      <c r="AN193">
+        <v>1.6</v>
+      </c>
+      <c r="AO193">
+        <v>1.1</v>
+      </c>
+      <c r="AP193">
+        <v>1.45</v>
+      </c>
+      <c r="AQ193">
+        <v>1.27</v>
+      </c>
+      <c r="AR193">
+        <v>1.45</v>
+      </c>
+      <c r="AS193">
+        <v>1.35</v>
+      </c>
+      <c r="AT193">
+        <v>2.8</v>
+      </c>
+      <c r="AU193">
+        <v>4</v>
+      </c>
+      <c r="AV193">
+        <v>6</v>
+      </c>
+      <c r="AW193">
+        <v>14</v>
+      </c>
+      <c r="AX193">
+        <v>4</v>
+      </c>
+      <c r="AY193">
+        <v>21</v>
+      </c>
+      <c r="AZ193">
+        <v>10</v>
+      </c>
+      <c r="BA193">
+        <v>4</v>
+      </c>
+      <c r="BB193">
+        <v>5</v>
+      </c>
+      <c r="BC193">
+        <v>9</v>
+      </c>
+      <c r="BD193">
+        <v>1.68</v>
+      </c>
+      <c r="BE193">
+        <v>6.5</v>
+      </c>
+      <c r="BF193">
+        <v>2.4</v>
+      </c>
+      <c r="BG193">
+        <v>1.25</v>
+      </c>
+      <c r="BH193">
+        <v>3.45</v>
+      </c>
+      <c r="BI193">
+        <v>1.44</v>
+      </c>
+      <c r="BJ193">
+        <v>2.55</v>
+      </c>
+      <c r="BK193">
+        <v>1.72</v>
+      </c>
+      <c r="BL193">
+        <v>1.98</v>
+      </c>
+      <c r="BM193">
+        <v>2.15</v>
+      </c>
+      <c r="BN193">
+        <v>1.61</v>
+      </c>
+      <c r="BO193">
+        <v>2.7</v>
+      </c>
+      <c r="BP193">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7492010</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45703.47916666666</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>83</v>
+      </c>
+      <c r="H194" t="s">
+        <v>76</v>
+      </c>
+      <c r="I194">
+        <v>2</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>2</v>
+      </c>
+      <c r="L194">
+        <v>2</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>2</v>
+      </c>
+      <c r="O194" t="s">
+        <v>225</v>
+      </c>
+      <c r="P194" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q194">
+        <v>4.5</v>
+      </c>
+      <c r="R194">
+        <v>2.4</v>
+      </c>
+      <c r="S194">
+        <v>2.2</v>
+      </c>
+      <c r="T194">
+        <v>1.29</v>
+      </c>
+      <c r="U194">
+        <v>3.5</v>
+      </c>
+      <c r="V194">
+        <v>2.25</v>
+      </c>
+      <c r="W194">
+        <v>1.57</v>
+      </c>
+      <c r="X194">
+        <v>5.5</v>
+      </c>
+      <c r="Y194">
+        <v>1.14</v>
+      </c>
+      <c r="Z194">
+        <v>4.6</v>
+      </c>
+      <c r="AA194">
+        <v>4.4</v>
+      </c>
+      <c r="AB194">
+        <v>1.69</v>
+      </c>
+      <c r="AC194">
+        <v>1.02</v>
+      </c>
+      <c r="AD194">
+        <v>19</v>
+      </c>
+      <c r="AE194">
+        <v>1.19</v>
+      </c>
+      <c r="AF194">
+        <v>4.75</v>
+      </c>
+      <c r="AG194">
+        <v>1.55</v>
+      </c>
+      <c r="AH194">
+        <v>2.3</v>
+      </c>
+      <c r="AI194">
+        <v>1.57</v>
+      </c>
+      <c r="AJ194">
+        <v>2.25</v>
+      </c>
+      <c r="AK194">
+        <v>2.1</v>
+      </c>
+      <c r="AL194">
+        <v>1.23</v>
+      </c>
+      <c r="AM194">
+        <v>1.2</v>
+      </c>
+      <c r="AN194">
+        <v>0.9</v>
+      </c>
+      <c r="AO194">
+        <v>0.8</v>
+      </c>
+      <c r="AP194">
+        <v>1.09</v>
+      </c>
+      <c r="AQ194">
+        <v>0.73</v>
+      </c>
+      <c r="AR194">
+        <v>1.33</v>
+      </c>
+      <c r="AS194">
+        <v>1.35</v>
+      </c>
+      <c r="AT194">
+        <v>2.68</v>
+      </c>
+      <c r="AU194">
+        <v>10</v>
+      </c>
+      <c r="AV194">
+        <v>3</v>
+      </c>
+      <c r="AW194">
+        <v>9</v>
+      </c>
+      <c r="AX194">
+        <v>15</v>
+      </c>
+      <c r="AY194">
+        <v>20</v>
+      </c>
+      <c r="AZ194">
+        <v>21</v>
+      </c>
+      <c r="BA194">
+        <v>2</v>
+      </c>
+      <c r="BB194">
+        <v>8</v>
+      </c>
+      <c r="BC194">
+        <v>10</v>
+      </c>
+      <c r="BD194">
+        <v>2.7</v>
+      </c>
+      <c r="BE194">
+        <v>6.75</v>
+      </c>
+      <c r="BF194">
+        <v>1.54</v>
+      </c>
+      <c r="BG194">
+        <v>1.22</v>
+      </c>
+      <c r="BH194">
+        <v>3.65</v>
+      </c>
+      <c r="BI194">
+        <v>1.41</v>
+      </c>
+      <c r="BJ194">
+        <v>2.65</v>
+      </c>
+      <c r="BK194">
+        <v>1.68</v>
+      </c>
+      <c r="BL194">
+        <v>2.04</v>
+      </c>
+      <c r="BM194">
+        <v>2.05</v>
+      </c>
+      <c r="BN194">
+        <v>1.67</v>
+      </c>
+      <c r="BO194">
+        <v>2.55</v>
+      </c>
+      <c r="BP194">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7492011</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45703.47916666666</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>78</v>
+      </c>
+      <c r="H195" t="s">
+        <v>73</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="M195">
+        <v>1</v>
+      </c>
+      <c r="N195">
+        <v>1</v>
+      </c>
+      <c r="O195" t="s">
+        <v>96</v>
+      </c>
+      <c r="P195" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q195">
+        <v>3.2</v>
+      </c>
+      <c r="R195">
+        <v>2.05</v>
+      </c>
+      <c r="S195">
+        <v>3.6</v>
+      </c>
+      <c r="T195">
+        <v>1.44</v>
+      </c>
+      <c r="U195">
+        <v>2.63</v>
+      </c>
+      <c r="V195">
+        <v>3.4</v>
+      </c>
+      <c r="W195">
+        <v>1.3</v>
+      </c>
+      <c r="X195">
+        <v>10</v>
+      </c>
+      <c r="Y195">
+        <v>1.06</v>
+      </c>
+      <c r="Z195">
+        <v>2.32</v>
+      </c>
+      <c r="AA195">
+        <v>3.39</v>
+      </c>
+      <c r="AB195">
+        <v>3.25</v>
+      </c>
+      <c r="AC195">
+        <v>1.08</v>
+      </c>
+      <c r="AD195">
+        <v>8.5</v>
+      </c>
+      <c r="AE195">
+        <v>1.4</v>
+      </c>
+      <c r="AF195">
+        <v>3</v>
+      </c>
+      <c r="AG195">
+        <v>2.02</v>
+      </c>
+      <c r="AH195">
+        <v>1.8</v>
+      </c>
+      <c r="AI195">
+        <v>1.91</v>
+      </c>
+      <c r="AJ195">
+        <v>1.91</v>
+      </c>
+      <c r="AK195">
+        <v>1.4</v>
+      </c>
+      <c r="AL195">
+        <v>1.34</v>
+      </c>
+      <c r="AM195">
+        <v>1.51</v>
+      </c>
+      <c r="AN195">
+        <v>0.9</v>
+      </c>
+      <c r="AO195">
+        <v>1</v>
+      </c>
+      <c r="AP195">
+        <v>0.82</v>
+      </c>
+      <c r="AQ195">
+        <v>1.17</v>
+      </c>
+      <c r="AR195">
+        <v>1.32</v>
+      </c>
+      <c r="AS195">
+        <v>1.22</v>
+      </c>
+      <c r="AT195">
+        <v>2.54</v>
+      </c>
+      <c r="AU195">
+        <v>2</v>
+      </c>
+      <c r="AV195">
+        <v>4</v>
+      </c>
+      <c r="AW195">
+        <v>4</v>
+      </c>
+      <c r="AX195">
+        <v>2</v>
+      </c>
+      <c r="AY195">
+        <v>8</v>
+      </c>
+      <c r="AZ195">
+        <v>6</v>
+      </c>
+      <c r="BA195">
+        <v>2</v>
+      </c>
+      <c r="BB195">
+        <v>6</v>
+      </c>
+      <c r="BC195">
+        <v>8</v>
+      </c>
+      <c r="BD195">
+        <v>1.81</v>
+      </c>
+      <c r="BE195">
+        <v>6.1</v>
+      </c>
+      <c r="BF195">
+        <v>2.23</v>
+      </c>
+      <c r="BG195">
+        <v>1.41</v>
+      </c>
+      <c r="BH195">
+        <v>2.63</v>
+      </c>
+      <c r="BI195">
+        <v>1.72</v>
+      </c>
+      <c r="BJ195">
+        <v>1.98</v>
+      </c>
+      <c r="BK195">
+        <v>2.17</v>
+      </c>
+      <c r="BL195">
+        <v>1.6</v>
+      </c>
+      <c r="BM195">
+        <v>2.8</v>
+      </c>
+      <c r="BN195">
+        <v>1.37</v>
+      </c>
+      <c r="BO195">
+        <v>3.7</v>
+      </c>
+      <c r="BP195">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7492003</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45703.60416666666</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>85</v>
+      </c>
+      <c r="H196" t="s">
+        <v>87</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+      <c r="N196">
+        <v>0</v>
+      </c>
+      <c r="O196" t="s">
+        <v>96</v>
+      </c>
+      <c r="P196" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q196">
+        <v>3.5</v>
+      </c>
+      <c r="R196">
+        <v>2.38</v>
+      </c>
+      <c r="S196">
+        <v>2.75</v>
+      </c>
+      <c r="T196">
+        <v>1.3</v>
+      </c>
+      <c r="U196">
+        <v>3.4</v>
+      </c>
+      <c r="V196">
+        <v>2.38</v>
+      </c>
+      <c r="W196">
+        <v>1.53</v>
+      </c>
+      <c r="X196">
+        <v>6</v>
+      </c>
+      <c r="Y196">
+        <v>1.13</v>
+      </c>
+      <c r="Z196">
+        <v>3.15</v>
+      </c>
+      <c r="AA196">
+        <v>3.8</v>
+      </c>
+      <c r="AB196">
+        <v>2.2</v>
+      </c>
+      <c r="AC196">
+        <v>1.03</v>
+      </c>
+      <c r="AD196">
+        <v>15</v>
+      </c>
+      <c r="AE196">
+        <v>1.2</v>
+      </c>
+      <c r="AF196">
+        <v>4.5</v>
+      </c>
+      <c r="AG196">
+        <v>1.58</v>
+      </c>
+      <c r="AH196">
+        <v>2.29</v>
+      </c>
+      <c r="AI196">
+        <v>1.5</v>
+      </c>
+      <c r="AJ196">
+        <v>2.5</v>
+      </c>
+      <c r="AK196">
+        <v>1.66</v>
+      </c>
+      <c r="AL196">
+        <v>1.27</v>
+      </c>
+      <c r="AM196">
+        <v>1.36</v>
+      </c>
+      <c r="AN196">
+        <v>2.36</v>
+      </c>
+      <c r="AO196">
+        <v>2.3</v>
+      </c>
+      <c r="AP196">
+        <v>2.25</v>
+      </c>
+      <c r="AQ196">
+        <v>2.18</v>
+      </c>
+      <c r="AR196">
+        <v>2.06</v>
+      </c>
+      <c r="AS196">
+        <v>1.92</v>
+      </c>
+      <c r="AT196">
+        <v>3.98</v>
+      </c>
+      <c r="AU196">
+        <v>4</v>
+      </c>
+      <c r="AV196">
+        <v>0</v>
+      </c>
+      <c r="AW196">
+        <v>12</v>
+      </c>
+      <c r="AX196">
+        <v>3</v>
+      </c>
+      <c r="AY196">
+        <v>22</v>
+      </c>
+      <c r="AZ196">
+        <v>4</v>
+      </c>
+      <c r="BA196">
+        <v>6</v>
+      </c>
+      <c r="BB196">
+        <v>0</v>
+      </c>
+      <c r="BC196">
+        <v>6</v>
+      </c>
+      <c r="BD196">
+        <v>2.3</v>
+      </c>
+      <c r="BE196">
+        <v>6.25</v>
+      </c>
+      <c r="BF196">
+        <v>1.76</v>
+      </c>
+      <c r="BG196">
+        <v>1.36</v>
+      </c>
+      <c r="BH196">
+        <v>2.8</v>
+      </c>
+      <c r="BI196">
+        <v>1.64</v>
+      </c>
+      <c r="BJ196">
+        <v>2.1</v>
+      </c>
+      <c r="BK196">
+        <v>2.02</v>
+      </c>
+      <c r="BL196">
+        <v>1.68</v>
+      </c>
+      <c r="BM196">
+        <v>2.55</v>
+      </c>
+      <c r="BN196">
+        <v>1.43</v>
+      </c>
+      <c r="BO196">
+        <v>3.4</v>
+      </c>
+      <c r="BP196">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="342">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -694,6 +694,12 @@
     <t>['33', '35']</t>
   </si>
   <si>
+    <t>['7']</t>
+  </si>
+  <si>
+    <t>['18', '37', '60']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1028,6 +1034,12 @@
   </si>
   <si>
     <t>['88']</t>
+  </si>
+  <si>
+    <t>['28', '44', '63']</t>
+  </si>
+  <si>
+    <t>['28', '49']</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1645,7 +1657,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2057,7 +2069,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2138,7 +2150,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2263,7 +2275,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2469,7 +2481,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2675,7 +2687,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3087,7 +3099,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3293,7 +3305,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3705,7 +3717,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3786,7 +3798,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3911,7 +3923,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4117,7 +4129,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4195,10 +4207,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ14">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4323,7 +4335,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4607,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ16">
         <v>0.73</v>
@@ -4735,7 +4747,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5019,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ18">
         <v>0.91</v>
@@ -5353,7 +5365,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5765,7 +5777,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6177,7 +6189,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6383,7 +6395,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6589,7 +6601,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6795,7 +6807,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -7001,7 +7013,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7207,7 +7219,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7288,7 +7300,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR29">
         <v>1.7</v>
@@ -7413,7 +7425,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7491,7 +7503,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ30">
         <v>1.17</v>
@@ -7619,7 +7631,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7697,7 +7709,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ31">
         <v>2.18</v>
@@ -7825,7 +7837,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7906,7 +7918,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ32">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR32">
         <v>1.36</v>
@@ -8031,7 +8043,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8112,7 +8124,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ33">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR33">
         <v>1.57</v>
@@ -8315,7 +8327,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ34">
         <v>1.27</v>
@@ -8443,7 +8455,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9061,7 +9073,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9473,7 +9485,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9679,7 +9691,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9885,7 +9897,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10297,7 +10309,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10503,7 +10515,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10709,7 +10721,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11121,7 +11133,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11202,7 +11214,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ48">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR48">
         <v>2.42</v>
@@ -11405,7 +11417,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49">
         <v>1.17</v>
@@ -11533,7 +11545,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11739,7 +11751,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11945,7 +11957,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12026,7 +12038,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ52">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -12229,7 +12241,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12357,7 +12369,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12435,7 +12447,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ54">
         <v>2.18</v>
@@ -12563,7 +12575,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12644,7 +12656,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ55">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR55">
         <v>2.29</v>
@@ -12769,7 +12781,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12975,7 +12987,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13387,7 +13399,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13593,7 +13605,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13799,7 +13811,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14211,7 +14223,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14417,7 +14429,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14623,7 +14635,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14829,7 +14841,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15241,7 +15253,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15528,7 +15540,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR69">
         <v>2.2</v>
@@ -15653,7 +15665,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15731,7 +15743,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ70">
         <v>2</v>
@@ -15859,7 +15871,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16349,10 +16361,10 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ73">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR73">
         <v>1.3</v>
@@ -16889,7 +16901,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16967,7 +16979,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ76">
         <v>0.18</v>
@@ -17095,7 +17107,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18000,7 +18012,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ81">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR81">
         <v>1.64</v>
@@ -18537,7 +18549,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18821,10 +18833,10 @@
         <v>0.5</v>
       </c>
       <c r="AP85">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ85">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR85">
         <v>0.97</v>
@@ -18949,7 +18961,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19155,7 +19167,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19648,7 +19660,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ89">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19773,7 +19785,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19979,7 +19991,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20057,7 +20069,7 @@
         <v>1.75</v>
       </c>
       <c r="AP91">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ91">
         <v>1.82</v>
@@ -20391,7 +20403,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -21009,7 +21021,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21499,7 +21511,7 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ98">
         <v>1.55</v>
@@ -21627,7 +21639,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21708,7 +21720,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ99">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -22039,7 +22051,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22120,7 +22132,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ101">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR101">
         <v>1.26</v>
@@ -22245,7 +22257,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22451,7 +22463,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22863,7 +22875,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23069,7 +23081,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23147,7 +23159,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ106">
         <v>1.5</v>
@@ -23275,7 +23287,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23562,7 +23574,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ108">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR108">
         <v>1.45</v>
@@ -23687,7 +23699,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23765,7 +23777,7 @@
         <v>1.67</v>
       </c>
       <c r="AP109">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ109">
         <v>1.64</v>
@@ -23893,7 +23905,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24099,7 +24111,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24305,7 +24317,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24511,7 +24523,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24589,7 +24601,7 @@
         <v>0.2</v>
       </c>
       <c r="AP113">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ113">
         <v>0.91</v>
@@ -24717,7 +24729,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25129,7 +25141,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25335,7 +25347,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25416,7 +25428,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ117">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR117">
         <v>1.29</v>
@@ -25747,7 +25759,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25953,7 +25965,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26159,7 +26171,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26365,7 +26377,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26652,7 +26664,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ123">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26777,7 +26789,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26983,7 +26995,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27061,7 +27073,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ125">
         <v>1.5</v>
@@ -27189,7 +27201,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27270,7 +27282,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ126">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR126">
         <v>1.74</v>
@@ -27395,7 +27407,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27601,7 +27613,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27807,7 +27819,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28013,7 +28025,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28219,7 +28231,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28297,10 +28309,10 @@
         <v>1.83</v>
       </c>
       <c r="AP131">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ131">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR131">
         <v>1.54</v>
@@ -28425,7 +28437,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28631,7 +28643,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28709,7 +28721,7 @@
         <v>0.71</v>
       </c>
       <c r="AP133">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ133">
         <v>0.73</v>
@@ -29249,7 +29261,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29455,7 +29467,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29945,7 +29957,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ139">
         <v>0.73</v>
@@ -30073,7 +30085,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30154,7 +30166,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ140">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR140">
         <v>1.59</v>
@@ -30485,7 +30497,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30897,7 +30909,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31103,7 +31115,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31309,7 +31321,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31593,7 +31605,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ147">
         <v>1.17</v>
@@ -32008,7 +32020,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ149">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR149">
         <v>2.17</v>
@@ -32339,7 +32351,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32626,7 +32638,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ152">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR152">
         <v>2.19</v>
@@ -32751,7 +32763,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32829,7 +32841,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ153">
         <v>0.64</v>
@@ -32957,7 +32969,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33241,7 +33253,7 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ155">
         <v>0.73</v>
@@ -33369,7 +33381,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33450,7 +33462,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ156">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR156">
         <v>1.22</v>
@@ -33575,7 +33587,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33781,7 +33793,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -33859,7 +33871,7 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ158">
         <v>1.09</v>
@@ -34193,7 +34205,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34399,7 +34411,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34605,7 +34617,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34686,7 +34698,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ162">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR162">
         <v>1.42</v>
@@ -34811,7 +34823,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34889,7 +34901,7 @@
         <v>0.63</v>
       </c>
       <c r="AP163">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ163">
         <v>0.91</v>
@@ -35017,7 +35029,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35098,7 +35110,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ164">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR164">
         <v>1.34</v>
@@ -35635,7 +35647,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35841,7 +35853,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36047,7 +36059,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36459,7 +36471,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36949,10 +36961,10 @@
         <v>1.56</v>
       </c>
       <c r="AP173">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ173">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR173">
         <v>1.38</v>
@@ -37077,7 +37089,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37283,7 +37295,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37364,7 +37376,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ175">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR175">
         <v>2.37</v>
@@ -37489,7 +37501,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37567,7 +37579,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP176">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ176">
         <v>0.73</v>
@@ -37901,7 +37913,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38313,7 +38325,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38391,7 +38403,7 @@
         <v>1.78</v>
       </c>
       <c r="AP180">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ180">
         <v>1.82</v>
@@ -38519,7 +38531,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38600,7 +38612,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ181">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR181">
         <v>2.14</v>
@@ -39137,7 +39149,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39343,7 +39355,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39961,7 +39973,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40167,7 +40179,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40785,7 +40797,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -40991,7 +41003,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41403,7 +41415,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41766,6 +41778,624 @@
       </c>
       <c r="BP196">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7492007</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45704.47916666666</v>
+      </c>
+      <c r="F197">
+        <v>22</v>
+      </c>
+      <c r="G197" t="s">
+        <v>84</v>
+      </c>
+      <c r="H197" t="s">
+        <v>72</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
+        <v>2</v>
+      </c>
+      <c r="K197">
+        <v>3</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>3</v>
+      </c>
+      <c r="N197">
+        <v>4</v>
+      </c>
+      <c r="O197" t="s">
+        <v>226</v>
+      </c>
+      <c r="P197" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q197">
+        <v>2.4</v>
+      </c>
+      <c r="R197">
+        <v>2.4</v>
+      </c>
+      <c r="S197">
+        <v>4</v>
+      </c>
+      <c r="T197">
+        <v>1.29</v>
+      </c>
+      <c r="U197">
+        <v>3.5</v>
+      </c>
+      <c r="V197">
+        <v>2.25</v>
+      </c>
+      <c r="W197">
+        <v>1.57</v>
+      </c>
+      <c r="X197">
+        <v>5.5</v>
+      </c>
+      <c r="Y197">
+        <v>1.14</v>
+      </c>
+      <c r="Z197">
+        <v>1.9</v>
+      </c>
+      <c r="AA197">
+        <v>4.1</v>
+      </c>
+      <c r="AB197">
+        <v>3.81</v>
+      </c>
+      <c r="AC197">
+        <v>1.02</v>
+      </c>
+      <c r="AD197">
+        <v>19</v>
+      </c>
+      <c r="AE197">
+        <v>1.17</v>
+      </c>
+      <c r="AF197">
+        <v>5</v>
+      </c>
+      <c r="AG197">
+        <v>1.57</v>
+      </c>
+      <c r="AH197">
+        <v>2.3</v>
+      </c>
+      <c r="AI197">
+        <v>1.5</v>
+      </c>
+      <c r="AJ197">
+        <v>2.5</v>
+      </c>
+      <c r="AK197">
+        <v>1.27</v>
+      </c>
+      <c r="AL197">
+        <v>1.25</v>
+      </c>
+      <c r="AM197">
+        <v>1.87</v>
+      </c>
+      <c r="AN197">
+        <v>1.3</v>
+      </c>
+      <c r="AO197">
+        <v>0.7</v>
+      </c>
+      <c r="AP197">
+        <v>1.18</v>
+      </c>
+      <c r="AQ197">
+        <v>0.91</v>
+      </c>
+      <c r="AR197">
+        <v>1.38</v>
+      </c>
+      <c r="AS197">
+        <v>1.2</v>
+      </c>
+      <c r="AT197">
+        <v>2.58</v>
+      </c>
+      <c r="AU197">
+        <v>2</v>
+      </c>
+      <c r="AV197">
+        <v>8</v>
+      </c>
+      <c r="AW197">
+        <v>12</v>
+      </c>
+      <c r="AX197">
+        <v>9</v>
+      </c>
+      <c r="AY197">
+        <v>19</v>
+      </c>
+      <c r="AZ197">
+        <v>23</v>
+      </c>
+      <c r="BA197">
+        <v>6</v>
+      </c>
+      <c r="BB197">
+        <v>4</v>
+      </c>
+      <c r="BC197">
+        <v>10</v>
+      </c>
+      <c r="BD197">
+        <v>1.78</v>
+      </c>
+      <c r="BE197">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF197">
+        <v>2.43</v>
+      </c>
+      <c r="BG197">
+        <v>1.19</v>
+      </c>
+      <c r="BH197">
+        <v>3.8</v>
+      </c>
+      <c r="BI197">
+        <v>1.39</v>
+      </c>
+      <c r="BJ197">
+        <v>2.67</v>
+      </c>
+      <c r="BK197">
+        <v>1.71</v>
+      </c>
+      <c r="BL197">
+        <v>2.02</v>
+      </c>
+      <c r="BM197">
+        <v>2.14</v>
+      </c>
+      <c r="BN197">
+        <v>1.6</v>
+      </c>
+      <c r="BO197">
+        <v>2.78</v>
+      </c>
+      <c r="BP197">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7492005</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45704.5625</v>
+      </c>
+      <c r="F198">
+        <v>22</v>
+      </c>
+      <c r="G198" t="s">
+        <v>82</v>
+      </c>
+      <c r="H198" t="s">
+        <v>81</v>
+      </c>
+      <c r="I198">
+        <v>2</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>2</v>
+      </c>
+      <c r="L198">
+        <v>3</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>4</v>
+      </c>
+      <c r="O198" t="s">
+        <v>227</v>
+      </c>
+      <c r="P198" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q198">
+        <v>1.73</v>
+      </c>
+      <c r="R198">
+        <v>2.88</v>
+      </c>
+      <c r="S198">
+        <v>6.5</v>
+      </c>
+      <c r="T198">
+        <v>1.22</v>
+      </c>
+      <c r="U198">
+        <v>4</v>
+      </c>
+      <c r="V198">
+        <v>2</v>
+      </c>
+      <c r="W198">
+        <v>1.73</v>
+      </c>
+      <c r="X198">
+        <v>4.33</v>
+      </c>
+      <c r="Y198">
+        <v>1.2</v>
+      </c>
+      <c r="Z198">
+        <v>1.32</v>
+      </c>
+      <c r="AA198">
+        <v>6.3</v>
+      </c>
+      <c r="AB198">
+        <v>8.4</v>
+      </c>
+      <c r="AC198">
+        <v>1.01</v>
+      </c>
+      <c r="AD198">
+        <v>23</v>
+      </c>
+      <c r="AE198">
+        <v>1.12</v>
+      </c>
+      <c r="AF198">
+        <v>6.5</v>
+      </c>
+      <c r="AG198">
+        <v>1.38</v>
+      </c>
+      <c r="AH198">
+        <v>2.9</v>
+      </c>
+      <c r="AI198">
+        <v>1.67</v>
+      </c>
+      <c r="AJ198">
+        <v>2.1</v>
+      </c>
+      <c r="AK198">
+        <v>1.08</v>
+      </c>
+      <c r="AL198">
+        <v>1.14</v>
+      </c>
+      <c r="AM198">
+        <v>3.25</v>
+      </c>
+      <c r="AN198">
+        <v>2.1</v>
+      </c>
+      <c r="AO198">
+        <v>0.3</v>
+      </c>
+      <c r="AP198">
+        <v>2.18</v>
+      </c>
+      <c r="AQ198">
+        <v>0.27</v>
+      </c>
+      <c r="AR198">
+        <v>1.84</v>
+      </c>
+      <c r="AS198">
+        <v>1.15</v>
+      </c>
+      <c r="AT198">
+        <v>2.99</v>
+      </c>
+      <c r="AU198">
+        <v>10</v>
+      </c>
+      <c r="AV198">
+        <v>5</v>
+      </c>
+      <c r="AW198">
+        <v>11</v>
+      </c>
+      <c r="AX198">
+        <v>6</v>
+      </c>
+      <c r="AY198">
+        <v>25</v>
+      </c>
+      <c r="AZ198">
+        <v>12</v>
+      </c>
+      <c r="BA198">
+        <v>4</v>
+      </c>
+      <c r="BB198">
+        <v>6</v>
+      </c>
+      <c r="BC198">
+        <v>10</v>
+      </c>
+      <c r="BD198">
+        <v>1.17</v>
+      </c>
+      <c r="BE198">
+        <v>13</v>
+      </c>
+      <c r="BF198">
+        <v>6.45</v>
+      </c>
+      <c r="BG198">
+        <v>1.15</v>
+      </c>
+      <c r="BH198">
+        <v>4.3</v>
+      </c>
+      <c r="BI198">
+        <v>1.31</v>
+      </c>
+      <c r="BJ198">
+        <v>2.92</v>
+      </c>
+      <c r="BK198">
+        <v>1.57</v>
+      </c>
+      <c r="BL198">
+        <v>2.19</v>
+      </c>
+      <c r="BM198">
+        <v>1.96</v>
+      </c>
+      <c r="BN198">
+        <v>1.75</v>
+      </c>
+      <c r="BO198">
+        <v>2.51</v>
+      </c>
+      <c r="BP198">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7492006</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45704.64583333334</v>
+      </c>
+      <c r="F199">
+        <v>22</v>
+      </c>
+      <c r="G199" t="s">
+        <v>86</v>
+      </c>
+      <c r="H199" t="s">
+        <v>75</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>2</v>
+      </c>
+      <c r="N199">
+        <v>2</v>
+      </c>
+      <c r="O199" t="s">
+        <v>96</v>
+      </c>
+      <c r="P199" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q199">
+        <v>4</v>
+      </c>
+      <c r="R199">
+        <v>2.2</v>
+      </c>
+      <c r="S199">
+        <v>2.75</v>
+      </c>
+      <c r="T199">
+        <v>1.4</v>
+      </c>
+      <c r="U199">
+        <v>2.75</v>
+      </c>
+      <c r="V199">
+        <v>2.75</v>
+      </c>
+      <c r="W199">
+        <v>1.4</v>
+      </c>
+      <c r="X199">
+        <v>8</v>
+      </c>
+      <c r="Y199">
+        <v>1.08</v>
+      </c>
+      <c r="Z199">
+        <v>3.28</v>
+      </c>
+      <c r="AA199">
+        <v>3.55</v>
+      </c>
+      <c r="AB199">
+        <v>2.23</v>
+      </c>
+      <c r="AC199">
+        <v>1.05</v>
+      </c>
+      <c r="AD199">
+        <v>11</v>
+      </c>
+      <c r="AE199">
+        <v>1.3</v>
+      </c>
+      <c r="AF199">
+        <v>3.6</v>
+      </c>
+      <c r="AG199">
+        <v>1.86</v>
+      </c>
+      <c r="AH199">
+        <v>1.95</v>
+      </c>
+      <c r="AI199">
+        <v>1.7</v>
+      </c>
+      <c r="AJ199">
+        <v>2.05</v>
+      </c>
+      <c r="AK199">
+        <v>1.66</v>
+      </c>
+      <c r="AL199">
+        <v>1.29</v>
+      </c>
+      <c r="AM199">
+        <v>1.34</v>
+      </c>
+      <c r="AN199">
+        <v>0.7</v>
+      </c>
+      <c r="AO199">
+        <v>1.4</v>
+      </c>
+      <c r="AP199">
+        <v>0.64</v>
+      </c>
+      <c r="AQ199">
+        <v>1.55</v>
+      </c>
+      <c r="AR199">
+        <v>1.37</v>
+      </c>
+      <c r="AS199">
+        <v>1.17</v>
+      </c>
+      <c r="AT199">
+        <v>2.54</v>
+      </c>
+      <c r="AU199">
+        <v>4</v>
+      </c>
+      <c r="AV199">
+        <v>6</v>
+      </c>
+      <c r="AW199">
+        <v>9</v>
+      </c>
+      <c r="AX199">
+        <v>1</v>
+      </c>
+      <c r="AY199">
+        <v>14</v>
+      </c>
+      <c r="AZ199">
+        <v>8</v>
+      </c>
+      <c r="BA199">
+        <v>8</v>
+      </c>
+      <c r="BB199">
+        <v>4</v>
+      </c>
+      <c r="BC199">
+        <v>12</v>
+      </c>
+      <c r="BD199">
+        <v>2.43</v>
+      </c>
+      <c r="BE199">
+        <v>8.5</v>
+      </c>
+      <c r="BF199">
+        <v>1.79</v>
+      </c>
+      <c r="BG199">
+        <v>1.24</v>
+      </c>
+      <c r="BH199">
+        <v>3.34</v>
+      </c>
+      <c r="BI199">
+        <v>1.47</v>
+      </c>
+      <c r="BJ199">
+        <v>2.42</v>
+      </c>
+      <c r="BK199">
+        <v>1.84</v>
+      </c>
+      <c r="BL199">
+        <v>1.86</v>
+      </c>
+      <c r="BM199">
+        <v>2.34</v>
+      </c>
+      <c r="BN199">
+        <v>1.5</v>
+      </c>
+      <c r="BO199">
+        <v>3.14</v>
+      </c>
+      <c r="BP199">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="343">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -698,6 +698,9 @@
   </si>
   <si>
     <t>['18', '37', '60']</t>
+  </si>
+  <si>
+    <t>['15', '33', '57', '76', '90+2']</t>
   </si>
   <si>
     <t>['12', '38', '90+11']</t>
@@ -1401,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1657,7 +1660,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2069,7 +2072,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2275,7 +2278,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2353,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -2481,7 +2484,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2562,7 +2565,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ6">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2687,7 +2690,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3099,7 +3102,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3305,7 +3308,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3717,7 +3720,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3923,7 +3926,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4129,7 +4132,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4335,7 +4338,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4747,7 +4750,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5365,7 +5368,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5777,7 +5780,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6061,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ23">
         <v>0.18</v>
@@ -6189,7 +6192,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6395,7 +6398,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6601,7 +6604,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6807,7 +6810,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -7013,7 +7016,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7094,7 +7097,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ28">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR28">
         <v>1.23</v>
@@ -7219,7 +7222,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7425,7 +7428,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7631,7 +7634,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7837,7 +7840,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8043,7 +8046,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8455,7 +8458,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9073,7 +9076,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9485,7 +9488,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9691,7 +9694,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9897,7 +9900,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -9975,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ42">
         <v>1.09</v>
@@ -10309,7 +10312,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10515,7 +10518,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10721,7 +10724,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10802,7 +10805,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR46">
         <v>1.82</v>
@@ -11133,7 +11136,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11545,7 +11548,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11751,7 +11754,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11957,7 +11960,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12369,7 +12372,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12575,7 +12578,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12781,7 +12784,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12987,7 +12990,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13399,7 +13402,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13477,7 +13480,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ59">
         <v>0.91</v>
@@ -13605,7 +13608,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13811,7 +13814,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14223,7 +14226,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14429,7 +14432,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14510,7 +14513,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ64">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR64">
         <v>1.11</v>
@@ -14635,7 +14638,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14841,7 +14844,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15253,7 +15256,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15665,7 +15668,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15871,7 +15874,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16901,7 +16904,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17107,7 +17110,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18009,7 +18012,7 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ81">
         <v>1.55</v>
@@ -18218,7 +18221,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ82">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18549,7 +18552,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18961,7 +18964,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19167,7 +19170,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19785,7 +19788,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19991,7 +19994,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20403,7 +20406,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -21021,7 +21024,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21514,7 +21517,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ98">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR98">
         <v>1.59</v>
@@ -21639,7 +21642,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22051,7 +22054,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22257,7 +22260,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22463,7 +22466,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22541,7 +22544,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ103">
         <v>1.27</v>
@@ -22875,7 +22878,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23081,7 +23084,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23287,7 +23290,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23699,7 +23702,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23905,7 +23908,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24111,7 +24114,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24317,7 +24320,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24398,7 +24401,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ112">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR112">
         <v>1.23</v>
@@ -24523,7 +24526,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24729,7 +24732,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25141,7 +25144,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25347,7 +25350,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25759,7 +25762,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25837,7 +25840,7 @@
         <v>2.17</v>
       </c>
       <c r="AP119">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ119">
         <v>1.82</v>
@@ -25965,7 +25968,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26171,7 +26174,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26377,7 +26380,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26789,7 +26792,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26870,7 +26873,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ124">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -26995,7 +26998,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27201,7 +27204,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27407,7 +27410,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27613,7 +27616,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27819,7 +27822,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28025,7 +28028,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28231,7 +28234,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28437,7 +28440,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28643,7 +28646,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -29261,7 +29264,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29467,7 +29470,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -30085,7 +30088,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30163,7 +30166,7 @@
         <v>0.29</v>
       </c>
       <c r="AP140">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ140">
         <v>0.27</v>
@@ -30497,7 +30500,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30909,7 +30912,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -30990,7 +30993,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ144">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -31115,7 +31118,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31321,7 +31324,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -32351,7 +32354,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32763,7 +32766,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32969,7 +32972,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33381,7 +33384,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33587,7 +33590,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33793,7 +33796,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34205,7 +34208,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34411,7 +34414,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34617,7 +34620,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34823,7 +34826,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -35029,7 +35032,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35647,7 +35650,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35725,7 +35728,7 @@
         <v>2.22</v>
       </c>
       <c r="AP167">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ167">
         <v>2.18</v>
@@ -35853,7 +35856,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -35934,7 +35937,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ168">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR168">
         <v>1.59</v>
@@ -36059,7 +36062,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36471,7 +36474,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -37089,7 +37092,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37295,7 +37298,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37501,7 +37504,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37913,7 +37916,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38325,7 +38328,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38531,7 +38534,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38818,7 +38821,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ182">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR182">
         <v>2.47</v>
@@ -39149,7 +39152,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39355,7 +39358,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39639,7 +39642,7 @@
         <v>0.7</v>
       </c>
       <c r="AP186">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ186">
         <v>0.64</v>
@@ -39973,7 +39976,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40179,7 +40182,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40797,7 +40800,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -41003,7 +41006,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41415,7 +41418,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41827,7 +41830,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42239,7 +42242,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42396,6 +42399,212 @@
       </c>
       <c r="BP199">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7492016</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45709.6875</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>73</v>
+      </c>
+      <c r="H200" t="s">
+        <v>84</v>
+      </c>
+      <c r="I200">
+        <v>2</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>2</v>
+      </c>
+      <c r="L200">
+        <v>5</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>5</v>
+      </c>
+      <c r="O200" t="s">
+        <v>228</v>
+      </c>
+      <c r="P200" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q200">
+        <v>2.75</v>
+      </c>
+      <c r="R200">
+        <v>2.2</v>
+      </c>
+      <c r="S200">
+        <v>3.75</v>
+      </c>
+      <c r="T200">
+        <v>1.36</v>
+      </c>
+      <c r="U200">
+        <v>3</v>
+      </c>
+      <c r="V200">
+        <v>2.63</v>
+      </c>
+      <c r="W200">
+        <v>1.44</v>
+      </c>
+      <c r="X200">
+        <v>7</v>
+      </c>
+      <c r="Y200">
+        <v>1.1</v>
+      </c>
+      <c r="Z200">
+        <v>2.2</v>
+      </c>
+      <c r="AA200">
+        <v>3.64</v>
+      </c>
+      <c r="AB200">
+        <v>3.28</v>
+      </c>
+      <c r="AC200">
+        <v>1.04</v>
+      </c>
+      <c r="AD200">
+        <v>12</v>
+      </c>
+      <c r="AE200">
+        <v>1.28</v>
+      </c>
+      <c r="AF200">
+        <v>3.75</v>
+      </c>
+      <c r="AG200">
+        <v>1.82</v>
+      </c>
+      <c r="AH200">
+        <v>2</v>
+      </c>
+      <c r="AI200">
+        <v>1.67</v>
+      </c>
+      <c r="AJ200">
+        <v>2.1</v>
+      </c>
+      <c r="AK200">
+        <v>1.34</v>
+      </c>
+      <c r="AL200">
+        <v>1.28</v>
+      </c>
+      <c r="AM200">
+        <v>1.66</v>
+      </c>
+      <c r="AN200">
+        <v>2.2</v>
+      </c>
+      <c r="AO200">
+        <v>1.55</v>
+      </c>
+      <c r="AP200">
+        <v>2.27</v>
+      </c>
+      <c r="AQ200">
+        <v>1.42</v>
+      </c>
+      <c r="AR200">
+        <v>1.47</v>
+      </c>
+      <c r="AS200">
+        <v>1.18</v>
+      </c>
+      <c r="AT200">
+        <v>2.65</v>
+      </c>
+      <c r="AU200">
+        <v>9</v>
+      </c>
+      <c r="AV200">
+        <v>4</v>
+      </c>
+      <c r="AW200">
+        <v>5</v>
+      </c>
+      <c r="AX200">
+        <v>7</v>
+      </c>
+      <c r="AY200">
+        <v>18</v>
+      </c>
+      <c r="AZ200">
+        <v>12</v>
+      </c>
+      <c r="BA200">
+        <v>3</v>
+      </c>
+      <c r="BB200">
+        <v>7</v>
+      </c>
+      <c r="BC200">
+        <v>10</v>
+      </c>
+      <c r="BD200">
+        <v>1.58</v>
+      </c>
+      <c r="BE200">
+        <v>6.4</v>
+      </c>
+      <c r="BF200">
+        <v>2.65</v>
+      </c>
+      <c r="BG200">
+        <v>1.44</v>
+      </c>
+      <c r="BH200">
+        <v>2.55</v>
+      </c>
+      <c r="BI200">
+        <v>1.73</v>
+      </c>
+      <c r="BJ200">
+        <v>1.96</v>
+      </c>
+      <c r="BK200">
+        <v>2.18</v>
+      </c>
+      <c r="BL200">
+        <v>1.58</v>
+      </c>
+      <c r="BM200">
+        <v>2.88</v>
+      </c>
+      <c r="BN200">
+        <v>1.35</v>
+      </c>
+      <c r="BO200">
+        <v>3.8</v>
+      </c>
+      <c r="BP200">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="347">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -703,6 +703,12 @@
     <t>['15', '33', '57', '76', '90+2']</t>
   </si>
   <si>
+    <t>['67', '90+5']</t>
+  </si>
+  <si>
+    <t>['25', '40', '75', '80', '83', '89']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1043,6 +1049,12 @@
   </si>
   <si>
     <t>['28', '49']</t>
+  </si>
+  <si>
+    <t>['9', '45']</t>
+  </si>
+  <si>
+    <t>['55', '61', '70']</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1660,7 +1672,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1738,10 +1750,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1947,7 +1959,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ3">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2072,7 +2084,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2278,7 +2290,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2484,7 +2496,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2690,7 +2702,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2768,10 +2780,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2974,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>1.64</v>
@@ -3102,7 +3114,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3180,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ9">
         <v>2.18</v>
@@ -3308,7 +3320,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3595,7 +3607,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ11">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3720,7 +3732,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3926,7 +3938,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4004,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ13">
         <v>1.82</v>
@@ -4132,7 +4144,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4338,7 +4350,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4750,7 +4762,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5037,7 +5049,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ18">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5368,7 +5380,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5446,7 +5458,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ20">
         <v>0.64</v>
@@ -5655,7 +5667,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ21">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR21">
         <v>1.16</v>
@@ -5780,7 +5792,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5861,7 +5873,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR22">
         <v>2.26</v>
@@ -6067,7 +6079,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ23">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR23">
         <v>1.5</v>
@@ -6192,7 +6204,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6270,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ24">
         <v>1.64</v>
@@ -6398,7 +6410,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6476,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ25">
         <v>1.5</v>
@@ -6604,7 +6616,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6682,7 +6694,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ26">
         <v>2.18</v>
@@ -6810,7 +6822,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6891,7 +6903,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ27">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.22</v>
@@ -7016,7 +7028,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7094,7 +7106,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ28">
         <v>1.42</v>
@@ -7222,7 +7234,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7428,7 +7440,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7634,7 +7646,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7840,7 +7852,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8046,7 +8058,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8458,7 +8470,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9076,7 +9088,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9154,10 +9166,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR38">
         <v>1.73</v>
@@ -9360,10 +9372,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9488,7 +9500,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9566,7 +9578,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ40">
         <v>0.64</v>
@@ -9694,7 +9706,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9772,7 +9784,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ41">
         <v>1.5</v>
@@ -9900,7 +9912,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -9981,7 +9993,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ42">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.82</v>
@@ -10187,7 +10199,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ43">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR43">
         <v>1.14</v>
@@ -10312,7 +10324,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10393,7 +10405,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ44">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10518,7 +10530,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10596,7 +10608,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ45">
         <v>1.64</v>
@@ -10724,7 +10736,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11136,7 +11148,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11548,7 +11560,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11754,7 +11766,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11960,7 +11972,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12372,7 +12384,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12578,7 +12590,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12784,7 +12796,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12862,10 +12874,10 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.91</v>
@@ -12990,7 +13002,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13277,7 +13289,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13402,7 +13414,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13483,7 +13495,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ59">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR59">
         <v>1.71</v>
@@ -13608,7 +13620,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13686,7 +13698,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ60">
         <v>1.33</v>
@@ -13814,7 +13826,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13892,7 +13904,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ61">
         <v>0.64</v>
@@ -14226,7 +14238,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14304,10 +14316,10 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ63">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR63">
         <v>1.07</v>
@@ -14432,7 +14444,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14510,7 +14522,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ64">
         <v>1.42</v>
@@ -14638,7 +14650,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14716,7 +14728,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ65">
         <v>1.27</v>
@@ -14844,7 +14856,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15256,7 +15268,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15668,7 +15680,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15749,7 +15761,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ70">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR70">
         <v>0.6899999999999999</v>
@@ -15874,7 +15886,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16779,7 +16791,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ75">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR75">
         <v>1.82</v>
@@ -16904,7 +16916,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16985,7 +16997,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ76">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17110,7 +17122,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17191,7 +17203,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.67</v>
@@ -17394,7 +17406,7 @@
         <v>1.5</v>
       </c>
       <c r="AP78">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ78">
         <v>0.64</v>
@@ -17600,10 +17612,10 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ79">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR79">
         <v>1.14</v>
@@ -17806,7 +17818,7 @@
         <v>2.5</v>
       </c>
       <c r="AP80">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
         <v>1.33</v>
@@ -18218,7 +18230,7 @@
         <v>2.5</v>
       </c>
       <c r="AP82">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ82">
         <v>1.42</v>
@@ -18552,7 +18564,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18964,7 +18976,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19042,7 +19054,7 @@
         <v>0.25</v>
       </c>
       <c r="AP86">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ86">
         <v>0.73</v>
@@ -19170,7 +19182,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19251,7 +19263,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ87">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -19788,7 +19800,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19994,7 +20006,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20281,7 +20293,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ92">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR92">
         <v>1.83</v>
@@ -20406,7 +20418,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20693,7 +20705,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ94">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR94">
         <v>2.18</v>
@@ -20896,7 +20908,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
         <v>1.17</v>
@@ -21024,7 +21036,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21308,10 +21320,10 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ97">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR97">
         <v>1.25</v>
@@ -21642,7 +21654,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21720,7 +21732,7 @@
         <v>2</v>
       </c>
       <c r="AP99">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ99">
         <v>1.55</v>
@@ -21926,10 +21938,10 @@
         <v>1.2</v>
       </c>
       <c r="AP100">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -22054,7 +22066,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22260,7 +22272,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22341,7 +22353,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ102">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR102">
         <v>1.35</v>
@@ -22466,7 +22478,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22753,7 +22765,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR104">
         <v>1.72</v>
@@ -22878,7 +22890,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23084,7 +23096,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23290,7 +23302,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23368,7 +23380,7 @@
         <v>2.67</v>
       </c>
       <c r="AP107">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ107">
         <v>2.18</v>
@@ -23574,7 +23586,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ108">
         <v>0.91</v>
@@ -23702,7 +23714,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23908,7 +23920,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23989,7 +24001,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ110">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR110">
         <v>2.1</v>
@@ -24114,7 +24126,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24192,7 +24204,7 @@
         <v>1.67</v>
       </c>
       <c r="AP111">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ111">
         <v>1.33</v>
@@ -24320,7 +24332,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24526,7 +24538,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24607,7 +24619,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ113">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR113">
         <v>1.55</v>
@@ -24732,7 +24744,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25019,7 +25031,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ115">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>2.31</v>
@@ -25144,7 +25156,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25222,7 +25234,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ116">
         <v>0.73</v>
@@ -25350,7 +25362,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25428,7 +25440,7 @@
         <v>2.2</v>
       </c>
       <c r="AP117">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ117">
         <v>1.55</v>
@@ -25762,7 +25774,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25968,7 +25980,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26049,7 +26061,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ120">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR120">
         <v>1.27</v>
@@ -26174,7 +26186,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26252,7 +26264,7 @@
         <v>2.43</v>
       </c>
       <c r="AP121">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ121">
         <v>2.18</v>
@@ -26380,7 +26392,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26461,7 +26473,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ122">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26664,7 +26676,7 @@
         <v>0.33</v>
       </c>
       <c r="AP123">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ123">
         <v>0.27</v>
@@ -26792,7 +26804,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26998,7 +27010,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27204,7 +27216,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27282,7 +27294,7 @@
         <v>0.5</v>
       </c>
       <c r="AP126">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ126">
         <v>0.91</v>
@@ -27410,7 +27422,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27616,7 +27628,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27822,7 +27834,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27900,10 +27912,10 @@
         <v>0.33</v>
       </c>
       <c r="AP129">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ129">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -28028,7 +28040,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28109,7 +28121,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ130">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR130">
         <v>1.98</v>
@@ -28234,7 +28246,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28440,7 +28452,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28646,7 +28658,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28727,7 +28739,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ133">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR133">
         <v>1.24</v>
@@ -29264,7 +29276,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29342,7 +29354,7 @@
         <v>0.33</v>
       </c>
       <c r="AP136">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ136">
         <v>0.73</v>
@@ -29470,7 +29482,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29548,10 +29560,10 @@
         <v>2.14</v>
       </c>
       <c r="AP137">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ137">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR137">
         <v>1.63</v>
@@ -29963,7 +29975,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ139">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR139">
         <v>1.27</v>
@@ -30088,7 +30100,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30372,10 +30384,10 @@
         <v>0.13</v>
       </c>
       <c r="AP141">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ141">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR141">
         <v>1.48</v>
@@ -30500,7 +30512,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30784,7 +30796,7 @@
         <v>2.13</v>
       </c>
       <c r="AP143">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ143">
         <v>2.18</v>
@@ -30912,7 +30924,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31118,7 +31130,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31324,7 +31336,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31402,7 +31414,7 @@
         <v>0.71</v>
       </c>
       <c r="AP146">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ146">
         <v>0.73</v>
@@ -31814,7 +31826,7 @@
         <v>1.14</v>
       </c>
       <c r="AP148">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ148">
         <v>1.27</v>
@@ -32229,7 +32241,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ150">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR150">
         <v>1.25</v>
@@ -32354,7 +32366,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32766,7 +32778,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32972,7 +32984,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33053,7 +33065,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ154">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33384,7 +33396,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33462,7 +33474,7 @@
         <v>0.5</v>
       </c>
       <c r="AP156">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ156">
         <v>0.91</v>
@@ -33590,7 +33602,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33796,7 +33808,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -33877,7 +33889,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ158">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>1.38</v>
@@ -34208,7 +34220,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34414,7 +34426,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34620,7 +34632,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34826,7 +34838,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34907,7 +34919,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ163">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR163">
         <v>1.3</v>
@@ -35032,7 +35044,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35110,7 +35122,7 @@
         <v>0.25</v>
       </c>
       <c r="AP164">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ164">
         <v>0.27</v>
@@ -35316,7 +35328,7 @@
         <v>1.5</v>
       </c>
       <c r="AP165">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ165">
         <v>1.5</v>
@@ -35650,7 +35662,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35856,7 +35868,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -35934,7 +35946,7 @@
         <v>1.78</v>
       </c>
       <c r="AP168">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ168">
         <v>1.42</v>
@@ -36062,7 +36074,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36143,7 +36155,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ169">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR169">
         <v>1.49</v>
@@ -36346,10 +36358,10 @@
         <v>0.11</v>
       </c>
       <c r="AP170">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ170">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR170">
         <v>1.47</v>
@@ -36474,7 +36486,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36761,7 +36773,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ172">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR172">
         <v>1.31</v>
@@ -37092,7 +37104,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37298,7 +37310,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37504,7 +37516,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37916,7 +37928,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -37997,7 +38009,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ178">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR178">
         <v>1.36</v>
@@ -38328,7 +38340,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38534,7 +38546,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -39024,10 +39036,10 @@
         <v>2.11</v>
       </c>
       <c r="AP183">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ183">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR183">
         <v>1.45</v>
@@ -39152,7 +39164,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39230,7 +39242,7 @@
         <v>1.33</v>
       </c>
       <c r="AP184">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ184">
         <v>1.5</v>
@@ -39358,7 +39370,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39439,7 +39451,7 @@
         <v>1</v>
       </c>
       <c r="AQ185">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR185">
         <v>1.84</v>
@@ -39848,10 +39860,10 @@
         <v>0.9</v>
       </c>
       <c r="AP187">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ187">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR187">
         <v>1.47</v>
@@ -39976,7 +39988,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40054,7 +40066,7 @@
         <v>1.7</v>
       </c>
       <c r="AP188">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ188">
         <v>1.64</v>
@@ -40182,7 +40194,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40260,10 +40272,10 @@
         <v>0.1</v>
       </c>
       <c r="AP189">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ189">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR189">
         <v>1.24</v>
@@ -40469,7 +40481,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ190">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR190">
         <v>1.45</v>
@@ -40800,7 +40812,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -41006,7 +41018,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41418,7 +41430,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41830,7 +41842,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42242,7 +42254,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42605,6 +42617,1036 @@
       </c>
       <c r="BP200">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7492020</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>81</v>
+      </c>
+      <c r="H201" t="s">
+        <v>85</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>2</v>
+      </c>
+      <c r="K201">
+        <v>2</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>2</v>
+      </c>
+      <c r="N201">
+        <v>2</v>
+      </c>
+      <c r="O201" t="s">
+        <v>96</v>
+      </c>
+      <c r="P201" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q201">
+        <v>8.5</v>
+      </c>
+      <c r="R201">
+        <v>2.75</v>
+      </c>
+      <c r="S201">
+        <v>1.67</v>
+      </c>
+      <c r="T201">
+        <v>1.22</v>
+      </c>
+      <c r="U201">
+        <v>4</v>
+      </c>
+      <c r="V201">
+        <v>2.1</v>
+      </c>
+      <c r="W201">
+        <v>1.67</v>
+      </c>
+      <c r="X201">
+        <v>4.5</v>
+      </c>
+      <c r="Y201">
+        <v>1.18</v>
+      </c>
+      <c r="Z201">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA201">
+        <v>6.5</v>
+      </c>
+      <c r="AB201">
+        <v>1.29</v>
+      </c>
+      <c r="AC201">
+        <v>1.01</v>
+      </c>
+      <c r="AD201">
+        <v>26</v>
+      </c>
+      <c r="AE201">
+        <v>1.13</v>
+      </c>
+      <c r="AF201">
+        <v>6</v>
+      </c>
+      <c r="AG201">
+        <v>1.38</v>
+      </c>
+      <c r="AH201">
+        <v>2.9</v>
+      </c>
+      <c r="AI201">
+        <v>1.91</v>
+      </c>
+      <c r="AJ201">
+        <v>1.91</v>
+      </c>
+      <c r="AK201">
+        <v>4.06</v>
+      </c>
+      <c r="AL201">
+        <v>1.14</v>
+      </c>
+      <c r="AM201">
+        <v>1.07</v>
+      </c>
+      <c r="AN201">
+        <v>0.91</v>
+      </c>
+      <c r="AO201">
+        <v>2</v>
+      </c>
+      <c r="AP201">
+        <v>0.83</v>
+      </c>
+      <c r="AQ201">
+        <v>2.09</v>
+      </c>
+      <c r="AR201">
+        <v>1.24</v>
+      </c>
+      <c r="AS201">
+        <v>1.49</v>
+      </c>
+      <c r="AT201">
+        <v>2.73</v>
+      </c>
+      <c r="AU201">
+        <v>4</v>
+      </c>
+      <c r="AV201">
+        <v>9</v>
+      </c>
+      <c r="AW201">
+        <v>1</v>
+      </c>
+      <c r="AX201">
+        <v>10</v>
+      </c>
+      <c r="AY201">
+        <v>5</v>
+      </c>
+      <c r="AZ201">
+        <v>20</v>
+      </c>
+      <c r="BA201">
+        <v>5</v>
+      </c>
+      <c r="BB201">
+        <v>11</v>
+      </c>
+      <c r="BC201">
+        <v>16</v>
+      </c>
+      <c r="BD201">
+        <v>4.9</v>
+      </c>
+      <c r="BE201">
+        <v>9</v>
+      </c>
+      <c r="BF201">
+        <v>1.19</v>
+      </c>
+      <c r="BG201">
+        <v>1.22</v>
+      </c>
+      <c r="BH201">
+        <v>3.7</v>
+      </c>
+      <c r="BI201">
+        <v>1.41</v>
+      </c>
+      <c r="BJ201">
+        <v>2.65</v>
+      </c>
+      <c r="BK201">
+        <v>1.65</v>
+      </c>
+      <c r="BL201">
+        <v>2.07</v>
+      </c>
+      <c r="BM201">
+        <v>2.02</v>
+      </c>
+      <c r="BN201">
+        <v>1.68</v>
+      </c>
+      <c r="BO201">
+        <v>2.55</v>
+      </c>
+      <c r="BP201">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7492019</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>70</v>
+      </c>
+      <c r="H202" t="s">
+        <v>74</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="M202">
+        <v>3</v>
+      </c>
+      <c r="N202">
+        <v>3</v>
+      </c>
+      <c r="O202" t="s">
+        <v>96</v>
+      </c>
+      <c r="P202" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q202">
+        <v>2.5</v>
+      </c>
+      <c r="R202">
+        <v>2.3</v>
+      </c>
+      <c r="S202">
+        <v>4</v>
+      </c>
+      <c r="T202">
+        <v>1.33</v>
+      </c>
+      <c r="U202">
+        <v>3.25</v>
+      </c>
+      <c r="V202">
+        <v>2.5</v>
+      </c>
+      <c r="W202">
+        <v>1.5</v>
+      </c>
+      <c r="X202">
+        <v>6.5</v>
+      </c>
+      <c r="Y202">
+        <v>1.11</v>
+      </c>
+      <c r="Z202">
+        <v>1.93</v>
+      </c>
+      <c r="AA202">
+        <v>3.8</v>
+      </c>
+      <c r="AB202">
+        <v>3.93</v>
+      </c>
+      <c r="AC202">
+        <v>1.03</v>
+      </c>
+      <c r="AD202">
+        <v>15</v>
+      </c>
+      <c r="AE202">
+        <v>1.22</v>
+      </c>
+      <c r="AF202">
+        <v>4.33</v>
+      </c>
+      <c r="AG202">
+        <v>1.65</v>
+      </c>
+      <c r="AH202">
+        <v>2.15</v>
+      </c>
+      <c r="AI202">
+        <v>1.62</v>
+      </c>
+      <c r="AJ202">
+        <v>2.2</v>
+      </c>
+      <c r="AK202">
+        <v>1.27</v>
+      </c>
+      <c r="AL202">
+        <v>1.3</v>
+      </c>
+      <c r="AM202">
+        <v>1.96</v>
+      </c>
+      <c r="AN202">
+        <v>1.82</v>
+      </c>
+      <c r="AO202">
+        <v>0.91</v>
+      </c>
+      <c r="AP202">
+        <v>1.67</v>
+      </c>
+      <c r="AQ202">
+        <v>1.08</v>
+      </c>
+      <c r="AR202">
+        <v>1.47</v>
+      </c>
+      <c r="AS202">
+        <v>0.99</v>
+      </c>
+      <c r="AT202">
+        <v>2.46</v>
+      </c>
+      <c r="AU202">
+        <v>6</v>
+      </c>
+      <c r="AV202">
+        <v>5</v>
+      </c>
+      <c r="AW202">
+        <v>3</v>
+      </c>
+      <c r="AX202">
+        <v>13</v>
+      </c>
+      <c r="AY202">
+        <v>10</v>
+      </c>
+      <c r="AZ202">
+        <v>20</v>
+      </c>
+      <c r="BA202">
+        <v>2</v>
+      </c>
+      <c r="BB202">
+        <v>4</v>
+      </c>
+      <c r="BC202">
+        <v>6</v>
+      </c>
+      <c r="BD202">
+        <v>1.54</v>
+      </c>
+      <c r="BE202">
+        <v>6.75</v>
+      </c>
+      <c r="BF202">
+        <v>2.7</v>
+      </c>
+      <c r="BG202">
+        <v>1.24</v>
+      </c>
+      <c r="BH202">
+        <v>3.55</v>
+      </c>
+      <c r="BI202">
+        <v>1.43</v>
+      </c>
+      <c r="BJ202">
+        <v>2.6</v>
+      </c>
+      <c r="BK202">
+        <v>1.71</v>
+      </c>
+      <c r="BL202">
+        <v>2</v>
+      </c>
+      <c r="BM202">
+        <v>2.08</v>
+      </c>
+      <c r="BN202">
+        <v>1.65</v>
+      </c>
+      <c r="BO202">
+        <v>2.65</v>
+      </c>
+      <c r="BP202">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7492018</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>75</v>
+      </c>
+      <c r="H203" t="s">
+        <v>78</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>2</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>2</v>
+      </c>
+      <c r="O203" t="s">
+        <v>229</v>
+      </c>
+      <c r="P203" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q203">
+        <v>2.5</v>
+      </c>
+      <c r="R203">
+        <v>2.1</v>
+      </c>
+      <c r="S203">
+        <v>5</v>
+      </c>
+      <c r="T203">
+        <v>1.44</v>
+      </c>
+      <c r="U203">
+        <v>2.63</v>
+      </c>
+      <c r="V203">
+        <v>3.25</v>
+      </c>
+      <c r="W203">
+        <v>1.33</v>
+      </c>
+      <c r="X203">
+        <v>10</v>
+      </c>
+      <c r="Y203">
+        <v>1.06</v>
+      </c>
+      <c r="Z203">
+        <v>1.85</v>
+      </c>
+      <c r="AA203">
+        <v>3.63</v>
+      </c>
+      <c r="AB203">
+        <v>4.6</v>
+      </c>
+      <c r="AC203">
+        <v>1.07</v>
+      </c>
+      <c r="AD203">
+        <v>10</v>
+      </c>
+      <c r="AE203">
+        <v>1.38</v>
+      </c>
+      <c r="AF203">
+        <v>3.1</v>
+      </c>
+      <c r="AG203">
+        <v>1.91</v>
+      </c>
+      <c r="AH203">
+        <v>1.83</v>
+      </c>
+      <c r="AI203">
+        <v>2</v>
+      </c>
+      <c r="AJ203">
+        <v>1.75</v>
+      </c>
+      <c r="AK203">
+        <v>1.22</v>
+      </c>
+      <c r="AL203">
+        <v>1.31</v>
+      </c>
+      <c r="AM203">
+        <v>2.07</v>
+      </c>
+      <c r="AN203">
+        <v>1.64</v>
+      </c>
+      <c r="AO203">
+        <v>1.09</v>
+      </c>
+      <c r="AP203">
+        <v>1.75</v>
+      </c>
+      <c r="AQ203">
+        <v>1</v>
+      </c>
+      <c r="AR203">
+        <v>1.46</v>
+      </c>
+      <c r="AS203">
+        <v>1.16</v>
+      </c>
+      <c r="AT203">
+        <v>2.62</v>
+      </c>
+      <c r="AU203">
+        <v>6</v>
+      </c>
+      <c r="AV203">
+        <v>0</v>
+      </c>
+      <c r="AW203">
+        <v>4</v>
+      </c>
+      <c r="AX203">
+        <v>13</v>
+      </c>
+      <c r="AY203">
+        <v>12</v>
+      </c>
+      <c r="AZ203">
+        <v>16</v>
+      </c>
+      <c r="BA203">
+        <v>6</v>
+      </c>
+      <c r="BB203">
+        <v>5</v>
+      </c>
+      <c r="BC203">
+        <v>11</v>
+      </c>
+      <c r="BD203">
+        <v>1.44</v>
+      </c>
+      <c r="BE203">
+        <v>6.75</v>
+      </c>
+      <c r="BF203">
+        <v>3.15</v>
+      </c>
+      <c r="BG203">
+        <v>1.3</v>
+      </c>
+      <c r="BH203">
+        <v>3.05</v>
+      </c>
+      <c r="BI203">
+        <v>1.52</v>
+      </c>
+      <c r="BJ203">
+        <v>2.32</v>
+      </c>
+      <c r="BK203">
+        <v>1.86</v>
+      </c>
+      <c r="BL203">
+        <v>1.82</v>
+      </c>
+      <c r="BM203">
+        <v>2.32</v>
+      </c>
+      <c r="BN203">
+        <v>1.52</v>
+      </c>
+      <c r="BO203">
+        <v>2.95</v>
+      </c>
+      <c r="BP203">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7492017</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>77</v>
+      </c>
+      <c r="H204" t="s">
+        <v>83</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>2</v>
+      </c>
+      <c r="O204" t="s">
+        <v>218</v>
+      </c>
+      <c r="P204" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q204">
+        <v>2.1</v>
+      </c>
+      <c r="R204">
+        <v>2.4</v>
+      </c>
+      <c r="S204">
+        <v>5.5</v>
+      </c>
+      <c r="T204">
+        <v>1.3</v>
+      </c>
+      <c r="U204">
+        <v>3.4</v>
+      </c>
+      <c r="V204">
+        <v>2.38</v>
+      </c>
+      <c r="W204">
+        <v>1.53</v>
+      </c>
+      <c r="X204">
+        <v>6</v>
+      </c>
+      <c r="Y204">
+        <v>1.13</v>
+      </c>
+      <c r="Z204">
+        <v>1.54</v>
+      </c>
+      <c r="AA204">
+        <v>4.6</v>
+      </c>
+      <c r="AB204">
+        <v>6</v>
+      </c>
+      <c r="AC204">
+        <v>1.02</v>
+      </c>
+      <c r="AD204">
+        <v>17</v>
+      </c>
+      <c r="AE204">
+        <v>1.19</v>
+      </c>
+      <c r="AF204">
+        <v>4.75</v>
+      </c>
+      <c r="AG204">
+        <v>1.57</v>
+      </c>
+      <c r="AH204">
+        <v>2.25</v>
+      </c>
+      <c r="AI204">
+        <v>1.7</v>
+      </c>
+      <c r="AJ204">
+        <v>2.05</v>
+      </c>
+      <c r="AK204">
+        <v>1.17</v>
+      </c>
+      <c r="AL204">
+        <v>1.23</v>
+      </c>
+      <c r="AM204">
+        <v>2.55</v>
+      </c>
+      <c r="AN204">
+        <v>1.18</v>
+      </c>
+      <c r="AO204">
+        <v>0.18</v>
+      </c>
+      <c r="AP204">
+        <v>1.17</v>
+      </c>
+      <c r="AQ204">
+        <v>0.25</v>
+      </c>
+      <c r="AR204">
+        <v>1.47</v>
+      </c>
+      <c r="AS204">
+        <v>1.25</v>
+      </c>
+      <c r="AT204">
+        <v>2.72</v>
+      </c>
+      <c r="AU204">
+        <v>7</v>
+      </c>
+      <c r="AV204">
+        <v>6</v>
+      </c>
+      <c r="AW204">
+        <v>7</v>
+      </c>
+      <c r="AX204">
+        <v>6</v>
+      </c>
+      <c r="AY204">
+        <v>16</v>
+      </c>
+      <c r="AZ204">
+        <v>14</v>
+      </c>
+      <c r="BA204">
+        <v>3</v>
+      </c>
+      <c r="BB204">
+        <v>5</v>
+      </c>
+      <c r="BC204">
+        <v>8</v>
+      </c>
+      <c r="BD204">
+        <v>1.4</v>
+      </c>
+      <c r="BE204">
+        <v>7</v>
+      </c>
+      <c r="BF204">
+        <v>3.3</v>
+      </c>
+      <c r="BG204">
+        <v>1.28</v>
+      </c>
+      <c r="BH204">
+        <v>3.2</v>
+      </c>
+      <c r="BI204">
+        <v>1.49</v>
+      </c>
+      <c r="BJ204">
+        <v>2.4</v>
+      </c>
+      <c r="BK204">
+        <v>1.77</v>
+      </c>
+      <c r="BL204">
+        <v>1.91</v>
+      </c>
+      <c r="BM204">
+        <v>2.2</v>
+      </c>
+      <c r="BN204">
+        <v>1.58</v>
+      </c>
+      <c r="BO204">
+        <v>2.8</v>
+      </c>
+      <c r="BP204">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7492014</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45710.60416666666</v>
+      </c>
+      <c r="F205">
+        <v>23</v>
+      </c>
+      <c r="G205" t="s">
+        <v>76</v>
+      </c>
+      <c r="H205" t="s">
+        <v>79</v>
+      </c>
+      <c r="I205">
+        <v>2</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>2</v>
+      </c>
+      <c r="L205">
+        <v>6</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>6</v>
+      </c>
+      <c r="O205" t="s">
+        <v>230</v>
+      </c>
+      <c r="P205" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q205">
+        <v>2</v>
+      </c>
+      <c r="R205">
+        <v>2.5</v>
+      </c>
+      <c r="S205">
+        <v>5.5</v>
+      </c>
+      <c r="T205">
+        <v>1.29</v>
+      </c>
+      <c r="U205">
+        <v>3.5</v>
+      </c>
+      <c r="V205">
+        <v>2.25</v>
+      </c>
+      <c r="W205">
+        <v>1.57</v>
+      </c>
+      <c r="X205">
+        <v>5.5</v>
+      </c>
+      <c r="Y205">
+        <v>1.14</v>
+      </c>
+      <c r="Z205">
+        <v>1.61</v>
+      </c>
+      <c r="AA205">
+        <v>4.4</v>
+      </c>
+      <c r="AB205">
+        <v>5.4</v>
+      </c>
+      <c r="AC205">
+        <v>1.02</v>
+      </c>
+      <c r="AD205">
+        <v>19</v>
+      </c>
+      <c r="AE205">
+        <v>1.19</v>
+      </c>
+      <c r="AF205">
+        <v>4.75</v>
+      </c>
+      <c r="AG205">
+        <v>1.67</v>
+      </c>
+      <c r="AH205">
+        <v>2.1</v>
+      </c>
+      <c r="AI205">
+        <v>1.67</v>
+      </c>
+      <c r="AJ205">
+        <v>2.1</v>
+      </c>
+      <c r="AK205">
+        <v>1.18</v>
+      </c>
+      <c r="AL205">
+        <v>1.23</v>
+      </c>
+      <c r="AM205">
+        <v>2.5</v>
+      </c>
+      <c r="AN205">
+        <v>1.91</v>
+      </c>
+      <c r="AO205">
+        <v>0.73</v>
+      </c>
+      <c r="AP205">
+        <v>2</v>
+      </c>
+      <c r="AQ205">
+        <v>0.67</v>
+      </c>
+      <c r="AR205">
+        <v>1.58</v>
+      </c>
+      <c r="AS205">
+        <v>1.31</v>
+      </c>
+      <c r="AT205">
+        <v>2.89</v>
+      </c>
+      <c r="AU205">
+        <v>10</v>
+      </c>
+      <c r="AV205">
+        <v>2</v>
+      </c>
+      <c r="AW205">
+        <v>15</v>
+      </c>
+      <c r="AX205">
+        <v>5</v>
+      </c>
+      <c r="AY205">
+        <v>25</v>
+      </c>
+      <c r="AZ205">
+        <v>8</v>
+      </c>
+      <c r="BA205">
+        <v>5</v>
+      </c>
+      <c r="BB205">
+        <v>3</v>
+      </c>
+      <c r="BC205">
+        <v>8</v>
+      </c>
+      <c r="BD205">
+        <v>1.42</v>
+      </c>
+      <c r="BE205">
+        <v>7</v>
+      </c>
+      <c r="BF205">
+        <v>3.2</v>
+      </c>
+      <c r="BG205">
+        <v>1.24</v>
+      </c>
+      <c r="BH205">
+        <v>3.55</v>
+      </c>
+      <c r="BI205">
+        <v>1.41</v>
+      </c>
+      <c r="BJ205">
+        <v>2.63</v>
+      </c>
+      <c r="BK205">
+        <v>1.7</v>
+      </c>
+      <c r="BL205">
+        <v>2</v>
+      </c>
+      <c r="BM205">
+        <v>2.08</v>
+      </c>
+      <c r="BN205">
+        <v>1.65</v>
+      </c>
+      <c r="BO205">
+        <v>2.6</v>
+      </c>
+      <c r="BP205">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="351">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -709,6 +709,15 @@
     <t>['25', '40', '75', '80', '83', '89']</t>
   </si>
   <si>
+    <t>['45+2', '64']</t>
+  </si>
+  <si>
+    <t>['45+2', '61', '83', '90+2']</t>
+  </si>
+  <si>
+    <t>['74']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -719,9 +728,6 @@
   </si>
   <si>
     <t>['12', '58']</t>
-  </si>
-  <si>
-    <t>['74']</t>
   </si>
   <si>
     <t>['19', '65', '82']</t>
@@ -1055,6 +1061,12 @@
   </si>
   <si>
     <t>['55', '61', '70']</t>
+  </si>
+  <si>
+    <t>['6', '13']</t>
+  </si>
+  <si>
+    <t>['9']</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1672,7 +1684,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1956,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0.25</v>
@@ -2084,7 +2096,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2290,7 +2302,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2371,7 +2383,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2496,7 +2508,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2702,7 +2714,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2989,7 +3001,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3114,7 +3126,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3320,7 +3332,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3401,7 +3413,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ10">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3732,7 +3744,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3938,7 +3950,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4144,7 +4156,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4350,7 +4362,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4762,7 +4774,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5252,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ19">
         <v>1.17</v>
@@ -5380,7 +5392,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5461,7 +5473,7 @@
         <v>2</v>
       </c>
       <c r="AQ20">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR20">
         <v>1.89</v>
@@ -5664,7 +5676,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
         <v>0.67</v>
@@ -5792,7 +5804,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6204,7 +6216,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6285,7 +6297,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ24">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
         <v>1.03</v>
@@ -6410,7 +6422,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6491,7 +6503,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ25">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR25">
         <v>1.46</v>
@@ -6616,7 +6628,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6822,7 +6834,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -7028,7 +7040,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7234,7 +7246,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7440,7 +7452,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7646,7 +7658,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7852,7 +7864,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8058,7 +8070,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8470,7 +8482,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9088,7 +9100,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9500,7 +9512,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9581,7 +9593,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ40">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9706,7 +9718,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9787,7 +9799,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ41">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR41">
         <v>1.28</v>
@@ -9912,7 +9924,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10196,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>1.08</v>
@@ -10324,7 +10336,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10402,7 +10414,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ44">
         <v>2.09</v>
@@ -10530,7 +10542,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10611,7 +10623,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ45">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR45">
         <v>1</v>
@@ -10736,7 +10748,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11148,7 +11160,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11560,7 +11572,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11766,7 +11778,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11972,7 +11984,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12384,7 +12396,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12590,7 +12602,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12796,7 +12808,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -13002,7 +13014,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13083,7 +13095,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ57">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR57">
         <v>2.44</v>
@@ -13414,7 +13426,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13620,7 +13632,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13826,7 +13838,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13907,7 +13919,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ61">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR61">
         <v>1.33</v>
@@ -14110,10 +14122,10 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ62">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR62">
         <v>1.47</v>
@@ -14238,7 +14250,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14444,7 +14456,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14650,7 +14662,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14856,7 +14868,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15268,7 +15280,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15346,7 +15358,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
         <v>1.17</v>
@@ -15680,7 +15692,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15886,7 +15898,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16173,7 +16185,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ72">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16585,7 +16597,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ74">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR74">
         <v>2.41</v>
@@ -16788,7 +16800,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ75">
         <v>0.67</v>
@@ -16916,7 +16928,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17122,7 +17134,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17409,7 +17421,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ78">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -18564,7 +18576,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18976,7 +18988,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19182,7 +19194,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19466,7 +19478,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
         <v>1.27</v>
@@ -19800,7 +19812,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19881,7 +19893,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ90">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR90">
         <v>2.13</v>
@@ -20006,7 +20018,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20290,7 +20302,7 @@
         <v>0.25</v>
       </c>
       <c r="AP92">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ92">
         <v>1.08</v>
@@ -20418,7 +20430,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20499,7 +20511,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ93">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR93">
         <v>2.3</v>
@@ -21036,7 +21048,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21654,7 +21666,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22066,7 +22078,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22272,7 +22284,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22478,7 +22490,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22890,7 +22902,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22968,7 +22980,7 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>1.82</v>
@@ -23096,7 +23108,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23177,7 +23189,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ106">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR106">
         <v>1.1</v>
@@ -23302,7 +23314,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23714,7 +23726,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23795,7 +23807,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ109">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -23920,7 +23932,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24126,7 +24138,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24332,7 +24344,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24538,7 +24550,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24744,7 +24756,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24822,10 +24834,10 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ114">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR114">
         <v>2.04</v>
@@ -25156,7 +25168,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25362,7 +25374,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25774,7 +25786,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25980,7 +25992,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26186,7 +26198,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26392,7 +26404,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26804,7 +26816,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27010,7 +27022,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27091,7 +27103,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ125">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR125">
         <v>1.33</v>
@@ -27216,7 +27228,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27422,7 +27434,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27500,10 +27512,10 @@
         <v>1.86</v>
       </c>
       <c r="AP127">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ127">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR127">
         <v>1.42</v>
@@ -27628,7 +27640,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27706,7 +27718,7 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ128">
         <v>1.33</v>
@@ -27834,7 +27846,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28040,7 +28052,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28246,7 +28258,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28452,7 +28464,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28658,7 +28670,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -29151,7 +29163,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ135">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR135">
         <v>1.23</v>
@@ -29276,7 +29288,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29482,7 +29494,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -30100,7 +30112,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30512,7 +30524,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30593,7 +30605,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ142">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR142">
         <v>1.26</v>
@@ -30924,7 +30936,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31002,7 +31014,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>1.42</v>
@@ -31130,7 +31142,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31211,7 +31223,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ145">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31336,7 +31348,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -32366,7 +32378,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32650,7 +32662,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ152">
         <v>0.91</v>
@@ -32778,7 +32790,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32859,7 +32871,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ153">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR153">
         <v>1.26</v>
@@ -32984,7 +32996,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33396,7 +33408,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33602,7 +33614,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33808,7 +33820,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34220,7 +34232,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34298,7 +34310,7 @@
         <v>2</v>
       </c>
       <c r="AP160">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ160">
         <v>1.82</v>
@@ -34426,7 +34438,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34632,7 +34644,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34838,7 +34850,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -35044,7 +35056,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35331,7 +35343,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ165">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR165">
         <v>1.46</v>
@@ -35537,7 +35549,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ166">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR166">
         <v>1.56</v>
@@ -35662,7 +35674,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35868,7 +35880,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36074,7 +36086,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36152,7 +36164,7 @@
         <v>2.25</v>
       </c>
       <c r="AP169">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ169">
         <v>2.09</v>
@@ -36486,7 +36498,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36567,7 +36579,7 @@
         <v>1</v>
       </c>
       <c r="AQ171">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR171">
         <v>1.74</v>
@@ -37104,7 +37116,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37310,7 +37322,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37388,7 +37400,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ175">
         <v>0.27</v>
@@ -37516,7 +37528,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37928,7 +37940,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38340,7 +38352,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38546,7 +38558,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38830,7 +38842,7 @@
         <v>1.7</v>
       </c>
       <c r="AP182">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ182">
         <v>1.42</v>
@@ -39164,7 +39176,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39245,7 +39257,7 @@
         <v>2</v>
       </c>
       <c r="AQ184">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR184">
         <v>1.55</v>
@@ -39370,7 +39382,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39657,7 +39669,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ186">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR186">
         <v>1.5</v>
@@ -39988,7 +40000,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40069,7 +40081,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ188">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR188">
         <v>1.5</v>
@@ -40194,7 +40206,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40478,7 +40490,7 @@
         <v>1.2</v>
       </c>
       <c r="AP190">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ190">
         <v>1</v>
@@ -40812,7 +40824,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -41018,7 +41030,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41430,7 +41442,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41842,7 +41854,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42254,7 +42266,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42666,7 +42678,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42872,7 +42884,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -43647,6 +43659,624 @@
       </c>
       <c r="BP205">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7492013</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45711.47916666666</v>
+      </c>
+      <c r="F206">
+        <v>23</v>
+      </c>
+      <c r="G206" t="s">
+        <v>71</v>
+      </c>
+      <c r="H206" t="s">
+        <v>86</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>2</v>
+      </c>
+      <c r="K206">
+        <v>3</v>
+      </c>
+      <c r="L206">
+        <v>2</v>
+      </c>
+      <c r="M206">
+        <v>2</v>
+      </c>
+      <c r="N206">
+        <v>4</v>
+      </c>
+      <c r="O206" t="s">
+        <v>231</v>
+      </c>
+      <c r="P206" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q206">
+        <v>1.91</v>
+      </c>
+      <c r="R206">
+        <v>2.63</v>
+      </c>
+      <c r="S206">
+        <v>6</v>
+      </c>
+      <c r="T206">
+        <v>1.25</v>
+      </c>
+      <c r="U206">
+        <v>3.75</v>
+      </c>
+      <c r="V206">
+        <v>2.2</v>
+      </c>
+      <c r="W206">
+        <v>1.62</v>
+      </c>
+      <c r="X206">
+        <v>5</v>
+      </c>
+      <c r="Y206">
+        <v>1.17</v>
+      </c>
+      <c r="Z206">
+        <v>1.43</v>
+      </c>
+      <c r="AA206">
+        <v>5.2</v>
+      </c>
+      <c r="AB206">
+        <v>7</v>
+      </c>
+      <c r="AC206">
+        <v>1.01</v>
+      </c>
+      <c r="AD206">
+        <v>21</v>
+      </c>
+      <c r="AE206">
+        <v>1.16</v>
+      </c>
+      <c r="AF206">
+        <v>5.5</v>
+      </c>
+      <c r="AG206">
+        <v>1.45</v>
+      </c>
+      <c r="AH206">
+        <v>2.63</v>
+      </c>
+      <c r="AI206">
+        <v>1.7</v>
+      </c>
+      <c r="AJ206">
+        <v>2.05</v>
+      </c>
+      <c r="AK206">
+        <v>1.1</v>
+      </c>
+      <c r="AL206">
+        <v>1.17</v>
+      </c>
+      <c r="AM206">
+        <v>2.8</v>
+      </c>
+      <c r="AN206">
+        <v>2.1</v>
+      </c>
+      <c r="AO206">
+        <v>0.64</v>
+      </c>
+      <c r="AP206">
+        <v>2</v>
+      </c>
+      <c r="AQ206">
+        <v>0.67</v>
+      </c>
+      <c r="AR206">
+        <v>1.45</v>
+      </c>
+      <c r="AS206">
+        <v>1.25</v>
+      </c>
+      <c r="AT206">
+        <v>2.7</v>
+      </c>
+      <c r="AU206">
+        <v>7</v>
+      </c>
+      <c r="AV206">
+        <v>3</v>
+      </c>
+      <c r="AW206">
+        <v>11</v>
+      </c>
+      <c r="AX206">
+        <v>2</v>
+      </c>
+      <c r="AY206">
+        <v>23</v>
+      </c>
+      <c r="AZ206">
+        <v>5</v>
+      </c>
+      <c r="BA206">
+        <v>7</v>
+      </c>
+      <c r="BB206">
+        <v>4</v>
+      </c>
+      <c r="BC206">
+        <v>11</v>
+      </c>
+      <c r="BD206">
+        <v>1.33</v>
+      </c>
+      <c r="BE206">
+        <v>7</v>
+      </c>
+      <c r="BF206">
+        <v>3.55</v>
+      </c>
+      <c r="BG206">
+        <v>1.26</v>
+      </c>
+      <c r="BH206">
+        <v>3.4</v>
+      </c>
+      <c r="BI206">
+        <v>1.46</v>
+      </c>
+      <c r="BJ206">
+        <v>2.48</v>
+      </c>
+      <c r="BK206">
+        <v>1.76</v>
+      </c>
+      <c r="BL206">
+        <v>1.93</v>
+      </c>
+      <c r="BM206">
+        <v>2.23</v>
+      </c>
+      <c r="BN206">
+        <v>1.57</v>
+      </c>
+      <c r="BO206">
+        <v>2.8</v>
+      </c>
+      <c r="BP206">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7492012</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45711.5625</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>87</v>
+      </c>
+      <c r="H207" t="s">
+        <v>82</v>
+      </c>
+      <c r="I207">
+        <v>1</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>4</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>4</v>
+      </c>
+      <c r="O207" t="s">
+        <v>232</v>
+      </c>
+      <c r="P207" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q207">
+        <v>1.73</v>
+      </c>
+      <c r="R207">
+        <v>2.88</v>
+      </c>
+      <c r="S207">
+        <v>7</v>
+      </c>
+      <c r="T207">
+        <v>1.2</v>
+      </c>
+      <c r="U207">
+        <v>4.33</v>
+      </c>
+      <c r="V207">
+        <v>1.91</v>
+      </c>
+      <c r="W207">
+        <v>1.8</v>
+      </c>
+      <c r="X207">
+        <v>4</v>
+      </c>
+      <c r="Y207">
+        <v>1.22</v>
+      </c>
+      <c r="Z207">
+        <v>1.26</v>
+      </c>
+      <c r="AA207">
+        <v>7.4</v>
+      </c>
+      <c r="AB207">
+        <v>9.5</v>
+      </c>
+      <c r="AC207">
+        <v>1.01</v>
+      </c>
+      <c r="AD207">
+        <v>29</v>
+      </c>
+      <c r="AE207">
+        <v>1.09</v>
+      </c>
+      <c r="AF207">
+        <v>7.5</v>
+      </c>
+      <c r="AG207">
+        <v>1.28</v>
+      </c>
+      <c r="AH207">
+        <v>3.55</v>
+      </c>
+      <c r="AI207">
+        <v>1.62</v>
+      </c>
+      <c r="AJ207">
+        <v>2.2</v>
+      </c>
+      <c r="AK207">
+        <v>1.07</v>
+      </c>
+      <c r="AL207">
+        <v>1.12</v>
+      </c>
+      <c r="AM207">
+        <v>3.6</v>
+      </c>
+      <c r="AN207">
+        <v>2.82</v>
+      </c>
+      <c r="AO207">
+        <v>1.64</v>
+      </c>
+      <c r="AP207">
+        <v>2.83</v>
+      </c>
+      <c r="AQ207">
+        <v>1.5</v>
+      </c>
+      <c r="AR207">
+        <v>2.52</v>
+      </c>
+      <c r="AS207">
+        <v>1.49</v>
+      </c>
+      <c r="AT207">
+        <v>4.01</v>
+      </c>
+      <c r="AU207">
+        <v>13</v>
+      </c>
+      <c r="AV207">
+        <v>3</v>
+      </c>
+      <c r="AW207">
+        <v>7</v>
+      </c>
+      <c r="AX207">
+        <v>5</v>
+      </c>
+      <c r="AY207">
+        <v>24</v>
+      </c>
+      <c r="AZ207">
+        <v>10</v>
+      </c>
+      <c r="BA207">
+        <v>4</v>
+      </c>
+      <c r="BB207">
+        <v>1</v>
+      </c>
+      <c r="BC207">
+        <v>5</v>
+      </c>
+      <c r="BD207">
+        <v>1.19</v>
+      </c>
+      <c r="BE207">
+        <v>8.5</v>
+      </c>
+      <c r="BF207">
+        <v>5.1</v>
+      </c>
+      <c r="BG207">
+        <v>1.25</v>
+      </c>
+      <c r="BH207">
+        <v>3.4</v>
+      </c>
+      <c r="BI207">
+        <v>1.46</v>
+      </c>
+      <c r="BJ207">
+        <v>2.5</v>
+      </c>
+      <c r="BK207">
+        <v>1.73</v>
+      </c>
+      <c r="BL207">
+        <v>1.97</v>
+      </c>
+      <c r="BM207">
+        <v>2.15</v>
+      </c>
+      <c r="BN207">
+        <v>1.61</v>
+      </c>
+      <c r="BO207">
+        <v>2.7</v>
+      </c>
+      <c r="BP207">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7492015</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45711.64583333334</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>72</v>
+      </c>
+      <c r="H208" t="s">
+        <v>80</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>1</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>2</v>
+      </c>
+      <c r="O208" t="s">
+        <v>233</v>
+      </c>
+      <c r="P208" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q208">
+        <v>3.75</v>
+      </c>
+      <c r="R208">
+        <v>2.5</v>
+      </c>
+      <c r="S208">
+        <v>2.5</v>
+      </c>
+      <c r="T208">
+        <v>1.25</v>
+      </c>
+      <c r="U208">
+        <v>3.75</v>
+      </c>
+      <c r="V208">
+        <v>2.2</v>
+      </c>
+      <c r="W208">
+        <v>1.62</v>
+      </c>
+      <c r="X208">
+        <v>5</v>
+      </c>
+      <c r="Y208">
+        <v>1.17</v>
+      </c>
+      <c r="Z208">
+        <v>3.58</v>
+      </c>
+      <c r="AA208">
+        <v>4</v>
+      </c>
+      <c r="AB208">
+        <v>1.98</v>
+      </c>
+      <c r="AC208">
+        <v>1.01</v>
+      </c>
+      <c r="AD208">
+        <v>21</v>
+      </c>
+      <c r="AE208">
+        <v>1.14</v>
+      </c>
+      <c r="AF208">
+        <v>6</v>
+      </c>
+      <c r="AG208">
+        <v>1.45</v>
+      </c>
+      <c r="AH208">
+        <v>2.63</v>
+      </c>
+      <c r="AI208">
+        <v>1.44</v>
+      </c>
+      <c r="AJ208">
+        <v>2.63</v>
+      </c>
+      <c r="AK208">
+        <v>1.82</v>
+      </c>
+      <c r="AL208">
+        <v>1.24</v>
+      </c>
+      <c r="AM208">
+        <v>1.31</v>
+      </c>
+      <c r="AN208">
+        <v>1</v>
+      </c>
+      <c r="AO208">
+        <v>1.5</v>
+      </c>
+      <c r="AP208">
+        <v>1</v>
+      </c>
+      <c r="AQ208">
+        <v>1.45</v>
+      </c>
+      <c r="AR208">
+        <v>1.84</v>
+      </c>
+      <c r="AS208">
+        <v>1.21</v>
+      </c>
+      <c r="AT208">
+        <v>3.05</v>
+      </c>
+      <c r="AU208">
+        <v>3</v>
+      </c>
+      <c r="AV208">
+        <v>8</v>
+      </c>
+      <c r="AW208">
+        <v>7</v>
+      </c>
+      <c r="AX208">
+        <v>7</v>
+      </c>
+      <c r="AY208">
+        <v>13</v>
+      </c>
+      <c r="AZ208">
+        <v>17</v>
+      </c>
+      <c r="BA208">
+        <v>4</v>
+      </c>
+      <c r="BB208">
+        <v>8</v>
+      </c>
+      <c r="BC208">
+        <v>12</v>
+      </c>
+      <c r="BD208">
+        <v>2.3</v>
+      </c>
+      <c r="BE208">
+        <v>6.5</v>
+      </c>
+      <c r="BF208">
+        <v>1.76</v>
+      </c>
+      <c r="BG208">
+        <v>1.25</v>
+      </c>
+      <c r="BH208">
+        <v>3.45</v>
+      </c>
+      <c r="BI208">
+        <v>1.44</v>
+      </c>
+      <c r="BJ208">
+        <v>2.55</v>
+      </c>
+      <c r="BK208">
+        <v>1.72</v>
+      </c>
+      <c r="BL208">
+        <v>1.98</v>
+      </c>
+      <c r="BM208">
+        <v>2.15</v>
+      </c>
+      <c r="BN208">
+        <v>1.61</v>
+      </c>
+      <c r="BO208">
+        <v>2.7</v>
+      </c>
+      <c r="BP208">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -712,7 +712,7 @@
     <t>['45+2', '64']</t>
   </si>
   <si>
-    <t>['45+2', '61', '83', '90+2']</t>
+    <t>['45+2', '61', '82', '90+2']</t>
   </si>
   <si>
     <t>['74']</t>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="352">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1068,6 +1068,9 @@
   <si>
     <t>['9']</t>
   </si>
+  <si>
+    <t>['45', '64', '90']</t>
+  </si>
 </sst>
 </file>
 
@@ -1428,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3207,7 +3210,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ9">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3822,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ12">
         <v>1.55</v>
@@ -6709,7 +6712,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ26">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR26">
         <v>1.4</v>
@@ -7739,7 +7742,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ31">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR31">
         <v>0.65</v>
@@ -8766,7 +8769,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ36">
         <v>0.73</v>
@@ -12477,7 +12480,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ54">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR54">
         <v>1.7</v>
@@ -12680,7 +12683,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ55">
         <v>0.91</v>
@@ -15564,7 +15567,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ69">
         <v>0.27</v>
@@ -15979,7 +15982,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ71">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR71">
         <v>1.42</v>
@@ -18657,7 +18660,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ84">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -19890,7 +19893,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ90">
         <v>1.5</v>
@@ -20714,7 +20717,7 @@
         <v>0</v>
       </c>
       <c r="AP94">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ94">
         <v>0.25</v>
@@ -23395,7 +23398,7 @@
         <v>2</v>
       </c>
       <c r="AQ107">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR107">
         <v>1.93</v>
@@ -24010,7 +24013,7 @@
         <v>0.83</v>
       </c>
       <c r="AP110">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ110">
         <v>0.67</v>
@@ -26279,7 +26282,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ121">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR121">
         <v>1.51</v>
@@ -28130,7 +28133,7 @@
         <v>0.86</v>
       </c>
       <c r="AP130">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -30811,7 +30814,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ143">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR143">
         <v>1.59</v>
@@ -32456,7 +32459,7 @@
         <v>1.63</v>
       </c>
       <c r="AP151">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ151">
         <v>1.33</v>
@@ -34104,7 +34107,7 @@
         <v>0.89</v>
       </c>
       <c r="AP159">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ159">
         <v>1.17</v>
@@ -35755,7 +35758,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ167">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR167">
         <v>1.56</v>
@@ -37194,7 +37197,7 @@
         <v>0.89</v>
       </c>
       <c r="AP174">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ174">
         <v>1.27</v>
@@ -40902,7 +40905,7 @@
         <v>1.7</v>
       </c>
       <c r="AP192">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ192">
         <v>1.82</v>
@@ -41729,7 +41732,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ196">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR196">
         <v>2.06</v>
@@ -44277,6 +44280,212 @@
       </c>
       <c r="BP208">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7492021</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45716.6875</v>
+      </c>
+      <c r="F209">
+        <v>24</v>
+      </c>
+      <c r="G209" t="s">
+        <v>80</v>
+      </c>
+      <c r="H209" t="s">
+        <v>87</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>2</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>3</v>
+      </c>
+      <c r="N209">
+        <v>4</v>
+      </c>
+      <c r="O209" t="s">
+        <v>97</v>
+      </c>
+      <c r="P209" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q209">
+        <v>4.5</v>
+      </c>
+      <c r="R209">
+        <v>2.5</v>
+      </c>
+      <c r="S209">
+        <v>2.2</v>
+      </c>
+      <c r="T209">
+        <v>1.25</v>
+      </c>
+      <c r="U209">
+        <v>3.75</v>
+      </c>
+      <c r="V209">
+        <v>2.2</v>
+      </c>
+      <c r="W209">
+        <v>1.62</v>
+      </c>
+      <c r="X209">
+        <v>5</v>
+      </c>
+      <c r="Y209">
+        <v>1.17</v>
+      </c>
+      <c r="Z209">
+        <v>4.9</v>
+      </c>
+      <c r="AA209">
+        <v>4.5</v>
+      </c>
+      <c r="AB209">
+        <v>1.65</v>
+      </c>
+      <c r="AC209">
+        <v>1.01</v>
+      </c>
+      <c r="AD209">
+        <v>23</v>
+      </c>
+      <c r="AE209">
+        <v>1.15</v>
+      </c>
+      <c r="AF209">
+        <v>5.5</v>
+      </c>
+      <c r="AG209">
+        <v>1.45</v>
+      </c>
+      <c r="AH209">
+        <v>2.63</v>
+      </c>
+      <c r="AI209">
+        <v>1.5</v>
+      </c>
+      <c r="AJ209">
+        <v>2.5</v>
+      </c>
+      <c r="AK209">
+        <v>2.2</v>
+      </c>
+      <c r="AL209">
+        <v>1.21</v>
+      </c>
+      <c r="AM209">
+        <v>1.19</v>
+      </c>
+      <c r="AN209">
+        <v>1.67</v>
+      </c>
+      <c r="AO209">
+        <v>2.18</v>
+      </c>
+      <c r="AP209">
+        <v>1.54</v>
+      </c>
+      <c r="AQ209">
+        <v>2.25</v>
+      </c>
+      <c r="AR209">
+        <v>1.85</v>
+      </c>
+      <c r="AS209">
+        <v>1.78</v>
+      </c>
+      <c r="AT209">
+        <v>3.63</v>
+      </c>
+      <c r="AU209">
+        <v>4</v>
+      </c>
+      <c r="AV209">
+        <v>9</v>
+      </c>
+      <c r="AW209">
+        <v>9</v>
+      </c>
+      <c r="AX209">
+        <v>9</v>
+      </c>
+      <c r="AY209">
+        <v>16</v>
+      </c>
+      <c r="AZ209">
+        <v>22</v>
+      </c>
+      <c r="BA209">
+        <v>4</v>
+      </c>
+      <c r="BB209">
+        <v>6</v>
+      </c>
+      <c r="BC209">
+        <v>10</v>
+      </c>
+      <c r="BD209">
+        <v>3.2</v>
+      </c>
+      <c r="BE209">
+        <v>6.75</v>
+      </c>
+      <c r="BF209">
+        <v>1.42</v>
+      </c>
+      <c r="BG209">
+        <v>1.37</v>
+      </c>
+      <c r="BH209">
+        <v>2.8</v>
+      </c>
+      <c r="BI209">
+        <v>1.65</v>
+      </c>
+      <c r="BJ209">
+        <v>2.08</v>
+      </c>
+      <c r="BK209">
+        <v>2.04</v>
+      </c>
+      <c r="BL209">
+        <v>1.68</v>
+      </c>
+      <c r="BM209">
+        <v>2.6</v>
+      </c>
+      <c r="BN209">
+        <v>1.43</v>
+      </c>
+      <c r="BO209">
+        <v>3.45</v>
+      </c>
+      <c r="BP209">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="359">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -718,6 +718,12 @@
     <t>['74']</t>
   </si>
   <si>
+    <t>['90']</t>
+  </si>
+  <si>
+    <t>['1']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1070,6 +1076,21 @@
   </si>
   <si>
     <t>['45', '64', '90']</t>
+  </si>
+  <si>
+    <t>['6', '48']</t>
+  </si>
+  <si>
+    <t>['50', '58']</t>
+  </si>
+  <si>
+    <t>['8', '18', '59']</t>
+  </si>
+  <si>
+    <t>['52', '58']</t>
+  </si>
+  <si>
+    <t>['26', '29', '33', '62']</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1687,7 +1708,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1768,7 +1789,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ2">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1971,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ3">
         <v>0.25</v>
@@ -2099,7 +2120,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2305,7 +2326,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2511,7 +2532,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -3129,7 +3150,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3335,7 +3356,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3413,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ10">
         <v>0.67</v>
@@ -3747,7 +3768,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3828,7 +3849,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ12">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3953,7 +3974,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4034,7 +4055,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ13">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4159,7 +4180,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4237,10 +4258,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4365,7 +4386,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4443,10 +4464,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ15">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4649,10 +4670,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ16">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4777,7 +4798,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5061,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ18">
         <v>1.08</v>
@@ -5395,7 +5416,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5679,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ21">
         <v>0.67</v>
@@ -5807,7 +5828,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5888,7 +5909,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR22">
         <v>2.26</v>
@@ -6219,7 +6240,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6425,7 +6446,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6631,7 +6652,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -7043,7 +7064,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7249,7 +7270,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7330,7 +7351,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR29">
         <v>1.7</v>
@@ -7455,7 +7476,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7533,7 +7554,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ30">
         <v>1.17</v>
@@ -7661,7 +7682,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7739,7 +7760,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ31">
         <v>2.25</v>
@@ -7867,7 +7888,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7948,7 +7969,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ32">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR32">
         <v>1.36</v>
@@ -8073,7 +8094,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8151,7 +8172,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
         <v>0.27</v>
@@ -8357,10 +8378,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ34">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR34">
         <v>1.86</v>
@@ -8485,7 +8506,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8566,7 +8587,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ35">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR35">
         <v>2.58</v>
@@ -8772,7 +8793,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ36">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR36">
         <v>2.62</v>
@@ -8975,7 +8996,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -9103,7 +9124,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9515,7 +9536,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9721,7 +9742,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9927,7 +9948,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10211,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ43">
         <v>1.08</v>
@@ -10339,7 +10360,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10420,7 +10441,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ44">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10545,7 +10566,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10751,7 +10772,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11038,7 +11059,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ47">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR47">
         <v>2.02</v>
@@ -11163,7 +11184,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11447,7 +11468,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ49">
         <v>1.17</v>
@@ -11575,7 +11596,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11656,7 +11677,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ50">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11781,7 +11802,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11859,10 +11880,10 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR51">
         <v>1.37</v>
@@ -11987,7 +12008,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12065,10 +12086,10 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ52">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -12271,7 +12292,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12399,7 +12420,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12477,7 +12498,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
         <v>2.25</v>
@@ -12605,7 +12626,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12686,7 +12707,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ55">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR55">
         <v>2.29</v>
@@ -12811,7 +12832,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -13017,7 +13038,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13429,7 +13450,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13635,7 +13656,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13841,7 +13862,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14253,7 +14274,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14459,7 +14480,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14665,7 +14686,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14746,7 +14767,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ65">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR65">
         <v>1.22</v>
@@ -14871,7 +14892,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14952,7 +14973,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ66">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15155,10 +15176,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ67">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR67">
         <v>1.52</v>
@@ -15283,7 +15304,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15361,7 +15382,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ68">
         <v>1.17</v>
@@ -15695,7 +15716,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15773,10 +15794,10 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ70">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR70">
         <v>0.6899999999999999</v>
@@ -15901,7 +15922,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15979,7 +16000,7 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ71">
         <v>2.25</v>
@@ -16391,10 +16412,10 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ73">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR73">
         <v>1.3</v>
@@ -16931,7 +16952,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17009,7 +17030,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
         <v>0.25</v>
@@ -17137,7 +17158,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18042,7 +18063,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ81">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR81">
         <v>1.64</v>
@@ -18579,7 +18600,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18657,7 +18678,7 @@
         <v>2.6</v>
       </c>
       <c r="AP84">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ84">
         <v>2.25</v>
@@ -18863,7 +18884,7 @@
         <v>0.5</v>
       </c>
       <c r="AP85">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ85">
         <v>0.27</v>
@@ -18991,7 +19012,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19072,7 +19093,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ86">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR86">
         <v>1.34</v>
@@ -19197,7 +19218,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19275,10 +19296,10 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -19481,10 +19502,10 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ88">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR88">
         <v>1.44</v>
@@ -19690,7 +19711,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ89">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19815,7 +19836,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -20021,7 +20042,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20099,10 +20120,10 @@
         <v>1.75</v>
       </c>
       <c r="AP91">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ91">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20433,7 +20454,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -21051,7 +21072,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21541,7 +21562,7 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ98">
         <v>1.42</v>
@@ -21669,7 +21690,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21750,7 +21771,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ99">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -22081,7 +22102,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22159,7 +22180,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ101">
         <v>0.27</v>
@@ -22287,7 +22308,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22368,7 +22389,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ102">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR102">
         <v>1.35</v>
@@ -22493,7 +22514,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22574,7 +22595,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ103">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -22905,7 +22926,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22983,10 +23004,10 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ105">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR105">
         <v>1.47</v>
@@ -23111,7 +23132,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23189,7 +23210,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ106">
         <v>1.45</v>
@@ -23317,7 +23338,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23604,7 +23625,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ108">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR108">
         <v>1.45</v>
@@ -23729,7 +23750,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23807,7 +23828,7 @@
         <v>1.67</v>
       </c>
       <c r="AP109">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ109">
         <v>1.5</v>
@@ -23935,7 +23956,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24141,7 +24162,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24347,7 +24368,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24425,7 +24446,7 @@
         <v>1.67</v>
       </c>
       <c r="AP112">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
         <v>1.42</v>
@@ -24553,7 +24574,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24631,7 +24652,7 @@
         <v>0.2</v>
       </c>
       <c r="AP113">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
         <v>1.08</v>
@@ -24759,7 +24780,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25171,7 +25192,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25252,7 +25273,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ116">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR116">
         <v>1.64</v>
@@ -25377,7 +25398,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25458,7 +25479,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ117">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR117">
         <v>1.29</v>
@@ -25789,7 +25810,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25870,7 +25891,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ119">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR119">
         <v>1.52</v>
@@ -25995,7 +26016,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26201,7 +26222,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26407,7 +26428,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26488,7 +26509,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ122">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26819,7 +26840,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26897,7 +26918,7 @@
         <v>1.86</v>
       </c>
       <c r="AP124">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ124">
         <v>1.42</v>
@@ -27025,7 +27046,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27103,7 +27124,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ125">
         <v>1.45</v>
@@ -27231,7 +27252,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27312,7 +27333,7 @@
         <v>2</v>
       </c>
       <c r="AQ126">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR126">
         <v>1.74</v>
@@ -27437,7 +27458,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27515,7 +27536,7 @@
         <v>1.86</v>
       </c>
       <c r="AP127">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ127">
         <v>1.5</v>
@@ -27643,7 +27664,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27849,7 +27870,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28055,7 +28076,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28261,7 +28282,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28339,10 +28360,10 @@
         <v>1.83</v>
       </c>
       <c r="AP131">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR131">
         <v>1.54</v>
@@ -28467,7 +28488,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28548,7 +28569,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR132">
         <v>1.76</v>
@@ -28673,7 +28694,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28751,7 +28772,7 @@
         <v>0.71</v>
       </c>
       <c r="AP133">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ133">
         <v>0.67</v>
@@ -29163,7 +29184,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ135">
         <v>0.67</v>
@@ -29291,7 +29312,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29372,7 +29393,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ136">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR136">
         <v>1.28</v>
@@ -29497,7 +29518,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29578,7 +29599,7 @@
         <v>2</v>
       </c>
       <c r="AQ137">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR137">
         <v>1.63</v>
@@ -29784,7 +29805,7 @@
         <v>1</v>
       </c>
       <c r="AQ138">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR138">
         <v>1.83</v>
@@ -29987,7 +30008,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ139">
         <v>0.67</v>
@@ -30115,7 +30136,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30527,7 +30548,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30605,7 +30626,7 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ142">
         <v>1.5</v>
@@ -30939,7 +30960,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31017,7 +31038,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ144">
         <v>1.42</v>
@@ -31145,7 +31166,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31351,7 +31372,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31432,7 +31453,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ146">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR146">
         <v>1.19</v>
@@ -31635,7 +31656,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ147">
         <v>1.17</v>
@@ -31844,7 +31865,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ148">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR148">
         <v>1.3</v>
@@ -32050,7 +32071,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ149">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR149">
         <v>2.17</v>
@@ -32253,7 +32274,7 @@
         <v>1.13</v>
       </c>
       <c r="AP150">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ150">
         <v>1</v>
@@ -32381,7 +32402,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32668,7 +32689,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ152">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR152">
         <v>2.19</v>
@@ -32793,7 +32814,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32871,7 +32892,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ153">
         <v>0.67</v>
@@ -32999,7 +33020,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33283,10 +33304,10 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ155">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR155">
         <v>1.87</v>
@@ -33411,7 +33432,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33492,7 +33513,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ156">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR156">
         <v>1.22</v>
@@ -33617,7 +33638,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33695,7 +33716,7 @@
         <v>1.44</v>
       </c>
       <c r="AP157">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ157">
         <v>1.33</v>
@@ -33823,7 +33844,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -33901,7 +33922,7 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -34235,7 +34256,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34316,7 +34337,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ160">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR160">
         <v>2.29</v>
@@ -34441,7 +34462,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34522,7 +34543,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ161">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR161">
         <v>2.2</v>
@@ -34647,7 +34668,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34728,7 +34749,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ162">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR162">
         <v>1.42</v>
@@ -34853,7 +34874,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34931,7 +34952,7 @@
         <v>0.63</v>
       </c>
       <c r="AP163">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ163">
         <v>1.08</v>
@@ -35059,7 +35080,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35677,7 +35698,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35883,7 +35904,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36089,7 +36110,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36167,10 +36188,10 @@
         <v>2.25</v>
       </c>
       <c r="AP169">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ169">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR169">
         <v>1.49</v>
@@ -36501,7 +36522,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36785,7 +36806,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP172">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ172">
         <v>0.67</v>
@@ -36991,10 +37012,10 @@
         <v>1.56</v>
       </c>
       <c r="AP173">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ173">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR173">
         <v>1.38</v>
@@ -37119,7 +37140,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37200,7 +37221,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ174">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR174">
         <v>1.91</v>
@@ -37325,7 +37346,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37531,7 +37552,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37609,10 +37630,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP176">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ176">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR176">
         <v>1.36</v>
@@ -37815,7 +37836,7 @@
         <v>0.8</v>
       </c>
       <c r="AP177">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ177">
         <v>1.17</v>
@@ -37943,7 +37964,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38021,7 +38042,7 @@
         <v>0.89</v>
       </c>
       <c r="AP178">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ178">
         <v>1.08</v>
@@ -38355,7 +38376,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38433,10 +38454,10 @@
         <v>1.78</v>
       </c>
       <c r="AP180">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ180">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR180">
         <v>1.83</v>
@@ -38561,7 +38582,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38642,7 +38663,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ181">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR181">
         <v>2.14</v>
@@ -39054,7 +39075,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ183">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR183">
         <v>1.45</v>
@@ -39179,7 +39200,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39385,7 +39406,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -40003,7 +40024,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40209,7 +40230,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40493,7 +40514,7 @@
         <v>1.2</v>
       </c>
       <c r="AP190">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ190">
         <v>1</v>
@@ -40827,7 +40848,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -40908,7 +40929,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ192">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR192">
         <v>1.88</v>
@@ -41033,7 +41054,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41114,7 +41135,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ193">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR193">
         <v>1.45</v>
@@ -41317,10 +41338,10 @@
         <v>0.8</v>
       </c>
       <c r="AP194">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ194">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR194">
         <v>1.33</v>
@@ -41445,7 +41466,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41523,7 +41544,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ195">
         <v>1.17</v>
@@ -41857,7 +41878,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -41935,10 +41956,10 @@
         <v>0.7</v>
       </c>
       <c r="AP197">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ197">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR197">
         <v>1.38</v>
@@ -42141,7 +42162,7 @@
         <v>0.3</v>
       </c>
       <c r="AP198">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ198">
         <v>0.27</v>
@@ -42269,7 +42290,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42347,10 +42368,10 @@
         <v>1.4</v>
       </c>
       <c r="AP199">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ199">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR199">
         <v>1.37</v>
@@ -42681,7 +42702,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42762,7 +42783,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ201">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR201">
         <v>1.24</v>
@@ -42887,7 +42908,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -43711,7 +43732,7 @@
         <v>231</v>
       </c>
       <c r="P206" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43789,7 +43810,7 @@
         <v>0.64</v>
       </c>
       <c r="AP206">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ206">
         <v>0.67</v>
@@ -44123,7 +44144,7 @@
         <v>233</v>
       </c>
       <c r="P208" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -44329,7 +44350,7 @@
         <v>97</v>
       </c>
       <c r="P209" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q209">
         <v>4.5</v>
@@ -44486,6 +44507,1242 @@
       </c>
       <c r="BP209">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7492025</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>84</v>
+      </c>
+      <c r="H210" t="s">
+        <v>77</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>2</v>
+      </c>
+      <c r="N210">
+        <v>3</v>
+      </c>
+      <c r="O210" t="s">
+        <v>234</v>
+      </c>
+      <c r="P210" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q210">
+        <v>3.1</v>
+      </c>
+      <c r="R210">
+        <v>2.3</v>
+      </c>
+      <c r="S210">
+        <v>3.1</v>
+      </c>
+      <c r="T210">
+        <v>1.33</v>
+      </c>
+      <c r="U210">
+        <v>3.25</v>
+      </c>
+      <c r="V210">
+        <v>2.5</v>
+      </c>
+      <c r="W210">
+        <v>1.5</v>
+      </c>
+      <c r="X210">
+        <v>6.5</v>
+      </c>
+      <c r="Y210">
+        <v>1.11</v>
+      </c>
+      <c r="Z210">
+        <v>2.53</v>
+      </c>
+      <c r="AA210">
+        <v>3.74</v>
+      </c>
+      <c r="AB210">
+        <v>2.68</v>
+      </c>
+      <c r="AC210">
+        <v>1.03</v>
+      </c>
+      <c r="AD210">
+        <v>15</v>
+      </c>
+      <c r="AE210">
+        <v>1.2</v>
+      </c>
+      <c r="AF210">
+        <v>4.5</v>
+      </c>
+      <c r="AG210">
+        <v>1.55</v>
+      </c>
+      <c r="AH210">
+        <v>2.3</v>
+      </c>
+      <c r="AI210">
+        <v>1.57</v>
+      </c>
+      <c r="AJ210">
+        <v>2.25</v>
+      </c>
+      <c r="AK210">
+        <v>1.44</v>
+      </c>
+      <c r="AL210">
+        <v>1.27</v>
+      </c>
+      <c r="AM210">
+        <v>1.55</v>
+      </c>
+      <c r="AN210">
+        <v>1.18</v>
+      </c>
+      <c r="AO210">
+        <v>1.82</v>
+      </c>
+      <c r="AP210">
+        <v>1.08</v>
+      </c>
+      <c r="AQ210">
+        <v>1.92</v>
+      </c>
+      <c r="AR210">
+        <v>1.38</v>
+      </c>
+      <c r="AS210">
+        <v>1.29</v>
+      </c>
+      <c r="AT210">
+        <v>2.67</v>
+      </c>
+      <c r="AU210">
+        <v>8</v>
+      </c>
+      <c r="AV210">
+        <v>4</v>
+      </c>
+      <c r="AW210">
+        <v>8</v>
+      </c>
+      <c r="AX210">
+        <v>6</v>
+      </c>
+      <c r="AY210">
+        <v>20</v>
+      </c>
+      <c r="AZ210">
+        <v>14</v>
+      </c>
+      <c r="BA210">
+        <v>8</v>
+      </c>
+      <c r="BB210">
+        <v>2</v>
+      </c>
+      <c r="BC210">
+        <v>10</v>
+      </c>
+      <c r="BD210">
+        <v>1.88</v>
+      </c>
+      <c r="BE210">
+        <v>6.4</v>
+      </c>
+      <c r="BF210">
+        <v>2.15</v>
+      </c>
+      <c r="BG210">
+        <v>1.34</v>
+      </c>
+      <c r="BH210">
+        <v>2.9</v>
+      </c>
+      <c r="BI210">
+        <v>1.58</v>
+      </c>
+      <c r="BJ210">
+        <v>2.18</v>
+      </c>
+      <c r="BK210">
+        <v>1.96</v>
+      </c>
+      <c r="BL210">
+        <v>1.74</v>
+      </c>
+      <c r="BM210">
+        <v>2.48</v>
+      </c>
+      <c r="BN210">
+        <v>1.47</v>
+      </c>
+      <c r="BO210">
+        <v>3.2</v>
+      </c>
+      <c r="BP210">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7492029</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>78</v>
+      </c>
+      <c r="H211" t="s">
+        <v>76</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211">
+        <v>2</v>
+      </c>
+      <c r="N211">
+        <v>2</v>
+      </c>
+      <c r="O211" t="s">
+        <v>96</v>
+      </c>
+      <c r="P211" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q211">
+        <v>4.33</v>
+      </c>
+      <c r="R211">
+        <v>2.25</v>
+      </c>
+      <c r="S211">
+        <v>2.5</v>
+      </c>
+      <c r="T211">
+        <v>1.36</v>
+      </c>
+      <c r="U211">
+        <v>3</v>
+      </c>
+      <c r="V211">
+        <v>2.63</v>
+      </c>
+      <c r="W211">
+        <v>1.44</v>
+      </c>
+      <c r="X211">
+        <v>7</v>
+      </c>
+      <c r="Y211">
+        <v>1.1</v>
+      </c>
+      <c r="Z211">
+        <v>3.91</v>
+      </c>
+      <c r="AA211">
+        <v>3.65</v>
+      </c>
+      <c r="AB211">
+        <v>1.98</v>
+      </c>
+      <c r="AC211">
+        <v>1.04</v>
+      </c>
+      <c r="AD211">
+        <v>13</v>
+      </c>
+      <c r="AE211">
+        <v>1.25</v>
+      </c>
+      <c r="AF211">
+        <v>4</v>
+      </c>
+      <c r="AG211">
+        <v>1.81</v>
+      </c>
+      <c r="AH211">
+        <v>2.01</v>
+      </c>
+      <c r="AI211">
+        <v>1.7</v>
+      </c>
+      <c r="AJ211">
+        <v>2.05</v>
+      </c>
+      <c r="AK211">
+        <v>1.87</v>
+      </c>
+      <c r="AL211">
+        <v>1.27</v>
+      </c>
+      <c r="AM211">
+        <v>1.25</v>
+      </c>
+      <c r="AN211">
+        <v>0.82</v>
+      </c>
+      <c r="AO211">
+        <v>0.73</v>
+      </c>
+      <c r="AP211">
+        <v>0.75</v>
+      </c>
+      <c r="AQ211">
+        <v>0.92</v>
+      </c>
+      <c r="AR211">
+        <v>1.27</v>
+      </c>
+      <c r="AS211">
+        <v>1.39</v>
+      </c>
+      <c r="AT211">
+        <v>2.66</v>
+      </c>
+      <c r="AU211">
+        <v>2</v>
+      </c>
+      <c r="AV211">
+        <v>4</v>
+      </c>
+      <c r="AW211">
+        <v>6</v>
+      </c>
+      <c r="AX211">
+        <v>11</v>
+      </c>
+      <c r="AY211">
+        <v>11</v>
+      </c>
+      <c r="AZ211">
+        <v>16</v>
+      </c>
+      <c r="BA211">
+        <v>7</v>
+      </c>
+      <c r="BB211">
+        <v>1</v>
+      </c>
+      <c r="BC211">
+        <v>8</v>
+      </c>
+      <c r="BD211">
+        <v>2.45</v>
+      </c>
+      <c r="BE211">
+        <v>6.4</v>
+      </c>
+      <c r="BF211">
+        <v>1.67</v>
+      </c>
+      <c r="BG211">
+        <v>1.3</v>
+      </c>
+      <c r="BH211">
+        <v>3.15</v>
+      </c>
+      <c r="BI211">
+        <v>1.52</v>
+      </c>
+      <c r="BJ211">
+        <v>2.33</v>
+      </c>
+      <c r="BK211">
+        <v>1.84</v>
+      </c>
+      <c r="BL211">
+        <v>1.84</v>
+      </c>
+      <c r="BM211">
+        <v>2.3</v>
+      </c>
+      <c r="BN211">
+        <v>1.53</v>
+      </c>
+      <c r="BO211">
+        <v>2.95</v>
+      </c>
+      <c r="BP211">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7492028</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>83</v>
+      </c>
+      <c r="H212" t="s">
+        <v>72</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>1</v>
+      </c>
+      <c r="O212" t="s">
+        <v>96</v>
+      </c>
+      <c r="P212" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q212">
+        <v>2.88</v>
+      </c>
+      <c r="R212">
+        <v>2.38</v>
+      </c>
+      <c r="S212">
+        <v>3.25</v>
+      </c>
+      <c r="T212">
+        <v>1.3</v>
+      </c>
+      <c r="U212">
+        <v>3.4</v>
+      </c>
+      <c r="V212">
+        <v>2.38</v>
+      </c>
+      <c r="W212">
+        <v>1.53</v>
+      </c>
+      <c r="X212">
+        <v>6</v>
+      </c>
+      <c r="Y212">
+        <v>1.13</v>
+      </c>
+      <c r="Z212">
+        <v>2.46</v>
+      </c>
+      <c r="AA212">
+        <v>3.58</v>
+      </c>
+      <c r="AB212">
+        <v>2.87</v>
+      </c>
+      <c r="AC212">
+        <v>1.03</v>
+      </c>
+      <c r="AD212">
+        <v>15</v>
+      </c>
+      <c r="AE212">
+        <v>1.19</v>
+      </c>
+      <c r="AF212">
+        <v>4.75</v>
+      </c>
+      <c r="AG212">
+        <v>1.6</v>
+      </c>
+      <c r="AH212">
+        <v>2.25</v>
+      </c>
+      <c r="AI212">
+        <v>1.5</v>
+      </c>
+      <c r="AJ212">
+        <v>2.5</v>
+      </c>
+      <c r="AK212">
+        <v>1.45</v>
+      </c>
+      <c r="AL212">
+        <v>1.26</v>
+      </c>
+      <c r="AM212">
+        <v>1.6</v>
+      </c>
+      <c r="AN212">
+        <v>1.09</v>
+      </c>
+      <c r="AO212">
+        <v>0.91</v>
+      </c>
+      <c r="AP212">
+        <v>1</v>
+      </c>
+      <c r="AQ212">
+        <v>1.08</v>
+      </c>
+      <c r="AR212">
+        <v>1.4</v>
+      </c>
+      <c r="AS212">
+        <v>1.26</v>
+      </c>
+      <c r="AT212">
+        <v>2.66</v>
+      </c>
+      <c r="AU212">
+        <v>4</v>
+      </c>
+      <c r="AV212">
+        <v>3</v>
+      </c>
+      <c r="AW212">
+        <v>10</v>
+      </c>
+      <c r="AX212">
+        <v>8</v>
+      </c>
+      <c r="AY212">
+        <v>20</v>
+      </c>
+      <c r="AZ212">
+        <v>14</v>
+      </c>
+      <c r="BA212">
+        <v>8</v>
+      </c>
+      <c r="BB212">
+        <v>4</v>
+      </c>
+      <c r="BC212">
+        <v>12</v>
+      </c>
+      <c r="BD212">
+        <v>1.74</v>
+      </c>
+      <c r="BE212">
+        <v>6.75</v>
+      </c>
+      <c r="BF212">
+        <v>2.3</v>
+      </c>
+      <c r="BG212">
+        <v>1.24</v>
+      </c>
+      <c r="BH212">
+        <v>3.55</v>
+      </c>
+      <c r="BI212">
+        <v>1.41</v>
+      </c>
+      <c r="BJ212">
+        <v>2.65</v>
+      </c>
+      <c r="BK212">
+        <v>1.67</v>
+      </c>
+      <c r="BL212">
+        <v>2.04</v>
+      </c>
+      <c r="BM212">
+        <v>2.07</v>
+      </c>
+      <c r="BN212">
+        <v>1.66</v>
+      </c>
+      <c r="BO212">
+        <v>2.65</v>
+      </c>
+      <c r="BP212">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7492024</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>86</v>
+      </c>
+      <c r="H213" t="s">
+        <v>70</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>2</v>
+      </c>
+      <c r="K213">
+        <v>2</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>3</v>
+      </c>
+      <c r="N213">
+        <v>3</v>
+      </c>
+      <c r="O213" t="s">
+        <v>96</v>
+      </c>
+      <c r="P213" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q213">
+        <v>3.4</v>
+      </c>
+      <c r="R213">
+        <v>2.3</v>
+      </c>
+      <c r="S213">
+        <v>2.88</v>
+      </c>
+      <c r="T213">
+        <v>1.33</v>
+      </c>
+      <c r="U213">
+        <v>3.25</v>
+      </c>
+      <c r="V213">
+        <v>2.5</v>
+      </c>
+      <c r="W213">
+        <v>1.5</v>
+      </c>
+      <c r="X213">
+        <v>6</v>
+      </c>
+      <c r="Y213">
+        <v>1.13</v>
+      </c>
+      <c r="Z213">
+        <v>2.92</v>
+      </c>
+      <c r="AA213">
+        <v>3.65</v>
+      </c>
+      <c r="AB213">
+        <v>2.39</v>
+      </c>
+      <c r="AC213">
+        <v>1.03</v>
+      </c>
+      <c r="AD213">
+        <v>13</v>
+      </c>
+      <c r="AE213">
+        <v>1.22</v>
+      </c>
+      <c r="AF213">
+        <v>4.33</v>
+      </c>
+      <c r="AG213">
+        <v>1.6</v>
+      </c>
+      <c r="AH213">
+        <v>2.25</v>
+      </c>
+      <c r="AI213">
+        <v>1.57</v>
+      </c>
+      <c r="AJ213">
+        <v>2.25</v>
+      </c>
+      <c r="AK213">
+        <v>1.55</v>
+      </c>
+      <c r="AL213">
+        <v>1.28</v>
+      </c>
+      <c r="AM213">
+        <v>1.44</v>
+      </c>
+      <c r="AN213">
+        <v>0.64</v>
+      </c>
+      <c r="AO213">
+        <v>1.27</v>
+      </c>
+      <c r="AP213">
+        <v>0.58</v>
+      </c>
+      <c r="AQ213">
+        <v>1.42</v>
+      </c>
+      <c r="AR213">
+        <v>1.38</v>
+      </c>
+      <c r="AS213">
+        <v>1.34</v>
+      </c>
+      <c r="AT213">
+        <v>2.72</v>
+      </c>
+      <c r="AU213">
+        <v>5</v>
+      </c>
+      <c r="AV213">
+        <v>6</v>
+      </c>
+      <c r="AW213">
+        <v>16</v>
+      </c>
+      <c r="AX213">
+        <v>8</v>
+      </c>
+      <c r="AY213">
+        <v>28</v>
+      </c>
+      <c r="AZ213">
+        <v>15</v>
+      </c>
+      <c r="BA213">
+        <v>6</v>
+      </c>
+      <c r="BB213">
+        <v>2</v>
+      </c>
+      <c r="BC213">
+        <v>8</v>
+      </c>
+      <c r="BD213">
+        <v>1.9</v>
+      </c>
+      <c r="BE213">
+        <v>6.4</v>
+      </c>
+      <c r="BF213">
+        <v>2.08</v>
+      </c>
+      <c r="BG213">
+        <v>1.26</v>
+      </c>
+      <c r="BH213">
+        <v>3.4</v>
+      </c>
+      <c r="BI213">
+        <v>1.46</v>
+      </c>
+      <c r="BJ213">
+        <v>2.48</v>
+      </c>
+      <c r="BK213">
+        <v>1.75</v>
+      </c>
+      <c r="BL213">
+        <v>1.95</v>
+      </c>
+      <c r="BM213">
+        <v>2.18</v>
+      </c>
+      <c r="BN213">
+        <v>1.58</v>
+      </c>
+      <c r="BO213">
+        <v>2.8</v>
+      </c>
+      <c r="BP213">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7492022</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>71</v>
+      </c>
+      <c r="H214" t="s">
+        <v>75</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>2</v>
+      </c>
+      <c r="N214">
+        <v>3</v>
+      </c>
+      <c r="O214" t="s">
+        <v>235</v>
+      </c>
+      <c r="P214" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q214">
+        <v>2.5</v>
+      </c>
+      <c r="R214">
+        <v>2.25</v>
+      </c>
+      <c r="S214">
+        <v>4.33</v>
+      </c>
+      <c r="T214">
+        <v>1.33</v>
+      </c>
+      <c r="U214">
+        <v>3.25</v>
+      </c>
+      <c r="V214">
+        <v>2.63</v>
+      </c>
+      <c r="W214">
+        <v>1.44</v>
+      </c>
+      <c r="X214">
+        <v>7</v>
+      </c>
+      <c r="Y214">
+        <v>1.1</v>
+      </c>
+      <c r="Z214">
+        <v>1.89</v>
+      </c>
+      <c r="AA214">
+        <v>4</v>
+      </c>
+      <c r="AB214">
+        <v>3.9</v>
+      </c>
+      <c r="AC214">
+        <v>1.03</v>
+      </c>
+      <c r="AD214">
+        <v>13</v>
+      </c>
+      <c r="AE214">
+        <v>1.26</v>
+      </c>
+      <c r="AF214">
+        <v>4</v>
+      </c>
+      <c r="AG214">
+        <v>1.67</v>
+      </c>
+      <c r="AH214">
+        <v>2.1</v>
+      </c>
+      <c r="AI214">
+        <v>1.67</v>
+      </c>
+      <c r="AJ214">
+        <v>2.1</v>
+      </c>
+      <c r="AK214">
+        <v>1.26</v>
+      </c>
+      <c r="AL214">
+        <v>1.27</v>
+      </c>
+      <c r="AM214">
+        <v>1.85</v>
+      </c>
+      <c r="AN214">
+        <v>2</v>
+      </c>
+      <c r="AO214">
+        <v>1.55</v>
+      </c>
+      <c r="AP214">
+        <v>1.83</v>
+      </c>
+      <c r="AQ214">
+        <v>1.67</v>
+      </c>
+      <c r="AR214">
+        <v>1.52</v>
+      </c>
+      <c r="AS214">
+        <v>1.17</v>
+      </c>
+      <c r="AT214">
+        <v>2.69</v>
+      </c>
+      <c r="AU214">
+        <v>5</v>
+      </c>
+      <c r="AV214">
+        <v>4</v>
+      </c>
+      <c r="AW214">
+        <v>9</v>
+      </c>
+      <c r="AX214">
+        <v>13</v>
+      </c>
+      <c r="AY214">
+        <v>16</v>
+      </c>
+      <c r="AZ214">
+        <v>22</v>
+      </c>
+      <c r="BA214">
+        <v>7</v>
+      </c>
+      <c r="BB214">
+        <v>1</v>
+      </c>
+      <c r="BC214">
+        <v>8</v>
+      </c>
+      <c r="BD214">
+        <v>1.65</v>
+      </c>
+      <c r="BE214">
+        <v>6.5</v>
+      </c>
+      <c r="BF214">
+        <v>2.48</v>
+      </c>
+      <c r="BG214">
+        <v>1.3</v>
+      </c>
+      <c r="BH214">
+        <v>3.15</v>
+      </c>
+      <c r="BI214">
+        <v>1.53</v>
+      </c>
+      <c r="BJ214">
+        <v>2.32</v>
+      </c>
+      <c r="BK214">
+        <v>1.86</v>
+      </c>
+      <c r="BL214">
+        <v>1.82</v>
+      </c>
+      <c r="BM214">
+        <v>2.35</v>
+      </c>
+      <c r="BN214">
+        <v>1.5</v>
+      </c>
+      <c r="BO214">
+        <v>3.05</v>
+      </c>
+      <c r="BP214">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7492023</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45717.60416666666</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>82</v>
+      </c>
+      <c r="H215" t="s">
+        <v>85</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>3</v>
+      </c>
+      <c r="K215">
+        <v>4</v>
+      </c>
+      <c r="L215">
+        <v>1</v>
+      </c>
+      <c r="M215">
+        <v>4</v>
+      </c>
+      <c r="N215">
+        <v>5</v>
+      </c>
+      <c r="O215" t="s">
+        <v>104</v>
+      </c>
+      <c r="P215" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q215">
+        <v>4.75</v>
+      </c>
+      <c r="R215">
+        <v>2.3</v>
+      </c>
+      <c r="S215">
+        <v>2.3</v>
+      </c>
+      <c r="T215">
+        <v>1.33</v>
+      </c>
+      <c r="U215">
+        <v>3.25</v>
+      </c>
+      <c r="V215">
+        <v>2.5</v>
+      </c>
+      <c r="W215">
+        <v>1.5</v>
+      </c>
+      <c r="X215">
+        <v>6.5</v>
+      </c>
+      <c r="Y215">
+        <v>1.11</v>
+      </c>
+      <c r="Z215">
+        <v>3.81</v>
+      </c>
+      <c r="AA215">
+        <v>3.86</v>
+      </c>
+      <c r="AB215">
+        <v>1.95</v>
+      </c>
+      <c r="AC215">
+        <v>1.03</v>
+      </c>
+      <c r="AD215">
+        <v>13</v>
+      </c>
+      <c r="AE215">
+        <v>1.24</v>
+      </c>
+      <c r="AF215">
+        <v>4.2</v>
+      </c>
+      <c r="AG215">
+        <v>1.67</v>
+      </c>
+      <c r="AH215">
+        <v>2.2</v>
+      </c>
+      <c r="AI215">
+        <v>1.67</v>
+      </c>
+      <c r="AJ215">
+        <v>2.1</v>
+      </c>
+      <c r="AK215">
+        <v>2</v>
+      </c>
+      <c r="AL215">
+        <v>1.25</v>
+      </c>
+      <c r="AM215">
+        <v>1.21</v>
+      </c>
+      <c r="AN215">
+        <v>2.18</v>
+      </c>
+      <c r="AO215">
+        <v>2.09</v>
+      </c>
+      <c r="AP215">
+        <v>2</v>
+      </c>
+      <c r="AQ215">
+        <v>2.17</v>
+      </c>
+      <c r="AR215">
+        <v>1.89</v>
+      </c>
+      <c r="AS215">
+        <v>1.58</v>
+      </c>
+      <c r="AT215">
+        <v>3.47</v>
+      </c>
+      <c r="AU215">
+        <v>4</v>
+      </c>
+      <c r="AV215">
+        <v>10</v>
+      </c>
+      <c r="AW215">
+        <v>4</v>
+      </c>
+      <c r="AX215">
+        <v>10</v>
+      </c>
+      <c r="AY215">
+        <v>9</v>
+      </c>
+      <c r="AZ215">
+        <v>24</v>
+      </c>
+      <c r="BA215">
+        <v>2</v>
+      </c>
+      <c r="BB215">
+        <v>6</v>
+      </c>
+      <c r="BC215">
+        <v>8</v>
+      </c>
+      <c r="BD215">
+        <v>2.65</v>
+      </c>
+      <c r="BE215">
+        <v>6.4</v>
+      </c>
+      <c r="BF215">
+        <v>1.56</v>
+      </c>
+      <c r="BG215">
+        <v>1.29</v>
+      </c>
+      <c r="BH215">
+        <v>3.2</v>
+      </c>
+      <c r="BI215">
+        <v>1.49</v>
+      </c>
+      <c r="BJ215">
+        <v>2.4</v>
+      </c>
+      <c r="BK215">
+        <v>1.79</v>
+      </c>
+      <c r="BL215">
+        <v>1.9</v>
+      </c>
+      <c r="BM215">
+        <v>2.28</v>
+      </c>
+      <c r="BN215">
+        <v>1.55</v>
+      </c>
+      <c r="BO215">
+        <v>2.9</v>
+      </c>
+      <c r="BP215">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="360">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1092,6 +1092,9 @@
   <si>
     <t>['26', '29', '33', '62']</t>
   </si>
+  <si>
+    <t>['42']</t>
+  </si>
 </sst>
 </file>
 
@@ -1452,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP215"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2201,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2610,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ6">
         <v>1.42</v>
@@ -3640,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -5291,7 +5294,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ19">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -6936,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7348,7 +7351,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ29">
         <v>1.67</v>
@@ -7557,7 +7560,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ30">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7966,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
         <v>1.08</v>
@@ -8175,7 +8178,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR33">
         <v>1.57</v>
@@ -11056,7 +11059,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ47">
         <v>1.42</v>
@@ -11265,7 +11268,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ48">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR48">
         <v>2.42</v>
@@ -11471,7 +11474,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ49">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR49">
         <v>0.41</v>
@@ -11674,7 +11677,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ50">
         <v>0.92</v>
@@ -14970,7 +14973,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ66">
         <v>0.92</v>
@@ -15385,7 +15388,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ68">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15591,7 +15594,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ69">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR69">
         <v>2.2</v>
@@ -16206,7 +16209,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ72">
         <v>1.5</v>
@@ -18472,10 +18475,10 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ83">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR83">
         <v>1.3</v>
@@ -18887,7 +18890,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ85">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR85">
         <v>0.97</v>
@@ -19708,7 +19711,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ89">
         <v>1.08</v>
@@ -20947,7 +20950,7 @@
         <v>2</v>
       </c>
       <c r="AQ95">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR95">
         <v>1.86</v>
@@ -22183,7 +22186,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ101">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR101">
         <v>1.26</v>
@@ -22386,7 +22389,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ102">
         <v>2.17</v>
@@ -22798,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ104">
         <v>0.25</v>
@@ -25685,7 +25688,7 @@
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR118">
         <v>1.77</v>
@@ -26094,7 +26097,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120">
         <v>0.25</v>
@@ -26506,7 +26509,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ122">
         <v>2.17</v>
@@ -26715,7 +26718,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ123">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -28981,7 +28984,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ134">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR134">
         <v>2.13</v>
@@ -30217,7 +30220,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ140">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR140">
         <v>1.59</v>
@@ -31244,7 +31247,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ145">
         <v>1.45</v>
@@ -31659,7 +31662,7 @@
         <v>2</v>
       </c>
       <c r="AQ147">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR147">
         <v>1.77</v>
@@ -33098,7 +33101,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ154">
         <v>1.08</v>
@@ -34131,7 +34134,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ159">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR159">
         <v>1.95</v>
@@ -34746,7 +34749,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ162">
         <v>1.67</v>
@@ -35161,7 +35164,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ164">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR164">
         <v>1.34</v>
@@ -35570,7 +35573,7 @@
         <v>0.78</v>
       </c>
       <c r="AP166">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ166">
         <v>0.67</v>
@@ -37427,7 +37430,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ175">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR175">
         <v>2.37</v>
@@ -37839,7 +37842,7 @@
         <v>1</v>
       </c>
       <c r="AQ177">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR177">
         <v>1.23</v>
@@ -38248,7 +38251,7 @@
         <v>1.4</v>
       </c>
       <c r="AP179">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ179">
         <v>1.33</v>
@@ -40720,7 +40723,7 @@
         <v>1.36</v>
       </c>
       <c r="AP191">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ191">
         <v>1.33</v>
@@ -41132,7 +41135,7 @@
         <v>1.1</v>
       </c>
       <c r="AP193">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ193">
         <v>1.42</v>
@@ -41547,7 +41550,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ195">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR195">
         <v>1.32</v>
@@ -42165,7 +42168,7 @@
         <v>2</v>
       </c>
       <c r="AQ198">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR198">
         <v>1.84</v>
@@ -45743,6 +45746,418 @@
       </c>
       <c r="BP215">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7492027</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45718.47916666666</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>79</v>
+      </c>
+      <c r="H216" t="s">
+        <v>81</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>1</v>
+      </c>
+      <c r="O216" t="s">
+        <v>96</v>
+      </c>
+      <c r="P216" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q216">
+        <v>2.1</v>
+      </c>
+      <c r="R216">
+        <v>2.38</v>
+      </c>
+      <c r="S216">
+        <v>5.5</v>
+      </c>
+      <c r="T216">
+        <v>1.33</v>
+      </c>
+      <c r="U216">
+        <v>3.25</v>
+      </c>
+      <c r="V216">
+        <v>2.5</v>
+      </c>
+      <c r="W216">
+        <v>1.5</v>
+      </c>
+      <c r="X216">
+        <v>6.5</v>
+      </c>
+      <c r="Y216">
+        <v>1.11</v>
+      </c>
+      <c r="Z216">
+        <v>1.55</v>
+      </c>
+      <c r="AA216">
+        <v>4.5</v>
+      </c>
+      <c r="AB216">
+        <v>5.9</v>
+      </c>
+      <c r="AC216">
+        <v>1.03</v>
+      </c>
+      <c r="AD216">
+        <v>15</v>
+      </c>
+      <c r="AE216">
+        <v>1.22</v>
+      </c>
+      <c r="AF216">
+        <v>4.33</v>
+      </c>
+      <c r="AG216">
+        <v>1.57</v>
+      </c>
+      <c r="AH216">
+        <v>2.3</v>
+      </c>
+      <c r="AI216">
+        <v>1.8</v>
+      </c>
+      <c r="AJ216">
+        <v>1.95</v>
+      </c>
+      <c r="AK216">
+        <v>1.15</v>
+      </c>
+      <c r="AL216">
+        <v>1.21</v>
+      </c>
+      <c r="AM216">
+        <v>2.4</v>
+      </c>
+      <c r="AN216">
+        <v>1.45</v>
+      </c>
+      <c r="AO216">
+        <v>0.27</v>
+      </c>
+      <c r="AP216">
+        <v>1.33</v>
+      </c>
+      <c r="AQ216">
+        <v>0.5</v>
+      </c>
+      <c r="AR216">
+        <v>1.5</v>
+      </c>
+      <c r="AS216">
+        <v>1.16</v>
+      </c>
+      <c r="AT216">
+        <v>2.66</v>
+      </c>
+      <c r="AU216">
+        <v>4</v>
+      </c>
+      <c r="AV216">
+        <v>4</v>
+      </c>
+      <c r="AW216">
+        <v>11</v>
+      </c>
+      <c r="AX216">
+        <v>7</v>
+      </c>
+      <c r="AY216">
+        <v>19</v>
+      </c>
+      <c r="AZ216">
+        <v>12</v>
+      </c>
+      <c r="BA216">
+        <v>11</v>
+      </c>
+      <c r="BB216">
+        <v>3</v>
+      </c>
+      <c r="BC216">
+        <v>14</v>
+      </c>
+      <c r="BD216">
+        <v>1.35</v>
+      </c>
+      <c r="BE216">
+        <v>10</v>
+      </c>
+      <c r="BF216">
+        <v>4.05</v>
+      </c>
+      <c r="BG216">
+        <v>1.19</v>
+      </c>
+      <c r="BH216">
+        <v>3.76</v>
+      </c>
+      <c r="BI216">
+        <v>1.4</v>
+      </c>
+      <c r="BJ216">
+        <v>2.64</v>
+      </c>
+      <c r="BK216">
+        <v>1.71</v>
+      </c>
+      <c r="BL216">
+        <v>2.02</v>
+      </c>
+      <c r="BM216">
+        <v>2.15</v>
+      </c>
+      <c r="BN216">
+        <v>1.59</v>
+      </c>
+      <c r="BO216">
+        <v>2.81</v>
+      </c>
+      <c r="BP216">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7492026</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45718.5625</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>74</v>
+      </c>
+      <c r="H217" t="s">
+        <v>73</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>0</v>
+      </c>
+      <c r="O217" t="s">
+        <v>96</v>
+      </c>
+      <c r="P217" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q217">
+        <v>3.4</v>
+      </c>
+      <c r="R217">
+        <v>2</v>
+      </c>
+      <c r="S217">
+        <v>3.5</v>
+      </c>
+      <c r="T217">
+        <v>1.5</v>
+      </c>
+      <c r="U217">
+        <v>2.5</v>
+      </c>
+      <c r="V217">
+        <v>3.4</v>
+      </c>
+      <c r="W217">
+        <v>1.3</v>
+      </c>
+      <c r="X217">
+        <v>10</v>
+      </c>
+      <c r="Y217">
+        <v>1.06</v>
+      </c>
+      <c r="Z217">
+        <v>2.62</v>
+      </c>
+      <c r="AA217">
+        <v>3.28</v>
+      </c>
+      <c r="AB217">
+        <v>2.87</v>
+      </c>
+      <c r="AC217">
+        <v>1.08</v>
+      </c>
+      <c r="AD217">
+        <v>8.5</v>
+      </c>
+      <c r="AE217">
+        <v>1.42</v>
+      </c>
+      <c r="AF217">
+        <v>2.9</v>
+      </c>
+      <c r="AG217">
+        <v>1.7</v>
+      </c>
+      <c r="AH217">
+        <v>2.05</v>
+      </c>
+      <c r="AI217">
+        <v>1.95</v>
+      </c>
+      <c r="AJ217">
+        <v>1.8</v>
+      </c>
+      <c r="AK217">
+        <v>1.42</v>
+      </c>
+      <c r="AL217">
+        <v>1.34</v>
+      </c>
+      <c r="AM217">
+        <v>1.49</v>
+      </c>
+      <c r="AN217">
+        <v>1.64</v>
+      </c>
+      <c r="AO217">
+        <v>1.17</v>
+      </c>
+      <c r="AP217">
+        <v>1.58</v>
+      </c>
+      <c r="AQ217">
+        <v>1.15</v>
+      </c>
+      <c r="AR217">
+        <v>1.54</v>
+      </c>
+      <c r="AS217">
+        <v>1.19</v>
+      </c>
+      <c r="AT217">
+        <v>2.73</v>
+      </c>
+      <c r="AU217">
+        <v>6</v>
+      </c>
+      <c r="AV217">
+        <v>4</v>
+      </c>
+      <c r="AW217">
+        <v>8</v>
+      </c>
+      <c r="AX217">
+        <v>4</v>
+      </c>
+      <c r="AY217">
+        <v>15</v>
+      </c>
+      <c r="AZ217">
+        <v>10</v>
+      </c>
+      <c r="BA217">
+        <v>5</v>
+      </c>
+      <c r="BB217">
+        <v>2</v>
+      </c>
+      <c r="BC217">
+        <v>7</v>
+      </c>
+      <c r="BD217">
+        <v>1.68</v>
+      </c>
+      <c r="BE217">
+        <v>6.75</v>
+      </c>
+      <c r="BF217">
+        <v>2.91</v>
+      </c>
+      <c r="BG217">
+        <v>1.29</v>
+      </c>
+      <c r="BH217">
+        <v>3.04</v>
+      </c>
+      <c r="BI217">
+        <v>1.56</v>
+      </c>
+      <c r="BJ217">
+        <v>2.21</v>
+      </c>
+      <c r="BK217">
+        <v>1.98</v>
+      </c>
+      <c r="BL217">
+        <v>1.74</v>
+      </c>
+      <c r="BM217">
+        <v>2.57</v>
+      </c>
+      <c r="BN217">
+        <v>1.42</v>
+      </c>
+      <c r="BO217">
+        <v>3.5</v>
+      </c>
+      <c r="BP217">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -45085,10 +45085,10 @@
         <v>8</v>
       </c>
       <c r="BB212">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC212">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD212">
         <v>1.74</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="367">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -724,6 +724,15 @@
     <t>['1']</t>
   </si>
   <si>
+    <t>['14', '28']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['30', '46']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1095,6 +1104,18 @@
   <si>
     <t>['42']</t>
   </si>
+  <si>
+    <t>['39', '48', '77']</t>
+  </si>
+  <si>
+    <t>['7', '90+4']</t>
+  </si>
+  <si>
+    <t>['31', '51', '71']</t>
+  </si>
+  <si>
+    <t>['15', '55']</t>
+  </si>
 </sst>
 </file>
 
@@ -1455,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1711,7 +1732,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1789,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ2">
         <v>2.17</v>
@@ -1998,7 +2019,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ3">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2123,7 +2144,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2329,7 +2350,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2407,10 +2428,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ5">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2535,7 +2556,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2616,7 +2637,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ6">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3025,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ8">
         <v>1.5</v>
@@ -3153,7 +3174,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3231,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ9">
         <v>2.25</v>
@@ -3359,7 +3380,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3771,7 +3792,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3852,7 +3873,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ12">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3977,7 +3998,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4055,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ13">
         <v>1.92</v>
@@ -4183,7 +4204,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4389,7 +4410,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4801,7 +4822,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4879,10 +4900,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5088,7 +5109,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ18">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5291,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ19">
         <v>1.15</v>
@@ -5419,7 +5440,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5497,7 +5518,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ20">
         <v>0.67</v>
@@ -5831,7 +5852,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6115,10 +6136,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ23">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR23">
         <v>1.5</v>
@@ -6243,7 +6264,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6321,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ24">
         <v>1.5</v>
@@ -6449,7 +6470,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6527,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ25">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR25">
         <v>1.46</v>
@@ -6655,7 +6676,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6733,7 +6754,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ26">
         <v>2.25</v>
@@ -7067,7 +7088,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7148,7 +7169,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ28">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR28">
         <v>1.23</v>
@@ -7273,7 +7294,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7354,7 +7375,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ29">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR29">
         <v>1.7</v>
@@ -7479,7 +7500,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7685,7 +7706,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7891,7 +7912,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8097,7 +8118,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8509,7 +8530,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8587,7 +8608,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ35">
         <v>1.92</v>
@@ -9002,7 +9023,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR37">
         <v>1.27</v>
@@ -9127,7 +9148,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9205,10 +9226,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ38">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR38">
         <v>1.73</v>
@@ -9411,7 +9432,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ39">
         <v>0.67</v>
@@ -9539,7 +9560,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9745,7 +9766,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9823,10 +9844,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ41">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR41">
         <v>1.28</v>
@@ -9951,7 +9972,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10029,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -10238,7 +10259,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ43">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR43">
         <v>1.14</v>
@@ -10363,7 +10384,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10441,7 +10462,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ44">
         <v>2.17</v>
@@ -10569,7 +10590,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10647,7 +10668,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ45">
         <v>1.5</v>
@@ -10775,7 +10796,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10856,7 +10877,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR46">
         <v>1.82</v>
@@ -11187,7 +11208,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11265,7 +11286,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ48">
         <v>0.5</v>
@@ -11599,7 +11620,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11805,7 +11826,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -12011,7 +12032,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12092,7 +12113,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ52">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -12298,7 +12319,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12423,7 +12444,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12629,7 +12650,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12835,7 +12856,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12913,7 +12934,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -13041,7 +13062,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13119,7 +13140,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ57">
         <v>1.5</v>
@@ -13328,7 +13349,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13453,7 +13474,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13531,10 +13552,10 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ59">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR59">
         <v>1.71</v>
@@ -13659,7 +13680,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13740,7 +13761,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ60">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR60">
         <v>1.26</v>
@@ -13865,7 +13886,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13943,7 +13964,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ61">
         <v>0.67</v>
@@ -14149,10 +14170,10 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ62">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR62">
         <v>1.47</v>
@@ -14277,7 +14298,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14355,7 +14376,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ63">
         <v>0.67</v>
@@ -14483,7 +14504,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14561,10 +14582,10 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ64">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR64">
         <v>1.11</v>
@@ -14689,7 +14710,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14895,7 +14916,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15307,7 +15328,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15719,7 +15740,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15925,7 +15946,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16621,10 +16642,10 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ74">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR74">
         <v>2.41</v>
@@ -16827,7 +16848,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ75">
         <v>0.67</v>
@@ -16955,7 +16976,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17036,7 +17057,7 @@
         <v>2</v>
       </c>
       <c r="AQ76">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17161,7 +17182,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17445,7 +17466,7 @@
         <v>1.5</v>
       </c>
       <c r="AP78">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ78">
         <v>0.67</v>
@@ -17651,10 +17672,10 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ79">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR79">
         <v>1.14</v>
@@ -17857,10 +17878,10 @@
         <v>2.5</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ80">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR80">
         <v>1.88</v>
@@ -18063,10 +18084,10 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ81">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR81">
         <v>1.64</v>
@@ -18269,10 +18290,10 @@
         <v>2.5</v>
       </c>
       <c r="AP82">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ82">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18603,7 +18624,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -19015,7 +19036,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19221,7 +19242,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19839,7 +19860,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -20045,7 +20066,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20329,10 +20350,10 @@
         <v>0.25</v>
       </c>
       <c r="AP92">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ92">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR92">
         <v>1.83</v>
@@ -20457,7 +20478,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20535,7 +20556,7 @@
         <v>1.2</v>
       </c>
       <c r="AP93">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ93">
         <v>0.67</v>
@@ -20744,7 +20765,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ94">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR94">
         <v>2.18</v>
@@ -20947,7 +20968,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ95">
         <v>1.15</v>
@@ -21075,7 +21096,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21156,7 +21177,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -21359,7 +21380,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ97">
         <v>0.67</v>
@@ -21568,7 +21589,7 @@
         <v>2</v>
       </c>
       <c r="AQ98">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR98">
         <v>1.59</v>
@@ -21693,7 +21714,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21771,10 +21792,10 @@
         <v>2</v>
       </c>
       <c r="AP99">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ99">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21977,7 +21998,7 @@
         <v>1.2</v>
       </c>
       <c r="AP100">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ100">
         <v>1</v>
@@ -22105,7 +22126,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22311,7 +22332,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22517,7 +22538,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22595,7 +22616,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ103">
         <v>1.42</v>
@@ -22804,7 +22825,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ104">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR104">
         <v>1.72</v>
@@ -22929,7 +22950,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23135,7 +23156,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23216,7 +23237,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ106">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR106">
         <v>1.1</v>
@@ -23341,7 +23362,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23419,7 +23440,7 @@
         <v>2.67</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ107">
         <v>2.25</v>
@@ -23753,7 +23774,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23959,7 +23980,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24165,7 +24186,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24243,10 +24264,10 @@
         <v>1.67</v>
       </c>
       <c r="AP111">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ111">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR111">
         <v>1.13</v>
@@ -24371,7 +24392,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24452,7 +24473,7 @@
         <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR112">
         <v>1.23</v>
@@ -24577,7 +24598,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24658,7 +24679,7 @@
         <v>2</v>
       </c>
       <c r="AQ113">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR113">
         <v>1.55</v>
@@ -24783,7 +24804,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24861,7 +24882,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ114">
         <v>0.67</v>
@@ -25067,7 +25088,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -25195,7 +25216,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25273,7 +25294,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ116">
         <v>0.92</v>
@@ -25401,7 +25422,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25479,10 +25500,10 @@
         <v>2.2</v>
       </c>
       <c r="AP117">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ117">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR117">
         <v>1.29</v>
@@ -25813,7 +25834,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25891,7 +25912,7 @@
         <v>2.17</v>
       </c>
       <c r="AP119">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ119">
         <v>1.92</v>
@@ -26019,7 +26040,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26100,7 +26121,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR120">
         <v>1.27</v>
@@ -26225,7 +26246,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26431,7 +26452,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26715,7 +26736,7 @@
         <v>0.33</v>
       </c>
       <c r="AP123">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ123">
         <v>0.5</v>
@@ -26843,7 +26864,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26924,7 +26945,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ124">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -27049,7 +27070,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27130,7 +27151,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ125">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR125">
         <v>1.33</v>
@@ -27255,7 +27276,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27333,7 +27354,7 @@
         <v>0.5</v>
       </c>
       <c r="AP126">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ126">
         <v>1.08</v>
@@ -27461,7 +27482,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27667,7 +27688,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27745,10 +27766,10 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ128">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR128">
         <v>2.15</v>
@@ -27873,7 +27894,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27951,10 +27972,10 @@
         <v>0.33</v>
       </c>
       <c r="AP129">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ129">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -28079,7 +28100,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28285,7 +28306,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28366,7 +28387,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR131">
         <v>1.54</v>
@@ -28491,7 +28512,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28697,7 +28718,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28981,7 +29002,7 @@
         <v>1.14</v>
       </c>
       <c r="AP134">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ134">
         <v>1.15</v>
@@ -29315,7 +29336,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29393,7 +29414,7 @@
         <v>0.33</v>
       </c>
       <c r="AP136">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ136">
         <v>0.92</v>
@@ -29521,7 +29542,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29599,7 +29620,7 @@
         <v>2.14</v>
       </c>
       <c r="AP137">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ137">
         <v>2.17</v>
@@ -30139,7 +30160,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30217,7 +30238,7 @@
         <v>0.29</v>
       </c>
       <c r="AP140">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ140">
         <v>0.5</v>
@@ -30426,7 +30447,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ141">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR141">
         <v>1.48</v>
@@ -30551,7 +30572,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30835,7 +30856,7 @@
         <v>2.13</v>
       </c>
       <c r="AP143">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ143">
         <v>2.25</v>
@@ -30963,7 +30984,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31044,7 +31065,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ144">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -31169,7 +31190,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31250,7 +31271,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ145">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31375,7 +31396,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31453,7 +31474,7 @@
         <v>0.71</v>
       </c>
       <c r="AP146">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ146">
         <v>0.92</v>
@@ -31865,7 +31886,7 @@
         <v>1.14</v>
       </c>
       <c r="AP148">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ148">
         <v>1.42</v>
@@ -32071,10 +32092,10 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ149">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR149">
         <v>2.17</v>
@@ -32405,7 +32426,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32486,7 +32507,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ151">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR151">
         <v>1.96</v>
@@ -32689,7 +32710,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ152">
         <v>1.08</v>
@@ -32817,7 +32838,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33023,7 +33044,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33104,7 +33125,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ154">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33435,7 +33456,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33513,7 +33534,7 @@
         <v>0.5</v>
       </c>
       <c r="AP156">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ156">
         <v>1.08</v>
@@ -33641,7 +33662,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33722,7 +33743,7 @@
         <v>1</v>
       </c>
       <c r="AQ157">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR157">
         <v>1.22</v>
@@ -33847,7 +33868,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34259,7 +34280,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34337,7 +34358,7 @@
         <v>2</v>
       </c>
       <c r="AP160">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ160">
         <v>1.92</v>
@@ -34465,7 +34486,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34543,7 +34564,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ161">
         <v>1.42</v>
@@ -34671,7 +34692,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34752,7 +34773,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ162">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR162">
         <v>1.42</v>
@@ -34877,7 +34898,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34958,7 +34979,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ163">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR163">
         <v>1.3</v>
@@ -35083,7 +35104,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35161,7 +35182,7 @@
         <v>0.25</v>
       </c>
       <c r="AP164">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ164">
         <v>0.5</v>
@@ -35370,7 +35391,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ165">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR165">
         <v>1.46</v>
@@ -35701,7 +35722,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35779,7 +35800,7 @@
         <v>2.22</v>
       </c>
       <c r="AP167">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ167">
         <v>2.25</v>
@@ -35907,7 +35928,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -35985,10 +36006,10 @@
         <v>1.78</v>
       </c>
       <c r="AP168">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ168">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR168">
         <v>1.59</v>
@@ -36113,7 +36134,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36397,10 +36418,10 @@
         <v>0.11</v>
       </c>
       <c r="AP170">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ170">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR170">
         <v>1.47</v>
@@ -36525,7 +36546,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -37018,7 +37039,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ173">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR173">
         <v>1.38</v>
@@ -37143,7 +37164,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37349,7 +37370,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37427,7 +37448,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ175">
         <v>0.5</v>
@@ -37555,7 +37576,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37967,7 +37988,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38048,7 +38069,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ178">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR178">
         <v>1.36</v>
@@ -38254,7 +38275,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ179">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR179">
         <v>1.41</v>
@@ -38379,7 +38400,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38585,7 +38606,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38663,7 +38684,7 @@
         <v>0.78</v>
       </c>
       <c r="AP181">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ181">
         <v>1.08</v>
@@ -38869,10 +38890,10 @@
         <v>1.7</v>
       </c>
       <c r="AP182">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ182">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR182">
         <v>2.47</v>
@@ -39075,7 +39096,7 @@
         <v>2.11</v>
       </c>
       <c r="AP183">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ183">
         <v>2.17</v>
@@ -39203,7 +39224,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39281,10 +39302,10 @@
         <v>1.33</v>
       </c>
       <c r="AP184">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ184">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR184">
         <v>1.55</v>
@@ -39409,7 +39430,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39693,7 +39714,7 @@
         <v>0.7</v>
       </c>
       <c r="AP186">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ186">
         <v>0.67</v>
@@ -39902,7 +39923,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ187">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR187">
         <v>1.47</v>
@@ -40027,7 +40048,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40105,7 +40126,7 @@
         <v>1.7</v>
       </c>
       <c r="AP188">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ188">
         <v>1.5</v>
@@ -40233,7 +40254,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40311,10 +40332,10 @@
         <v>0.1</v>
       </c>
       <c r="AP189">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ189">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR189">
         <v>1.24</v>
@@ -40726,7 +40747,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ191">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR191">
         <v>1.56</v>
@@ -40851,7 +40872,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -41057,7 +41078,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41469,7 +41490,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41753,7 +41774,7 @@
         <v>2.3</v>
       </c>
       <c r="AP196">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ196">
         <v>2.25</v>
@@ -41881,7 +41902,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42293,7 +42314,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42374,7 +42395,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ199">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR199">
         <v>1.37</v>
@@ -42577,10 +42598,10 @@
         <v>1.55</v>
       </c>
       <c r="AP200">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ200">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR200">
         <v>1.47</v>
@@ -42705,7 +42726,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42783,7 +42804,7 @@
         <v>2</v>
       </c>
       <c r="AP201">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ201">
         <v>2.17</v>
@@ -42911,7 +42932,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -42989,10 +43010,10 @@
         <v>0.91</v>
       </c>
       <c r="AP202">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ202">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR202">
         <v>1.47</v>
@@ -43401,10 +43422,10 @@
         <v>0.18</v>
       </c>
       <c r="AP204">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ204">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="AR204">
         <v>1.47</v>
@@ -43607,7 +43628,7 @@
         <v>0.73</v>
       </c>
       <c r="AP205">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ205">
         <v>0.67</v>
@@ -43735,7 +43756,7 @@
         <v>231</v>
       </c>
       <c r="P206" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44019,7 +44040,7 @@
         <v>1.64</v>
       </c>
       <c r="AP207">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AQ207">
         <v>1.5</v>
@@ -44147,7 +44168,7 @@
         <v>233</v>
       </c>
       <c r="P208" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -44228,7 +44249,7 @@
         <v>1</v>
       </c>
       <c r="AQ208">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR208">
         <v>1.84</v>
@@ -44353,7 +44374,7 @@
         <v>97</v>
       </c>
       <c r="P209" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q209">
         <v>4.5</v>
@@ -44559,7 +44580,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44765,7 +44786,7 @@
         <v>96</v>
       </c>
       <c r="P211" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45177,7 +45198,7 @@
         <v>96</v>
       </c>
       <c r="P213" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q213">
         <v>3.4</v>
@@ -45383,7 +45404,7 @@
         <v>235</v>
       </c>
       <c r="P214" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q214">
         <v>2.5</v>
@@ -45464,7 +45485,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ214">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR214">
         <v>1.52</v>
@@ -45589,7 +45610,7 @@
         <v>104</v>
       </c>
       <c r="P215" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q215">
         <v>4.75</v>
@@ -45795,7 +45816,7 @@
         <v>96</v>
       </c>
       <c r="P216" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q216">
         <v>2.1</v>
@@ -46158,6 +46179,1448 @@
       </c>
       <c r="BP217">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7492037</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45723.6875</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>70</v>
+      </c>
+      <c r="H218" t="s">
+        <v>75</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+      <c r="L218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>3</v>
+      </c>
+      <c r="N218">
+        <v>4</v>
+      </c>
+      <c r="O218" t="s">
+        <v>171</v>
+      </c>
+      <c r="P218" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q218">
+        <v>3.1</v>
+      </c>
+      <c r="R218">
+        <v>2.25</v>
+      </c>
+      <c r="S218">
+        <v>3.2</v>
+      </c>
+      <c r="T218">
+        <v>1.36</v>
+      </c>
+      <c r="U218">
+        <v>3</v>
+      </c>
+      <c r="V218">
+        <v>2.63</v>
+      </c>
+      <c r="W218">
+        <v>1.44</v>
+      </c>
+      <c r="X218">
+        <v>7</v>
+      </c>
+      <c r="Y218">
+        <v>1.1</v>
+      </c>
+      <c r="Z218">
+        <v>2.56</v>
+      </c>
+      <c r="AA218">
+        <v>3.45</v>
+      </c>
+      <c r="AB218">
+        <v>2.83</v>
+      </c>
+      <c r="AC218">
+        <v>1.04</v>
+      </c>
+      <c r="AD218">
+        <v>12</v>
+      </c>
+      <c r="AE218">
+        <v>1.26</v>
+      </c>
+      <c r="AF218">
+        <v>4</v>
+      </c>
+      <c r="AG218">
+        <v>1.75</v>
+      </c>
+      <c r="AH218">
+        <v>1.95</v>
+      </c>
+      <c r="AI218">
+        <v>1.62</v>
+      </c>
+      <c r="AJ218">
+        <v>2.2</v>
+      </c>
+      <c r="AK218">
+        <v>1.44</v>
+      </c>
+      <c r="AL218">
+        <v>1.29</v>
+      </c>
+      <c r="AM218">
+        <v>1.52</v>
+      </c>
+      <c r="AN218">
+        <v>1.67</v>
+      </c>
+      <c r="AO218">
+        <v>1.67</v>
+      </c>
+      <c r="AP218">
+        <v>1.54</v>
+      </c>
+      <c r="AQ218">
+        <v>1.77</v>
+      </c>
+      <c r="AR218">
+        <v>1.45</v>
+      </c>
+      <c r="AS218">
+        <v>1.22</v>
+      </c>
+      <c r="AT218">
+        <v>2.67</v>
+      </c>
+      <c r="AU218">
+        <v>5</v>
+      </c>
+      <c r="AV218">
+        <v>9</v>
+      </c>
+      <c r="AW218">
+        <v>8</v>
+      </c>
+      <c r="AX218">
+        <v>8</v>
+      </c>
+      <c r="AY218">
+        <v>16</v>
+      </c>
+      <c r="AZ218">
+        <v>18</v>
+      </c>
+      <c r="BA218">
+        <v>4</v>
+      </c>
+      <c r="BB218">
+        <v>3</v>
+      </c>
+      <c r="BC218">
+        <v>7</v>
+      </c>
+      <c r="BD218">
+        <v>1.93</v>
+      </c>
+      <c r="BE218">
+        <v>6.4</v>
+      </c>
+      <c r="BF218">
+        <v>2.07</v>
+      </c>
+      <c r="BG218">
+        <v>1.28</v>
+      </c>
+      <c r="BH218">
+        <v>3.3</v>
+      </c>
+      <c r="BI218">
+        <v>1.49</v>
+      </c>
+      <c r="BJ218">
+        <v>2.4</v>
+      </c>
+      <c r="BK218">
+        <v>1.78</v>
+      </c>
+      <c r="BL218">
+        <v>1.91</v>
+      </c>
+      <c r="BM218">
+        <v>2.23</v>
+      </c>
+      <c r="BN218">
+        <v>1.56</v>
+      </c>
+      <c r="BO218">
+        <v>2.85</v>
+      </c>
+      <c r="BP218">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7492030</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F219">
+        <v>25</v>
+      </c>
+      <c r="G219" t="s">
+        <v>85</v>
+      </c>
+      <c r="H219" t="s">
+        <v>84</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>1</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+      <c r="M219">
+        <v>2</v>
+      </c>
+      <c r="N219">
+        <v>2</v>
+      </c>
+      <c r="O219" t="s">
+        <v>96</v>
+      </c>
+      <c r="P219" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q219">
+        <v>1.67</v>
+      </c>
+      <c r="R219">
+        <v>2.75</v>
+      </c>
+      <c r="S219">
+        <v>9</v>
+      </c>
+      <c r="T219">
+        <v>1.25</v>
+      </c>
+      <c r="U219">
+        <v>3.75</v>
+      </c>
+      <c r="V219">
+        <v>2.25</v>
+      </c>
+      <c r="W219">
+        <v>1.57</v>
+      </c>
+      <c r="X219">
+        <v>5.5</v>
+      </c>
+      <c r="Y219">
+        <v>1.14</v>
+      </c>
+      <c r="Z219">
+        <v>1.25</v>
+      </c>
+      <c r="AA219">
+        <v>6.9</v>
+      </c>
+      <c r="AB219">
+        <v>11</v>
+      </c>
+      <c r="AC219">
+        <v>1.01</v>
+      </c>
+      <c r="AD219">
+        <v>23</v>
+      </c>
+      <c r="AE219">
+        <v>1.16</v>
+      </c>
+      <c r="AF219">
+        <v>5.5</v>
+      </c>
+      <c r="AG219">
+        <v>1.45</v>
+      </c>
+      <c r="AH219">
+        <v>2.63</v>
+      </c>
+      <c r="AI219">
+        <v>2</v>
+      </c>
+      <c r="AJ219">
+        <v>1.75</v>
+      </c>
+      <c r="AK219">
+        <v>1.04</v>
+      </c>
+      <c r="AL219">
+        <v>1.12</v>
+      </c>
+      <c r="AM219">
+        <v>3.9</v>
+      </c>
+      <c r="AN219">
+        <v>2.25</v>
+      </c>
+      <c r="AO219">
+        <v>1.42</v>
+      </c>
+      <c r="AP219">
+        <v>2.08</v>
+      </c>
+      <c r="AQ219">
+        <v>1.54</v>
+      </c>
+      <c r="AR219">
+        <v>2.05</v>
+      </c>
+      <c r="AS219">
+        <v>1.19</v>
+      </c>
+      <c r="AT219">
+        <v>3.24</v>
+      </c>
+      <c r="AU219">
+        <v>5</v>
+      </c>
+      <c r="AV219">
+        <v>8</v>
+      </c>
+      <c r="AW219">
+        <v>13</v>
+      </c>
+      <c r="AX219">
+        <v>4</v>
+      </c>
+      <c r="AY219">
+        <v>22</v>
+      </c>
+      <c r="AZ219">
+        <v>12</v>
+      </c>
+      <c r="BA219">
+        <v>10</v>
+      </c>
+      <c r="BB219">
+        <v>3</v>
+      </c>
+      <c r="BC219">
+        <v>13</v>
+      </c>
+      <c r="BD219">
+        <v>1.11</v>
+      </c>
+      <c r="BE219">
+        <v>10</v>
+      </c>
+      <c r="BF219">
+        <v>6.75</v>
+      </c>
+      <c r="BG219">
+        <v>1.3</v>
+      </c>
+      <c r="BH219">
+        <v>3.15</v>
+      </c>
+      <c r="BI219">
+        <v>1.52</v>
+      </c>
+      <c r="BJ219">
+        <v>2.33</v>
+      </c>
+      <c r="BK219">
+        <v>1.82</v>
+      </c>
+      <c r="BL219">
+        <v>1.86</v>
+      </c>
+      <c r="BM219">
+        <v>2.23</v>
+      </c>
+      <c r="BN219">
+        <v>1.56</v>
+      </c>
+      <c r="BO219">
+        <v>2.9</v>
+      </c>
+      <c r="BP219">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7492031</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F220">
+        <v>25</v>
+      </c>
+      <c r="G220" t="s">
+        <v>87</v>
+      </c>
+      <c r="H220" t="s">
+        <v>83</v>
+      </c>
+      <c r="I220">
+        <v>2</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>3</v>
+      </c>
+      <c r="L220">
+        <v>2</v>
+      </c>
+      <c r="M220">
+        <v>3</v>
+      </c>
+      <c r="N220">
+        <v>5</v>
+      </c>
+      <c r="O220" t="s">
+        <v>236</v>
+      </c>
+      <c r="P220" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q220">
+        <v>1.4</v>
+      </c>
+      <c r="R220">
+        <v>3.4</v>
+      </c>
+      <c r="S220">
+        <v>12</v>
+      </c>
+      <c r="T220">
+        <v>1.17</v>
+      </c>
+      <c r="U220">
+        <v>5</v>
+      </c>
+      <c r="V220">
+        <v>1.83</v>
+      </c>
+      <c r="W220">
+        <v>1.83</v>
+      </c>
+      <c r="X220">
+        <v>3.75</v>
+      </c>
+      <c r="Y220">
+        <v>1.25</v>
+      </c>
+      <c r="Z220">
+        <v>1.11</v>
+      </c>
+      <c r="AA220">
+        <v>13</v>
+      </c>
+      <c r="AB220">
+        <v>17</v>
+      </c>
+      <c r="AC220">
+        <v>1.01</v>
+      </c>
+      <c r="AD220">
+        <v>14</v>
+      </c>
+      <c r="AE220">
+        <v>1.07</v>
+      </c>
+      <c r="AF220">
+        <v>8.5</v>
+      </c>
+      <c r="AG220">
+        <v>1.3</v>
+      </c>
+      <c r="AH220">
+        <v>3.33</v>
+      </c>
+      <c r="AI220">
+        <v>2</v>
+      </c>
+      <c r="AJ220">
+        <v>1.75</v>
+      </c>
+      <c r="AK220">
+        <v>1.01</v>
+      </c>
+      <c r="AL220">
+        <v>1.07</v>
+      </c>
+      <c r="AM220">
+        <v>5.75</v>
+      </c>
+      <c r="AN220">
+        <v>2.83</v>
+      </c>
+      <c r="AO220">
+        <v>0.25</v>
+      </c>
+      <c r="AP220">
+        <v>2.62</v>
+      </c>
+      <c r="AQ220">
+        <v>0.46</v>
+      </c>
+      <c r="AR220">
+        <v>2.53</v>
+      </c>
+      <c r="AS220">
+        <v>1.27</v>
+      </c>
+      <c r="AT220">
+        <v>3.8</v>
+      </c>
+      <c r="AU220">
+        <v>6</v>
+      </c>
+      <c r="AV220">
+        <v>6</v>
+      </c>
+      <c r="AW220">
+        <v>9</v>
+      </c>
+      <c r="AX220">
+        <v>3</v>
+      </c>
+      <c r="AY220">
+        <v>16</v>
+      </c>
+      <c r="AZ220">
+        <v>9</v>
+      </c>
+      <c r="BA220">
+        <v>9</v>
+      </c>
+      <c r="BB220">
+        <v>3</v>
+      </c>
+      <c r="BC220">
+        <v>12</v>
+      </c>
+      <c r="BD220">
+        <v>1.06</v>
+      </c>
+      <c r="BE220">
+        <v>13</v>
+      </c>
+      <c r="BF220">
+        <v>9</v>
+      </c>
+      <c r="BG220">
+        <v>1.2</v>
+      </c>
+      <c r="BH220">
+        <v>3.9</v>
+      </c>
+      <c r="BI220">
+        <v>1.37</v>
+      </c>
+      <c r="BJ220">
+        <v>2.8</v>
+      </c>
+      <c r="BK220">
+        <v>1.6</v>
+      </c>
+      <c r="BL220">
+        <v>2.17</v>
+      </c>
+      <c r="BM220">
+        <v>1.94</v>
+      </c>
+      <c r="BN220">
+        <v>1.76</v>
+      </c>
+      <c r="BO220">
+        <v>2.4</v>
+      </c>
+      <c r="BP220">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7492032</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>76</v>
+      </c>
+      <c r="H221" t="s">
+        <v>74</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>1</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+      <c r="M221">
+        <v>1</v>
+      </c>
+      <c r="N221">
+        <v>1</v>
+      </c>
+      <c r="O221" t="s">
+        <v>96</v>
+      </c>
+      <c r="P221" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q221">
+        <v>2</v>
+      </c>
+      <c r="R221">
+        <v>2.4</v>
+      </c>
+      <c r="S221">
+        <v>6</v>
+      </c>
+      <c r="T221">
+        <v>1.33</v>
+      </c>
+      <c r="U221">
+        <v>3.25</v>
+      </c>
+      <c r="V221">
+        <v>2.5</v>
+      </c>
+      <c r="W221">
+        <v>1.5</v>
+      </c>
+      <c r="X221">
+        <v>6.5</v>
+      </c>
+      <c r="Y221">
+        <v>1.11</v>
+      </c>
+      <c r="Z221">
+        <v>1.48</v>
+      </c>
+      <c r="AA221">
+        <v>4.8</v>
+      </c>
+      <c r="AB221">
+        <v>6.6</v>
+      </c>
+      <c r="AC221">
+        <v>1.03</v>
+      </c>
+      <c r="AD221">
+        <v>15</v>
+      </c>
+      <c r="AE221">
+        <v>1.2</v>
+      </c>
+      <c r="AF221">
+        <v>4.5</v>
+      </c>
+      <c r="AG221">
+        <v>1.67</v>
+      </c>
+      <c r="AH221">
+        <v>2.12</v>
+      </c>
+      <c r="AI221">
+        <v>1.8</v>
+      </c>
+      <c r="AJ221">
+        <v>1.95</v>
+      </c>
+      <c r="AK221">
+        <v>1.12</v>
+      </c>
+      <c r="AL221">
+        <v>1.19</v>
+      </c>
+      <c r="AM221">
+        <v>2.6</v>
+      </c>
+      <c r="AN221">
+        <v>2</v>
+      </c>
+      <c r="AO221">
+        <v>1.08</v>
+      </c>
+      <c r="AP221">
+        <v>1.85</v>
+      </c>
+      <c r="AQ221">
+        <v>1.23</v>
+      </c>
+      <c r="AR221">
+        <v>1.67</v>
+      </c>
+      <c r="AS221">
+        <v>1.07</v>
+      </c>
+      <c r="AT221">
+        <v>2.74</v>
+      </c>
+      <c r="AU221">
+        <v>2</v>
+      </c>
+      <c r="AV221">
+        <v>2</v>
+      </c>
+      <c r="AW221">
+        <v>13</v>
+      </c>
+      <c r="AX221">
+        <v>5</v>
+      </c>
+      <c r="AY221">
+        <v>18</v>
+      </c>
+      <c r="AZ221">
+        <v>10</v>
+      </c>
+      <c r="BA221">
+        <v>12</v>
+      </c>
+      <c r="BB221">
+        <v>3</v>
+      </c>
+      <c r="BC221">
+        <v>15</v>
+      </c>
+      <c r="BD221">
+        <v>1.34</v>
+      </c>
+      <c r="BE221">
+        <v>7.5</v>
+      </c>
+      <c r="BF221">
+        <v>3.55</v>
+      </c>
+      <c r="BG221">
+        <v>1.26</v>
+      </c>
+      <c r="BH221">
+        <v>3.4</v>
+      </c>
+      <c r="BI221">
+        <v>1.47</v>
+      </c>
+      <c r="BJ221">
+        <v>2.48</v>
+      </c>
+      <c r="BK221">
+        <v>1.75</v>
+      </c>
+      <c r="BL221">
+        <v>1.95</v>
+      </c>
+      <c r="BM221">
+        <v>2.15</v>
+      </c>
+      <c r="BN221">
+        <v>1.61</v>
+      </c>
+      <c r="BO221">
+        <v>2.7</v>
+      </c>
+      <c r="BP221">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7492036</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>77</v>
+      </c>
+      <c r="H222" t="s">
+        <v>78</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>1</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
+      </c>
+      <c r="L222">
+        <v>1</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>2</v>
+      </c>
+      <c r="O222" t="s">
+        <v>237</v>
+      </c>
+      <c r="P222" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q222">
+        <v>2.38</v>
+      </c>
+      <c r="R222">
+        <v>2.2</v>
+      </c>
+      <c r="S222">
+        <v>5</v>
+      </c>
+      <c r="T222">
+        <v>1.4</v>
+      </c>
+      <c r="U222">
+        <v>2.75</v>
+      </c>
+      <c r="V222">
+        <v>2.75</v>
+      </c>
+      <c r="W222">
+        <v>1.4</v>
+      </c>
+      <c r="X222">
+        <v>8</v>
+      </c>
+      <c r="Y222">
+        <v>1.08</v>
+      </c>
+      <c r="Z222">
+        <v>1.73</v>
+      </c>
+      <c r="AA222">
+        <v>4</v>
+      </c>
+      <c r="AB222">
+        <v>4.75</v>
+      </c>
+      <c r="AC222">
+        <v>1.04</v>
+      </c>
+      <c r="AD222">
+        <v>13</v>
+      </c>
+      <c r="AE222">
+        <v>1.24</v>
+      </c>
+      <c r="AF222">
+        <v>4.2</v>
+      </c>
+      <c r="AG222">
+        <v>1.85</v>
+      </c>
+      <c r="AH222">
+        <v>1.96</v>
+      </c>
+      <c r="AI222">
+        <v>1.8</v>
+      </c>
+      <c r="AJ222">
+        <v>1.95</v>
+      </c>
+      <c r="AK222">
+        <v>1.18</v>
+      </c>
+      <c r="AL222">
+        <v>1.25</v>
+      </c>
+      <c r="AM222">
+        <v>2.15</v>
+      </c>
+      <c r="AN222">
+        <v>1.17</v>
+      </c>
+      <c r="AO222">
+        <v>1</v>
+      </c>
+      <c r="AP222">
+        <v>1.15</v>
+      </c>
+      <c r="AQ222">
+        <v>1</v>
+      </c>
+      <c r="AR222">
+        <v>1.49</v>
+      </c>
+      <c r="AS222">
+        <v>1.15</v>
+      </c>
+      <c r="AT222">
+        <v>2.64</v>
+      </c>
+      <c r="AU222">
+        <v>5</v>
+      </c>
+      <c r="AV222">
+        <v>5</v>
+      </c>
+      <c r="AW222">
+        <v>12</v>
+      </c>
+      <c r="AX222">
+        <v>10</v>
+      </c>
+      <c r="AY222">
+        <v>21</v>
+      </c>
+      <c r="AZ222">
+        <v>19</v>
+      </c>
+      <c r="BA222">
+        <v>6</v>
+      </c>
+      <c r="BB222">
+        <v>6</v>
+      </c>
+      <c r="BC222">
+        <v>12</v>
+      </c>
+      <c r="BD222">
+        <v>1.46</v>
+      </c>
+      <c r="BE222">
+        <v>6.75</v>
+      </c>
+      <c r="BF222">
+        <v>3.05</v>
+      </c>
+      <c r="BG222">
+        <v>1.33</v>
+      </c>
+      <c r="BH222">
+        <v>2.95</v>
+      </c>
+      <c r="BI222">
+        <v>1.57</v>
+      </c>
+      <c r="BJ222">
+        <v>2.23</v>
+      </c>
+      <c r="BK222">
+        <v>1.91</v>
+      </c>
+      <c r="BL222">
+        <v>1.77</v>
+      </c>
+      <c r="BM222">
+        <v>2.4</v>
+      </c>
+      <c r="BN222">
+        <v>1.49</v>
+      </c>
+      <c r="BO222">
+        <v>3.15</v>
+      </c>
+      <c r="BP222">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7492038</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>81</v>
+      </c>
+      <c r="H223" t="s">
+        <v>80</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>1</v>
+      </c>
+      <c r="K223">
+        <v>2</v>
+      </c>
+      <c r="L223">
+        <v>2</v>
+      </c>
+      <c r="M223">
+        <v>2</v>
+      </c>
+      <c r="N223">
+        <v>4</v>
+      </c>
+      <c r="O223" t="s">
+        <v>238</v>
+      </c>
+      <c r="P223" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q223">
+        <v>5.5</v>
+      </c>
+      <c r="R223">
+        <v>2.5</v>
+      </c>
+      <c r="S223">
+        <v>2</v>
+      </c>
+      <c r="T223">
+        <v>1.25</v>
+      </c>
+      <c r="U223">
+        <v>3.75</v>
+      </c>
+      <c r="V223">
+        <v>2.2</v>
+      </c>
+      <c r="W223">
+        <v>1.62</v>
+      </c>
+      <c r="X223">
+        <v>5</v>
+      </c>
+      <c r="Y223">
+        <v>1.17</v>
+      </c>
+      <c r="Z223">
+        <v>6</v>
+      </c>
+      <c r="AA223">
+        <v>4.75</v>
+      </c>
+      <c r="AB223">
+        <v>1.52</v>
+      </c>
+      <c r="AC223">
+        <v>1.01</v>
+      </c>
+      <c r="AD223">
+        <v>19</v>
+      </c>
+      <c r="AE223">
+        <v>1.16</v>
+      </c>
+      <c r="AF223">
+        <v>5.5</v>
+      </c>
+      <c r="AG223">
+        <v>1.48</v>
+      </c>
+      <c r="AH223">
+        <v>2.54</v>
+      </c>
+      <c r="AI223">
+        <v>1.62</v>
+      </c>
+      <c r="AJ223">
+        <v>2.2</v>
+      </c>
+      <c r="AK223">
+        <v>2.45</v>
+      </c>
+      <c r="AL223">
+        <v>1.2</v>
+      </c>
+      <c r="AM223">
+        <v>1.15</v>
+      </c>
+      <c r="AN223">
+        <v>0.83</v>
+      </c>
+      <c r="AO223">
+        <v>1.45</v>
+      </c>
+      <c r="AP223">
+        <v>0.85</v>
+      </c>
+      <c r="AQ223">
+        <v>1.42</v>
+      </c>
+      <c r="AR223">
+        <v>1.19</v>
+      </c>
+      <c r="AS223">
+        <v>1.28</v>
+      </c>
+      <c r="AT223">
+        <v>2.47</v>
+      </c>
+      <c r="AU223">
+        <v>6</v>
+      </c>
+      <c r="AV223">
+        <v>3</v>
+      </c>
+      <c r="AW223">
+        <v>12</v>
+      </c>
+      <c r="AX223">
+        <v>3</v>
+      </c>
+      <c r="AY223">
+        <v>20</v>
+      </c>
+      <c r="AZ223">
+        <v>6</v>
+      </c>
+      <c r="BA223">
+        <v>3</v>
+      </c>
+      <c r="BB223">
+        <v>1</v>
+      </c>
+      <c r="BC223">
+        <v>4</v>
+      </c>
+      <c r="BD223">
+        <v>3.15</v>
+      </c>
+      <c r="BE223">
+        <v>7</v>
+      </c>
+      <c r="BF223">
+        <v>1.42</v>
+      </c>
+      <c r="BG223">
+        <v>1.29</v>
+      </c>
+      <c r="BH223">
+        <v>3.15</v>
+      </c>
+      <c r="BI223">
+        <v>1.49</v>
+      </c>
+      <c r="BJ223">
+        <v>2.4</v>
+      </c>
+      <c r="BK223">
+        <v>1.8</v>
+      </c>
+      <c r="BL223">
+        <v>1.88</v>
+      </c>
+      <c r="BM223">
+        <v>2.23</v>
+      </c>
+      <c r="BN223">
+        <v>1.56</v>
+      </c>
+      <c r="BO223">
+        <v>2.9</v>
+      </c>
+      <c r="BP223">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7492035</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45724.60416666666</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>73</v>
+      </c>
+      <c r="H224" t="s">
+        <v>71</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>0</v>
+      </c>
+      <c r="O224" t="s">
+        <v>96</v>
+      </c>
+      <c r="P224" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q224">
+        <v>3.1</v>
+      </c>
+      <c r="R224">
+        <v>2.2</v>
+      </c>
+      <c r="S224">
+        <v>3.2</v>
+      </c>
+      <c r="T224">
+        <v>1.36</v>
+      </c>
+      <c r="U224">
+        <v>3</v>
+      </c>
+      <c r="V224">
+        <v>2.63</v>
+      </c>
+      <c r="W224">
+        <v>1.44</v>
+      </c>
+      <c r="X224">
+        <v>7</v>
+      </c>
+      <c r="Y224">
+        <v>1.1</v>
+      </c>
+      <c r="Z224">
+        <v>2.59</v>
+      </c>
+      <c r="AA224">
+        <v>3.5</v>
+      </c>
+      <c r="AB224">
+        <v>2.76</v>
+      </c>
+      <c r="AC224">
+        <v>1.04</v>
+      </c>
+      <c r="AD224">
+        <v>13</v>
+      </c>
+      <c r="AE224">
+        <v>1.24</v>
+      </c>
+      <c r="AF224">
+        <v>4.2</v>
+      </c>
+      <c r="AG224">
+        <v>1.65</v>
+      </c>
+      <c r="AH224">
+        <v>2.15</v>
+      </c>
+      <c r="AI224">
+        <v>1.62</v>
+      </c>
+      <c r="AJ224">
+        <v>2.2</v>
+      </c>
+      <c r="AK224">
+        <v>1.47</v>
+      </c>
+      <c r="AL224">
+        <v>1.29</v>
+      </c>
+      <c r="AM224">
+        <v>1.5</v>
+      </c>
+      <c r="AN224">
+        <v>2.27</v>
+      </c>
+      <c r="AO224">
+        <v>1.33</v>
+      </c>
+      <c r="AP224">
+        <v>2.17</v>
+      </c>
+      <c r="AQ224">
+        <v>1.31</v>
+      </c>
+      <c r="AR224">
+        <v>1.49</v>
+      </c>
+      <c r="AS224">
+        <v>1.13</v>
+      </c>
+      <c r="AT224">
+        <v>2.62</v>
+      </c>
+      <c r="AU224">
+        <v>3</v>
+      </c>
+      <c r="AV224">
+        <v>4</v>
+      </c>
+      <c r="AW224">
+        <v>8</v>
+      </c>
+      <c r="AX224">
+        <v>15</v>
+      </c>
+      <c r="AY224">
+        <v>13</v>
+      </c>
+      <c r="AZ224">
+        <v>23</v>
+      </c>
+      <c r="BA224">
+        <v>2</v>
+      </c>
+      <c r="BB224">
+        <v>6</v>
+      </c>
+      <c r="BC224">
+        <v>8</v>
+      </c>
+      <c r="BD224">
+        <v>1.82</v>
+      </c>
+      <c r="BE224">
+        <v>5.8</v>
+      </c>
+      <c r="BF224">
+        <v>2.23</v>
+      </c>
+      <c r="BG224">
+        <v>1.41</v>
+      </c>
+      <c r="BH224">
+        <v>2.65</v>
+      </c>
+      <c r="BI224">
+        <v>1.68</v>
+      </c>
+      <c r="BJ224">
+        <v>2.02</v>
+      </c>
+      <c r="BK224">
+        <v>2.12</v>
+      </c>
+      <c r="BL224">
+        <v>1.63</v>
+      </c>
+      <c r="BM224">
+        <v>2.7</v>
+      </c>
+      <c r="BN224">
+        <v>1.4</v>
+      </c>
+      <c r="BO224">
+        <v>3.65</v>
+      </c>
+      <c r="BP224">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="369">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,9 @@
     <t>['30', '46']</t>
   </si>
   <si>
+    <t>['13']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1116,6 +1119,9 @@
   <si>
     <t>['15', '55']</t>
   </si>
+  <si>
+    <t>['62', '78']</t>
+  </si>
 </sst>
 </file>
 
@@ -1476,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP224"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1732,7 +1738,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2144,7 +2150,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2350,7 +2356,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2556,7 +2562,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2843,7 +2849,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3174,7 +3180,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3380,7 +3386,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3461,7 +3467,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ10">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3792,7 +3798,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3998,7 +4004,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4204,7 +4210,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4282,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ14">
         <v>1.08</v>
@@ -4410,7 +4416,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4822,7 +4828,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5440,7 +5446,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5521,7 +5527,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ20">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR20">
         <v>1.89</v>
@@ -5727,7 +5733,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ21">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR21">
         <v>1.16</v>
@@ -5852,7 +5858,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6264,7 +6270,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6470,7 +6476,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6676,7 +6682,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -7088,7 +7094,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7294,7 +7300,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7500,7 +7506,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7706,7 +7712,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7912,7 +7918,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8118,7 +8124,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8402,7 +8408,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ34">
         <v>1.42</v>
@@ -8530,7 +8536,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9148,7 +9154,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9435,7 +9441,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ39">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9560,7 +9566,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9641,7 +9647,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ40">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9766,7 +9772,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9972,7 +9978,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10384,7 +10390,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10590,7 +10596,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10796,7 +10802,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11208,7 +11214,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11620,7 +11626,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11826,7 +11832,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -12032,7 +12038,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12444,7 +12450,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12522,7 +12528,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ54">
         <v>2.25</v>
@@ -12650,7 +12656,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12856,7 +12862,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -13062,7 +13068,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13474,7 +13480,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13680,7 +13686,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13886,7 +13892,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13967,7 +13973,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ61">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR61">
         <v>1.33</v>
@@ -14298,7 +14304,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14379,7 +14385,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ63">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR63">
         <v>1.07</v>
@@ -14504,7 +14510,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14710,7 +14716,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14916,7 +14922,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15328,7 +15334,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15740,7 +15746,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15946,7 +15952,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16851,7 +16857,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ75">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR75">
         <v>1.82</v>
@@ -16976,7 +16982,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17054,7 +17060,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ76">
         <v>0.46</v>
@@ -17182,7 +17188,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17469,7 +17475,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ78">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -18624,7 +18630,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -19036,7 +19042,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19242,7 +19248,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19860,7 +19866,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -20066,7 +20072,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20478,7 +20484,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20559,7 +20565,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ93">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR93">
         <v>2.3</v>
@@ -21096,7 +21102,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21383,7 +21389,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ97">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR97">
         <v>1.25</v>
@@ -21586,7 +21592,7 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ98">
         <v>1.54</v>
@@ -21714,7 +21720,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22126,7 +22132,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22332,7 +22338,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22538,7 +22544,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22950,7 +22956,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23156,7 +23162,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23362,7 +23368,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23774,7 +23780,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23980,7 +23986,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24061,7 +24067,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ110">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR110">
         <v>2.1</v>
@@ -24186,7 +24192,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24392,7 +24398,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24598,7 +24604,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24676,7 +24682,7 @@
         <v>0.2</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ113">
         <v>1.23</v>
@@ -24804,7 +24810,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24885,7 +24891,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ114">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR114">
         <v>2.04</v>
@@ -25216,7 +25222,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25422,7 +25428,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25834,7 +25840,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -26040,7 +26046,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26246,7 +26252,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26452,7 +26458,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26864,7 +26870,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27070,7 +27076,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27276,7 +27282,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27482,7 +27488,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27688,7 +27694,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27894,7 +27900,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28100,7 +28106,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28306,7 +28312,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28384,7 +28390,7 @@
         <v>1.83</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ131">
         <v>1.77</v>
@@ -28512,7 +28518,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28718,7 +28724,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28799,7 +28805,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ133">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR133">
         <v>1.24</v>
@@ -29211,7 +29217,7 @@
         <v>1</v>
       </c>
       <c r="AQ135">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR135">
         <v>1.23</v>
@@ -29336,7 +29342,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29542,7 +29548,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -30035,7 +30041,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ139">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR139">
         <v>1.27</v>
@@ -30160,7 +30166,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30572,7 +30578,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30984,7 +30990,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31190,7 +31196,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31396,7 +31402,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31680,7 +31686,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ147">
         <v>1.15</v>
@@ -32426,7 +32432,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32838,7 +32844,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32919,7 +32925,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ153">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR153">
         <v>1.26</v>
@@ -33044,7 +33050,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33328,7 +33334,7 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ155">
         <v>0.92</v>
@@ -33456,7 +33462,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33662,7 +33668,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33868,7 +33874,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34280,7 +34286,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34486,7 +34492,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34692,7 +34698,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34898,7 +34904,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -35104,7 +35110,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35597,7 +35603,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ166">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR166">
         <v>1.56</v>
@@ -35722,7 +35728,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35928,7 +35934,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36134,7 +36140,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36546,7 +36552,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36833,7 +36839,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ172">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR172">
         <v>1.31</v>
@@ -37164,7 +37170,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37370,7 +37376,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37576,7 +37582,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37988,7 +37994,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38400,7 +38406,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38478,7 +38484,7 @@
         <v>1.78</v>
       </c>
       <c r="AP180">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ180">
         <v>1.92</v>
@@ -38606,7 +38612,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -39224,7 +39230,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39430,7 +39436,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39511,7 +39517,7 @@
         <v>1</v>
       </c>
       <c r="AQ185">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR185">
         <v>1.84</v>
@@ -39717,7 +39723,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ186">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR186">
         <v>1.5</v>
@@ -40048,7 +40054,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40254,7 +40260,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40872,7 +40878,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -41078,7 +41084,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41490,7 +41496,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41902,7 +41908,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42186,7 +42192,7 @@
         <v>0.3</v>
       </c>
       <c r="AP198">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ198">
         <v>0.5</v>
@@ -42314,7 +42320,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42726,7 +42732,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42932,7 +42938,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -43631,7 +43637,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ205">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR205">
         <v>1.58</v>
@@ -43756,7 +43762,7 @@
         <v>231</v>
       </c>
       <c r="P206" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43837,7 +43843,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ206">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR206">
         <v>1.45</v>
@@ -44168,7 +44174,7 @@
         <v>233</v>
       </c>
       <c r="P208" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -44374,7 +44380,7 @@
         <v>97</v>
       </c>
       <c r="P209" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q209">
         <v>4.5</v>
@@ -44580,7 +44586,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44786,7 +44792,7 @@
         <v>96</v>
       </c>
       <c r="P211" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45198,7 +45204,7 @@
         <v>96</v>
       </c>
       <c r="P213" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q213">
         <v>3.4</v>
@@ -45404,7 +45410,7 @@
         <v>235</v>
       </c>
       <c r="P214" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q214">
         <v>2.5</v>
@@ -45610,7 +45616,7 @@
         <v>104</v>
       </c>
       <c r="P215" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q215">
         <v>4.75</v>
@@ -45688,7 +45694,7 @@
         <v>2.09</v>
       </c>
       <c r="AP215">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ215">
         <v>2.17</v>
@@ -45816,7 +45822,7 @@
         <v>96</v>
       </c>
       <c r="P216" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q216">
         <v>2.1</v>
@@ -46228,7 +46234,7 @@
         <v>171</v>
       </c>
       <c r="P218" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q218">
         <v>3.1</v>
@@ -46434,7 +46440,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q219">
         <v>1.67</v>
@@ -46640,7 +46646,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q220">
         <v>1.4</v>
@@ -46846,7 +46852,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q221">
         <v>2</v>
@@ -46945,16 +46951,16 @@
         <v>2</v>
       </c>
       <c r="AW221">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AX221">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY221">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ221">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA221">
         <v>12</v>
@@ -47258,7 +47264,7 @@
         <v>238</v>
       </c>
       <c r="P223" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q223">
         <v>5.5</v>
@@ -47621,6 +47627,418 @@
       </c>
       <c r="BP224">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7492033</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45725.47916666666</v>
+      </c>
+      <c r="F225">
+        <v>25</v>
+      </c>
+      <c r="G225" t="s">
+        <v>82</v>
+      </c>
+      <c r="H225" t="s">
+        <v>79</v>
+      </c>
+      <c r="I225">
+        <v>1</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>1</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>2</v>
+      </c>
+      <c r="N225">
+        <v>3</v>
+      </c>
+      <c r="O225" t="s">
+        <v>239</v>
+      </c>
+      <c r="P225" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q225">
+        <v>2.2</v>
+      </c>
+      <c r="R225">
+        <v>2.38</v>
+      </c>
+      <c r="S225">
+        <v>4.75</v>
+      </c>
+      <c r="T225">
+        <v>1.3</v>
+      </c>
+      <c r="U225">
+        <v>3.4</v>
+      </c>
+      <c r="V225">
+        <v>2.5</v>
+      </c>
+      <c r="W225">
+        <v>1.5</v>
+      </c>
+      <c r="X225">
+        <v>6</v>
+      </c>
+      <c r="Y225">
+        <v>1.13</v>
+      </c>
+      <c r="Z225">
+        <v>1.67</v>
+      </c>
+      <c r="AA225">
+        <v>4.2</v>
+      </c>
+      <c r="AB225">
+        <v>5</v>
+      </c>
+      <c r="AC225">
+        <v>1.03</v>
+      </c>
+      <c r="AD225">
+        <v>15</v>
+      </c>
+      <c r="AE225">
+        <v>1.22</v>
+      </c>
+      <c r="AF225">
+        <v>4.33</v>
+      </c>
+      <c r="AG225">
+        <v>1.65</v>
+      </c>
+      <c r="AH225">
+        <v>2.16</v>
+      </c>
+      <c r="AI225">
+        <v>1.67</v>
+      </c>
+      <c r="AJ225">
+        <v>2.1</v>
+      </c>
+      <c r="AK225">
+        <v>1.17</v>
+      </c>
+      <c r="AL225">
+        <v>1.24</v>
+      </c>
+      <c r="AM225">
+        <v>2.2</v>
+      </c>
+      <c r="AN225">
+        <v>2</v>
+      </c>
+      <c r="AO225">
+        <v>0.67</v>
+      </c>
+      <c r="AP225">
+        <v>1.85</v>
+      </c>
+      <c r="AQ225">
+        <v>0.85</v>
+      </c>
+      <c r="AR225">
+        <v>1.82</v>
+      </c>
+      <c r="AS225">
+        <v>1.27</v>
+      </c>
+      <c r="AT225">
+        <v>3.09</v>
+      </c>
+      <c r="AU225">
+        <v>4</v>
+      </c>
+      <c r="AV225">
+        <v>4</v>
+      </c>
+      <c r="AW225">
+        <v>11</v>
+      </c>
+      <c r="AX225">
+        <v>8</v>
+      </c>
+      <c r="AY225">
+        <v>18</v>
+      </c>
+      <c r="AZ225">
+        <v>13</v>
+      </c>
+      <c r="BA225">
+        <v>1</v>
+      </c>
+      <c r="BB225">
+        <v>5</v>
+      </c>
+      <c r="BC225">
+        <v>6</v>
+      </c>
+      <c r="BD225">
+        <v>1.45</v>
+      </c>
+      <c r="BE225">
+        <v>7</v>
+      </c>
+      <c r="BF225">
+        <v>3.05</v>
+      </c>
+      <c r="BG225">
+        <v>1.25</v>
+      </c>
+      <c r="BH225">
+        <v>3.45</v>
+      </c>
+      <c r="BI225">
+        <v>1.44</v>
+      </c>
+      <c r="BJ225">
+        <v>2.55</v>
+      </c>
+      <c r="BK225">
+        <v>1.72</v>
+      </c>
+      <c r="BL225">
+        <v>1.98</v>
+      </c>
+      <c r="BM225">
+        <v>2.12</v>
+      </c>
+      <c r="BN225">
+        <v>1.63</v>
+      </c>
+      <c r="BO225">
+        <v>2.65</v>
+      </c>
+      <c r="BP225">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7492034</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45725.5625</v>
+      </c>
+      <c r="F226">
+        <v>25</v>
+      </c>
+      <c r="G226" t="s">
+        <v>72</v>
+      </c>
+      <c r="H226" t="s">
+        <v>86</v>
+      </c>
+      <c r="I226">
+        <v>1</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>1</v>
+      </c>
+      <c r="L226">
+        <v>1</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>2</v>
+      </c>
+      <c r="O226" t="s">
+        <v>97</v>
+      </c>
+      <c r="P226" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q226">
+        <v>2.3</v>
+      </c>
+      <c r="R226">
+        <v>2.38</v>
+      </c>
+      <c r="S226">
+        <v>4.5</v>
+      </c>
+      <c r="T226">
+        <v>1.3</v>
+      </c>
+      <c r="U226">
+        <v>3.4</v>
+      </c>
+      <c r="V226">
+        <v>2.5</v>
+      </c>
+      <c r="W226">
+        <v>1.5</v>
+      </c>
+      <c r="X226">
+        <v>6</v>
+      </c>
+      <c r="Y226">
+        <v>1.13</v>
+      </c>
+      <c r="Z226">
+        <v>1.8</v>
+      </c>
+      <c r="AA226">
+        <v>4</v>
+      </c>
+      <c r="AB226">
+        <v>4.3</v>
+      </c>
+      <c r="AC226">
+        <v>1.03</v>
+      </c>
+      <c r="AD226">
+        <v>15</v>
+      </c>
+      <c r="AE226">
+        <v>1.2</v>
+      </c>
+      <c r="AF226">
+        <v>4.5</v>
+      </c>
+      <c r="AG226">
+        <v>1.62</v>
+      </c>
+      <c r="AH226">
+        <v>2.21</v>
+      </c>
+      <c r="AI226">
+        <v>1.62</v>
+      </c>
+      <c r="AJ226">
+        <v>2.2</v>
+      </c>
+      <c r="AK226">
+        <v>1.23</v>
+      </c>
+      <c r="AL226">
+        <v>1.24</v>
+      </c>
+      <c r="AM226">
+        <v>2</v>
+      </c>
+      <c r="AN226">
+        <v>1</v>
+      </c>
+      <c r="AO226">
+        <v>0.67</v>
+      </c>
+      <c r="AP226">
+        <v>1</v>
+      </c>
+      <c r="AQ226">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR226">
+        <v>1.78</v>
+      </c>
+      <c r="AS226">
+        <v>1.2</v>
+      </c>
+      <c r="AT226">
+        <v>2.98</v>
+      </c>
+      <c r="AU226">
+        <v>4</v>
+      </c>
+      <c r="AV226">
+        <v>6</v>
+      </c>
+      <c r="AW226">
+        <v>13</v>
+      </c>
+      <c r="AX226">
+        <v>18</v>
+      </c>
+      <c r="AY226">
+        <v>24</v>
+      </c>
+      <c r="AZ226">
+        <v>30</v>
+      </c>
+      <c r="BA226">
+        <v>6</v>
+      </c>
+      <c r="BB226">
+        <v>4</v>
+      </c>
+      <c r="BC226">
+        <v>10</v>
+      </c>
+      <c r="BD226">
+        <v>1.5</v>
+      </c>
+      <c r="BE226">
+        <v>6.75</v>
+      </c>
+      <c r="BF226">
+        <v>2.8</v>
+      </c>
+      <c r="BG226">
+        <v>1.24</v>
+      </c>
+      <c r="BH226">
+        <v>3.55</v>
+      </c>
+      <c r="BI226">
+        <v>1.43</v>
+      </c>
+      <c r="BJ226">
+        <v>2.6</v>
+      </c>
+      <c r="BK226">
+        <v>1.7</v>
+      </c>
+      <c r="BL226">
+        <v>2</v>
+      </c>
+      <c r="BM226">
+        <v>2.08</v>
+      </c>
+      <c r="BN226">
+        <v>1.65</v>
+      </c>
+      <c r="BO226">
+        <v>2.65</v>
+      </c>
+      <c r="BP226">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="375">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,21 @@
     <t>['13']</t>
   </si>
   <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['34', '74']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['38', '45+1']</t>
+  </si>
+  <si>
+    <t>['17', '48']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1045,9 +1060,6 @@
     <t>['33', '63']</t>
   </si>
   <si>
-    <t>['83']</t>
-  </si>
-  <si>
     <t>['50']</t>
   </si>
   <si>
@@ -1121,6 +1133,12 @@
   </si>
   <si>
     <t>['62', '78']</t>
+  </si>
+  <si>
+    <t>['58', '79']</t>
+  </si>
+  <si>
+    <t>['7', '28', '47', '81']</t>
   </si>
 </sst>
 </file>
@@ -1482,7 +1500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1738,7 +1756,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2022,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ3">
         <v>0.46</v>
@@ -2150,7 +2168,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2356,7 +2374,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2562,7 +2580,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2640,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ6">
         <v>1.54</v>
@@ -2846,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ7">
         <v>0.85</v>
@@ -3180,7 +3198,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3261,7 +3279,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ9">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3386,7 +3404,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3464,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ10">
         <v>0.6899999999999999</v>
@@ -3670,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3798,7 +3816,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -4004,7 +4022,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4085,7 +4103,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ13">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4210,7 +4228,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4291,7 +4309,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ14">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4416,7 +4434,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4497,7 +4515,7 @@
         <v>1</v>
       </c>
       <c r="AQ15">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4700,10 +4718,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4828,7 +4846,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5321,7 +5339,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ19">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5446,7 +5464,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5730,7 +5748,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ21">
         <v>0.85</v>
@@ -5858,7 +5876,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6270,7 +6288,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6476,7 +6494,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6682,7 +6700,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6763,7 +6781,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ26">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR26">
         <v>1.4</v>
@@ -6966,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7094,7 +7112,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7172,7 +7190,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ28">
         <v>1.54</v>
@@ -7300,7 +7318,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7378,7 +7396,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ29">
         <v>1.77</v>
@@ -7506,7 +7524,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7587,7 +7605,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ30">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7712,7 +7730,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7790,10 +7808,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR31">
         <v>0.65</v>
@@ -7918,7 +7936,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7996,10 +8014,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ32">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.36</v>
@@ -8124,7 +8142,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8411,7 +8429,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ34">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR34">
         <v>1.86</v>
@@ -8536,7 +8554,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8617,7 +8635,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ35">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR35">
         <v>2.58</v>
@@ -8823,7 +8841,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ36">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR36">
         <v>2.62</v>
@@ -9026,7 +9044,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ37">
         <v>1.31</v>
@@ -9154,7 +9172,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9566,7 +9584,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9644,7 +9662,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ40">
         <v>0.6899999999999999</v>
@@ -9772,7 +9790,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9978,7 +9996,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10262,7 +10280,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ43">
         <v>1.23</v>
@@ -10390,7 +10408,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10596,7 +10614,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10802,7 +10820,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11086,10 +11104,10 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ47">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR47">
         <v>2.02</v>
@@ -11214,7 +11232,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11498,10 +11516,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ49">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR49">
         <v>0.41</v>
@@ -11626,7 +11644,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11704,10 +11722,10 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ50">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11832,7 +11850,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11913,7 +11931,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR51">
         <v>1.37</v>
@@ -12038,7 +12056,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12116,7 +12134,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ52">
         <v>1.77</v>
@@ -12450,7 +12468,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12531,7 +12549,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ54">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR54">
         <v>1.7</v>
@@ -12656,7 +12674,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12737,7 +12755,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ55">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>2.29</v>
@@ -12862,7 +12880,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -13068,7 +13086,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13480,7 +13498,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13686,7 +13704,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13764,7 +13782,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ60">
         <v>1.31</v>
@@ -13892,7 +13910,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14304,7 +14322,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14510,7 +14528,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14716,7 +14734,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14794,10 +14812,10 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ65">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR65">
         <v>1.22</v>
@@ -14922,7 +14940,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15000,10 +15018,10 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ66">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15206,10 +15224,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ67">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR67">
         <v>1.52</v>
@@ -15334,7 +15352,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15412,10 +15430,10 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ68">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15746,7 +15764,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15824,7 +15842,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ70">
         <v>2.17</v>
@@ -15952,7 +15970,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16033,7 +16051,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR71">
         <v>1.42</v>
@@ -16236,7 +16254,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ72">
         <v>1.5</v>
@@ -16445,7 +16463,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ73">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>1.3</v>
@@ -16982,7 +17000,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17188,7 +17206,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18502,10 +18520,10 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ83">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR83">
         <v>1.3</v>
@@ -18630,7 +18648,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18708,10 +18726,10 @@
         <v>2.6</v>
       </c>
       <c r="AP84">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ84">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -18914,7 +18932,7 @@
         <v>0.5</v>
       </c>
       <c r="AP85">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ85">
         <v>0.5</v>
@@ -19042,7 +19060,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19120,10 +19138,10 @@
         <v>0.25</v>
       </c>
       <c r="AP86">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ86">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR86">
         <v>1.34</v>
@@ -19248,7 +19266,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19532,10 +19550,10 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ88">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR88">
         <v>1.44</v>
@@ -19738,10 +19756,10 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ89">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19866,7 +19884,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -20072,7 +20090,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20153,7 +20171,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ91">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20484,7 +20502,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20977,7 +20995,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ95">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR95">
         <v>1.86</v>
@@ -21102,7 +21120,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21720,7 +21738,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22132,7 +22150,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22210,7 +22228,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ101">
         <v>0.5</v>
@@ -22338,7 +22356,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22416,7 +22434,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ102">
         <v>2.17</v>
@@ -22544,7 +22562,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22625,7 +22643,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ103">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -22828,7 +22846,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ104">
         <v>0.46</v>
@@ -22956,7 +22974,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23034,10 +23052,10 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ105">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR105">
         <v>1.47</v>
@@ -23162,7 +23180,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23240,7 +23258,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ106">
         <v>1.42</v>
@@ -23368,7 +23386,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23449,7 +23467,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ107">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR107">
         <v>1.93</v>
@@ -23652,10 +23670,10 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ108">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.45</v>
@@ -23780,7 +23798,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23986,7 +24004,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24192,7 +24210,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24398,7 +24416,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24604,7 +24622,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24810,7 +24828,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25222,7 +25240,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25303,7 +25321,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ116">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR116">
         <v>1.64</v>
@@ -25428,7 +25446,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25715,7 +25733,7 @@
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR118">
         <v>1.77</v>
@@ -25840,7 +25858,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25921,7 +25939,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ119">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR119">
         <v>1.52</v>
@@ -26046,7 +26064,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26124,7 +26142,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ120">
         <v>0.46</v>
@@ -26252,7 +26270,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26330,10 +26348,10 @@
         <v>2.43</v>
       </c>
       <c r="AP121">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ121">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR121">
         <v>1.51</v>
@@ -26458,7 +26476,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26536,7 +26554,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ122">
         <v>2.17</v>
@@ -26870,7 +26888,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26948,7 +26966,7 @@
         <v>1.86</v>
       </c>
       <c r="AP124">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ124">
         <v>1.54</v>
@@ -27076,7 +27094,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27282,7 +27300,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27363,7 +27381,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ126">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR126">
         <v>1.74</v>
@@ -27488,7 +27506,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27566,7 +27584,7 @@
         <v>1.86</v>
       </c>
       <c r="AP127">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ127">
         <v>1.5</v>
@@ -27694,7 +27712,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27900,7 +27918,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28106,7 +28124,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28312,7 +28330,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28518,7 +28536,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28599,7 +28617,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR132">
         <v>1.76</v>
@@ -28724,7 +28742,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28802,7 +28820,7 @@
         <v>0.71</v>
       </c>
       <c r="AP133">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ133">
         <v>0.85</v>
@@ -29011,7 +29029,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ134">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR134">
         <v>2.13</v>
@@ -29342,7 +29360,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29423,7 +29441,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ136">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR136">
         <v>1.28</v>
@@ -29548,7 +29566,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29835,7 +29853,7 @@
         <v>1</v>
       </c>
       <c r="AQ138">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR138">
         <v>1.83</v>
@@ -30166,7 +30184,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30450,7 +30468,7 @@
         <v>0.13</v>
       </c>
       <c r="AP141">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ141">
         <v>0.46</v>
@@ -30578,7 +30596,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30656,7 +30674,7 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ142">
         <v>1.5</v>
@@ -30865,7 +30883,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ143">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR143">
         <v>1.59</v>
@@ -30990,7 +31008,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31068,7 +31086,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ144">
         <v>1.54</v>
@@ -31196,7 +31214,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31274,7 +31292,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ145">
         <v>1.42</v>
@@ -31402,7 +31420,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31483,7 +31501,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ146">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR146">
         <v>1.19</v>
@@ -31689,7 +31707,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ147">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR147">
         <v>1.77</v>
@@ -31895,7 +31913,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ148">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR148">
         <v>1.3</v>
@@ -32432,7 +32450,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32719,7 +32737,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ152">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>2.19</v>
@@ -32844,7 +32862,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32922,7 +32940,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ153">
         <v>0.6899999999999999</v>
@@ -33050,7 +33068,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33128,7 +33146,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ154">
         <v>1.23</v>
@@ -33337,7 +33355,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ155">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR155">
         <v>1.87</v>
@@ -33462,7 +33480,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33543,7 +33561,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ156">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR156">
         <v>1.22</v>
@@ -33668,7 +33686,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33874,7 +33892,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34161,7 +34179,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ159">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR159">
         <v>1.95</v>
@@ -34286,7 +34304,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34367,7 +34385,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ160">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR160">
         <v>2.29</v>
@@ -34492,7 +34510,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34573,7 +34591,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ161">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR161">
         <v>2.2</v>
@@ -34698,7 +34716,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34776,7 +34794,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ162">
         <v>1.77</v>
@@ -34904,7 +34922,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34982,7 +35000,7 @@
         <v>0.63</v>
       </c>
       <c r="AP163">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ163">
         <v>1.23</v>
@@ -35110,7 +35128,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35394,7 +35412,7 @@
         <v>1.5</v>
       </c>
       <c r="AP165">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ165">
         <v>1.42</v>
@@ -35600,7 +35618,7 @@
         <v>0.78</v>
       </c>
       <c r="AP166">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ166">
         <v>0.6899999999999999</v>
@@ -35728,7 +35746,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35809,7 +35827,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ167">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR167">
         <v>1.56</v>
@@ -35934,7 +35952,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36140,7 +36158,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36218,7 +36236,7 @@
         <v>2.25</v>
       </c>
       <c r="AP169">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ169">
         <v>2.17</v>
@@ -36552,7 +36570,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36836,7 +36854,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP172">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ172">
         <v>0.85</v>
@@ -37042,7 +37060,7 @@
         <v>1.56</v>
       </c>
       <c r="AP173">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ173">
         <v>1.77</v>
@@ -37170,7 +37188,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37251,7 +37269,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ174">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR174">
         <v>1.91</v>
@@ -37376,7 +37394,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37582,7 +37600,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37663,7 +37681,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ176">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR176">
         <v>1.36</v>
@@ -37869,7 +37887,7 @@
         <v>1</v>
       </c>
       <c r="AQ177">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR177">
         <v>1.23</v>
@@ -37994,7 +38012,7 @@
         <v>217</v>
       </c>
       <c r="P178" t="s">
-        <v>343</v>
+        <v>242</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38072,7 +38090,7 @@
         <v>0.89</v>
       </c>
       <c r="AP178">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ178">
         <v>1.23</v>
@@ -38278,7 +38296,7 @@
         <v>1.4</v>
       </c>
       <c r="AP179">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ179">
         <v>1.31</v>
@@ -38406,7 +38424,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38487,7 +38505,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ180">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR180">
         <v>1.83</v>
@@ -38612,7 +38630,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38693,7 +38711,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ181">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR181">
         <v>2.14</v>
@@ -39230,7 +39248,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39436,7 +39454,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39926,7 +39944,7 @@
         <v>0.9</v>
       </c>
       <c r="AP187">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ187">
         <v>1.23</v>
@@ -40054,7 +40072,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40260,7 +40278,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40544,7 +40562,7 @@
         <v>1.2</v>
       </c>
       <c r="AP190">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ190">
         <v>1</v>
@@ -40750,7 +40768,7 @@
         <v>1.36</v>
       </c>
       <c r="AP191">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ191">
         <v>1.31</v>
@@ -40878,7 +40896,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -40959,7 +40977,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ192">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR192">
         <v>1.88</v>
@@ -41084,7 +41102,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41162,10 +41180,10 @@
         <v>1.1</v>
       </c>
       <c r="AP193">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ193">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR193">
         <v>1.45</v>
@@ -41371,7 +41389,7 @@
         <v>1</v>
       </c>
       <c r="AQ194">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR194">
         <v>1.33</v>
@@ -41496,7 +41514,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41574,10 +41592,10 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ195">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR195">
         <v>1.32</v>
@@ -41783,7 +41801,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ196">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR196">
         <v>2.06</v>
@@ -41908,7 +41926,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -41986,10 +42004,10 @@
         <v>0.7</v>
       </c>
       <c r="AP197">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ197">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR197">
         <v>1.38</v>
@@ -42320,7 +42338,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42732,7 +42750,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42938,7 +42956,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -43222,7 +43240,7 @@
         <v>1.09</v>
       </c>
       <c r="AP203">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ203">
         <v>1</v>
@@ -43762,7 +43780,7 @@
         <v>231</v>
       </c>
       <c r="P206" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43840,7 +43858,7 @@
         <v>0.64</v>
       </c>
       <c r="AP206">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ206">
         <v>0.6899999999999999</v>
@@ -44174,7 +44192,7 @@
         <v>233</v>
       </c>
       <c r="P208" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -44380,7 +44398,7 @@
         <v>97</v>
       </c>
       <c r="P209" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q209">
         <v>4.5</v>
@@ -44461,7 +44479,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ209">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR209">
         <v>1.85</v>
@@ -44586,7 +44604,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44664,10 +44682,10 @@
         <v>1.82</v>
       </c>
       <c r="AP210">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ210">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR210">
         <v>1.38</v>
@@ -44792,7 +44810,7 @@
         <v>96</v>
       </c>
       <c r="P211" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -44870,10 +44888,10 @@
         <v>0.73</v>
       </c>
       <c r="AP211">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ211">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR211">
         <v>1.27</v>
@@ -45079,7 +45097,7 @@
         <v>1</v>
       </c>
       <c r="AQ212">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR212">
         <v>1.4</v>
@@ -45204,7 +45222,7 @@
         <v>96</v>
       </c>
       <c r="P213" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q213">
         <v>3.4</v>
@@ -45285,7 +45303,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ213">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR213">
         <v>1.38</v>
@@ -45410,7 +45428,7 @@
         <v>235</v>
       </c>
       <c r="P214" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q214">
         <v>2.5</v>
@@ -45488,7 +45506,7 @@
         <v>1.55</v>
       </c>
       <c r="AP214">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ214">
         <v>1.77</v>
@@ -45616,7 +45634,7 @@
         <v>104</v>
       </c>
       <c r="P215" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q215">
         <v>4.75</v>
@@ -45822,7 +45840,7 @@
         <v>96</v>
       </c>
       <c r="P216" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q216">
         <v>2.1</v>
@@ -45900,7 +45918,7 @@
         <v>0.27</v>
       </c>
       <c r="AP216">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ216">
         <v>0.5</v>
@@ -46106,10 +46124,10 @@
         <v>1.17</v>
       </c>
       <c r="AP217">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ217">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR217">
         <v>1.54</v>
@@ -46234,7 +46252,7 @@
         <v>171</v>
       </c>
       <c r="P218" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q218">
         <v>3.1</v>
@@ -46440,7 +46458,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q219">
         <v>1.67</v>
@@ -46646,7 +46664,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q220">
         <v>1.4</v>
@@ -46852,7 +46870,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q221">
         <v>2</v>
@@ -47264,7 +47282,7 @@
         <v>238</v>
       </c>
       <c r="P223" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q223">
         <v>5.5</v>
@@ -47676,7 +47694,7 @@
         <v>239</v>
       </c>
       <c r="P225" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47882,7 +47900,7 @@
         <v>97</v>
       </c>
       <c r="P226" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q226">
         <v>2.3</v>
@@ -48039,6 +48057,1242 @@
       </c>
       <c r="BP226">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7492047</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45730.6875</v>
+      </c>
+      <c r="F227">
+        <v>26</v>
+      </c>
+      <c r="G227" t="s">
+        <v>78</v>
+      </c>
+      <c r="H227" t="s">
+        <v>72</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>0</v>
+      </c>
+      <c r="L227">
+        <v>1</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
+      </c>
+      <c r="N227">
+        <v>1</v>
+      </c>
+      <c r="O227" t="s">
+        <v>240</v>
+      </c>
+      <c r="P227" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q227">
+        <v>2.88</v>
+      </c>
+      <c r="R227">
+        <v>2.1</v>
+      </c>
+      <c r="S227">
+        <v>3.75</v>
+      </c>
+      <c r="T227">
+        <v>1.44</v>
+      </c>
+      <c r="U227">
+        <v>2.63</v>
+      </c>
+      <c r="V227">
+        <v>3.25</v>
+      </c>
+      <c r="W227">
+        <v>1.33</v>
+      </c>
+      <c r="X227">
+        <v>9</v>
+      </c>
+      <c r="Y227">
+        <v>1.07</v>
+      </c>
+      <c r="Z227">
+        <v>2.33</v>
+      </c>
+      <c r="AA227">
+        <v>3.5</v>
+      </c>
+      <c r="AB227">
+        <v>3.13</v>
+      </c>
+      <c r="AC227">
+        <v>1.06</v>
+      </c>
+      <c r="AD227">
+        <v>8.5</v>
+      </c>
+      <c r="AE227">
+        <v>1.34</v>
+      </c>
+      <c r="AF227">
+        <v>3.36</v>
+      </c>
+      <c r="AG227">
+        <v>1.86</v>
+      </c>
+      <c r="AH227">
+        <v>1.95</v>
+      </c>
+      <c r="AI227">
+        <v>1.8</v>
+      </c>
+      <c r="AJ227">
+        <v>1.95</v>
+      </c>
+      <c r="AK227">
+        <v>1.33</v>
+      </c>
+      <c r="AL227">
+        <v>1.31</v>
+      </c>
+      <c r="AM227">
+        <v>1.63</v>
+      </c>
+      <c r="AN227">
+        <v>0.75</v>
+      </c>
+      <c r="AO227">
+        <v>1.08</v>
+      </c>
+      <c r="AP227">
+        <v>0.92</v>
+      </c>
+      <c r="AQ227">
+        <v>1</v>
+      </c>
+      <c r="AR227">
+        <v>1.25</v>
+      </c>
+      <c r="AS227">
+        <v>1.26</v>
+      </c>
+      <c r="AT227">
+        <v>2.51</v>
+      </c>
+      <c r="AU227">
+        <v>6</v>
+      </c>
+      <c r="AV227">
+        <v>0</v>
+      </c>
+      <c r="AW227">
+        <v>5</v>
+      </c>
+      <c r="AX227">
+        <v>5</v>
+      </c>
+      <c r="AY227">
+        <v>14</v>
+      </c>
+      <c r="AZ227">
+        <v>6</v>
+      </c>
+      <c r="BA227">
+        <v>11</v>
+      </c>
+      <c r="BB227">
+        <v>2</v>
+      </c>
+      <c r="BC227">
+        <v>13</v>
+      </c>
+      <c r="BD227">
+        <v>1.73</v>
+      </c>
+      <c r="BE227">
+        <v>6.4</v>
+      </c>
+      <c r="BF227">
+        <v>2.33</v>
+      </c>
+      <c r="BG227">
+        <v>1.35</v>
+      </c>
+      <c r="BH227">
+        <v>2.9</v>
+      </c>
+      <c r="BI227">
+        <v>1.58</v>
+      </c>
+      <c r="BJ227">
+        <v>2.18</v>
+      </c>
+      <c r="BK227">
+        <v>1.95</v>
+      </c>
+      <c r="BL227">
+        <v>1.74</v>
+      </c>
+      <c r="BM227">
+        <v>2.48</v>
+      </c>
+      <c r="BN227">
+        <v>1.46</v>
+      </c>
+      <c r="BO227">
+        <v>3.3</v>
+      </c>
+      <c r="BP227">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7492044</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45731.47916666666</v>
+      </c>
+      <c r="F228">
+        <v>26</v>
+      </c>
+      <c r="G228" t="s">
+        <v>75</v>
+      </c>
+      <c r="H228" t="s">
+        <v>73</v>
+      </c>
+      <c r="I228">
+        <v>1</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <v>2</v>
+      </c>
+      <c r="M228">
+        <v>2</v>
+      </c>
+      <c r="N228">
+        <v>4</v>
+      </c>
+      <c r="O228" t="s">
+        <v>241</v>
+      </c>
+      <c r="P228" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q228">
+        <v>2.63</v>
+      </c>
+      <c r="R228">
+        <v>2.1</v>
+      </c>
+      <c r="S228">
+        <v>4.33</v>
+      </c>
+      <c r="T228">
+        <v>1.44</v>
+      </c>
+      <c r="U228">
+        <v>2.63</v>
+      </c>
+      <c r="V228">
+        <v>3.25</v>
+      </c>
+      <c r="W228">
+        <v>1.33</v>
+      </c>
+      <c r="X228">
+        <v>9</v>
+      </c>
+      <c r="Y228">
+        <v>1.07</v>
+      </c>
+      <c r="Z228">
+        <v>1.99</v>
+      </c>
+      <c r="AA228">
+        <v>3.51</v>
+      </c>
+      <c r="AB228">
+        <v>4</v>
+      </c>
+      <c r="AC228">
+        <v>1.06</v>
+      </c>
+      <c r="AD228">
+        <v>8.5</v>
+      </c>
+      <c r="AE228">
+        <v>1.36</v>
+      </c>
+      <c r="AF228">
+        <v>3.29</v>
+      </c>
+      <c r="AG228">
+        <v>1.91</v>
+      </c>
+      <c r="AH228">
+        <v>1.83</v>
+      </c>
+      <c r="AI228">
+        <v>1.91</v>
+      </c>
+      <c r="AJ228">
+        <v>1.91</v>
+      </c>
+      <c r="AK228">
+        <v>1.25</v>
+      </c>
+      <c r="AL228">
+        <v>1.3</v>
+      </c>
+      <c r="AM228">
+        <v>1.8</v>
+      </c>
+      <c r="AN228">
+        <v>1.75</v>
+      </c>
+      <c r="AO228">
+        <v>1.15</v>
+      </c>
+      <c r="AP228">
+        <v>1.69</v>
+      </c>
+      <c r="AQ228">
+        <v>1.14</v>
+      </c>
+      <c r="AR228">
+        <v>1.46</v>
+      </c>
+      <c r="AS228">
+        <v>1.18</v>
+      </c>
+      <c r="AT228">
+        <v>2.64</v>
+      </c>
+      <c r="AU228">
+        <v>4</v>
+      </c>
+      <c r="AV228">
+        <v>8</v>
+      </c>
+      <c r="AW228">
+        <v>3</v>
+      </c>
+      <c r="AX228">
+        <v>8</v>
+      </c>
+      <c r="AY228">
+        <v>8</v>
+      </c>
+      <c r="AZ228">
+        <v>22</v>
+      </c>
+      <c r="BA228">
+        <v>1</v>
+      </c>
+      <c r="BB228">
+        <v>4</v>
+      </c>
+      <c r="BC228">
+        <v>5</v>
+      </c>
+      <c r="BD228">
+        <v>1.44</v>
+      </c>
+      <c r="BE228">
+        <v>9.1</v>
+      </c>
+      <c r="BF228">
+        <v>3.5</v>
+      </c>
+      <c r="BG228">
+        <v>1.31</v>
+      </c>
+      <c r="BH228">
+        <v>2.92</v>
+      </c>
+      <c r="BI228">
+        <v>1.58</v>
+      </c>
+      <c r="BJ228">
+        <v>2.17</v>
+      </c>
+      <c r="BK228">
+        <v>2.02</v>
+      </c>
+      <c r="BL228">
+        <v>1.71</v>
+      </c>
+      <c r="BM228">
+        <v>2.64</v>
+      </c>
+      <c r="BN228">
+        <v>1.4</v>
+      </c>
+      <c r="BO228">
+        <v>3.58</v>
+      </c>
+      <c r="BP228">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7492043</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45731.47916666666</v>
+      </c>
+      <c r="F229">
+        <v>26</v>
+      </c>
+      <c r="G229" t="s">
+        <v>74</v>
+      </c>
+      <c r="H229" t="s">
+        <v>77</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>1</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
+      </c>
+      <c r="N229">
+        <v>1</v>
+      </c>
+      <c r="O229" t="s">
+        <v>93</v>
+      </c>
+      <c r="P229" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q229">
+        <v>3.25</v>
+      </c>
+      <c r="R229">
+        <v>2.1</v>
+      </c>
+      <c r="S229">
+        <v>3.4</v>
+      </c>
+      <c r="T229">
+        <v>1.44</v>
+      </c>
+      <c r="U229">
+        <v>2.63</v>
+      </c>
+      <c r="V229">
+        <v>3.25</v>
+      </c>
+      <c r="W229">
+        <v>1.33</v>
+      </c>
+      <c r="X229">
+        <v>9</v>
+      </c>
+      <c r="Y229">
+        <v>1.07</v>
+      </c>
+      <c r="Z229">
+        <v>2.68</v>
+      </c>
+      <c r="AA229">
+        <v>3.31</v>
+      </c>
+      <c r="AB229">
+        <v>2.78</v>
+      </c>
+      <c r="AC229">
+        <v>1.06</v>
+      </c>
+      <c r="AD229">
+        <v>8.5</v>
+      </c>
+      <c r="AE229">
+        <v>1.32</v>
+      </c>
+      <c r="AF229">
+        <v>3.51</v>
+      </c>
+      <c r="AG229">
+        <v>2.01</v>
+      </c>
+      <c r="AH229">
+        <v>1.81</v>
+      </c>
+      <c r="AI229">
+        <v>1.8</v>
+      </c>
+      <c r="AJ229">
+        <v>1.95</v>
+      </c>
+      <c r="AK229">
+        <v>1.46</v>
+      </c>
+      <c r="AL229">
+        <v>1.32</v>
+      </c>
+      <c r="AM229">
+        <v>1.47</v>
+      </c>
+      <c r="AN229">
+        <v>1.58</v>
+      </c>
+      <c r="AO229">
+        <v>1.92</v>
+      </c>
+      <c r="AP229">
+        <v>1.69</v>
+      </c>
+      <c r="AQ229">
+        <v>1.77</v>
+      </c>
+      <c r="AR229">
+        <v>1.55</v>
+      </c>
+      <c r="AS229">
+        <v>1.29</v>
+      </c>
+      <c r="AT229">
+        <v>2.84</v>
+      </c>
+      <c r="AU229">
+        <v>3</v>
+      </c>
+      <c r="AV229">
+        <v>3</v>
+      </c>
+      <c r="AW229">
+        <v>7</v>
+      </c>
+      <c r="AX229">
+        <v>11</v>
+      </c>
+      <c r="AY229">
+        <v>11</v>
+      </c>
+      <c r="AZ229">
+        <v>15</v>
+      </c>
+      <c r="BA229">
+        <v>1</v>
+      </c>
+      <c r="BB229">
+        <v>4</v>
+      </c>
+      <c r="BC229">
+        <v>5</v>
+      </c>
+      <c r="BD229">
+        <v>1.94</v>
+      </c>
+      <c r="BE229">
+        <v>6.6</v>
+      </c>
+      <c r="BF229">
+        <v>2.38</v>
+      </c>
+      <c r="BG229">
+        <v>1.21</v>
+      </c>
+      <c r="BH229">
+        <v>3.58</v>
+      </c>
+      <c r="BI229">
+        <v>1.43</v>
+      </c>
+      <c r="BJ229">
+        <v>2.54</v>
+      </c>
+      <c r="BK229">
+        <v>1.77</v>
+      </c>
+      <c r="BL229">
+        <v>1.94</v>
+      </c>
+      <c r="BM229">
+        <v>2.23</v>
+      </c>
+      <c r="BN229">
+        <v>1.55</v>
+      </c>
+      <c r="BO229">
+        <v>2.97</v>
+      </c>
+      <c r="BP229">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7492045</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45731.47916666666</v>
+      </c>
+      <c r="F230">
+        <v>26</v>
+      </c>
+      <c r="G230" t="s">
+        <v>79</v>
+      </c>
+      <c r="H230" t="s">
+        <v>87</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>1</v>
+      </c>
+      <c r="M230">
+        <v>1</v>
+      </c>
+      <c r="N230">
+        <v>2</v>
+      </c>
+      <c r="O230" t="s">
+        <v>242</v>
+      </c>
+      <c r="P230" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q230">
+        <v>7</v>
+      </c>
+      <c r="R230">
+        <v>2.5</v>
+      </c>
+      <c r="S230">
+        <v>1.83</v>
+      </c>
+      <c r="T230">
+        <v>1.3</v>
+      </c>
+      <c r="U230">
+        <v>3.4</v>
+      </c>
+      <c r="V230">
+        <v>2.38</v>
+      </c>
+      <c r="W230">
+        <v>1.53</v>
+      </c>
+      <c r="X230">
+        <v>6</v>
+      </c>
+      <c r="Y230">
+        <v>1.13</v>
+      </c>
+      <c r="Z230">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA230">
+        <v>5.2</v>
+      </c>
+      <c r="AB230">
+        <v>1.37</v>
+      </c>
+      <c r="AC230">
+        <v>1.03</v>
+      </c>
+      <c r="AD230">
+        <v>13</v>
+      </c>
+      <c r="AE230">
+        <v>1.2</v>
+      </c>
+      <c r="AF230">
+        <v>4.2</v>
+      </c>
+      <c r="AG230">
+        <v>1.57</v>
+      </c>
+      <c r="AH230">
+        <v>2.31</v>
+      </c>
+      <c r="AI230">
+        <v>1.95</v>
+      </c>
+      <c r="AJ230">
+        <v>1.8</v>
+      </c>
+      <c r="AK230">
+        <v>2.95</v>
+      </c>
+      <c r="AL230">
+        <v>1.17</v>
+      </c>
+      <c r="AM230">
+        <v>1.09</v>
+      </c>
+      <c r="AN230">
+        <v>1.33</v>
+      </c>
+      <c r="AO230">
+        <v>2.25</v>
+      </c>
+      <c r="AP230">
+        <v>1.31</v>
+      </c>
+      <c r="AQ230">
+        <v>2.15</v>
+      </c>
+      <c r="AR230">
+        <v>1.53</v>
+      </c>
+      <c r="AS230">
+        <v>1.79</v>
+      </c>
+      <c r="AT230">
+        <v>3.32</v>
+      </c>
+      <c r="AU230">
+        <v>4</v>
+      </c>
+      <c r="AV230">
+        <v>5</v>
+      </c>
+      <c r="AW230">
+        <v>4</v>
+      </c>
+      <c r="AX230">
+        <v>7</v>
+      </c>
+      <c r="AY230">
+        <v>8</v>
+      </c>
+      <c r="AZ230">
+        <v>19</v>
+      </c>
+      <c r="BA230">
+        <v>2</v>
+      </c>
+      <c r="BB230">
+        <v>14</v>
+      </c>
+      <c r="BC230">
+        <v>16</v>
+      </c>
+      <c r="BD230">
+        <v>5.05</v>
+      </c>
+      <c r="BE230">
+        <v>10.5</v>
+      </c>
+      <c r="BF230">
+        <v>1.26</v>
+      </c>
+      <c r="BG230">
+        <v>1.27</v>
+      </c>
+      <c r="BH230">
+        <v>3.14</v>
+      </c>
+      <c r="BI230">
+        <v>1.53</v>
+      </c>
+      <c r="BJ230">
+        <v>2.28</v>
+      </c>
+      <c r="BK230">
+        <v>1.93</v>
+      </c>
+      <c r="BL230">
+        <v>1.78</v>
+      </c>
+      <c r="BM230">
+        <v>2.5</v>
+      </c>
+      <c r="BN230">
+        <v>1.44</v>
+      </c>
+      <c r="BO230">
+        <v>3.34</v>
+      </c>
+      <c r="BP230">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7492042</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45731.47916666666</v>
+      </c>
+      <c r="F231">
+        <v>26</v>
+      </c>
+      <c r="G231" t="s">
+        <v>84</v>
+      </c>
+      <c r="H231" t="s">
+        <v>70</v>
+      </c>
+      <c r="I231">
+        <v>2</v>
+      </c>
+      <c r="J231">
+        <v>2</v>
+      </c>
+      <c r="K231">
+        <v>4</v>
+      </c>
+      <c r="L231">
+        <v>2</v>
+      </c>
+      <c r="M231">
+        <v>4</v>
+      </c>
+      <c r="N231">
+        <v>6</v>
+      </c>
+      <c r="O231" t="s">
+        <v>243</v>
+      </c>
+      <c r="P231" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q231">
+        <v>2.75</v>
+      </c>
+      <c r="R231">
+        <v>2.38</v>
+      </c>
+      <c r="S231">
+        <v>3.4</v>
+      </c>
+      <c r="T231">
+        <v>1.29</v>
+      </c>
+      <c r="U231">
+        <v>3.5</v>
+      </c>
+      <c r="V231">
+        <v>2.38</v>
+      </c>
+      <c r="W231">
+        <v>1.53</v>
+      </c>
+      <c r="X231">
+        <v>5.5</v>
+      </c>
+      <c r="Y231">
+        <v>1.14</v>
+      </c>
+      <c r="Z231">
+        <v>2.43</v>
+      </c>
+      <c r="AA231">
+        <v>3.65</v>
+      </c>
+      <c r="AB231">
+        <v>2.85</v>
+      </c>
+      <c r="AC231">
+        <v>1.03</v>
+      </c>
+      <c r="AD231">
+        <v>13</v>
+      </c>
+      <c r="AE231">
+        <v>1.18</v>
+      </c>
+      <c r="AF231">
+        <v>4.5</v>
+      </c>
+      <c r="AG231">
+        <v>1.57</v>
+      </c>
+      <c r="AH231">
+        <v>2.3</v>
+      </c>
+      <c r="AI231">
+        <v>1.5</v>
+      </c>
+      <c r="AJ231">
+        <v>2.5</v>
+      </c>
+      <c r="AK231">
+        <v>1.43</v>
+      </c>
+      <c r="AL231">
+        <v>1.27</v>
+      </c>
+      <c r="AM231">
+        <v>1.57</v>
+      </c>
+      <c r="AN231">
+        <v>1.08</v>
+      </c>
+      <c r="AO231">
+        <v>1.42</v>
+      </c>
+      <c r="AP231">
+        <v>1</v>
+      </c>
+      <c r="AQ231">
+        <v>1.54</v>
+      </c>
+      <c r="AR231">
+        <v>1.44</v>
+      </c>
+      <c r="AS231">
+        <v>1.36</v>
+      </c>
+      <c r="AT231">
+        <v>2.8</v>
+      </c>
+      <c r="AU231">
+        <v>3</v>
+      </c>
+      <c r="AV231">
+        <v>8</v>
+      </c>
+      <c r="AW231">
+        <v>21</v>
+      </c>
+      <c r="AX231">
+        <v>6</v>
+      </c>
+      <c r="AY231">
+        <v>27</v>
+      </c>
+      <c r="AZ231">
+        <v>14</v>
+      </c>
+      <c r="BA231">
+        <v>4</v>
+      </c>
+      <c r="BB231">
+        <v>1</v>
+      </c>
+      <c r="BC231">
+        <v>5</v>
+      </c>
+      <c r="BD231">
+        <v>1.7</v>
+      </c>
+      <c r="BE231">
+        <v>6.75</v>
+      </c>
+      <c r="BF231">
+        <v>2.85</v>
+      </c>
+      <c r="BG231">
+        <v>1.23</v>
+      </c>
+      <c r="BH231">
+        <v>3.42</v>
+      </c>
+      <c r="BI231">
+        <v>1.45</v>
+      </c>
+      <c r="BJ231">
+        <v>2.48</v>
+      </c>
+      <c r="BK231">
+        <v>1.81</v>
+      </c>
+      <c r="BL231">
+        <v>1.89</v>
+      </c>
+      <c r="BM231">
+        <v>2.3</v>
+      </c>
+      <c r="BN231">
+        <v>1.52</v>
+      </c>
+      <c r="BO231">
+        <v>3.05</v>
+      </c>
+      <c r="BP231">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7492040</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45731.60416666666</v>
+      </c>
+      <c r="F232">
+        <v>26</v>
+      </c>
+      <c r="G232" t="s">
+        <v>71</v>
+      </c>
+      <c r="H232" t="s">
+        <v>76</v>
+      </c>
+      <c r="I232">
+        <v>1</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>1</v>
+      </c>
+      <c r="L232">
+        <v>2</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>2</v>
+      </c>
+      <c r="O232" t="s">
+        <v>244</v>
+      </c>
+      <c r="P232" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q232">
+        <v>2.88</v>
+      </c>
+      <c r="R232">
+        <v>2.38</v>
+      </c>
+      <c r="S232">
+        <v>3.2</v>
+      </c>
+      <c r="T232">
+        <v>1.29</v>
+      </c>
+      <c r="U232">
+        <v>3.5</v>
+      </c>
+      <c r="V232">
+        <v>2.38</v>
+      </c>
+      <c r="W232">
+        <v>1.53</v>
+      </c>
+      <c r="X232">
+        <v>5.5</v>
+      </c>
+      <c r="Y232">
+        <v>1.14</v>
+      </c>
+      <c r="Z232">
+        <v>2.52</v>
+      </c>
+      <c r="AA232">
+        <v>3.71</v>
+      </c>
+      <c r="AB232">
+        <v>2.71</v>
+      </c>
+      <c r="AC232">
+        <v>1.02</v>
+      </c>
+      <c r="AD232">
+        <v>13.5</v>
+      </c>
+      <c r="AE232">
+        <v>1.17</v>
+      </c>
+      <c r="AF232">
+        <v>4.6</v>
+      </c>
+      <c r="AG232">
+        <v>1.55</v>
+      </c>
+      <c r="AH232">
+        <v>2.36</v>
+      </c>
+      <c r="AI232">
+        <v>1.5</v>
+      </c>
+      <c r="AJ232">
+        <v>2.5</v>
+      </c>
+      <c r="AK232">
+        <v>1.46</v>
+      </c>
+      <c r="AL232">
+        <v>1.27</v>
+      </c>
+      <c r="AM232">
+        <v>1.53</v>
+      </c>
+      <c r="AN232">
+        <v>1.83</v>
+      </c>
+      <c r="AO232">
+        <v>0.92</v>
+      </c>
+      <c r="AP232">
+        <v>1.92</v>
+      </c>
+      <c r="AQ232">
+        <v>0.85</v>
+      </c>
+      <c r="AR232">
+        <v>1.52</v>
+      </c>
+      <c r="AS232">
+        <v>1.4</v>
+      </c>
+      <c r="AT232">
+        <v>2.92</v>
+      </c>
+      <c r="AU232">
+        <v>6</v>
+      </c>
+      <c r="AV232">
+        <v>10</v>
+      </c>
+      <c r="AW232">
+        <v>10</v>
+      </c>
+      <c r="AX232">
+        <v>16</v>
+      </c>
+      <c r="AY232">
+        <v>19</v>
+      </c>
+      <c r="AZ232">
+        <v>32</v>
+      </c>
+      <c r="BA232">
+        <v>3</v>
+      </c>
+      <c r="BB232">
+        <v>12</v>
+      </c>
+      <c r="BC232">
+        <v>15</v>
+      </c>
+      <c r="BD232">
+        <v>1.95</v>
+      </c>
+      <c r="BE232">
+        <v>6.5</v>
+      </c>
+      <c r="BF232">
+        <v>2.38</v>
+      </c>
+      <c r="BG232">
+        <v>1.21</v>
+      </c>
+      <c r="BH232">
+        <v>3.58</v>
+      </c>
+      <c r="BI232">
+        <v>1.43</v>
+      </c>
+      <c r="BJ232">
+        <v>2.54</v>
+      </c>
+      <c r="BK232">
+        <v>1.77</v>
+      </c>
+      <c r="BL232">
+        <v>1.94</v>
+      </c>
+      <c r="BM232">
+        <v>2.23</v>
+      </c>
+      <c r="BN232">
+        <v>1.55</v>
+      </c>
+      <c r="BO232">
+        <v>2.97</v>
+      </c>
+      <c r="BP232">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="376">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -748,7 +748,10 @@
     <t>['38', '45+1']</t>
   </si>
   <si>
-    <t>['17', '48']</t>
+    <t>['18', '48']</t>
+  </si>
+  <si>
+    <t>['33', '47', '90+3']</t>
   </si>
   <si>
     <t>['12', '38', '90+11']</t>
@@ -1500,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP232"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1756,7 +1759,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2168,7 +2171,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2249,7 +2252,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2374,7 +2377,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2580,7 +2583,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -3198,7 +3201,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3404,7 +3407,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3816,7 +3819,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -4022,7 +4025,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4228,7 +4231,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4434,7 +4437,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4846,7 +4849,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5130,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ18">
         <v>1.23</v>
@@ -5464,7 +5467,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5876,7 +5879,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6288,7 +6291,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6494,7 +6497,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6700,7 +6703,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -7112,7 +7115,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7318,7 +7321,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7524,7 +7527,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7602,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ30">
         <v>1.14</v>
@@ -7730,7 +7733,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7936,7 +7939,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8142,7 +8145,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8223,7 +8226,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR33">
         <v>1.57</v>
@@ -8554,7 +8557,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9172,7 +9175,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9584,7 +9587,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9790,7 +9793,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9996,7 +9999,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10408,7 +10411,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10614,7 +10617,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10820,7 +10823,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11232,7 +11235,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11313,7 +11316,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ48">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR48">
         <v>2.42</v>
@@ -11644,7 +11647,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11850,7 +11853,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -12056,7 +12059,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12340,7 +12343,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ53">
         <v>1.31</v>
@@ -12468,7 +12471,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12674,7 +12677,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12880,7 +12883,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -13086,7 +13089,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13498,7 +13501,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13704,7 +13707,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13910,7 +13913,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14322,7 +14325,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14528,7 +14531,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14734,7 +14737,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14940,7 +14943,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15352,7 +15355,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15639,7 +15642,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ69">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR69">
         <v>2.2</v>
@@ -15764,7 +15767,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15970,7 +15973,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16460,7 +16463,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -17000,7 +17003,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17206,7 +17209,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18648,7 +18651,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18935,7 +18938,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR85">
         <v>0.97</v>
@@ -19060,7 +19063,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19266,7 +19269,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19884,7 +19887,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -20090,7 +20093,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20168,7 +20171,7 @@
         <v>1.75</v>
       </c>
       <c r="AP91">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ91">
         <v>1.77</v>
@@ -20502,7 +20505,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -21120,7 +21123,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21738,7 +21741,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22150,7 +22153,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22231,7 +22234,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ101">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR101">
         <v>1.26</v>
@@ -22356,7 +22359,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22562,7 +22565,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22974,7 +22977,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23180,7 +23183,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23386,7 +23389,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23798,7 +23801,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23876,7 +23879,7 @@
         <v>1.67</v>
       </c>
       <c r="AP109">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ109">
         <v>1.5</v>
@@ -24004,7 +24007,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24210,7 +24213,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24416,7 +24419,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24622,7 +24625,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24828,7 +24831,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25240,7 +25243,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25446,7 +25449,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25858,7 +25861,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -26064,7 +26067,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26270,7 +26273,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26476,7 +26479,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26763,7 +26766,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ123">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26888,7 +26891,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27094,7 +27097,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27172,7 +27175,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ125">
         <v>1.42</v>
@@ -27300,7 +27303,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27506,7 +27509,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27712,7 +27715,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27918,7 +27921,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28124,7 +28127,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28330,7 +28333,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28536,7 +28539,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28742,7 +28745,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -29360,7 +29363,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29566,7 +29569,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -30056,7 +30059,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ139">
         <v>0.85</v>
@@ -30184,7 +30187,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30265,7 +30268,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ140">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR140">
         <v>1.59</v>
@@ -30596,7 +30599,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -31008,7 +31011,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31214,7 +31217,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31420,7 +31423,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -32450,7 +32453,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32862,7 +32865,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33068,7 +33071,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33480,7 +33483,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33686,7 +33689,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33892,7 +33895,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -33970,7 +33973,7 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -34304,7 +34307,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34510,7 +34513,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34716,7 +34719,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34922,7 +34925,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -35128,7 +35131,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35209,7 +35212,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ164">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR164">
         <v>1.34</v>
@@ -35746,7 +35749,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35952,7 +35955,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36158,7 +36161,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36570,7 +36573,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -37188,7 +37191,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37394,7 +37397,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37475,7 +37478,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ175">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR175">
         <v>2.37</v>
@@ -37600,7 +37603,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37678,7 +37681,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP176">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ176">
         <v>0.85</v>
@@ -38424,7 +38427,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38630,7 +38633,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -39248,7 +39251,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39454,7 +39457,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -40072,7 +40075,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40278,7 +40281,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40896,7 +40899,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -41102,7 +41105,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41514,7 +41517,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41926,7 +41929,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42213,7 +42216,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ198">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR198">
         <v>1.84</v>
@@ -42338,7 +42341,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42416,7 +42419,7 @@
         <v>1.4</v>
       </c>
       <c r="AP199">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ199">
         <v>1.77</v>
@@ -42750,7 +42753,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42956,7 +42959,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -43780,7 +43783,7 @@
         <v>231</v>
       </c>
       <c r="P206" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44192,7 +44195,7 @@
         <v>233</v>
       </c>
       <c r="P208" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -44398,7 +44401,7 @@
         <v>97</v>
       </c>
       <c r="P209" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q209">
         <v>4.5</v>
@@ -44604,7 +44607,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44810,7 +44813,7 @@
         <v>96</v>
       </c>
       <c r="P211" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45222,7 +45225,7 @@
         <v>96</v>
       </c>
       <c r="P213" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q213">
         <v>3.4</v>
@@ -45300,7 +45303,7 @@
         <v>1.27</v>
       </c>
       <c r="AP213">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ213">
         <v>1.54</v>
@@ -45428,7 +45431,7 @@
         <v>235</v>
       </c>
       <c r="P214" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q214">
         <v>2.5</v>
@@ -45634,7 +45637,7 @@
         <v>104</v>
       </c>
       <c r="P215" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q215">
         <v>4.75</v>
@@ -45840,7 +45843,7 @@
         <v>96</v>
       </c>
       <c r="P216" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q216">
         <v>2.1</v>
@@ -45921,7 +45924,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ216">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR216">
         <v>1.5</v>
@@ -46252,7 +46255,7 @@
         <v>171</v>
       </c>
       <c r="P218" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q218">
         <v>3.1</v>
@@ -46458,7 +46461,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q219">
         <v>1.67</v>
@@ -46664,7 +46667,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q220">
         <v>1.4</v>
@@ -46870,7 +46873,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q221">
         <v>2</v>
@@ -47282,7 +47285,7 @@
         <v>238</v>
       </c>
       <c r="P223" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q223">
         <v>5.5</v>
@@ -47694,7 +47697,7 @@
         <v>239</v>
       </c>
       <c r="P225" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47900,7 +47903,7 @@
         <v>97</v>
       </c>
       <c r="P226" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q226">
         <v>2.3</v>
@@ -48312,7 +48315,7 @@
         <v>241</v>
       </c>
       <c r="P228" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q228">
         <v>2.63</v>
@@ -48930,7 +48933,7 @@
         <v>243</v>
       </c>
       <c r="P231" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q231">
         <v>2.75</v>
@@ -49292,6 +49295,212 @@
         <v>2.97</v>
       </c>
       <c r="BP232">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7492041</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45732.5625</v>
+      </c>
+      <c r="F233">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>86</v>
+      </c>
+      <c r="H233" t="s">
+        <v>81</v>
+      </c>
+      <c r="I233">
+        <v>1</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+      <c r="L233">
+        <v>3</v>
+      </c>
+      <c r="M233">
+        <v>1</v>
+      </c>
+      <c r="N233">
+        <v>4</v>
+      </c>
+      <c r="O233" t="s">
+        <v>245</v>
+      </c>
+      <c r="P233" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q233">
+        <v>2.63</v>
+      </c>
+      <c r="R233">
+        <v>2.25</v>
+      </c>
+      <c r="S233">
+        <v>4</v>
+      </c>
+      <c r="T233">
+        <v>1.36</v>
+      </c>
+      <c r="U233">
+        <v>3</v>
+      </c>
+      <c r="V233">
+        <v>2.63</v>
+      </c>
+      <c r="W233">
+        <v>1.44</v>
+      </c>
+      <c r="X233">
+        <v>7</v>
+      </c>
+      <c r="Y233">
+        <v>1.1</v>
+      </c>
+      <c r="Z233">
+        <v>1.88</v>
+      </c>
+      <c r="AA233">
+        <v>3.82</v>
+      </c>
+      <c r="AB233">
+        <v>4.1</v>
+      </c>
+      <c r="AC233">
+        <v>1.05</v>
+      </c>
+      <c r="AD233">
+        <v>9.5</v>
+      </c>
+      <c r="AE233">
+        <v>1.25</v>
+      </c>
+      <c r="AF233">
+        <v>3.8</v>
+      </c>
+      <c r="AG233">
+        <v>1.67</v>
+      </c>
+      <c r="AH233">
+        <v>2.1</v>
+      </c>
+      <c r="AI233">
+        <v>1.67</v>
+      </c>
+      <c r="AJ233">
+        <v>2.1</v>
+      </c>
+      <c r="AK233">
+        <v>1.28</v>
+      </c>
+      <c r="AL233">
+        <v>1.28</v>
+      </c>
+      <c r="AM233">
+        <v>1.78</v>
+      </c>
+      <c r="AN233">
+        <v>0.58</v>
+      </c>
+      <c r="AO233">
+        <v>0.5</v>
+      </c>
+      <c r="AP233">
+        <v>0.77</v>
+      </c>
+      <c r="AQ233">
+        <v>0.46</v>
+      </c>
+      <c r="AR233">
+        <v>1.43</v>
+      </c>
+      <c r="AS233">
+        <v>1.17</v>
+      </c>
+      <c r="AT233">
+        <v>2.6</v>
+      </c>
+      <c r="AU233">
+        <v>6</v>
+      </c>
+      <c r="AV233">
+        <v>5</v>
+      </c>
+      <c r="AW233">
+        <v>9</v>
+      </c>
+      <c r="AX233">
+        <v>12</v>
+      </c>
+      <c r="AY233">
+        <v>16</v>
+      </c>
+      <c r="AZ233">
+        <v>21</v>
+      </c>
+      <c r="BA233">
+        <v>3</v>
+      </c>
+      <c r="BB233">
+        <v>5</v>
+      </c>
+      <c r="BC233">
+        <v>8</v>
+      </c>
+      <c r="BD233">
+        <v>1.57</v>
+      </c>
+      <c r="BE233">
+        <v>9.1</v>
+      </c>
+      <c r="BF233">
+        <v>2.94</v>
+      </c>
+      <c r="BG233">
+        <v>1.22</v>
+      </c>
+      <c r="BH233">
+        <v>3.5</v>
+      </c>
+      <c r="BI233">
+        <v>1.44</v>
+      </c>
+      <c r="BJ233">
+        <v>2.51</v>
+      </c>
+      <c r="BK233">
+        <v>1.78</v>
+      </c>
+      <c r="BL233">
+        <v>1.93</v>
+      </c>
+      <c r="BM233">
+        <v>2.25</v>
+      </c>
+      <c r="BN233">
+        <v>1.54</v>
+      </c>
+      <c r="BO233">
+        <v>2.97</v>
+      </c>
+      <c r="BP233">
         <v>1.3</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="379">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -754,6 +754,9 @@
     <t>['33', '47', '90+3']</t>
   </si>
   <si>
+    <t>['14', '48', '62']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1143,6 +1146,12 @@
   <si>
     <t>['7', '28', '47', '81']</t>
   </si>
+  <si>
+    <t>['27', '32', '90+6']</t>
+  </si>
+  <si>
+    <t>['56', '67', '88', '90+4']</t>
+  </si>
 </sst>
 </file>
 
@@ -1503,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1759,7 +1768,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1840,7 +1849,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ2">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2171,7 +2180,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2377,7 +2386,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2583,7 +2592,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -3076,7 +3085,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3201,7 +3210,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3407,7 +3416,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3819,7 +3828,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3897,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ12">
         <v>1.77</v>
@@ -4025,7 +4034,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4231,7 +4240,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4437,7 +4446,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4515,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ15">
         <v>1.54</v>
@@ -4849,7 +4858,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5467,7 +5476,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5879,7 +5888,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5960,7 +5969,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR22">
         <v>2.26</v>
@@ -6291,7 +6300,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6372,7 +6381,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR24">
         <v>1.03</v>
@@ -6497,7 +6506,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6703,7 +6712,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -7115,7 +7124,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7321,7 +7330,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7527,7 +7536,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7733,7 +7742,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7939,7 +7948,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8145,7 +8154,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8223,7 +8232,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ33">
         <v>0.46</v>
@@ -8557,7 +8566,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8841,7 +8850,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ36">
         <v>0.85</v>
@@ -9175,7 +9184,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9587,7 +9596,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9793,7 +9802,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9999,7 +10008,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10411,7 +10420,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10492,7 +10501,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ44">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10617,7 +10626,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10698,7 +10707,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR45">
         <v>1</v>
@@ -10823,7 +10832,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11235,7 +11244,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11647,7 +11656,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11853,7 +11862,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11931,7 +11940,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ51">
         <v>1.77</v>
@@ -12059,7 +12068,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12471,7 +12480,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12677,7 +12686,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12755,7 +12764,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -12883,7 +12892,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -13089,7 +13098,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13170,7 +13179,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ57">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR57">
         <v>2.44</v>
@@ -13501,7 +13510,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13707,7 +13716,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13913,7 +13922,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14325,7 +14334,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14531,7 +14540,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14737,7 +14746,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14943,7 +14952,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15355,7 +15364,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15639,7 +15648,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ69">
         <v>0.46</v>
@@ -15767,7 +15776,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15848,7 +15857,7 @@
         <v>1</v>
       </c>
       <c r="AQ70">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR70">
         <v>0.6899999999999999</v>
@@ -15973,7 +15982,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16051,7 +16060,7 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ71">
         <v>2.15</v>
@@ -16260,7 +16269,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ72">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -17003,7 +17012,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17209,7 +17218,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18651,7 +18660,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -19063,7 +19072,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19269,7 +19278,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19347,10 +19356,10 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ87">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -19887,7 +19896,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19965,10 +19974,10 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ90">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR90">
         <v>2.13</v>
@@ -20093,7 +20102,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20505,7 +20514,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20789,7 +20798,7 @@
         <v>0</v>
       </c>
       <c r="AP94">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ94">
         <v>0.46</v>
@@ -21123,7 +21132,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21741,7 +21750,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22153,7 +22162,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22359,7 +22368,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22440,7 +22449,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ102">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR102">
         <v>1.35</v>
@@ -22565,7 +22574,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22977,7 +22986,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23183,7 +23192,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23389,7 +23398,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23801,7 +23810,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23882,7 +23891,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ109">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -24007,7 +24016,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24085,7 +24094,7 @@
         <v>0.83</v>
       </c>
       <c r="AP110">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ110">
         <v>0.85</v>
@@ -24213,7 +24222,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24419,7 +24428,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24497,7 +24506,7 @@
         <v>1.67</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ112">
         <v>1.54</v>
@@ -24625,7 +24634,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24831,7 +24840,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25243,7 +25252,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25449,7 +25458,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25861,7 +25870,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -26067,7 +26076,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26273,7 +26282,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26479,7 +26488,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26560,7 +26569,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ122">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26891,7 +26900,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27097,7 +27106,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27303,7 +27312,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27509,7 +27518,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27590,7 +27599,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ127">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR127">
         <v>1.42</v>
@@ -27715,7 +27724,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27921,7 +27930,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28127,7 +28136,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28205,7 +28214,7 @@
         <v>0.86</v>
       </c>
       <c r="AP130">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28333,7 +28342,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28539,7 +28548,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28745,7 +28754,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -29235,7 +29244,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ135">
         <v>0.6899999999999999</v>
@@ -29363,7 +29372,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29569,7 +29578,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29650,7 +29659,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ137">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR137">
         <v>1.63</v>
@@ -30187,7 +30196,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30599,7 +30608,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30680,7 +30689,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ142">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR142">
         <v>1.26</v>
@@ -31011,7 +31020,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31217,7 +31226,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31423,7 +31432,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -32325,7 +32334,7 @@
         <v>1.13</v>
       </c>
       <c r="AP150">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ150">
         <v>1</v>
@@ -32453,7 +32462,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32531,7 +32540,7 @@
         <v>1.63</v>
       </c>
       <c r="AP151">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ151">
         <v>1.31</v>
@@ -32865,7 +32874,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33071,7 +33080,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33483,7 +33492,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33689,7 +33698,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33767,7 +33776,7 @@
         <v>1.44</v>
       </c>
       <c r="AP157">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ157">
         <v>1.31</v>
@@ -33895,7 +33904,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34179,7 +34188,7 @@
         <v>0.89</v>
       </c>
       <c r="AP159">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ159">
         <v>1.14</v>
@@ -34307,7 +34316,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34513,7 +34522,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34719,7 +34728,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34925,7 +34934,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -35131,7 +35140,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35749,7 +35758,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35955,7 +35964,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36161,7 +36170,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36242,7 +36251,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ169">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR169">
         <v>1.49</v>
@@ -36573,7 +36582,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36654,7 +36663,7 @@
         <v>1</v>
       </c>
       <c r="AQ171">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR171">
         <v>1.74</v>
@@ -37191,7 +37200,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37269,7 +37278,7 @@
         <v>0.89</v>
       </c>
       <c r="AP174">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ174">
         <v>1.54</v>
@@ -37397,7 +37406,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37603,7 +37612,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37887,7 +37896,7 @@
         <v>0.8</v>
       </c>
       <c r="AP177">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ177">
         <v>1.14</v>
@@ -38427,7 +38436,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38633,7 +38642,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -39126,7 +39135,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ183">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR183">
         <v>1.45</v>
@@ -39251,7 +39260,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39457,7 +39466,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -40075,7 +40084,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40156,7 +40165,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ188">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR188">
         <v>1.5</v>
@@ -40281,7 +40290,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40899,7 +40908,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -40977,7 +40986,7 @@
         <v>1.7</v>
       </c>
       <c r="AP192">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ192">
         <v>1.77</v>
@@ -41105,7 +41114,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41389,7 +41398,7 @@
         <v>0.8</v>
       </c>
       <c r="AP194">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ194">
         <v>0.85</v>
@@ -41517,7 +41526,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41929,7 +41938,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42341,7 +42350,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42753,7 +42762,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42834,7 +42843,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ201">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR201">
         <v>1.24</v>
@@ -42959,7 +42968,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -43783,7 +43792,7 @@
         <v>231</v>
       </c>
       <c r="P206" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44070,7 +44079,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ207">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR207">
         <v>2.52</v>
@@ -44195,7 +44204,7 @@
         <v>233</v>
       </c>
       <c r="P208" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -44401,7 +44410,7 @@
         <v>97</v>
       </c>
       <c r="P209" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q209">
         <v>4.5</v>
@@ -44479,7 +44488,7 @@
         <v>2.18</v>
       </c>
       <c r="AP209">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ209">
         <v>2.15</v>
@@ -44607,7 +44616,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44813,7 +44822,7 @@
         <v>96</v>
       </c>
       <c r="P211" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45097,7 +45106,7 @@
         <v>0.91</v>
       </c>
       <c r="AP212">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ212">
         <v>1</v>
@@ -45225,7 +45234,7 @@
         <v>96</v>
       </c>
       <c r="P213" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q213">
         <v>3.4</v>
@@ -45431,7 +45440,7 @@
         <v>235</v>
       </c>
       <c r="P214" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q214">
         <v>2.5</v>
@@ -45637,7 +45646,7 @@
         <v>104</v>
       </c>
       <c r="P215" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q215">
         <v>4.75</v>
@@ -45718,7 +45727,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ215">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR215">
         <v>1.89</v>
@@ -45843,7 +45852,7 @@
         <v>96</v>
       </c>
       <c r="P216" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q216">
         <v>2.1</v>
@@ -46255,7 +46264,7 @@
         <v>171</v>
       </c>
       <c r="P218" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q218">
         <v>3.1</v>
@@ -46461,7 +46470,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q219">
         <v>1.67</v>
@@ -46667,7 +46676,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q220">
         <v>1.4</v>
@@ -46873,7 +46882,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q221">
         <v>2</v>
@@ -47285,7 +47294,7 @@
         <v>238</v>
       </c>
       <c r="P223" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q223">
         <v>5.5</v>
@@ -47697,7 +47706,7 @@
         <v>239</v>
       </c>
       <c r="P225" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47903,7 +47912,7 @@
         <v>97</v>
       </c>
       <c r="P226" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q226">
         <v>2.3</v>
@@ -48315,7 +48324,7 @@
         <v>241</v>
       </c>
       <c r="P228" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q228">
         <v>2.63</v>
@@ -48620,16 +48629,16 @@
         <v>3</v>
       </c>
       <c r="AW229">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX229">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AY229">
         <v>11</v>
       </c>
       <c r="AZ229">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA229">
         <v>1</v>
@@ -48933,7 +48942,7 @@
         <v>243</v>
       </c>
       <c r="P231" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q231">
         <v>2.75</v>
@@ -49303,7 +49312,7 @@
         <v>232</v>
       </c>
       <c r="B233">
-        <v>7492041</v>
+        <v>7492046</v>
       </c>
       <c r="C233" t="s">
         <v>68</v>
@@ -49312,55 +49321,55 @@
         <v>69</v>
       </c>
       <c r="E233" s="2">
-        <v>45732.5625</v>
+        <v>45732.51388888889</v>
       </c>
       <c r="F233">
         <v>26</v>
       </c>
       <c r="G233" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H233" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L233">
+        <v>1</v>
+      </c>
+      <c r="M233">
         <v>3</v>
-      </c>
-      <c r="M233">
-        <v>1</v>
       </c>
       <c r="N233">
         <v>4</v>
       </c>
       <c r="O233" t="s">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="P233" t="s">
-        <v>319</v>
+        <v>377</v>
       </c>
       <c r="Q233">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="R233">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S233">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="T233">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U233">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V233">
         <v>2.63</v>
@@ -49369,139 +49378,551 @@
         <v>1.44</v>
       </c>
       <c r="X233">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y233">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z233">
-        <v>1.88</v>
+        <v>3.27</v>
       </c>
       <c r="AA233">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="AB233">
-        <v>4.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC233">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD233">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="AE233">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF233">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AG233">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH233">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI233">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ233">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK233">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AL233">
         <v>1.28</v>
       </c>
       <c r="AM233">
+        <v>1.34</v>
+      </c>
+      <c r="AN233">
+        <v>1</v>
+      </c>
+      <c r="AO233">
+        <v>1.5</v>
+      </c>
+      <c r="AP233">
+        <v>0.92</v>
+      </c>
+      <c r="AQ233">
+        <v>1.62</v>
+      </c>
+      <c r="AR233">
+        <v>1.41</v>
+      </c>
+      <c r="AS233">
+        <v>1.44</v>
+      </c>
+      <c r="AT233">
+        <v>2.85</v>
+      </c>
+      <c r="AU233">
+        <v>8</v>
+      </c>
+      <c r="AV233">
+        <v>8</v>
+      </c>
+      <c r="AW233">
+        <v>10</v>
+      </c>
+      <c r="AX233">
+        <v>11</v>
+      </c>
+      <c r="AY233">
+        <v>24</v>
+      </c>
+      <c r="AZ233">
+        <v>25</v>
+      </c>
+      <c r="BA233">
+        <v>8</v>
+      </c>
+      <c r="BB233">
+        <v>3</v>
+      </c>
+      <c r="BC233">
+        <v>11</v>
+      </c>
+      <c r="BD233">
+        <v>2.16</v>
+      </c>
+      <c r="BE233">
+        <v>6.65</v>
+      </c>
+      <c r="BF233">
+        <v>2.11</v>
+      </c>
+      <c r="BG233">
+        <v>1.18</v>
+      </c>
+      <c r="BH233">
+        <v>3.92</v>
+      </c>
+      <c r="BI233">
+        <v>1.37</v>
+      </c>
+      <c r="BJ233">
+        <v>2.75</v>
+      </c>
+      <c r="BK233">
+        <v>1.67</v>
+      </c>
+      <c r="BL233">
+        <v>2.07</v>
+      </c>
+      <c r="BM233">
+        <v>2.09</v>
+      </c>
+      <c r="BN233">
+        <v>1.63</v>
+      </c>
+      <c r="BO233">
+        <v>2.7</v>
+      </c>
+      <c r="BP233">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7492041</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45732.5625</v>
+      </c>
+      <c r="F234">
+        <v>26</v>
+      </c>
+      <c r="G234" t="s">
+        <v>86</v>
+      </c>
+      <c r="H234" t="s">
+        <v>81</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>3</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>4</v>
+      </c>
+      <c r="O234" t="s">
+        <v>245</v>
+      </c>
+      <c r="P234" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q234">
+        <v>2.63</v>
+      </c>
+      <c r="R234">
+        <v>2.25</v>
+      </c>
+      <c r="S234">
+        <v>4</v>
+      </c>
+      <c r="T234">
+        <v>1.36</v>
+      </c>
+      <c r="U234">
+        <v>3</v>
+      </c>
+      <c r="V234">
+        <v>2.63</v>
+      </c>
+      <c r="W234">
+        <v>1.44</v>
+      </c>
+      <c r="X234">
+        <v>7</v>
+      </c>
+      <c r="Y234">
+        <v>1.1</v>
+      </c>
+      <c r="Z234">
+        <v>1.88</v>
+      </c>
+      <c r="AA234">
+        <v>3.82</v>
+      </c>
+      <c r="AB234">
+        <v>4.1</v>
+      </c>
+      <c r="AC234">
+        <v>1.05</v>
+      </c>
+      <c r="AD234">
+        <v>9.5</v>
+      </c>
+      <c r="AE234">
+        <v>1.25</v>
+      </c>
+      <c r="AF234">
+        <v>3.8</v>
+      </c>
+      <c r="AG234">
+        <v>1.67</v>
+      </c>
+      <c r="AH234">
+        <v>2.1</v>
+      </c>
+      <c r="AI234">
+        <v>1.67</v>
+      </c>
+      <c r="AJ234">
+        <v>2.1</v>
+      </c>
+      <c r="AK234">
+        <v>1.28</v>
+      </c>
+      <c r="AL234">
+        <v>1.28</v>
+      </c>
+      <c r="AM234">
         <v>1.78</v>
       </c>
-      <c r="AN233">
+      <c r="AN234">
         <v>0.58</v>
       </c>
-      <c r="AO233">
+      <c r="AO234">
         <v>0.5</v>
       </c>
-      <c r="AP233">
+      <c r="AP234">
         <v>0.77</v>
       </c>
-      <c r="AQ233">
+      <c r="AQ234">
         <v>0.46</v>
       </c>
-      <c r="AR233">
+      <c r="AR234">
         <v>1.43</v>
       </c>
-      <c r="AS233">
+      <c r="AS234">
         <v>1.17</v>
       </c>
-      <c r="AT233">
+      <c r="AT234">
         <v>2.6</v>
       </c>
-      <c r="AU233">
+      <c r="AU234">
         <v>6</v>
       </c>
-      <c r="AV233">
+      <c r="AV234">
         <v>5</v>
       </c>
-      <c r="AW233">
+      <c r="AW234">
         <v>9</v>
       </c>
-      <c r="AX233">
+      <c r="AX234">
         <v>12</v>
       </c>
-      <c r="AY233">
+      <c r="AY234">
         <v>16</v>
       </c>
-      <c r="AZ233">
+      <c r="AZ234">
         <v>21</v>
       </c>
-      <c r="BA233">
+      <c r="BA234">
         <v>3</v>
       </c>
-      <c r="BB233">
+      <c r="BB234">
         <v>5</v>
       </c>
-      <c r="BC233">
+      <c r="BC234">
         <v>8</v>
       </c>
-      <c r="BD233">
+      <c r="BD234">
         <v>1.57</v>
       </c>
-      <c r="BE233">
+      <c r="BE234">
         <v>9.1</v>
       </c>
-      <c r="BF233">
+      <c r="BF234">
         <v>2.94</v>
       </c>
-      <c r="BG233">
+      <c r="BG234">
         <v>1.22</v>
       </c>
-      <c r="BH233">
+      <c r="BH234">
         <v>3.5</v>
       </c>
-      <c r="BI233">
+      <c r="BI234">
         <v>1.44</v>
       </c>
-      <c r="BJ233">
+      <c r="BJ234">
         <v>2.51</v>
       </c>
-      <c r="BK233">
+      <c r="BK234">
         <v>1.78</v>
       </c>
-      <c r="BL233">
+      <c r="BL234">
         <v>1.93</v>
       </c>
-      <c r="BM233">
+      <c r="BM234">
         <v>2.25</v>
       </c>
-      <c r="BN233">
+      <c r="BN234">
         <v>1.54</v>
       </c>
-      <c r="BO233">
+      <c r="BO234">
         <v>2.97</v>
       </c>
-      <c r="BP233">
+      <c r="BP234">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7492039</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45732.64583333334</v>
+      </c>
+      <c r="F235">
+        <v>26</v>
+      </c>
+      <c r="G235" t="s">
+        <v>80</v>
+      </c>
+      <c r="H235" t="s">
+        <v>85</v>
+      </c>
+      <c r="I235">
+        <v>1</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>3</v>
+      </c>
+      <c r="M235">
+        <v>4</v>
+      </c>
+      <c r="N235">
+        <v>7</v>
+      </c>
+      <c r="O235" t="s">
+        <v>246</v>
+      </c>
+      <c r="P235" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q235">
+        <v>3.5</v>
+      </c>
+      <c r="R235">
+        <v>2.3</v>
+      </c>
+      <c r="S235">
+        <v>2.88</v>
+      </c>
+      <c r="T235">
+        <v>1.33</v>
+      </c>
+      <c r="U235">
+        <v>3.25</v>
+      </c>
+      <c r="V235">
+        <v>2.5</v>
+      </c>
+      <c r="W235">
+        <v>1.5</v>
+      </c>
+      <c r="X235">
+        <v>6.5</v>
+      </c>
+      <c r="Y235">
+        <v>1.11</v>
+      </c>
+      <c r="Z235">
+        <v>3.08</v>
+      </c>
+      <c r="AA235">
+        <v>3.63</v>
+      </c>
+      <c r="AB235">
+        <v>2.3</v>
+      </c>
+      <c r="AC235">
+        <v>1.04</v>
+      </c>
+      <c r="AD235">
+        <v>10</v>
+      </c>
+      <c r="AE235">
+        <v>1.22</v>
+      </c>
+      <c r="AF235">
+        <v>4.2</v>
+      </c>
+      <c r="AG235">
+        <v>1.61</v>
+      </c>
+      <c r="AH235">
+        <v>2.2</v>
+      </c>
+      <c r="AI235">
+        <v>1.57</v>
+      </c>
+      <c r="AJ235">
+        <v>2.25</v>
+      </c>
+      <c r="AK235">
+        <v>1.61</v>
+      </c>
+      <c r="AL235">
+        <v>1.28</v>
+      </c>
+      <c r="AM235">
+        <v>1.38</v>
+      </c>
+      <c r="AN235">
+        <v>1.54</v>
+      </c>
+      <c r="AO235">
+        <v>2.17</v>
+      </c>
+      <c r="AP235">
+        <v>1.43</v>
+      </c>
+      <c r="AQ235">
+        <v>2.23</v>
+      </c>
+      <c r="AR235">
+        <v>1.83</v>
+      </c>
+      <c r="AS235">
+        <v>1.64</v>
+      </c>
+      <c r="AT235">
+        <v>3.47</v>
+      </c>
+      <c r="AU235">
+        <v>7</v>
+      </c>
+      <c r="AV235">
+        <v>5</v>
+      </c>
+      <c r="AW235">
+        <v>5</v>
+      </c>
+      <c r="AX235">
+        <v>10</v>
+      </c>
+      <c r="AY235">
+        <v>13</v>
+      </c>
+      <c r="AZ235">
+        <v>16</v>
+      </c>
+      <c r="BA235">
+        <v>1</v>
+      </c>
+      <c r="BB235">
+        <v>10</v>
+      </c>
+      <c r="BC235">
+        <v>11</v>
+      </c>
+      <c r="BD235">
+        <v>2.39</v>
+      </c>
+      <c r="BE235">
+        <v>6.6</v>
+      </c>
+      <c r="BF235">
+        <v>1.93</v>
+      </c>
+      <c r="BG235">
+        <v>1.22</v>
+      </c>
+      <c r="BH235">
+        <v>3.5</v>
+      </c>
+      <c r="BI235">
+        <v>1.44</v>
+      </c>
+      <c r="BJ235">
+        <v>2.51</v>
+      </c>
+      <c r="BK235">
+        <v>1.79</v>
+      </c>
+      <c r="BL235">
+        <v>1.92</v>
+      </c>
+      <c r="BM235">
+        <v>2.28</v>
+      </c>
+      <c r="BN235">
+        <v>1.53</v>
+      </c>
+      <c r="BO235">
+        <v>3.04</v>
+      </c>
+      <c r="BP235">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="380">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -755,6 +755,9 @@
   </si>
   <si>
     <t>['14', '48', '62']</t>
+  </si>
+  <si>
+    <t>['20', '60', '87']</t>
   </si>
   <si>
     <t>['12', '38', '90+11']</t>
@@ -1512,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP235"/>
+  <dimension ref="A1:BP236"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1768,7 +1771,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2055,7 +2058,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ3">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2180,7 +2183,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2386,7 +2389,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2592,7 +2595,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -3210,7 +3213,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3416,7 +3419,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3828,7 +3831,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -4034,7 +4037,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4240,7 +4243,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4446,7 +4449,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4858,7 +4861,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4936,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ17">
         <v>1.31</v>
@@ -5476,7 +5479,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5888,7 +5891,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6175,7 +6178,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ23">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR23">
         <v>1.5</v>
@@ -6300,7 +6303,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6506,7 +6509,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6712,7 +6715,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -7124,7 +7127,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7330,7 +7333,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7536,7 +7539,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7742,7 +7745,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7948,7 +7951,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8154,7 +8157,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8566,7 +8569,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8644,7 +8647,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ35">
         <v>1.77</v>
@@ -9184,7 +9187,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9265,7 +9268,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ38">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR38">
         <v>1.73</v>
@@ -9596,7 +9599,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9802,7 +9805,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10008,7 +10011,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10420,7 +10423,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10626,7 +10629,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10832,7 +10835,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11244,7 +11247,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11322,7 +11325,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ48">
         <v>0.46</v>
@@ -11656,7 +11659,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11862,7 +11865,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -12068,7 +12071,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12480,7 +12483,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12686,7 +12689,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12892,7 +12895,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -13098,7 +13101,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13176,7 +13179,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ57">
         <v>1.62</v>
@@ -13385,7 +13388,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13510,7 +13513,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13716,7 +13719,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13922,7 +13925,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14334,7 +14337,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14540,7 +14543,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14746,7 +14749,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14952,7 +14955,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15364,7 +15367,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15776,7 +15779,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15982,7 +15985,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16678,7 +16681,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ74">
         <v>1.42</v>
@@ -17012,7 +17015,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17093,7 +17096,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ76">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17218,7 +17221,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18660,7 +18663,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -19072,7 +19075,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19278,7 +19281,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19896,7 +19899,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -20102,7 +20105,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20514,7 +20517,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20592,7 +20595,7 @@
         <v>1.2</v>
       </c>
       <c r="AP93">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ93">
         <v>0.6899999999999999</v>
@@ -20801,7 +20804,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ94">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR94">
         <v>2.18</v>
@@ -21132,7 +21135,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21750,7 +21753,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22162,7 +22165,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22368,7 +22371,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22574,7 +22577,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22861,7 +22864,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ104">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR104">
         <v>1.72</v>
@@ -22986,7 +22989,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23192,7 +23195,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23398,7 +23401,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23810,7 +23813,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -24016,7 +24019,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24222,7 +24225,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24428,7 +24431,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24634,7 +24637,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24840,7 +24843,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25124,7 +25127,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -25252,7 +25255,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25458,7 +25461,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25870,7 +25873,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -26076,7 +26079,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26157,7 +26160,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ120">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR120">
         <v>1.27</v>
@@ -26282,7 +26285,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26488,7 +26491,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26900,7 +26903,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27106,7 +27109,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27312,7 +27315,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27518,7 +27521,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27724,7 +27727,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27930,7 +27933,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28136,7 +28139,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28342,7 +28345,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28548,7 +28551,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28754,7 +28757,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -29038,7 +29041,7 @@
         <v>1.14</v>
       </c>
       <c r="AP134">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ134">
         <v>1.14</v>
@@ -29372,7 +29375,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29578,7 +29581,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -30196,7 +30199,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30483,7 +30486,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ141">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR141">
         <v>1.48</v>
@@ -30608,7 +30611,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -31020,7 +31023,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31226,7 +31229,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31432,7 +31435,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -32128,7 +32131,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ149">
         <v>1.77</v>
@@ -32462,7 +32465,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32874,7 +32877,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33080,7 +33083,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33492,7 +33495,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33698,7 +33701,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33904,7 +33907,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34316,7 +34319,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34522,7 +34525,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34600,7 +34603,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ161">
         <v>1.54</v>
@@ -34728,7 +34731,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34934,7 +34937,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -35140,7 +35143,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35758,7 +35761,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35964,7 +35967,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36170,7 +36173,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36457,7 +36460,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ170">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR170">
         <v>1.47</v>
@@ -36582,7 +36585,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -37200,7 +37203,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37406,7 +37409,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37612,7 +37615,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -38436,7 +38439,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38642,7 +38645,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38720,7 +38723,7 @@
         <v>0.78</v>
       </c>
       <c r="AP181">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ181">
         <v>1</v>
@@ -39260,7 +39263,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39466,7 +39469,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -40084,7 +40087,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40290,7 +40293,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40371,7 +40374,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ189">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR189">
         <v>1.24</v>
@@ -40908,7 +40911,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -41114,7 +41117,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41526,7 +41529,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41810,7 +41813,7 @@
         <v>2.3</v>
       </c>
       <c r="AP196">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ196">
         <v>2.15</v>
@@ -41938,7 +41941,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42350,7 +42353,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42762,7 +42765,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42968,7 +42971,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -43461,7 +43464,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ204">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR204">
         <v>1.47</v>
@@ -43792,7 +43795,7 @@
         <v>231</v>
       </c>
       <c r="P206" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44204,7 +44207,7 @@
         <v>233</v>
       </c>
       <c r="P208" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -44410,7 +44413,7 @@
         <v>97</v>
       </c>
       <c r="P209" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q209">
         <v>4.5</v>
@@ -44616,7 +44619,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44822,7 +44825,7 @@
         <v>96</v>
       </c>
       <c r="P211" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45234,7 +45237,7 @@
         <v>96</v>
       </c>
       <c r="P213" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q213">
         <v>3.4</v>
@@ -45440,7 +45443,7 @@
         <v>235</v>
       </c>
       <c r="P214" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q214">
         <v>2.5</v>
@@ -45646,7 +45649,7 @@
         <v>104</v>
       </c>
       <c r="P215" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q215">
         <v>4.75</v>
@@ -45852,7 +45855,7 @@
         <v>96</v>
       </c>
       <c r="P216" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q216">
         <v>2.1</v>
@@ -46264,7 +46267,7 @@
         <v>171</v>
       </c>
       <c r="P218" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q218">
         <v>3.1</v>
@@ -46470,7 +46473,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q219">
         <v>1.67</v>
@@ -46548,7 +46551,7 @@
         <v>1.42</v>
       </c>
       <c r="AP219">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ219">
         <v>1.54</v>
@@ -46676,7 +46679,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q220">
         <v>1.4</v>
@@ -46757,7 +46760,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ220">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR220">
         <v>2.53</v>
@@ -46882,7 +46885,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q221">
         <v>2</v>
@@ -47294,7 +47297,7 @@
         <v>238</v>
       </c>
       <c r="P223" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q223">
         <v>5.5</v>
@@ -47706,7 +47709,7 @@
         <v>239</v>
       </c>
       <c r="P225" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47912,7 +47915,7 @@
         <v>97</v>
       </c>
       <c r="P226" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q226">
         <v>2.3</v>
@@ -48324,7 +48327,7 @@
         <v>241</v>
       </c>
       <c r="P228" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q228">
         <v>2.63</v>
@@ -48942,7 +48945,7 @@
         <v>243</v>
       </c>
       <c r="P231" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q231">
         <v>2.75</v>
@@ -49354,7 +49357,7 @@
         <v>171</v>
       </c>
       <c r="P233" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49560,7 +49563,7 @@
         <v>245</v>
       </c>
       <c r="P234" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q234">
         <v>2.63</v>
@@ -49766,7 +49769,7 @@
         <v>246</v>
       </c>
       <c r="P235" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q235">
         <v>3.5</v>
@@ -49923,6 +49926,212 @@
       </c>
       <c r="BP235">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7492048</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45744.6875</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>85</v>
+      </c>
+      <c r="H236" t="s">
+        <v>83</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236">
+        <v>2</v>
+      </c>
+      <c r="L236">
+        <v>3</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+      <c r="N236">
+        <v>4</v>
+      </c>
+      <c r="O236" t="s">
+        <v>247</v>
+      </c>
+      <c r="P236" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q236">
+        <v>1.67</v>
+      </c>
+      <c r="R236">
+        <v>2.75</v>
+      </c>
+      <c r="S236">
+        <v>8.5</v>
+      </c>
+      <c r="T236">
+        <v>1.25</v>
+      </c>
+      <c r="U236">
+        <v>3.75</v>
+      </c>
+      <c r="V236">
+        <v>2.2</v>
+      </c>
+      <c r="W236">
+        <v>1.62</v>
+      </c>
+      <c r="X236">
+        <v>5</v>
+      </c>
+      <c r="Y236">
+        <v>1.17</v>
+      </c>
+      <c r="Z236">
+        <v>1.26</v>
+      </c>
+      <c r="AA236">
+        <v>6.6</v>
+      </c>
+      <c r="AB236">
+        <v>11</v>
+      </c>
+      <c r="AC236">
+        <v>1.01</v>
+      </c>
+      <c r="AD236">
+        <v>17</v>
+      </c>
+      <c r="AE236">
+        <v>1.14</v>
+      </c>
+      <c r="AF236">
+        <v>5.5</v>
+      </c>
+      <c r="AG236">
+        <v>1.46</v>
+      </c>
+      <c r="AH236">
+        <v>2.6</v>
+      </c>
+      <c r="AI236">
+        <v>1.91</v>
+      </c>
+      <c r="AJ236">
+        <v>1.91</v>
+      </c>
+      <c r="AK236">
+        <v>1.05</v>
+      </c>
+      <c r="AL236">
+        <v>1.13</v>
+      </c>
+      <c r="AM236">
+        <v>3.7</v>
+      </c>
+      <c r="AN236">
+        <v>2.08</v>
+      </c>
+      <c r="AO236">
+        <v>0.46</v>
+      </c>
+      <c r="AP236">
+        <v>2.14</v>
+      </c>
+      <c r="AQ236">
+        <v>0.43</v>
+      </c>
+      <c r="AR236">
+        <v>2.04</v>
+      </c>
+      <c r="AS236">
+        <v>1.26</v>
+      </c>
+      <c r="AT236">
+        <v>3.3</v>
+      </c>
+      <c r="AU236">
+        <v>6</v>
+      </c>
+      <c r="AV236">
+        <v>4</v>
+      </c>
+      <c r="AW236">
+        <v>9</v>
+      </c>
+      <c r="AX236">
+        <v>5</v>
+      </c>
+      <c r="AY236">
+        <v>20</v>
+      </c>
+      <c r="AZ236">
+        <v>10</v>
+      </c>
+      <c r="BA236">
+        <v>3</v>
+      </c>
+      <c r="BB236">
+        <v>2</v>
+      </c>
+      <c r="BC236">
+        <v>5</v>
+      </c>
+      <c r="BD236">
+        <v>1.11</v>
+      </c>
+      <c r="BE236">
+        <v>14.5</v>
+      </c>
+      <c r="BF236">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BG236">
+        <v>1.13</v>
+      </c>
+      <c r="BH236">
+        <v>4.5</v>
+      </c>
+      <c r="BI236">
+        <v>1.3</v>
+      </c>
+      <c r="BJ236">
+        <v>3.08</v>
+      </c>
+      <c r="BK236">
+        <v>1.55</v>
+      </c>
+      <c r="BL236">
+        <v>2.29</v>
+      </c>
+      <c r="BM236">
+        <v>1.88</v>
+      </c>
+      <c r="BN236">
+        <v>1.78</v>
+      </c>
+      <c r="BO236">
+        <v>2.38</v>
+      </c>
+      <c r="BP236">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="385">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,15 @@
     <t>['20', '60', '87']</t>
   </si>
   <si>
+    <t>['17', '53', '71']</t>
+  </si>
+  <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['39', '42', '72']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -961,9 +970,6 @@
     <t>['27', '69']</t>
   </si>
   <si>
-    <t>['56']</t>
-  </si>
-  <si>
     <t>['60', '71']</t>
   </si>
   <si>
@@ -1154,6 +1160,15 @@
   </si>
   <si>
     <t>['56', '67', '88', '90+4']</t>
+  </si>
+  <si>
+    <t>['27', '90+3']</t>
+  </si>
+  <si>
+    <t>['25', '59', '90+3']</t>
+  </si>
+  <si>
+    <t>['30', '48']</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP236"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1771,7 +1786,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1849,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ2">
         <v>2.23</v>
@@ -2183,7 +2198,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2389,7 +2404,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2467,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2595,7 +2610,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2676,7 +2691,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ6">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2882,7 +2897,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ7">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3085,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ8">
         <v>1.62</v>
@@ -3213,7 +3228,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3291,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ9">
         <v>2.15</v>
@@ -3419,7 +3434,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3500,7 +3515,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ10">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3706,7 +3721,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3831,7 +3846,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3912,7 +3927,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ12">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4037,7 +4052,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4115,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ13">
         <v>1.77</v>
@@ -4243,7 +4258,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4321,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4449,7 +4464,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4861,7 +4876,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4942,7 +4957,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ17">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5148,7 +5163,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ18">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5351,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ19">
         <v>1.14</v>
@@ -5479,7 +5494,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5557,10 +5572,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ20">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR20">
         <v>1.89</v>
@@ -5766,7 +5781,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ21">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR21">
         <v>1.16</v>
@@ -5891,7 +5906,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6175,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>0.43</v>
@@ -6303,7 +6318,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6381,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ24">
         <v>1.62</v>
@@ -6509,7 +6524,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6587,10 +6602,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ25">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR25">
         <v>1.46</v>
@@ -6715,7 +6730,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6793,7 +6808,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ26">
         <v>2.15</v>
@@ -7002,7 +7017,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR27">
         <v>1.22</v>
@@ -7127,7 +7142,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7208,7 +7223,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ28">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR28">
         <v>1.23</v>
@@ -7333,7 +7348,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7414,7 +7429,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ29">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR29">
         <v>1.7</v>
@@ -7539,7 +7554,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7745,7 +7760,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7951,7 +7966,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8157,7 +8172,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8441,7 +8456,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ34">
         <v>1.54</v>
@@ -8569,7 +8584,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9062,7 +9077,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ37">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR37">
         <v>1.27</v>
@@ -9187,7 +9202,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9265,7 +9280,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ38">
         <v>0.43</v>
@@ -9471,10 +9486,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ39">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9599,7 +9614,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9680,7 +9695,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ40">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9805,7 +9820,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9883,10 +9898,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ41">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR41">
         <v>1.28</v>
@@ -10011,7 +10026,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10089,10 +10104,10 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR42">
         <v>1.82</v>
@@ -10298,7 +10313,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ43">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR43">
         <v>1.14</v>
@@ -10423,7 +10438,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10501,7 +10516,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ44">
         <v>2.23</v>
@@ -10629,7 +10644,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10707,7 +10722,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ45">
         <v>1.62</v>
@@ -10835,7 +10850,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10916,7 +10931,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR46">
         <v>1.82</v>
@@ -11247,7 +11262,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11659,7 +11674,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11865,7 +11880,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -12071,7 +12086,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12152,7 +12167,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ52">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -12358,7 +12373,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ53">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12483,7 +12498,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12561,7 +12576,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ54">
         <v>2.15</v>
@@ -12689,7 +12704,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12895,7 +12910,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12973,10 +12988,10 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR56">
         <v>1.91</v>
@@ -13101,7 +13116,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13513,7 +13528,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13591,10 +13606,10 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR59">
         <v>1.71</v>
@@ -13719,7 +13734,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13800,7 +13815,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ60">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR60">
         <v>1.26</v>
@@ -13925,7 +13940,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14003,10 +14018,10 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ61">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR61">
         <v>1.33</v>
@@ -14209,10 +14224,10 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ62">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR62">
         <v>1.47</v>
@@ -14337,7 +14352,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14415,10 +14430,10 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ63">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR63">
         <v>1.07</v>
@@ -14543,7 +14558,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14621,10 +14636,10 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ64">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR64">
         <v>1.11</v>
@@ -14749,7 +14764,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14955,7 +14970,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15367,7 +15382,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15779,7 +15794,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15985,7 +16000,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16684,7 +16699,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ74">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR74">
         <v>2.41</v>
@@ -16887,10 +16902,10 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ75">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.82</v>
@@ -17015,7 +17030,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17093,7 +17108,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ76">
         <v>0.43</v>
@@ -17221,7 +17236,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17302,7 +17317,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR77">
         <v>1.67</v>
@@ -17505,10 +17520,10 @@
         <v>1.5</v>
       </c>
       <c r="AP78">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ78">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -17711,10 +17726,10 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ79">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR79">
         <v>1.14</v>
@@ -17917,10 +17932,10 @@
         <v>2.5</v>
       </c>
       <c r="AP80">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ80">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR80">
         <v>1.88</v>
@@ -18123,10 +18138,10 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR81">
         <v>1.64</v>
@@ -18329,10 +18344,10 @@
         <v>2.5</v>
       </c>
       <c r="AP82">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ82">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18663,7 +18678,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -19075,7 +19090,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19281,7 +19296,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19899,7 +19914,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -20105,7 +20120,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20389,10 +20404,10 @@
         <v>0.25</v>
       </c>
       <c r="AP92">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ92">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR92">
         <v>1.83</v>
@@ -20517,7 +20532,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20598,7 +20613,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ93">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR93">
         <v>2.3</v>
@@ -21007,7 +21022,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ95">
         <v>1.14</v>
@@ -21135,7 +21150,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21216,7 +21231,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -21419,10 +21434,10 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ97">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.25</v>
@@ -21625,10 +21640,10 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ98">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR98">
         <v>1.59</v>
@@ -21753,7 +21768,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21831,10 +21846,10 @@
         <v>2</v>
       </c>
       <c r="AP99">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ99">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -22037,10 +22052,10 @@
         <v>1.2</v>
       </c>
       <c r="AP100">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -22165,7 +22180,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22371,7 +22386,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22577,7 +22592,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22655,7 +22670,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ103">
         <v>1.54</v>
@@ -22989,7 +23004,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23195,7 +23210,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23276,7 +23291,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR106">
         <v>1.1</v>
@@ -23401,7 +23416,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23479,7 +23494,7 @@
         <v>2.67</v>
       </c>
       <c r="AP107">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ107">
         <v>2.15</v>
@@ -23813,7 +23828,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -24019,7 +24034,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24100,7 +24115,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ110">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR110">
         <v>2.1</v>
@@ -24225,7 +24240,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24303,10 +24318,10 @@
         <v>1.67</v>
       </c>
       <c r="AP111">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ111">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR111">
         <v>1.13</v>
@@ -24431,7 +24446,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>315</v>
+        <v>249</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24512,7 +24527,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ112">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR112">
         <v>1.23</v>
@@ -24637,7 +24652,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24715,10 +24730,10 @@
         <v>0.2</v>
       </c>
       <c r="AP113">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ113">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR113">
         <v>1.55</v>
@@ -24843,7 +24858,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24921,10 +24936,10 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ114">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR114">
         <v>2.04</v>
@@ -25130,7 +25145,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR115">
         <v>2.31</v>
@@ -25255,7 +25270,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25333,7 +25348,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ116">
         <v>0.85</v>
@@ -25461,7 +25476,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25539,10 +25554,10 @@
         <v>2.2</v>
       </c>
       <c r="AP117">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ117">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR117">
         <v>1.29</v>
@@ -25873,7 +25888,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25951,7 +25966,7 @@
         <v>2.17</v>
       </c>
       <c r="AP119">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
         <v>1.77</v>
@@ -26079,7 +26094,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26285,7 +26300,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26491,7 +26506,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26775,7 +26790,7 @@
         <v>0.33</v>
       </c>
       <c r="AP123">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ123">
         <v>0.46</v>
@@ -26903,7 +26918,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26984,7 +26999,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ124">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -27109,7 +27124,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27190,7 +27205,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ125">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR125">
         <v>1.33</v>
@@ -27315,7 +27330,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27393,7 +27408,7 @@
         <v>0.5</v>
       </c>
       <c r="AP126">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ126">
         <v>1</v>
@@ -27521,7 +27536,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27727,7 +27742,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27805,10 +27820,10 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ128">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR128">
         <v>2.15</v>
@@ -27933,7 +27948,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28011,10 +28026,10 @@
         <v>0.33</v>
       </c>
       <c r="AP129">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ129">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -28139,7 +28154,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28220,7 +28235,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR130">
         <v>1.98</v>
@@ -28345,7 +28360,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28423,10 +28438,10 @@
         <v>1.83</v>
       </c>
       <c r="AP131">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ131">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR131">
         <v>1.54</v>
@@ -28551,7 +28566,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28757,7 +28772,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28838,7 +28853,7 @@
         <v>1</v>
       </c>
       <c r="AQ133">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR133">
         <v>1.24</v>
@@ -29250,7 +29265,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ135">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR135">
         <v>1.23</v>
@@ -29375,7 +29390,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29453,7 +29468,7 @@
         <v>0.33</v>
       </c>
       <c r="AP136">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ136">
         <v>0.85</v>
@@ -29581,7 +29596,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29659,7 +29674,7 @@
         <v>2.14</v>
       </c>
       <c r="AP137">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ137">
         <v>2.23</v>
@@ -30074,7 +30089,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ139">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.27</v>
@@ -30199,7 +30214,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30277,7 +30292,7 @@
         <v>0.29</v>
       </c>
       <c r="AP140">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ140">
         <v>0.46</v>
@@ -30611,7 +30626,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30895,7 +30910,7 @@
         <v>2.13</v>
       </c>
       <c r="AP143">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ143">
         <v>2.15</v>
@@ -31023,7 +31038,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31104,7 +31119,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ144">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -31229,7 +31244,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31310,7 +31325,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ145">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31435,7 +31450,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31513,7 +31528,7 @@
         <v>0.71</v>
       </c>
       <c r="AP146">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ146">
         <v>0.85</v>
@@ -31719,7 +31734,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ147">
         <v>1.14</v>
@@ -31925,7 +31940,7 @@
         <v>1.14</v>
       </c>
       <c r="AP148">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ148">
         <v>1.54</v>
@@ -32134,7 +32149,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ149">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR149">
         <v>2.17</v>
@@ -32340,7 +32355,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ150">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR150">
         <v>1.25</v>
@@ -32465,7 +32480,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32546,7 +32561,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ151">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR151">
         <v>1.96</v>
@@ -32749,7 +32764,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -32877,7 +32892,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32958,7 +32973,7 @@
         <v>1</v>
       </c>
       <c r="AQ153">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR153">
         <v>1.26</v>
@@ -33083,7 +33098,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33164,7 +33179,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ154">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33367,7 +33382,7 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ155">
         <v>0.85</v>
@@ -33495,7 +33510,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33573,7 +33588,7 @@
         <v>0.5</v>
       </c>
       <c r="AP156">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -33701,7 +33716,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33782,7 +33797,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ157">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR157">
         <v>1.22</v>
@@ -33907,7 +33922,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -33988,7 +34003,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR158">
         <v>1.38</v>
@@ -34319,7 +34334,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34397,7 +34412,7 @@
         <v>2</v>
       </c>
       <c r="AP160">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ160">
         <v>1.77</v>
@@ -34525,7 +34540,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34731,7 +34746,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34812,7 +34827,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ162">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR162">
         <v>1.42</v>
@@ -34937,7 +34952,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -35018,7 +35033,7 @@
         <v>1</v>
       </c>
       <c r="AQ163">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR163">
         <v>1.3</v>
@@ -35143,7 +35158,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35221,7 +35236,7 @@
         <v>0.25</v>
       </c>
       <c r="AP164">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ164">
         <v>0.46</v>
@@ -35430,7 +35445,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ165">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR165">
         <v>1.46</v>
@@ -35636,7 +35651,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ166">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR166">
         <v>1.56</v>
@@ -35761,7 +35776,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35839,7 +35854,7 @@
         <v>2.22</v>
       </c>
       <c r="AP167">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ167">
         <v>2.15</v>
@@ -35967,7 +35982,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36045,10 +36060,10 @@
         <v>1.78</v>
       </c>
       <c r="AP168">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ168">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR168">
         <v>1.59</v>
@@ -36173,7 +36188,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36457,7 +36472,7 @@
         <v>0.11</v>
       </c>
       <c r="AP170">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ170">
         <v>0.43</v>
@@ -36585,7 +36600,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36872,7 +36887,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ172">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR172">
         <v>1.31</v>
@@ -37078,7 +37093,7 @@
         <v>1</v>
       </c>
       <c r="AQ173">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR173">
         <v>1.38</v>
@@ -37203,7 +37218,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37409,7 +37424,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37487,7 +37502,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ175">
         <v>0.46</v>
@@ -37615,7 +37630,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -38108,7 +38123,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ178">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR178">
         <v>1.36</v>
@@ -38314,7 +38329,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ179">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR179">
         <v>1.41</v>
@@ -38439,7 +38454,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38517,7 +38532,7 @@
         <v>1.78</v>
       </c>
       <c r="AP180">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ180">
         <v>1.77</v>
@@ -38645,7 +38660,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38929,10 +38944,10 @@
         <v>1.7</v>
       </c>
       <c r="AP182">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ182">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR182">
         <v>2.47</v>
@@ -39135,7 +39150,7 @@
         <v>2.11</v>
       </c>
       <c r="AP183">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ183">
         <v>2.23</v>
@@ -39263,7 +39278,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39341,10 +39356,10 @@
         <v>1.33</v>
       </c>
       <c r="AP184">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ184">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR184">
         <v>1.55</v>
@@ -39469,7 +39484,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39550,7 +39565,7 @@
         <v>1</v>
       </c>
       <c r="AQ185">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR185">
         <v>1.84</v>
@@ -39753,10 +39768,10 @@
         <v>0.7</v>
       </c>
       <c r="AP186">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ186">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR186">
         <v>1.5</v>
@@ -39962,7 +39977,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ187">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR187">
         <v>1.47</v>
@@ -40087,7 +40102,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40165,7 +40180,7 @@
         <v>1.7</v>
       </c>
       <c r="AP188">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ188">
         <v>1.62</v>
@@ -40293,7 +40308,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40371,7 +40386,7 @@
         <v>0.1</v>
       </c>
       <c r="AP189">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ189">
         <v>0.43</v>
@@ -40580,7 +40595,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ190">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR190">
         <v>1.45</v>
@@ -40786,7 +40801,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ191">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR191">
         <v>1.56</v>
@@ -40911,7 +40926,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -41117,7 +41132,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41529,7 +41544,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41941,7 +41956,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42225,7 +42240,7 @@
         <v>0.3</v>
       </c>
       <c r="AP198">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ198">
         <v>0.46</v>
@@ -42353,7 +42368,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42434,7 +42449,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ199">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR199">
         <v>1.37</v>
@@ -42637,10 +42652,10 @@
         <v>1.55</v>
       </c>
       <c r="AP200">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ200">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR200">
         <v>1.47</v>
@@ -42765,7 +42780,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42843,7 +42858,7 @@
         <v>2</v>
       </c>
       <c r="AP201">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ201">
         <v>2.23</v>
@@ -42971,7 +42986,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -43049,10 +43064,10 @@
         <v>0.91</v>
       </c>
       <c r="AP202">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ202">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR202">
         <v>1.47</v>
@@ -43258,7 +43273,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ203">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR203">
         <v>1.46</v>
@@ -43461,7 +43476,7 @@
         <v>0.18</v>
       </c>
       <c r="AP204">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ204">
         <v>0.43</v>
@@ -43667,10 +43682,10 @@
         <v>0.73</v>
       </c>
       <c r="AP205">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ205">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR205">
         <v>1.58</v>
@@ -43795,7 +43810,7 @@
         <v>231</v>
       </c>
       <c r="P206" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43876,7 +43891,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ206">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR206">
         <v>1.45</v>
@@ -44079,7 +44094,7 @@
         <v>1.64</v>
       </c>
       <c r="AP207">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ207">
         <v>1.62</v>
@@ -44207,7 +44222,7 @@
         <v>233</v>
       </c>
       <c r="P208" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -44288,7 +44303,7 @@
         <v>1</v>
       </c>
       <c r="AQ208">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR208">
         <v>1.84</v>
@@ -44413,7 +44428,7 @@
         <v>97</v>
       </c>
       <c r="P209" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q209">
         <v>4.5</v>
@@ -44619,7 +44634,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44825,7 +44840,7 @@
         <v>96</v>
       </c>
       <c r="P211" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45237,7 +45252,7 @@
         <v>96</v>
       </c>
       <c r="P213" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q213">
         <v>3.4</v>
@@ -45443,7 +45458,7 @@
         <v>235</v>
       </c>
       <c r="P214" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q214">
         <v>2.5</v>
@@ -45524,7 +45539,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ214">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR214">
         <v>1.52</v>
@@ -45649,7 +45664,7 @@
         <v>104</v>
       </c>
       <c r="P215" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q215">
         <v>4.75</v>
@@ -45727,7 +45742,7 @@
         <v>2.09</v>
       </c>
       <c r="AP215">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ215">
         <v>2.23</v>
@@ -45855,7 +45870,7 @@
         <v>96</v>
       </c>
       <c r="P216" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q216">
         <v>2.1</v>
@@ -46267,7 +46282,7 @@
         <v>171</v>
       </c>
       <c r="P218" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q218">
         <v>3.1</v>
@@ -46345,10 +46360,10 @@
         <v>1.67</v>
       </c>
       <c r="AP218">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ218">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR218">
         <v>1.45</v>
@@ -46473,7 +46488,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q219">
         <v>1.67</v>
@@ -46554,7 +46569,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ219">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR219">
         <v>2.05</v>
@@ -46679,7 +46694,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q220">
         <v>1.4</v>
@@ -46757,7 +46772,7 @@
         <v>0.25</v>
       </c>
       <c r="AP220">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ220">
         <v>0.43</v>
@@ -46885,7 +46900,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q221">
         <v>2</v>
@@ -46963,10 +46978,10 @@
         <v>1.08</v>
       </c>
       <c r="AP221">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ221">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR221">
         <v>1.67</v>
@@ -47169,10 +47184,10 @@
         <v>1</v>
       </c>
       <c r="AP222">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ222">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR222">
         <v>1.49</v>
@@ -47297,7 +47312,7 @@
         <v>238</v>
       </c>
       <c r="P223" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q223">
         <v>5.5</v>
@@ -47375,10 +47390,10 @@
         <v>1.45</v>
       </c>
       <c r="AP223">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ223">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR223">
         <v>1.19</v>
@@ -47581,10 +47596,10 @@
         <v>1.33</v>
       </c>
       <c r="AP224">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ224">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR224">
         <v>1.49</v>
@@ -47709,7 +47724,7 @@
         <v>239</v>
       </c>
       <c r="P225" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47787,10 +47802,10 @@
         <v>0.67</v>
       </c>
       <c r="AP225">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ225">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR225">
         <v>1.82</v>
@@ -47915,7 +47930,7 @@
         <v>97</v>
       </c>
       <c r="P226" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q226">
         <v>2.3</v>
@@ -47996,7 +48011,7 @@
         <v>1</v>
       </c>
       <c r="AQ226">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR226">
         <v>1.78</v>
@@ -48327,7 +48342,7 @@
         <v>241</v>
       </c>
       <c r="P228" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q228">
         <v>2.63</v>
@@ -48945,7 +48960,7 @@
         <v>243</v>
       </c>
       <c r="P231" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q231">
         <v>2.75</v>
@@ -49357,7 +49372,7 @@
         <v>171</v>
       </c>
       <c r="P233" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49563,7 +49578,7 @@
         <v>245</v>
       </c>
       <c r="P234" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q234">
         <v>2.63</v>
@@ -49769,7 +49784,7 @@
         <v>246</v>
       </c>
       <c r="P235" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q235">
         <v>3.5</v>
@@ -50132,6 +50147,1654 @@
       </c>
       <c r="BP236">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7492049</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F237">
+        <v>27</v>
+      </c>
+      <c r="G237" t="s">
+        <v>87</v>
+      </c>
+      <c r="H237" t="s">
+        <v>78</v>
+      </c>
+      <c r="I237">
+        <v>1</v>
+      </c>
+      <c r="J237">
+        <v>1</v>
+      </c>
+      <c r="K237">
+        <v>2</v>
+      </c>
+      <c r="L237">
+        <v>3</v>
+      </c>
+      <c r="M237">
+        <v>2</v>
+      </c>
+      <c r="N237">
+        <v>5</v>
+      </c>
+      <c r="O237" t="s">
+        <v>248</v>
+      </c>
+      <c r="P237" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q237">
+        <v>1.5</v>
+      </c>
+      <c r="R237">
+        <v>3</v>
+      </c>
+      <c r="S237">
+        <v>12</v>
+      </c>
+      <c r="T237">
+        <v>1.22</v>
+      </c>
+      <c r="U237">
+        <v>4</v>
+      </c>
+      <c r="V237">
+        <v>2.1</v>
+      </c>
+      <c r="W237">
+        <v>1.67</v>
+      </c>
+      <c r="X237">
+        <v>4.5</v>
+      </c>
+      <c r="Y237">
+        <v>1.18</v>
+      </c>
+      <c r="Z237">
+        <v>1.16</v>
+      </c>
+      <c r="AA237">
+        <v>9.4</v>
+      </c>
+      <c r="AB237">
+        <v>15</v>
+      </c>
+      <c r="AC237">
+        <v>1.01</v>
+      </c>
+      <c r="AD237">
+        <v>17</v>
+      </c>
+      <c r="AE237">
+        <v>1.12</v>
+      </c>
+      <c r="AF237">
+        <v>5.75</v>
+      </c>
+      <c r="AG237">
+        <v>1.44</v>
+      </c>
+      <c r="AH237">
+        <v>2.67</v>
+      </c>
+      <c r="AI237">
+        <v>2.2</v>
+      </c>
+      <c r="AJ237">
+        <v>1.62</v>
+      </c>
+      <c r="AK237">
+        <v>1.02</v>
+      </c>
+      <c r="AL237">
+        <v>1.09</v>
+      </c>
+      <c r="AM237">
+        <v>5</v>
+      </c>
+      <c r="AN237">
+        <v>2.62</v>
+      </c>
+      <c r="AO237">
+        <v>1</v>
+      </c>
+      <c r="AP237">
+        <v>2.64</v>
+      </c>
+      <c r="AQ237">
+        <v>0.93</v>
+      </c>
+      <c r="AR237">
+        <v>2.48</v>
+      </c>
+      <c r="AS237">
+        <v>1.19</v>
+      </c>
+      <c r="AT237">
+        <v>3.67</v>
+      </c>
+      <c r="AU237">
+        <v>10</v>
+      </c>
+      <c r="AV237">
+        <v>5</v>
+      </c>
+      <c r="AW237">
+        <v>10</v>
+      </c>
+      <c r="AX237">
+        <v>6</v>
+      </c>
+      <c r="AY237">
+        <v>24</v>
+      </c>
+      <c r="AZ237">
+        <v>11</v>
+      </c>
+      <c r="BA237">
+        <v>5</v>
+      </c>
+      <c r="BB237">
+        <v>4</v>
+      </c>
+      <c r="BC237">
+        <v>9</v>
+      </c>
+      <c r="BD237">
+        <v>1.06</v>
+      </c>
+      <c r="BE237">
+        <v>17.5</v>
+      </c>
+      <c r="BF237">
+        <v>12</v>
+      </c>
+      <c r="BG237">
+        <v>1.16</v>
+      </c>
+      <c r="BH237">
+        <v>4.1</v>
+      </c>
+      <c r="BI237">
+        <v>1.33</v>
+      </c>
+      <c r="BJ237">
+        <v>2.83</v>
+      </c>
+      <c r="BK237">
+        <v>1.61</v>
+      </c>
+      <c r="BL237">
+        <v>2.12</v>
+      </c>
+      <c r="BM237">
+        <v>2.03</v>
+      </c>
+      <c r="BN237">
+        <v>1.7</v>
+      </c>
+      <c r="BO237">
+        <v>2.6</v>
+      </c>
+      <c r="BP237">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7492052</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F238">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>72</v>
+      </c>
+      <c r="H238" t="s">
+        <v>74</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>1</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+      <c r="N238">
+        <v>2</v>
+      </c>
+      <c r="O238" t="s">
+        <v>157</v>
+      </c>
+      <c r="P238" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q238">
+        <v>3.1</v>
+      </c>
+      <c r="R238">
+        <v>2.1</v>
+      </c>
+      <c r="S238">
+        <v>3.6</v>
+      </c>
+      <c r="T238">
+        <v>1.44</v>
+      </c>
+      <c r="U238">
+        <v>2.63</v>
+      </c>
+      <c r="V238">
+        <v>3.25</v>
+      </c>
+      <c r="W238">
+        <v>1.33</v>
+      </c>
+      <c r="X238">
+        <v>9</v>
+      </c>
+      <c r="Y238">
+        <v>1.07</v>
+      </c>
+      <c r="Z238">
+        <v>2.42</v>
+      </c>
+      <c r="AA238">
+        <v>3.33</v>
+      </c>
+      <c r="AB238">
+        <v>3.11</v>
+      </c>
+      <c r="AC238">
+        <v>1.06</v>
+      </c>
+      <c r="AD238">
+        <v>8.5</v>
+      </c>
+      <c r="AE238">
+        <v>1.33</v>
+      </c>
+      <c r="AF238">
+        <v>3.2</v>
+      </c>
+      <c r="AG238">
+        <v>2.02</v>
+      </c>
+      <c r="AH238">
+        <v>1.8</v>
+      </c>
+      <c r="AI238">
+        <v>1.8</v>
+      </c>
+      <c r="AJ238">
+        <v>1.95</v>
+      </c>
+      <c r="AK238">
+        <v>1.4</v>
+      </c>
+      <c r="AL238">
+        <v>1.3</v>
+      </c>
+      <c r="AM238">
+        <v>1.57</v>
+      </c>
+      <c r="AN238">
+        <v>1</v>
+      </c>
+      <c r="AO238">
+        <v>1.23</v>
+      </c>
+      <c r="AP238">
+        <v>1</v>
+      </c>
+      <c r="AQ238">
+        <v>1.21</v>
+      </c>
+      <c r="AR238">
+        <v>1.78</v>
+      </c>
+      <c r="AS238">
+        <v>1.04</v>
+      </c>
+      <c r="AT238">
+        <v>2.82</v>
+      </c>
+      <c r="AU238">
+        <v>5</v>
+      </c>
+      <c r="AV238">
+        <v>5</v>
+      </c>
+      <c r="AW238">
+        <v>9</v>
+      </c>
+      <c r="AX238">
+        <v>7</v>
+      </c>
+      <c r="AY238">
+        <v>16</v>
+      </c>
+      <c r="AZ238">
+        <v>14</v>
+      </c>
+      <c r="BA238">
+        <v>2</v>
+      </c>
+      <c r="BB238">
+        <v>2</v>
+      </c>
+      <c r="BC238">
+        <v>4</v>
+      </c>
+      <c r="BD238">
+        <v>1.78</v>
+      </c>
+      <c r="BE238">
+        <v>8.5</v>
+      </c>
+      <c r="BF238">
+        <v>2.45</v>
+      </c>
+      <c r="BG238">
+        <v>1.23</v>
+      </c>
+      <c r="BH238">
+        <v>3.42</v>
+      </c>
+      <c r="BI238">
+        <v>1.46</v>
+      </c>
+      <c r="BJ238">
+        <v>2.45</v>
+      </c>
+      <c r="BK238">
+        <v>1.83</v>
+      </c>
+      <c r="BL238">
+        <v>1.87</v>
+      </c>
+      <c r="BM238">
+        <v>2.32</v>
+      </c>
+      <c r="BN238">
+        <v>1.51</v>
+      </c>
+      <c r="BO238">
+        <v>3.08</v>
+      </c>
+      <c r="BP238">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7492054</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F239">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>77</v>
+      </c>
+      <c r="H239" t="s">
+        <v>86</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>1</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+      <c r="M239">
+        <v>1</v>
+      </c>
+      <c r="N239">
+        <v>1</v>
+      </c>
+      <c r="O239" t="s">
+        <v>96</v>
+      </c>
+      <c r="P239" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q239">
+        <v>2.2</v>
+      </c>
+      <c r="R239">
+        <v>2.3</v>
+      </c>
+      <c r="S239">
+        <v>5</v>
+      </c>
+      <c r="T239">
+        <v>1.33</v>
+      </c>
+      <c r="U239">
+        <v>3.25</v>
+      </c>
+      <c r="V239">
+        <v>2.63</v>
+      </c>
+      <c r="W239">
+        <v>1.44</v>
+      </c>
+      <c r="X239">
+        <v>6.5</v>
+      </c>
+      <c r="Y239">
+        <v>1.11</v>
+      </c>
+      <c r="Z239">
+        <v>1.66</v>
+      </c>
+      <c r="AA239">
+        <v>4.3</v>
+      </c>
+      <c r="AB239">
+        <v>5</v>
+      </c>
+      <c r="AC239">
+        <v>1.04</v>
+      </c>
+      <c r="AD239">
+        <v>10</v>
+      </c>
+      <c r="AE239">
+        <v>1.22</v>
+      </c>
+      <c r="AF239">
+        <v>4.2</v>
+      </c>
+      <c r="AG239">
+        <v>1.55</v>
+      </c>
+      <c r="AH239">
+        <v>2.3</v>
+      </c>
+      <c r="AI239">
+        <v>1.7</v>
+      </c>
+      <c r="AJ239">
+        <v>2.05</v>
+      </c>
+      <c r="AK239">
+        <v>1.17</v>
+      </c>
+      <c r="AL239">
+        <v>1.23</v>
+      </c>
+      <c r="AM239">
+        <v>2.2</v>
+      </c>
+      <c r="AN239">
+        <v>1.15</v>
+      </c>
+      <c r="AO239">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP239">
+        <v>1.07</v>
+      </c>
+      <c r="AQ239">
+        <v>0.86</v>
+      </c>
+      <c r="AR239">
+        <v>1.52</v>
+      </c>
+      <c r="AS239">
+        <v>1.3</v>
+      </c>
+      <c r="AT239">
+        <v>2.82</v>
+      </c>
+      <c r="AU239">
+        <v>3</v>
+      </c>
+      <c r="AV239">
+        <v>5</v>
+      </c>
+      <c r="AW239">
+        <v>7</v>
+      </c>
+      <c r="AX239">
+        <v>7</v>
+      </c>
+      <c r="AY239">
+        <v>11</v>
+      </c>
+      <c r="AZ239">
+        <v>12</v>
+      </c>
+      <c r="BA239">
+        <v>4</v>
+      </c>
+      <c r="BB239">
+        <v>5</v>
+      </c>
+      <c r="BC239">
+        <v>9</v>
+      </c>
+      <c r="BD239">
+        <v>1.55</v>
+      </c>
+      <c r="BE239">
+        <v>9</v>
+      </c>
+      <c r="BF239">
+        <v>3.02</v>
+      </c>
+      <c r="BG239">
+        <v>1.22</v>
+      </c>
+      <c r="BH239">
+        <v>3.5</v>
+      </c>
+      <c r="BI239">
+        <v>1.43</v>
+      </c>
+      <c r="BJ239">
+        <v>2.54</v>
+      </c>
+      <c r="BK239">
+        <v>1.77</v>
+      </c>
+      <c r="BL239">
+        <v>1.94</v>
+      </c>
+      <c r="BM239">
+        <v>2.23</v>
+      </c>
+      <c r="BN239">
+        <v>1.55</v>
+      </c>
+      <c r="BO239">
+        <v>2.97</v>
+      </c>
+      <c r="BP239">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7492055</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F240">
+        <v>27</v>
+      </c>
+      <c r="G240" t="s">
+        <v>70</v>
+      </c>
+      <c r="H240" t="s">
+        <v>71</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>1</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>1</v>
+      </c>
+      <c r="O240" t="s">
+        <v>249</v>
+      </c>
+      <c r="P240" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q240">
+        <v>3.2</v>
+      </c>
+      <c r="R240">
+        <v>2.4</v>
+      </c>
+      <c r="S240">
+        <v>2.75</v>
+      </c>
+      <c r="T240">
+        <v>1.25</v>
+      </c>
+      <c r="U240">
+        <v>3.75</v>
+      </c>
+      <c r="V240">
+        <v>2.25</v>
+      </c>
+      <c r="W240">
+        <v>1.57</v>
+      </c>
+      <c r="X240">
+        <v>5.5</v>
+      </c>
+      <c r="Y240">
+        <v>1.14</v>
+      </c>
+      <c r="Z240">
+        <v>3.03</v>
+      </c>
+      <c r="AA240">
+        <v>3.57</v>
+      </c>
+      <c r="AB240">
+        <v>2.35</v>
+      </c>
+      <c r="AC240">
+        <v>1.01</v>
+      </c>
+      <c r="AD240">
+        <v>13</v>
+      </c>
+      <c r="AE240">
+        <v>1.17</v>
+      </c>
+      <c r="AF240">
+        <v>5</v>
+      </c>
+      <c r="AG240">
+        <v>1.55</v>
+      </c>
+      <c r="AH240">
+        <v>2.3</v>
+      </c>
+      <c r="AI240">
+        <v>1.44</v>
+      </c>
+      <c r="AJ240">
+        <v>2.63</v>
+      </c>
+      <c r="AK240">
+        <v>1.61</v>
+      </c>
+      <c r="AL240">
+        <v>1.26</v>
+      </c>
+      <c r="AM240">
+        <v>1.41</v>
+      </c>
+      <c r="AN240">
+        <v>1.54</v>
+      </c>
+      <c r="AO240">
+        <v>1.31</v>
+      </c>
+      <c r="AP240">
+        <v>1.64</v>
+      </c>
+      <c r="AQ240">
+        <v>1.21</v>
+      </c>
+      <c r="AR240">
+        <v>1.45</v>
+      </c>
+      <c r="AS240">
+        <v>1.18</v>
+      </c>
+      <c r="AT240">
+        <v>2.63</v>
+      </c>
+      <c r="AU240">
+        <v>4</v>
+      </c>
+      <c r="AV240">
+        <v>4</v>
+      </c>
+      <c r="AW240">
+        <v>13</v>
+      </c>
+      <c r="AX240">
+        <v>16</v>
+      </c>
+      <c r="AY240">
+        <v>20</v>
+      </c>
+      <c r="AZ240">
+        <v>22</v>
+      </c>
+      <c r="BA240">
+        <v>5</v>
+      </c>
+      <c r="BB240">
+        <v>8</v>
+      </c>
+      <c r="BC240">
+        <v>13</v>
+      </c>
+      <c r="BD240">
+        <v>2.07</v>
+      </c>
+      <c r="BE240">
+        <v>8.4</v>
+      </c>
+      <c r="BF240">
+        <v>2.06</v>
+      </c>
+      <c r="BG240">
+        <v>1.22</v>
+      </c>
+      <c r="BH240">
+        <v>3.5</v>
+      </c>
+      <c r="BI240">
+        <v>1.44</v>
+      </c>
+      <c r="BJ240">
+        <v>2.5</v>
+      </c>
+      <c r="BK240">
+        <v>1.8</v>
+      </c>
+      <c r="BL240">
+        <v>1.9</v>
+      </c>
+      <c r="BM240">
+        <v>2.28</v>
+      </c>
+      <c r="BN240">
+        <v>1.53</v>
+      </c>
+      <c r="BO240">
+        <v>3.04</v>
+      </c>
+      <c r="BP240">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7492056</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F241">
+        <v>27</v>
+      </c>
+      <c r="G241" t="s">
+        <v>81</v>
+      </c>
+      <c r="H241" t="s">
+        <v>84</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+      <c r="M241">
+        <v>3</v>
+      </c>
+      <c r="N241">
+        <v>3</v>
+      </c>
+      <c r="O241" t="s">
+        <v>96</v>
+      </c>
+      <c r="P241" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q241">
+        <v>3.6</v>
+      </c>
+      <c r="R241">
+        <v>2.3</v>
+      </c>
+      <c r="S241">
+        <v>2.75</v>
+      </c>
+      <c r="T241">
+        <v>1.33</v>
+      </c>
+      <c r="U241">
+        <v>3.25</v>
+      </c>
+      <c r="V241">
+        <v>2.5</v>
+      </c>
+      <c r="W241">
+        <v>1.5</v>
+      </c>
+      <c r="X241">
+        <v>6</v>
+      </c>
+      <c r="Y241">
+        <v>1.13</v>
+      </c>
+      <c r="Z241">
+        <v>3.31</v>
+      </c>
+      <c r="AA241">
+        <v>3.77</v>
+      </c>
+      <c r="AB241">
+        <v>2.14</v>
+      </c>
+      <c r="AC241">
+        <v>1.04</v>
+      </c>
+      <c r="AD241">
+        <v>10</v>
+      </c>
+      <c r="AE241">
+        <v>1.22</v>
+      </c>
+      <c r="AF241">
+        <v>4.2</v>
+      </c>
+      <c r="AG241">
+        <v>1.73</v>
+      </c>
+      <c r="AH241">
+        <v>2</v>
+      </c>
+      <c r="AI241">
+        <v>1.57</v>
+      </c>
+      <c r="AJ241">
+        <v>2.25</v>
+      </c>
+      <c r="AK241">
+        <v>1.65</v>
+      </c>
+      <c r="AL241">
+        <v>1.28</v>
+      </c>
+      <c r="AM241">
+        <v>1.36</v>
+      </c>
+      <c r="AN241">
+        <v>0.85</v>
+      </c>
+      <c r="AO241">
+        <v>1.54</v>
+      </c>
+      <c r="AP241">
+        <v>0.79</v>
+      </c>
+      <c r="AQ241">
+        <v>1.64</v>
+      </c>
+      <c r="AR241">
+        <v>1.25</v>
+      </c>
+      <c r="AS241">
+        <v>1.22</v>
+      </c>
+      <c r="AT241">
+        <v>2.47</v>
+      </c>
+      <c r="AU241">
+        <v>0</v>
+      </c>
+      <c r="AV241">
+        <v>8</v>
+      </c>
+      <c r="AW241">
+        <v>12</v>
+      </c>
+      <c r="AX241">
+        <v>7</v>
+      </c>
+      <c r="AY241">
+        <v>16</v>
+      </c>
+      <c r="AZ241">
+        <v>18</v>
+      </c>
+      <c r="BA241">
+        <v>3</v>
+      </c>
+      <c r="BB241">
+        <v>4</v>
+      </c>
+      <c r="BC241">
+        <v>7</v>
+      </c>
+      <c r="BD241">
+        <v>2.36</v>
+      </c>
+      <c r="BE241">
+        <v>8.5</v>
+      </c>
+      <c r="BF241">
+        <v>1.83</v>
+      </c>
+      <c r="BG241">
+        <v>1.22</v>
+      </c>
+      <c r="BH241">
+        <v>3.5</v>
+      </c>
+      <c r="BI241">
+        <v>1.44</v>
+      </c>
+      <c r="BJ241">
+        <v>2.51</v>
+      </c>
+      <c r="BK241">
+        <v>1.79</v>
+      </c>
+      <c r="BL241">
+        <v>1.92</v>
+      </c>
+      <c r="BM241">
+        <v>2.28</v>
+      </c>
+      <c r="BN241">
+        <v>1.53</v>
+      </c>
+      <c r="BO241">
+        <v>3.04</v>
+      </c>
+      <c r="BP241">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7492051</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45745.60416666666</v>
+      </c>
+      <c r="F242">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>82</v>
+      </c>
+      <c r="H242" t="s">
+        <v>80</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>1</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>1</v>
+      </c>
+      <c r="O242" t="s">
+        <v>237</v>
+      </c>
+      <c r="P242" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q242">
+        <v>2.88</v>
+      </c>
+      <c r="R242">
+        <v>2.4</v>
+      </c>
+      <c r="S242">
+        <v>3.2</v>
+      </c>
+      <c r="T242">
+        <v>1.29</v>
+      </c>
+      <c r="U242">
+        <v>3.5</v>
+      </c>
+      <c r="V242">
+        <v>2.25</v>
+      </c>
+      <c r="W242">
+        <v>1.57</v>
+      </c>
+      <c r="X242">
+        <v>5.5</v>
+      </c>
+      <c r="Y242">
+        <v>1.14</v>
+      </c>
+      <c r="Z242">
+        <v>2.36</v>
+      </c>
+      <c r="AA242">
+        <v>3.65</v>
+      </c>
+      <c r="AB242">
+        <v>2.97</v>
+      </c>
+      <c r="AC242">
+        <v>1.01</v>
+      </c>
+      <c r="AD242">
+        <v>13</v>
+      </c>
+      <c r="AE242">
+        <v>1.18</v>
+      </c>
+      <c r="AF242">
+        <v>4.75</v>
+      </c>
+      <c r="AG242">
+        <v>1.47</v>
+      </c>
+      <c r="AH242">
+        <v>2.57</v>
+      </c>
+      <c r="AI242">
+        <v>1.5</v>
+      </c>
+      <c r="AJ242">
+        <v>2.5</v>
+      </c>
+      <c r="AK242">
+        <v>1.42</v>
+      </c>
+      <c r="AL242">
+        <v>1.27</v>
+      </c>
+      <c r="AM242">
+        <v>1.57</v>
+      </c>
+      <c r="AN242">
+        <v>1.85</v>
+      </c>
+      <c r="AO242">
+        <v>1.42</v>
+      </c>
+      <c r="AP242">
+        <v>1.93</v>
+      </c>
+      <c r="AQ242">
+        <v>1.31</v>
+      </c>
+      <c r="AR242">
+        <v>1.79</v>
+      </c>
+      <c r="AS242">
+        <v>1.23</v>
+      </c>
+      <c r="AT242">
+        <v>3.02</v>
+      </c>
+      <c r="AU242">
+        <v>7</v>
+      </c>
+      <c r="AV242">
+        <v>3</v>
+      </c>
+      <c r="AW242">
+        <v>13</v>
+      </c>
+      <c r="AX242">
+        <v>6</v>
+      </c>
+      <c r="AY242">
+        <v>22</v>
+      </c>
+      <c r="AZ242">
+        <v>11</v>
+      </c>
+      <c r="BA242">
+        <v>6</v>
+      </c>
+      <c r="BB242">
+        <v>10</v>
+      </c>
+      <c r="BC242">
+        <v>16</v>
+      </c>
+      <c r="BD242">
+        <v>1.99</v>
+      </c>
+      <c r="BE242">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF242">
+        <v>2.13</v>
+      </c>
+      <c r="BG242">
+        <v>1.19</v>
+      </c>
+      <c r="BH242">
+        <v>3.8</v>
+      </c>
+      <c r="BI242">
+        <v>1.39</v>
+      </c>
+      <c r="BJ242">
+        <v>2.67</v>
+      </c>
+      <c r="BK242">
+        <v>1.71</v>
+      </c>
+      <c r="BL242">
+        <v>2.02</v>
+      </c>
+      <c r="BM242">
+        <v>2.14</v>
+      </c>
+      <c r="BN242">
+        <v>1.6</v>
+      </c>
+      <c r="BO242">
+        <v>2.81</v>
+      </c>
+      <c r="BP242">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7492053</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45746.4375</v>
+      </c>
+      <c r="F243">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>73</v>
+      </c>
+      <c r="H243" t="s">
+        <v>79</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243">
+        <v>1</v>
+      </c>
+      <c r="K243">
+        <v>2</v>
+      </c>
+      <c r="L243">
+        <v>1</v>
+      </c>
+      <c r="M243">
+        <v>2</v>
+      </c>
+      <c r="N243">
+        <v>3</v>
+      </c>
+      <c r="O243" t="s">
+        <v>161</v>
+      </c>
+      <c r="P243" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q243">
+        <v>2.63</v>
+      </c>
+      <c r="R243">
+        <v>2.1</v>
+      </c>
+      <c r="S243">
+        <v>4.5</v>
+      </c>
+      <c r="T243">
+        <v>1.44</v>
+      </c>
+      <c r="U243">
+        <v>2.63</v>
+      </c>
+      <c r="V243">
+        <v>3.25</v>
+      </c>
+      <c r="W243">
+        <v>1.33</v>
+      </c>
+      <c r="X243">
+        <v>9</v>
+      </c>
+      <c r="Y243">
+        <v>1.07</v>
+      </c>
+      <c r="Z243">
+        <v>2.04</v>
+      </c>
+      <c r="AA243">
+        <v>3.45</v>
+      </c>
+      <c r="AB243">
+        <v>3.95</v>
+      </c>
+      <c r="AC243">
+        <v>1.06</v>
+      </c>
+      <c r="AD243">
+        <v>8.5</v>
+      </c>
+      <c r="AE243">
+        <v>1.35</v>
+      </c>
+      <c r="AF243">
+        <v>3.1</v>
+      </c>
+      <c r="AG243">
+        <v>2</v>
+      </c>
+      <c r="AH243">
+        <v>1.75</v>
+      </c>
+      <c r="AI243">
+        <v>1.95</v>
+      </c>
+      <c r="AJ243">
+        <v>1.8</v>
+      </c>
+      <c r="AK243">
+        <v>1.27</v>
+      </c>
+      <c r="AL243">
+        <v>1.3</v>
+      </c>
+      <c r="AM243">
+        <v>1.77</v>
+      </c>
+      <c r="AN243">
+        <v>2.17</v>
+      </c>
+      <c r="AO243">
+        <v>0.85</v>
+      </c>
+      <c r="AP243">
+        <v>2</v>
+      </c>
+      <c r="AQ243">
+        <v>1</v>
+      </c>
+      <c r="AR243">
+        <v>1.46</v>
+      </c>
+      <c r="AS243">
+        <v>1.27</v>
+      </c>
+      <c r="AT243">
+        <v>2.73</v>
+      </c>
+      <c r="AU243">
+        <v>4</v>
+      </c>
+      <c r="AV243">
+        <v>7</v>
+      </c>
+      <c r="AW243">
+        <v>6</v>
+      </c>
+      <c r="AX243">
+        <v>4</v>
+      </c>
+      <c r="AY243">
+        <v>11</v>
+      </c>
+      <c r="AZ243">
+        <v>12</v>
+      </c>
+      <c r="BA243">
+        <v>3</v>
+      </c>
+      <c r="BB243">
+        <v>3</v>
+      </c>
+      <c r="BC243">
+        <v>6</v>
+      </c>
+      <c r="BD243">
+        <v>1.62</v>
+      </c>
+      <c r="BE243">
+        <v>8.6</v>
+      </c>
+      <c r="BF243">
+        <v>2.83</v>
+      </c>
+      <c r="BG243">
+        <v>1.32</v>
+      </c>
+      <c r="BH243">
+        <v>2.88</v>
+      </c>
+      <c r="BI243">
+        <v>1.61</v>
+      </c>
+      <c r="BJ243">
+        <v>2.12</v>
+      </c>
+      <c r="BK243">
+        <v>2.06</v>
+      </c>
+      <c r="BL243">
+        <v>1.68</v>
+      </c>
+      <c r="BM243">
+        <v>2.71</v>
+      </c>
+      <c r="BN243">
+        <v>1.38</v>
+      </c>
+      <c r="BO243">
+        <v>3.72</v>
+      </c>
+      <c r="BP243">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7492050</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45746.52083333334</v>
+      </c>
+      <c r="F244">
+        <v>27</v>
+      </c>
+      <c r="G244" t="s">
+        <v>76</v>
+      </c>
+      <c r="H244" t="s">
+        <v>75</v>
+      </c>
+      <c r="I244">
+        <v>2</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>2</v>
+      </c>
+      <c r="L244">
+        <v>3</v>
+      </c>
+      <c r="M244">
+        <v>1</v>
+      </c>
+      <c r="N244">
+        <v>4</v>
+      </c>
+      <c r="O244" t="s">
+        <v>250</v>
+      </c>
+      <c r="P244" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q244">
+        <v>2.3</v>
+      </c>
+      <c r="R244">
+        <v>2.3</v>
+      </c>
+      <c r="S244">
+        <v>4.75</v>
+      </c>
+      <c r="T244">
+        <v>1.33</v>
+      </c>
+      <c r="U244">
+        <v>3.25</v>
+      </c>
+      <c r="V244">
+        <v>2.5</v>
+      </c>
+      <c r="W244">
+        <v>1.5</v>
+      </c>
+      <c r="X244">
+        <v>6.5</v>
+      </c>
+      <c r="Y244">
+        <v>1.11</v>
+      </c>
+      <c r="Z244">
+        <v>1.7</v>
+      </c>
+      <c r="AA244">
+        <v>4.2</v>
+      </c>
+      <c r="AB244">
+        <v>4.8</v>
+      </c>
+      <c r="AC244">
+        <v>1.04</v>
+      </c>
+      <c r="AD244">
+        <v>10</v>
+      </c>
+      <c r="AE244">
+        <v>1.22</v>
+      </c>
+      <c r="AF244">
+        <v>4.2</v>
+      </c>
+      <c r="AG244">
+        <v>1.67</v>
+      </c>
+      <c r="AH244">
+        <v>2.1</v>
+      </c>
+      <c r="AI244">
+        <v>1.67</v>
+      </c>
+      <c r="AJ244">
+        <v>2.1</v>
+      </c>
+      <c r="AK244">
+        <v>1.19</v>
+      </c>
+      <c r="AL244">
+        <v>1.23</v>
+      </c>
+      <c r="AM244">
+        <v>2.15</v>
+      </c>
+      <c r="AN244">
+        <v>1.85</v>
+      </c>
+      <c r="AO244">
+        <v>1.77</v>
+      </c>
+      <c r="AP244">
+        <v>1.93</v>
+      </c>
+      <c r="AQ244">
+        <v>1.64</v>
+      </c>
+      <c r="AR244">
+        <v>1.64</v>
+      </c>
+      <c r="AS244">
+        <v>1.27</v>
+      </c>
+      <c r="AT244">
+        <v>2.91</v>
+      </c>
+      <c r="AU244">
+        <v>8</v>
+      </c>
+      <c r="AV244">
+        <v>4</v>
+      </c>
+      <c r="AW244">
+        <v>11</v>
+      </c>
+      <c r="AX244">
+        <v>8</v>
+      </c>
+      <c r="AY244">
+        <v>22</v>
+      </c>
+      <c r="AZ244">
+        <v>17</v>
+      </c>
+      <c r="BA244">
+        <v>6</v>
+      </c>
+      <c r="BB244">
+        <v>4</v>
+      </c>
+      <c r="BC244">
+        <v>10</v>
+      </c>
+      <c r="BD244">
+        <v>1.49</v>
+      </c>
+      <c r="BE244">
+        <v>6.75</v>
+      </c>
+      <c r="BF244">
+        <v>2.9</v>
+      </c>
+      <c r="BG244">
+        <v>1.28</v>
+      </c>
+      <c r="BH244">
+        <v>3.3</v>
+      </c>
+      <c r="BI244">
+        <v>1.49</v>
+      </c>
+      <c r="BJ244">
+        <v>2.4</v>
+      </c>
+      <c r="BK244">
+        <v>1.78</v>
+      </c>
+      <c r="BL244">
+        <v>1.91</v>
+      </c>
+      <c r="BM244">
+        <v>2.2</v>
+      </c>
+      <c r="BN244">
+        <v>1.58</v>
+      </c>
+      <c r="BO244">
+        <v>2.8</v>
+      </c>
+      <c r="BP244">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -51340,10 +51340,10 @@
         <v>6</v>
       </c>
       <c r="BB242">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC242">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD242">
         <v>1.99</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="386">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1170,6 +1170,9 @@
   <si>
     <t>['30', '48']</t>
   </si>
+  <si>
+    <t>['42', '60', '90+3']</t>
+  </si>
 </sst>
 </file>
 
@@ -1530,7 +1533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2688,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ6">
         <v>1.64</v>
@@ -3309,7 +3312,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ9">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -6811,7 +6814,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ26">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR26">
         <v>1.4</v>
@@ -7014,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ27">
         <v>0.93</v>
@@ -7426,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ29">
         <v>1.64</v>
@@ -7841,7 +7844,7 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR31">
         <v>0.65</v>
@@ -11134,7 +11137,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ47">
         <v>1.54</v>
@@ -12579,7 +12582,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ54">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR54">
         <v>1.7</v>
@@ -15048,7 +15051,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ66">
         <v>0.85</v>
@@ -16081,7 +16084,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ71">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR71">
         <v>1.42</v>
@@ -18759,7 +18762,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ84">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -19786,7 +19789,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -22876,7 +22879,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ104">
         <v>0.43</v>
@@ -23497,7 +23500,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ107">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR107">
         <v>1.93</v>
@@ -26381,7 +26384,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ121">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR121">
         <v>1.51</v>
@@ -26584,7 +26587,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ122">
         <v>2.23</v>
@@ -30913,7 +30916,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ143">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR143">
         <v>1.59</v>
@@ -31322,7 +31325,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ145">
         <v>1.31</v>
@@ -35648,7 +35651,7 @@
         <v>0.78</v>
       </c>
       <c r="AP166">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ166">
         <v>0.86</v>
@@ -35857,7 +35860,7 @@
         <v>2</v>
       </c>
       <c r="AQ167">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR167">
         <v>1.56</v>
@@ -40798,7 +40801,7 @@
         <v>1.36</v>
       </c>
       <c r="AP191">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ191">
         <v>1.21</v>
@@ -41831,7 +41834,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ196">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR196">
         <v>2.06</v>
@@ -44509,7 +44512,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ209">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR209">
         <v>1.85</v>
@@ -46154,7 +46157,7 @@
         <v>1.17</v>
       </c>
       <c r="AP217">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ217">
         <v>1.14</v>
@@ -48626,7 +48629,7 @@
         <v>1.92</v>
       </c>
       <c r="AP229">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ229">
         <v>1.77</v>
@@ -48835,7 +48838,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ230">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR230">
         <v>1.53</v>
@@ -51795,6 +51798,212 @@
       </c>
       <c r="BP244">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7492061</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45751.64583333334</v>
+      </c>
+      <c r="F245">
+        <v>28</v>
+      </c>
+      <c r="G245" t="s">
+        <v>74</v>
+      </c>
+      <c r="H245" t="s">
+        <v>87</v>
+      </c>
+      <c r="I245">
+        <v>1</v>
+      </c>
+      <c r="J245">
+        <v>1</v>
+      </c>
+      <c r="K245">
+        <v>2</v>
+      </c>
+      <c r="L245">
+        <v>1</v>
+      </c>
+      <c r="M245">
+        <v>3</v>
+      </c>
+      <c r="N245">
+        <v>4</v>
+      </c>
+      <c r="O245" t="s">
+        <v>221</v>
+      </c>
+      <c r="P245" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q245">
+        <v>6.5</v>
+      </c>
+      <c r="R245">
+        <v>2.4</v>
+      </c>
+      <c r="S245">
+        <v>1.95</v>
+      </c>
+      <c r="T245">
+        <v>1.33</v>
+      </c>
+      <c r="U245">
+        <v>3.25</v>
+      </c>
+      <c r="V245">
+        <v>2.5</v>
+      </c>
+      <c r="W245">
+        <v>1.5</v>
+      </c>
+      <c r="X245">
+        <v>6.5</v>
+      </c>
+      <c r="Y245">
+        <v>1.11</v>
+      </c>
+      <c r="Z245">
+        <v>7.1</v>
+      </c>
+      <c r="AA245">
+        <v>4.8</v>
+      </c>
+      <c r="AB245">
+        <v>1.46</v>
+      </c>
+      <c r="AC245">
+        <v>1.03</v>
+      </c>
+      <c r="AD245">
+        <v>11</v>
+      </c>
+      <c r="AE245">
+        <v>1.2</v>
+      </c>
+      <c r="AF245">
+        <v>4.33</v>
+      </c>
+      <c r="AG245">
+        <v>1.67</v>
+      </c>
+      <c r="AH245">
+        <v>2.1</v>
+      </c>
+      <c r="AI245">
+        <v>1.91</v>
+      </c>
+      <c r="AJ245">
+        <v>1.91</v>
+      </c>
+      <c r="AK245">
+        <v>2.7</v>
+      </c>
+      <c r="AL245">
+        <v>1.19</v>
+      </c>
+      <c r="AM245">
+        <v>1.1</v>
+      </c>
+      <c r="AN245">
+        <v>1.69</v>
+      </c>
+      <c r="AO245">
+        <v>2.15</v>
+      </c>
+      <c r="AP245">
+        <v>1.57</v>
+      </c>
+      <c r="AQ245">
+        <v>2.21</v>
+      </c>
+      <c r="AR245">
+        <v>1.52</v>
+      </c>
+      <c r="AS245">
+        <v>1.81</v>
+      </c>
+      <c r="AT245">
+        <v>3.33</v>
+      </c>
+      <c r="AU245">
+        <v>4</v>
+      </c>
+      <c r="AV245">
+        <v>9</v>
+      </c>
+      <c r="AW245">
+        <v>3</v>
+      </c>
+      <c r="AX245">
+        <v>12</v>
+      </c>
+      <c r="AY245">
+        <v>8</v>
+      </c>
+      <c r="AZ245">
+        <v>24</v>
+      </c>
+      <c r="BA245">
+        <v>2</v>
+      </c>
+      <c r="BB245">
+        <v>4</v>
+      </c>
+      <c r="BC245">
+        <v>6</v>
+      </c>
+      <c r="BD245">
+        <v>5.3</v>
+      </c>
+      <c r="BE245">
+        <v>11</v>
+      </c>
+      <c r="BF245">
+        <v>1.24</v>
+      </c>
+      <c r="BG245">
+        <v>1.27</v>
+      </c>
+      <c r="BH245">
+        <v>3.14</v>
+      </c>
+      <c r="BI245">
+        <v>1.52</v>
+      </c>
+      <c r="BJ245">
+        <v>2.3</v>
+      </c>
+      <c r="BK245">
+        <v>1.92</v>
+      </c>
+      <c r="BL245">
+        <v>1.79</v>
+      </c>
+      <c r="BM245">
+        <v>2.48</v>
+      </c>
+      <c r="BN245">
+        <v>1.45</v>
+      </c>
+      <c r="BO245">
+        <v>3.28</v>
+      </c>
+      <c r="BP245">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="391">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -769,6 +769,15 @@
     <t>['39', '42', '72']</t>
   </si>
   <si>
+    <t>['24', '43', '84']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
+    <t>['28', '84']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -1093,9 +1102,6 @@
     <t>['10', '26']</t>
   </si>
   <si>
-    <t>['88']</t>
-  </si>
-  <si>
     <t>['28', '44', '63']</t>
   </si>
   <si>
@@ -1172,6 +1178,15 @@
   </si>
   <si>
     <t>['42', '60', '90+3']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['34', '51', '68', '78']</t>
+  </si>
+  <si>
+    <t>['8', '11', '48', '85']</t>
   </si>
 </sst>
 </file>
@@ -1533,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP245"/>
+  <dimension ref="A1:BP251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1789,7 +1804,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1870,7 +1885,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ2">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2073,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0.43</v>
@@ -2201,7 +2216,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2282,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2407,7 +2422,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2485,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ5">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2613,7 +2628,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2897,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -3106,7 +3121,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ8">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3231,7 +3246,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3437,7 +3452,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3849,7 +3864,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -4055,7 +4070,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4261,7 +4276,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4342,7 +4357,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4467,7 +4482,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4545,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ15">
         <v>1.54</v>
@@ -4751,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ16">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4879,7 +4894,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5163,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ18">
         <v>1.21</v>
@@ -5497,7 +5512,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5781,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
         <v>1</v>
@@ -5909,7 +5924,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5990,7 +6005,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR22">
         <v>2.26</v>
@@ -6193,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ23">
         <v>0.43</v>
@@ -6321,7 +6336,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6402,7 +6417,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ24">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
         <v>1.03</v>
@@ -6527,7 +6542,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6608,7 +6623,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ25">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR25">
         <v>1.46</v>
@@ -6733,7 +6748,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -7145,7 +7160,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7223,7 +7238,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ28">
         <v>1.64</v>
@@ -7351,7 +7366,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7557,7 +7572,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7635,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ30">
         <v>1.14</v>
@@ -7763,7 +7778,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7841,7 +7856,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31">
         <v>2.21</v>
@@ -7969,7 +7984,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8050,7 +8065,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR32">
         <v>1.36</v>
@@ -8175,7 +8190,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8253,10 +8268,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ33">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR33">
         <v>1.57</v>
@@ -8587,7 +8602,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8874,7 +8889,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ36">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>2.62</v>
@@ -9205,7 +9220,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9617,7 +9632,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9695,7 +9710,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ40">
         <v>0.86</v>
@@ -9823,7 +9838,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9904,7 +9919,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ41">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR41">
         <v>1.28</v>
@@ -10029,7 +10044,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10107,7 +10122,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ42">
         <v>0.93</v>
@@ -10313,7 +10328,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>1.21</v>
@@ -10441,7 +10456,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10522,7 +10537,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ44">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10647,7 +10662,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10728,7 +10743,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ45">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR45">
         <v>1</v>
@@ -10853,7 +10868,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11265,7 +11280,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11346,7 +11361,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ48">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR48">
         <v>2.42</v>
@@ -11549,7 +11564,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ49">
         <v>1.14</v>
@@ -11677,7 +11692,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11758,7 +11773,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ50">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11883,7 +11898,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11961,7 +11976,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ51">
         <v>1.77</v>
@@ -12089,7 +12104,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12373,7 +12388,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ53">
         <v>1.21</v>
@@ -12501,7 +12516,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12707,7 +12722,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12788,7 +12803,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR55">
         <v>2.29</v>
@@ -12913,7 +12928,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -13119,7 +13134,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13200,7 +13215,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ57">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR57">
         <v>2.44</v>
@@ -13531,7 +13546,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13609,7 +13624,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ59">
         <v>1.21</v>
@@ -13737,7 +13752,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13815,7 +13830,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ60">
         <v>1.21</v>
@@ -13943,7 +13958,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14230,7 +14245,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ62">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR62">
         <v>1.47</v>
@@ -14355,7 +14370,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14561,7 +14576,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14767,7 +14782,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14845,7 +14860,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65">
         <v>1.54</v>
@@ -14973,7 +14988,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15054,7 +15069,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ66">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15385,7 +15400,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15463,7 +15478,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
         <v>1.14</v>
@@ -15672,7 +15687,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ69">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR69">
         <v>2.2</v>
@@ -15797,7 +15812,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15875,10 +15890,10 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ70">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR70">
         <v>0.6899999999999999</v>
@@ -16003,7 +16018,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16081,7 +16096,7 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ71">
         <v>2.21</v>
@@ -16290,7 +16305,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ72">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16493,10 +16508,10 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR73">
         <v>1.3</v>
@@ -16702,7 +16717,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ74">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR74">
         <v>2.41</v>
@@ -17033,7 +17048,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17239,7 +17254,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18141,7 +18156,7 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ81">
         <v>1.64</v>
@@ -18681,7 +18696,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18965,10 +18980,10 @@
         <v>0.5</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ85">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR85">
         <v>0.97</v>
@@ -19093,7 +19108,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19171,10 +19186,10 @@
         <v>0.25</v>
       </c>
       <c r="AP86">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ86">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.34</v>
@@ -19299,7 +19314,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19377,10 +19392,10 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ87">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -19583,7 +19598,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
         <v>1.54</v>
@@ -19792,7 +19807,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19917,7 +19932,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19998,7 +20013,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ90">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR90">
         <v>2.13</v>
@@ -20123,7 +20138,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20201,7 +20216,7 @@
         <v>1.75</v>
       </c>
       <c r="AP91">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ91">
         <v>1.77</v>
@@ -20535,7 +20550,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -21153,7 +21168,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21771,7 +21786,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22183,7 +22198,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22264,7 +22279,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ101">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR101">
         <v>1.26</v>
@@ -22389,7 +22404,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22470,7 +22485,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ102">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR102">
         <v>1.35</v>
@@ -22595,7 +22610,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22673,7 +22688,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ103">
         <v>1.54</v>
@@ -23007,7 +23022,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23085,7 +23100,7 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>1.77</v>
@@ -23213,7 +23228,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23291,10 +23306,10 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ106">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR106">
         <v>1.1</v>
@@ -23419,7 +23434,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23703,10 +23718,10 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR108">
         <v>1.45</v>
@@ -23831,7 +23846,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23909,10 +23924,10 @@
         <v>1.67</v>
       </c>
       <c r="AP109">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ109">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -24037,7 +24052,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24243,7 +24258,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24527,7 +24542,7 @@
         <v>1.67</v>
       </c>
       <c r="AP112">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ112">
         <v>1.64</v>
@@ -24655,7 +24670,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24861,7 +24876,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25273,7 +25288,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25354,7 +25369,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ116">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR116">
         <v>1.64</v>
@@ -25479,7 +25494,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25891,7 +25906,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25969,7 +25984,7 @@
         <v>2.17</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ119">
         <v>1.77</v>
@@ -26097,7 +26112,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26303,7 +26318,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26381,7 +26396,7 @@
         <v>2.43</v>
       </c>
       <c r="AP121">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ121">
         <v>2.21</v>
@@ -26509,7 +26524,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26590,7 +26605,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ122">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26796,7 +26811,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ123">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26921,7 +26936,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27127,7 +27142,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27205,10 +27220,10 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ125">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR125">
         <v>1.33</v>
@@ -27333,7 +27348,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27414,7 +27429,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ126">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR126">
         <v>1.74</v>
@@ -27539,7 +27554,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27617,10 +27632,10 @@
         <v>1.86</v>
       </c>
       <c r="AP127">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ127">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR127">
         <v>1.42</v>
@@ -27745,7 +27760,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27951,7 +27966,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -28157,7 +28172,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28363,7 +28378,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28569,7 +28584,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28775,7 +28790,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28853,7 +28868,7 @@
         <v>0.71</v>
       </c>
       <c r="AP133">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ133">
         <v>1</v>
@@ -29265,7 +29280,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ135">
         <v>0.86</v>
@@ -29393,7 +29408,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29474,7 +29489,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ136">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR136">
         <v>1.28</v>
@@ -29599,7 +29614,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29680,7 +29695,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ137">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR137">
         <v>1.63</v>
@@ -30089,7 +30104,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30217,7 +30232,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30295,10 +30310,10 @@
         <v>0.29</v>
       </c>
       <c r="AP140">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ140">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR140">
         <v>1.59</v>
@@ -30501,7 +30516,7 @@
         <v>0.13</v>
       </c>
       <c r="AP141">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ141">
         <v>0.43</v>
@@ -30629,7 +30644,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30710,7 +30725,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ142">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR142">
         <v>1.26</v>
@@ -31041,7 +31056,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31119,7 +31134,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>1.64</v>
@@ -31247,7 +31262,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31328,7 +31343,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ145">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31453,7 +31468,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31534,7 +31549,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ146">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR146">
         <v>1.19</v>
@@ -32355,7 +32370,7 @@
         <v>1.13</v>
       </c>
       <c r="AP150">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ150">
         <v>0.93</v>
@@ -32483,7 +32498,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32770,7 +32785,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ152">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR152">
         <v>2.19</v>
@@ -32895,7 +32910,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32973,7 +32988,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ153">
         <v>0.86</v>
@@ -33101,7 +33116,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33388,7 +33403,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ155">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR155">
         <v>1.87</v>
@@ -33513,7 +33528,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33594,7 +33609,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR156">
         <v>1.22</v>
@@ -33719,7 +33734,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33797,7 +33812,7 @@
         <v>1.44</v>
       </c>
       <c r="AP157">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ157">
         <v>1.21</v>
@@ -33925,7 +33940,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34003,7 +34018,7 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ158">
         <v>0.93</v>
@@ -34337,7 +34352,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34543,7 +34558,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34749,7 +34764,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34955,7 +34970,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -35033,7 +35048,7 @@
         <v>0.63</v>
       </c>
       <c r="AP163">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ163">
         <v>1.21</v>
@@ -35161,7 +35176,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35242,7 +35257,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ164">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR164">
         <v>1.34</v>
@@ -35445,10 +35460,10 @@
         <v>1.5</v>
       </c>
       <c r="AP165">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ165">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR165">
         <v>1.46</v>
@@ -35779,7 +35794,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q167">
         <v>7</v>
@@ -35857,7 +35872,7 @@
         <v>2.22</v>
       </c>
       <c r="AP167">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ167">
         <v>2.21</v>
@@ -35985,7 +36000,7 @@
         <v>209</v>
       </c>
       <c r="P168" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q168">
         <v>2.1</v>
@@ -36191,7 +36206,7 @@
         <v>210</v>
       </c>
       <c r="P169" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36269,10 +36284,10 @@
         <v>2.25</v>
       </c>
       <c r="AP169">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ169">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR169">
         <v>1.49</v>
@@ -36603,7 +36618,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36684,7 +36699,7 @@
         <v>1</v>
       </c>
       <c r="AQ171">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR171">
         <v>1.74</v>
@@ -37093,7 +37108,7 @@
         <v>1.56</v>
       </c>
       <c r="AP173">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ173">
         <v>1.64</v>
@@ -37221,7 +37236,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q174">
         <v>2</v>
@@ -37427,7 +37442,7 @@
         <v>216</v>
       </c>
       <c r="P175" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q175">
         <v>1.25</v>
@@ -37508,7 +37523,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ175">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR175">
         <v>2.37</v>
@@ -37633,7 +37648,7 @@
         <v>151</v>
       </c>
       <c r="P176" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37711,10 +37726,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP176">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ176">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR176">
         <v>1.36</v>
@@ -37917,7 +37932,7 @@
         <v>0.8</v>
       </c>
       <c r="AP177">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ177">
         <v>1.14</v>
@@ -38457,7 +38472,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38663,7 +38678,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -38744,7 +38759,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ181">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR181">
         <v>2.14</v>
@@ -39156,7 +39171,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ183">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR183">
         <v>1.45</v>
@@ -39281,7 +39296,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39362,7 +39377,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ184">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR184">
         <v>1.55</v>
@@ -39487,7 +39502,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39771,7 +39786,7 @@
         <v>0.7</v>
       </c>
       <c r="AP186">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ186">
         <v>0.86</v>
@@ -39977,7 +39992,7 @@
         <v>0.9</v>
       </c>
       <c r="AP187">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ187">
         <v>1.21</v>
@@ -40105,7 +40120,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40186,7 +40201,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ188">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR188">
         <v>1.5</v>
@@ -40311,7 +40326,7 @@
         <v>223</v>
       </c>
       <c r="P189" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40595,7 +40610,7 @@
         <v>1.2</v>
       </c>
       <c r="AP190">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ190">
         <v>0.93</v>
@@ -40929,7 +40944,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q192">
         <v>2.3</v>
@@ -41135,7 +41150,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q193">
         <v>2.88</v>
@@ -41419,10 +41434,10 @@
         <v>0.8</v>
       </c>
       <c r="AP194">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ194">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR194">
         <v>1.33</v>
@@ -41547,7 +41562,7 @@
         <v>96</v>
       </c>
       <c r="P195" t="s">
-        <v>359</v>
+        <v>252</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41959,7 +41974,7 @@
         <v>226</v>
       </c>
       <c r="P197" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q197">
         <v>2.4</v>
@@ -42037,10 +42052,10 @@
         <v>0.7</v>
       </c>
       <c r="AP197">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ197">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR197">
         <v>1.38</v>
@@ -42246,7 +42261,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ198">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR198">
         <v>1.84</v>
@@ -42371,7 +42386,7 @@
         <v>96</v>
       </c>
       <c r="P199" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q199">
         <v>4</v>
@@ -42449,7 +42464,7 @@
         <v>1.4</v>
       </c>
       <c r="AP199">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ199">
         <v>1.64</v>
@@ -42655,7 +42670,7 @@
         <v>1.55</v>
       </c>
       <c r="AP200">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ200">
         <v>1.64</v>
@@ -42783,7 +42798,7 @@
         <v>96</v>
       </c>
       <c r="P201" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q201">
         <v>8.5</v>
@@ -42864,7 +42879,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ201">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR201">
         <v>1.24</v>
@@ -42989,7 +43004,7 @@
         <v>96</v>
       </c>
       <c r="P202" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q202">
         <v>2.5</v>
@@ -43273,7 +43288,7 @@
         <v>1.09</v>
       </c>
       <c r="AP203">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ203">
         <v>0.93</v>
@@ -43813,7 +43828,7 @@
         <v>231</v>
       </c>
       <c r="P206" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43891,7 +43906,7 @@
         <v>0.64</v>
       </c>
       <c r="AP206">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ206">
         <v>0.86</v>
@@ -44100,7 +44115,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ207">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR207">
         <v>2.52</v>
@@ -44225,7 +44240,7 @@
         <v>233</v>
       </c>
       <c r="P208" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -44306,7 +44321,7 @@
         <v>1</v>
       </c>
       <c r="AQ208">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR208">
         <v>1.84</v>
@@ -44431,7 +44446,7 @@
         <v>97</v>
       </c>
       <c r="P209" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q209">
         <v>4.5</v>
@@ -44637,7 +44652,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44715,7 +44730,7 @@
         <v>1.82</v>
       </c>
       <c r="AP210">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ210">
         <v>1.77</v>
@@ -44843,7 +44858,7 @@
         <v>96</v>
       </c>
       <c r="P211" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -44924,7 +44939,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ211">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR211">
         <v>1.27</v>
@@ -45127,10 +45142,10 @@
         <v>0.91</v>
       </c>
       <c r="AP212">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ212">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR212">
         <v>1.4</v>
@@ -45255,7 +45270,7 @@
         <v>96</v>
       </c>
       <c r="P213" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q213">
         <v>3.4</v>
@@ -45333,7 +45348,7 @@
         <v>1.27</v>
       </c>
       <c r="AP213">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ213">
         <v>1.54</v>
@@ -45461,7 +45476,7 @@
         <v>235</v>
       </c>
       <c r="P214" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q214">
         <v>2.5</v>
@@ -45539,7 +45554,7 @@
         <v>1.55</v>
       </c>
       <c r="AP214">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ214">
         <v>1.64</v>
@@ -45667,7 +45682,7 @@
         <v>104</v>
       </c>
       <c r="P215" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q215">
         <v>4.75</v>
@@ -45748,7 +45763,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ215">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR215">
         <v>1.89</v>
@@ -45873,7 +45888,7 @@
         <v>96</v>
       </c>
       <c r="P216" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q216">
         <v>2.1</v>
@@ -45954,7 +45969,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ216">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR216">
         <v>1.5</v>
@@ -46285,7 +46300,7 @@
         <v>171</v>
       </c>
       <c r="P218" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q218">
         <v>3.1</v>
@@ -46491,7 +46506,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q219">
         <v>1.67</v>
@@ -46697,7 +46712,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q220">
         <v>1.4</v>
@@ -46903,7 +46918,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q221">
         <v>2</v>
@@ -47315,7 +47330,7 @@
         <v>238</v>
       </c>
       <c r="P223" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q223">
         <v>5.5</v>
@@ -47396,7 +47411,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ223">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR223">
         <v>1.19</v>
@@ -47599,7 +47614,7 @@
         <v>1.33</v>
       </c>
       <c r="AP224">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ224">
         <v>1.21</v>
@@ -47727,7 +47742,7 @@
         <v>239</v>
       </c>
       <c r="P225" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47933,7 +47948,7 @@
         <v>97</v>
       </c>
       <c r="P226" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q226">
         <v>2.3</v>
@@ -48220,7 +48235,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ227">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR227">
         <v>1.25</v>
@@ -48345,7 +48360,7 @@
         <v>241</v>
       </c>
       <c r="P228" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q228">
         <v>2.63</v>
@@ -48423,7 +48438,7 @@
         <v>1.15</v>
       </c>
       <c r="AP228">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ228">
         <v>1.14</v>
@@ -48963,7 +48978,7 @@
         <v>243</v>
       </c>
       <c r="P231" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q231">
         <v>2.75</v>
@@ -49041,7 +49056,7 @@
         <v>1.42</v>
       </c>
       <c r="AP231">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ231">
         <v>1.54</v>
@@ -49247,10 +49262,10 @@
         <v>0.92</v>
       </c>
       <c r="AP232">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ232">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR232">
         <v>1.52</v>
@@ -49375,7 +49390,7 @@
         <v>171</v>
       </c>
       <c r="P233" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49453,10 +49468,10 @@
         <v>1.5</v>
       </c>
       <c r="AP233">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ233">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR233">
         <v>1.41</v>
@@ -49581,7 +49596,7 @@
         <v>245</v>
       </c>
       <c r="P234" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q234">
         <v>2.63</v>
@@ -49659,10 +49674,10 @@
         <v>0.5</v>
       </c>
       <c r="AP234">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ234">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR234">
         <v>1.43</v>
@@ -49787,7 +49802,7 @@
         <v>246</v>
       </c>
       <c r="P235" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q235">
         <v>3.5</v>
@@ -49868,7 +49883,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ235">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR235">
         <v>1.83</v>
@@ -50199,7 +50214,7 @@
         <v>248</v>
       </c>
       <c r="P237" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q237">
         <v>1.5</v>
@@ -50611,7 +50626,7 @@
         <v>96</v>
       </c>
       <c r="P239" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q239">
         <v>2.2</v>
@@ -51023,7 +51038,7 @@
         <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q241">
         <v>3.6</v>
@@ -51310,7 +51325,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ242">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR242">
         <v>1.79</v>
@@ -51435,7 +51450,7 @@
         <v>161</v>
       </c>
       <c r="P243" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q243">
         <v>2.63</v>
@@ -51513,7 +51528,7 @@
         <v>0.85</v>
       </c>
       <c r="AP243">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ243">
         <v>1</v>
@@ -51847,7 +51862,7 @@
         <v>221</v>
       </c>
       <c r="P245" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q245">
         <v>6.5</v>
@@ -52004,6 +52019,1242 @@
       </c>
       <c r="BP245">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7492057</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45752.4375</v>
+      </c>
+      <c r="F246">
+        <v>28</v>
+      </c>
+      <c r="G246" t="s">
+        <v>71</v>
+      </c>
+      <c r="H246" t="s">
+        <v>72</v>
+      </c>
+      <c r="I246">
+        <v>2</v>
+      </c>
+      <c r="J246">
+        <v>1</v>
+      </c>
+      <c r="K246">
+        <v>3</v>
+      </c>
+      <c r="L246">
+        <v>3</v>
+      </c>
+      <c r="M246">
+        <v>1</v>
+      </c>
+      <c r="N246">
+        <v>4</v>
+      </c>
+      <c r="O246" t="s">
+        <v>251</v>
+      </c>
+      <c r="P246" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q246">
+        <v>2</v>
+      </c>
+      <c r="R246">
+        <v>2.5</v>
+      </c>
+      <c r="S246">
+        <v>5.5</v>
+      </c>
+      <c r="T246">
+        <v>1.25</v>
+      </c>
+      <c r="U246">
+        <v>3.75</v>
+      </c>
+      <c r="V246">
+        <v>2.2</v>
+      </c>
+      <c r="W246">
+        <v>1.62</v>
+      </c>
+      <c r="X246">
+        <v>5</v>
+      </c>
+      <c r="Y246">
+        <v>1.17</v>
+      </c>
+      <c r="Z246">
+        <v>1.54</v>
+      </c>
+      <c r="AA246">
+        <v>4.75</v>
+      </c>
+      <c r="AB246">
+        <v>5.8</v>
+      </c>
+      <c r="AC246">
+        <v>0</v>
+      </c>
+      <c r="AD246">
+        <v>0</v>
+      </c>
+      <c r="AE246">
+        <v>1.11</v>
+      </c>
+      <c r="AF246">
+        <v>5.1</v>
+      </c>
+      <c r="AG246">
+        <v>1.68</v>
+      </c>
+      <c r="AH246">
+        <v>2.19</v>
+      </c>
+      <c r="AI246">
+        <v>1.62</v>
+      </c>
+      <c r="AJ246">
+        <v>2.2</v>
+      </c>
+      <c r="AK246">
+        <v>1.2</v>
+      </c>
+      <c r="AL246">
+        <v>1.24</v>
+      </c>
+      <c r="AM246">
+        <v>2.39</v>
+      </c>
+      <c r="AN246">
+        <v>1.92</v>
+      </c>
+      <c r="AO246">
+        <v>1</v>
+      </c>
+      <c r="AP246">
+        <v>2</v>
+      </c>
+      <c r="AQ246">
+        <v>0.93</v>
+      </c>
+      <c r="AR246">
+        <v>1.53</v>
+      </c>
+      <c r="AS246">
+        <v>1.21</v>
+      </c>
+      <c r="AT246">
+        <v>2.74</v>
+      </c>
+      <c r="AU246">
+        <v>6</v>
+      </c>
+      <c r="AV246">
+        <v>6</v>
+      </c>
+      <c r="AW246">
+        <v>12</v>
+      </c>
+      <c r="AX246">
+        <v>4</v>
+      </c>
+      <c r="AY246">
+        <v>22</v>
+      </c>
+      <c r="AZ246">
+        <v>11</v>
+      </c>
+      <c r="BA246">
+        <v>8</v>
+      </c>
+      <c r="BB246">
+        <v>2</v>
+      </c>
+      <c r="BC246">
+        <v>10</v>
+      </c>
+      <c r="BD246">
+        <v>1.49</v>
+      </c>
+      <c r="BE246">
+        <v>9.4</v>
+      </c>
+      <c r="BF246">
+        <v>3.22</v>
+      </c>
+      <c r="BG246">
+        <v>1.18</v>
+      </c>
+      <c r="BH246">
+        <v>3.9</v>
+      </c>
+      <c r="BI246">
+        <v>1.47</v>
+      </c>
+      <c r="BJ246">
+        <v>2.62</v>
+      </c>
+      <c r="BK246">
+        <v>1.76</v>
+      </c>
+      <c r="BL246">
+        <v>2.07</v>
+      </c>
+      <c r="BM246">
+        <v>2.16</v>
+      </c>
+      <c r="BN246">
+        <v>1.69</v>
+      </c>
+      <c r="BO246">
+        <v>2.78</v>
+      </c>
+      <c r="BP246">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7492058</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45752.4375</v>
+      </c>
+      <c r="F247">
+        <v>28</v>
+      </c>
+      <c r="G247" t="s">
+        <v>86</v>
+      </c>
+      <c r="H247" t="s">
+        <v>85</v>
+      </c>
+      <c r="I247">
+        <v>0</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>0</v>
+      </c>
+      <c r="L247">
+        <v>0</v>
+      </c>
+      <c r="M247">
+        <v>1</v>
+      </c>
+      <c r="N247">
+        <v>1</v>
+      </c>
+      <c r="O247" t="s">
+        <v>96</v>
+      </c>
+      <c r="P247" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q247">
+        <v>6.5</v>
+      </c>
+      <c r="R247">
+        <v>2.5</v>
+      </c>
+      <c r="S247">
+        <v>1.91</v>
+      </c>
+      <c r="T247">
+        <v>1.3</v>
+      </c>
+      <c r="U247">
+        <v>3.4</v>
+      </c>
+      <c r="V247">
+        <v>2.38</v>
+      </c>
+      <c r="W247">
+        <v>1.53</v>
+      </c>
+      <c r="X247">
+        <v>6</v>
+      </c>
+      <c r="Y247">
+        <v>1.13</v>
+      </c>
+      <c r="Z247">
+        <v>6.5</v>
+      </c>
+      <c r="AA247">
+        <v>4.9</v>
+      </c>
+      <c r="AB247">
+        <v>1.48</v>
+      </c>
+      <c r="AC247">
+        <v>0</v>
+      </c>
+      <c r="AD247">
+        <v>0</v>
+      </c>
+      <c r="AE247">
+        <v>1.16</v>
+      </c>
+      <c r="AF247">
+        <v>4.25</v>
+      </c>
+      <c r="AG247">
+        <v>1.57</v>
+      </c>
+      <c r="AH247">
+        <v>2.25</v>
+      </c>
+      <c r="AI247">
+        <v>1.8</v>
+      </c>
+      <c r="AJ247">
+        <v>1.95</v>
+      </c>
+      <c r="AK247">
+        <v>2.77</v>
+      </c>
+      <c r="AL247">
+        <v>1.22</v>
+      </c>
+      <c r="AM247">
+        <v>1.14</v>
+      </c>
+      <c r="AN247">
+        <v>0.77</v>
+      </c>
+      <c r="AO247">
+        <v>2.23</v>
+      </c>
+      <c r="AP247">
+        <v>0.71</v>
+      </c>
+      <c r="AQ247">
+        <v>2.29</v>
+      </c>
+      <c r="AR247">
+        <v>1.46</v>
+      </c>
+      <c r="AS247">
+        <v>1.65</v>
+      </c>
+      <c r="AT247">
+        <v>3.11</v>
+      </c>
+      <c r="AU247">
+        <v>3</v>
+      </c>
+      <c r="AV247">
+        <v>3</v>
+      </c>
+      <c r="AW247">
+        <v>9</v>
+      </c>
+      <c r="AX247">
+        <v>4</v>
+      </c>
+      <c r="AY247">
+        <v>12</v>
+      </c>
+      <c r="AZ247">
+        <v>7</v>
+      </c>
+      <c r="BA247">
+        <v>4</v>
+      </c>
+      <c r="BB247">
+        <v>0</v>
+      </c>
+      <c r="BC247">
+        <v>4</v>
+      </c>
+      <c r="BD247">
+        <v>4.6</v>
+      </c>
+      <c r="BE247">
+        <v>10.5</v>
+      </c>
+      <c r="BF247">
+        <v>1.29</v>
+      </c>
+      <c r="BG247">
+        <v>1.22</v>
+      </c>
+      <c r="BH247">
+        <v>3.5</v>
+      </c>
+      <c r="BI247">
+        <v>1.53</v>
+      </c>
+      <c r="BJ247">
+        <v>2.46</v>
+      </c>
+      <c r="BK247">
+        <v>1.85</v>
+      </c>
+      <c r="BL247">
+        <v>1.97</v>
+      </c>
+      <c r="BM247">
+        <v>2.26</v>
+      </c>
+      <c r="BN247">
+        <v>1.62</v>
+      </c>
+      <c r="BO247">
+        <v>2.97</v>
+      </c>
+      <c r="BP247">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7492060</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45752.4375</v>
+      </c>
+      <c r="F248">
+        <v>28</v>
+      </c>
+      <c r="G248" t="s">
+        <v>73</v>
+      </c>
+      <c r="H248" t="s">
+        <v>76</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>1</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248">
+        <v>1</v>
+      </c>
+      <c r="M248">
+        <v>4</v>
+      </c>
+      <c r="N248">
+        <v>5</v>
+      </c>
+      <c r="O248" t="s">
+        <v>252</v>
+      </c>
+      <c r="P248" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q248">
+        <v>3.6</v>
+      </c>
+      <c r="R248">
+        <v>2.25</v>
+      </c>
+      <c r="S248">
+        <v>2.88</v>
+      </c>
+      <c r="T248">
+        <v>1.36</v>
+      </c>
+      <c r="U248">
+        <v>3</v>
+      </c>
+      <c r="V248">
+        <v>2.63</v>
+      </c>
+      <c r="W248">
+        <v>1.44</v>
+      </c>
+      <c r="X248">
+        <v>7</v>
+      </c>
+      <c r="Y248">
+        <v>1.1</v>
+      </c>
+      <c r="Z248">
+        <v>3.06</v>
+      </c>
+      <c r="AA248">
+        <v>3.59</v>
+      </c>
+      <c r="AB248">
+        <v>2.33</v>
+      </c>
+      <c r="AC248">
+        <v>0</v>
+      </c>
+      <c r="AD248">
+        <v>0</v>
+      </c>
+      <c r="AE248">
+        <v>1.18</v>
+      </c>
+      <c r="AF248">
+        <v>4.35</v>
+      </c>
+      <c r="AG248">
+        <v>1.81</v>
+      </c>
+      <c r="AH248">
+        <v>2.01</v>
+      </c>
+      <c r="AI248">
+        <v>1.67</v>
+      </c>
+      <c r="AJ248">
+        <v>2.1</v>
+      </c>
+      <c r="AK248">
+        <v>1.72</v>
+      </c>
+      <c r="AL248">
+        <v>1.32</v>
+      </c>
+      <c r="AM248">
+        <v>1.38</v>
+      </c>
+      <c r="AN248">
+        <v>2</v>
+      </c>
+      <c r="AO248">
+        <v>0.85</v>
+      </c>
+      <c r="AP248">
+        <v>1.86</v>
+      </c>
+      <c r="AQ248">
+        <v>1</v>
+      </c>
+      <c r="AR248">
+        <v>1.45</v>
+      </c>
+      <c r="AS248">
+        <v>1.52</v>
+      </c>
+      <c r="AT248">
+        <v>2.97</v>
+      </c>
+      <c r="AU248">
+        <v>4</v>
+      </c>
+      <c r="AV248">
+        <v>8</v>
+      </c>
+      <c r="AW248">
+        <v>9</v>
+      </c>
+      <c r="AX248">
+        <v>11</v>
+      </c>
+      <c r="AY248">
+        <v>16</v>
+      </c>
+      <c r="AZ248">
+        <v>25</v>
+      </c>
+      <c r="BA248">
+        <v>3</v>
+      </c>
+      <c r="BB248">
+        <v>4</v>
+      </c>
+      <c r="BC248">
+        <v>7</v>
+      </c>
+      <c r="BD248">
+        <v>2.52</v>
+      </c>
+      <c r="BE248">
+        <v>6.55</v>
+      </c>
+      <c r="BF248">
+        <v>1.86</v>
+      </c>
+      <c r="BG248">
+        <v>1.26</v>
+      </c>
+      <c r="BH248">
+        <v>3.22</v>
+      </c>
+      <c r="BI248">
+        <v>1.6</v>
+      </c>
+      <c r="BJ248">
+        <v>2.32</v>
+      </c>
+      <c r="BK248">
+        <v>1.98</v>
+      </c>
+      <c r="BL248">
+        <v>1.85</v>
+      </c>
+      <c r="BM248">
+        <v>2.49</v>
+      </c>
+      <c r="BN248">
+        <v>1.53</v>
+      </c>
+      <c r="BO248">
+        <v>3.28</v>
+      </c>
+      <c r="BP248">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7492062</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45752.4375</v>
+      </c>
+      <c r="F249">
+        <v>28</v>
+      </c>
+      <c r="G249" t="s">
+        <v>75</v>
+      </c>
+      <c r="H249" t="s">
+        <v>81</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>1</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249">
+        <v>1</v>
+      </c>
+      <c r="M249">
+        <v>1</v>
+      </c>
+      <c r="N249">
+        <v>2</v>
+      </c>
+      <c r="O249" t="s">
+        <v>181</v>
+      </c>
+      <c r="P249" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q249">
+        <v>1.95</v>
+      </c>
+      <c r="R249">
+        <v>2.4</v>
+      </c>
+      <c r="S249">
+        <v>6</v>
+      </c>
+      <c r="T249">
+        <v>1.3</v>
+      </c>
+      <c r="U249">
+        <v>3.4</v>
+      </c>
+      <c r="V249">
+        <v>2.5</v>
+      </c>
+      <c r="W249">
+        <v>1.5</v>
+      </c>
+      <c r="X249">
+        <v>6</v>
+      </c>
+      <c r="Y249">
+        <v>1.13</v>
+      </c>
+      <c r="Z249">
+        <v>1.5</v>
+      </c>
+      <c r="AA249">
+        <v>4.8</v>
+      </c>
+      <c r="AB249">
+        <v>6.3</v>
+      </c>
+      <c r="AC249">
+        <v>0</v>
+      </c>
+      <c r="AD249">
+        <v>0</v>
+      </c>
+      <c r="AE249">
+        <v>1.14</v>
+      </c>
+      <c r="AF249">
+        <v>5.05</v>
+      </c>
+      <c r="AG249">
+        <v>1.61</v>
+      </c>
+      <c r="AH249">
+        <v>2.2</v>
+      </c>
+      <c r="AI249">
+        <v>1.8</v>
+      </c>
+      <c r="AJ249">
+        <v>1.95</v>
+      </c>
+      <c r="AK249">
+        <v>1.14</v>
+      </c>
+      <c r="AL249">
+        <v>1.21</v>
+      </c>
+      <c r="AM249">
+        <v>2.87</v>
+      </c>
+      <c r="AN249">
+        <v>1.69</v>
+      </c>
+      <c r="AO249">
+        <v>0.46</v>
+      </c>
+      <c r="AP249">
+        <v>1.64</v>
+      </c>
+      <c r="AQ249">
+        <v>0.5</v>
+      </c>
+      <c r="AR249">
+        <v>1.43</v>
+      </c>
+      <c r="AS249">
+        <v>1.21</v>
+      </c>
+      <c r="AT249">
+        <v>2.64</v>
+      </c>
+      <c r="AU249">
+        <v>4</v>
+      </c>
+      <c r="AV249">
+        <v>6</v>
+      </c>
+      <c r="AW249">
+        <v>10</v>
+      </c>
+      <c r="AX249">
+        <v>4</v>
+      </c>
+      <c r="AY249">
+        <v>17</v>
+      </c>
+      <c r="AZ249">
+        <v>10</v>
+      </c>
+      <c r="BA249">
+        <v>4</v>
+      </c>
+      <c r="BB249">
+        <v>4</v>
+      </c>
+      <c r="BC249">
+        <v>8</v>
+      </c>
+      <c r="BD249">
+        <v>1.26</v>
+      </c>
+      <c r="BE249">
+        <v>11</v>
+      </c>
+      <c r="BF249">
+        <v>4.95</v>
+      </c>
+      <c r="BG249">
+        <v>1.19</v>
+      </c>
+      <c r="BH249">
+        <v>3.82</v>
+      </c>
+      <c r="BI249">
+        <v>1.39</v>
+      </c>
+      <c r="BJ249">
+        <v>2.67</v>
+      </c>
+      <c r="BK249">
+        <v>1.75</v>
+      </c>
+      <c r="BL249">
+        <v>2.08</v>
+      </c>
+      <c r="BM249">
+        <v>2.19</v>
+      </c>
+      <c r="BN249">
+        <v>1.68</v>
+      </c>
+      <c r="BO249">
+        <v>2.74</v>
+      </c>
+      <c r="BP249">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7492064</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45752.4375</v>
+      </c>
+      <c r="F250">
+        <v>28</v>
+      </c>
+      <c r="G250" t="s">
+        <v>83</v>
+      </c>
+      <c r="H250" t="s">
+        <v>80</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>2</v>
+      </c>
+      <c r="K250">
+        <v>2</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>4</v>
+      </c>
+      <c r="N250">
+        <v>4</v>
+      </c>
+      <c r="O250" t="s">
+        <v>96</v>
+      </c>
+      <c r="P250" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q250">
+        <v>3.5</v>
+      </c>
+      <c r="R250">
+        <v>2.38</v>
+      </c>
+      <c r="S250">
+        <v>2.63</v>
+      </c>
+      <c r="T250">
+        <v>1.3</v>
+      </c>
+      <c r="U250">
+        <v>3.4</v>
+      </c>
+      <c r="V250">
+        <v>2.38</v>
+      </c>
+      <c r="W250">
+        <v>1.53</v>
+      </c>
+      <c r="X250">
+        <v>6</v>
+      </c>
+      <c r="Y250">
+        <v>1.13</v>
+      </c>
+      <c r="Z250">
+        <v>3.23</v>
+      </c>
+      <c r="AA250">
+        <v>3.8</v>
+      </c>
+      <c r="AB250">
+        <v>2.17</v>
+      </c>
+      <c r="AC250">
+        <v>0</v>
+      </c>
+      <c r="AD250">
+        <v>0</v>
+      </c>
+      <c r="AE250">
+        <v>1.13</v>
+      </c>
+      <c r="AF250">
+        <v>4.7</v>
+      </c>
+      <c r="AG250">
+        <v>1.55</v>
+      </c>
+      <c r="AH250">
+        <v>2.3</v>
+      </c>
+      <c r="AI250">
+        <v>1.53</v>
+      </c>
+      <c r="AJ250">
+        <v>2.38</v>
+      </c>
+      <c r="AK250">
+        <v>1.53</v>
+      </c>
+      <c r="AL250">
+        <v>1.32</v>
+      </c>
+      <c r="AM250">
+        <v>1.53</v>
+      </c>
+      <c r="AN250">
+        <v>0.92</v>
+      </c>
+      <c r="AO250">
+        <v>1.31</v>
+      </c>
+      <c r="AP250">
+        <v>0.86</v>
+      </c>
+      <c r="AQ250">
+        <v>1.43</v>
+      </c>
+      <c r="AR250">
+        <v>1.48</v>
+      </c>
+      <c r="AS250">
+        <v>1.23</v>
+      </c>
+      <c r="AT250">
+        <v>2.71</v>
+      </c>
+      <c r="AU250">
+        <v>2</v>
+      </c>
+      <c r="AV250">
+        <v>7</v>
+      </c>
+      <c r="AW250">
+        <v>9</v>
+      </c>
+      <c r="AX250">
+        <v>8</v>
+      </c>
+      <c r="AY250">
+        <v>12</v>
+      </c>
+      <c r="AZ250">
+        <v>18</v>
+      </c>
+      <c r="BA250">
+        <v>2</v>
+      </c>
+      <c r="BB250">
+        <v>4</v>
+      </c>
+      <c r="BC250">
+        <v>6</v>
+      </c>
+      <c r="BD250">
+        <v>2.11</v>
+      </c>
+      <c r="BE250">
+        <v>6.65</v>
+      </c>
+      <c r="BF250">
+        <v>2.16</v>
+      </c>
+      <c r="BG250">
+        <v>1.16</v>
+      </c>
+      <c r="BH250">
+        <v>4.05</v>
+      </c>
+      <c r="BI250">
+        <v>1.34</v>
+      </c>
+      <c r="BJ250">
+        <v>2.78</v>
+      </c>
+      <c r="BK250">
+        <v>1.72</v>
+      </c>
+      <c r="BL250">
+        <v>2.13</v>
+      </c>
+      <c r="BM250">
+        <v>2.12</v>
+      </c>
+      <c r="BN250">
+        <v>1.72</v>
+      </c>
+      <c r="BO250">
+        <v>2.67</v>
+      </c>
+      <c r="BP250">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7492059</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45752.5625</v>
+      </c>
+      <c r="F251">
+        <v>28</v>
+      </c>
+      <c r="G251" t="s">
+        <v>84</v>
+      </c>
+      <c r="H251" t="s">
+        <v>82</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>1</v>
+      </c>
+      <c r="L251">
+        <v>2</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>2</v>
+      </c>
+      <c r="O251" t="s">
+        <v>253</v>
+      </c>
+      <c r="P251" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q251">
+        <v>3.1</v>
+      </c>
+      <c r="R251">
+        <v>2.4</v>
+      </c>
+      <c r="S251">
+        <v>3</v>
+      </c>
+      <c r="T251">
+        <v>1.29</v>
+      </c>
+      <c r="U251">
+        <v>3.5</v>
+      </c>
+      <c r="V251">
+        <v>2.25</v>
+      </c>
+      <c r="W251">
+        <v>1.57</v>
+      </c>
+      <c r="X251">
+        <v>5.5</v>
+      </c>
+      <c r="Y251">
+        <v>1.14</v>
+      </c>
+      <c r="Z251">
+        <v>2.68</v>
+      </c>
+      <c r="AA251">
+        <v>3.66</v>
+      </c>
+      <c r="AB251">
+        <v>2.58</v>
+      </c>
+      <c r="AC251">
+        <v>0</v>
+      </c>
+      <c r="AD251">
+        <v>0</v>
+      </c>
+      <c r="AE251">
+        <v>1.13</v>
+      </c>
+      <c r="AF251">
+        <v>4.75</v>
+      </c>
+      <c r="AG251">
+        <v>1.57</v>
+      </c>
+      <c r="AH251">
+        <v>2.3</v>
+      </c>
+      <c r="AI251">
+        <v>1.44</v>
+      </c>
+      <c r="AJ251">
+        <v>2.63</v>
+      </c>
+      <c r="AK251">
+        <v>1.42</v>
+      </c>
+      <c r="AL251">
+        <v>1.31</v>
+      </c>
+      <c r="AM251">
+        <v>1.68</v>
+      </c>
+      <c r="AN251">
+        <v>1</v>
+      </c>
+      <c r="AO251">
+        <v>1.62</v>
+      </c>
+      <c r="AP251">
+        <v>1.14</v>
+      </c>
+      <c r="AQ251">
+        <v>1.5</v>
+      </c>
+      <c r="AR251">
+        <v>1.51</v>
+      </c>
+      <c r="AS251">
+        <v>1.49</v>
+      </c>
+      <c r="AT251">
+        <v>3</v>
+      </c>
+      <c r="AU251">
+        <v>5</v>
+      </c>
+      <c r="AV251">
+        <v>0</v>
+      </c>
+      <c r="AW251">
+        <v>8</v>
+      </c>
+      <c r="AX251">
+        <v>10</v>
+      </c>
+      <c r="AY251">
+        <v>15</v>
+      </c>
+      <c r="AZ251">
+        <v>11</v>
+      </c>
+      <c r="BA251">
+        <v>5</v>
+      </c>
+      <c r="BB251">
+        <v>6</v>
+      </c>
+      <c r="BC251">
+        <v>11</v>
+      </c>
+      <c r="BD251">
+        <v>1.9</v>
+      </c>
+      <c r="BE251">
+        <v>6.6</v>
+      </c>
+      <c r="BF251">
+        <v>2.44</v>
+      </c>
+      <c r="BG251">
+        <v>1.22</v>
+      </c>
+      <c r="BH251">
+        <v>3.48</v>
+      </c>
+      <c r="BI251">
+        <v>1.51</v>
+      </c>
+      <c r="BJ251">
+        <v>2.51</v>
+      </c>
+      <c r="BK251">
+        <v>1.84</v>
+      </c>
+      <c r="BL251">
+        <v>1.98</v>
+      </c>
+      <c r="BM251">
+        <v>2.27</v>
+      </c>
+      <c r="BN251">
+        <v>1.61</v>
+      </c>
+      <c r="BO251">
+        <v>3.05</v>
+      </c>
+      <c r="BP251">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="392">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -778,6 +778,9 @@
     <t>['28', '84']</t>
   </si>
   <si>
+    <t>['85']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -965,9 +968,6 @@
   </si>
   <si>
     <t>['20', '85']</t>
-  </si>
-  <si>
-    <t>['85']</t>
   </si>
   <si>
     <t>['22', '49', '58', '90+4']</t>
@@ -1187,6 +1187,9 @@
   </si>
   <si>
     <t>['8', '11', '48', '85']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1804,7 +1807,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -2216,7 +2219,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2422,7 +2425,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2628,7 +2631,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -3246,7 +3249,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3452,7 +3455,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3530,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ10">
         <v>0.86</v>
@@ -3736,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11">
         <v>0.93</v>
@@ -3864,7 +3867,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -4070,7 +4073,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4151,7 +4154,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ13">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4276,7 +4279,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4482,7 +4485,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4563,7 +4566,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ15">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4894,7 +4897,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5512,7 +5515,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5924,7 +5927,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6336,7 +6339,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6542,7 +6545,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6748,7 +6751,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -7160,7 +7163,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7366,7 +7369,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7572,7 +7575,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7778,7 +7781,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7984,7 +7987,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8062,7 +8065,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ32">
         <v>0.93</v>
@@ -8190,7 +8193,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8477,7 +8480,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ34">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR34">
         <v>1.86</v>
@@ -8602,7 +8605,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8683,7 +8686,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ35">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR35">
         <v>2.58</v>
@@ -9092,7 +9095,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ37">
         <v>1.21</v>
@@ -9220,7 +9223,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9632,7 +9635,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9838,7 +9841,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10044,7 +10047,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10456,7 +10459,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10662,7 +10665,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10868,7 +10871,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11155,7 +11158,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ47">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR47">
         <v>2.02</v>
@@ -11280,7 +11283,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11692,7 +11695,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11770,7 +11773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11898,7 +11901,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11979,7 +11982,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ51">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR51">
         <v>1.37</v>
@@ -12104,7 +12107,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12182,7 +12185,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ52">
         <v>1.64</v>
@@ -12516,7 +12519,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12722,7 +12725,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12928,7 +12931,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -13134,7 +13137,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13546,7 +13549,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13752,7 +13755,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13958,7 +13961,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14370,7 +14373,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14576,7 +14579,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14782,7 +14785,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14863,7 +14866,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
         <v>1.22</v>
@@ -14988,7 +14991,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15272,10 +15275,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ67">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR67">
         <v>1.52</v>
@@ -15400,7 +15403,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15812,7 +15815,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -16018,7 +16021,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -16302,7 +16305,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ72">
         <v>1.5</v>
@@ -17048,7 +17051,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -17254,7 +17257,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18568,7 +18571,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ83">
         <v>1.14</v>
@@ -18696,7 +18699,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18774,7 +18777,7 @@
         <v>2.6</v>
       </c>
       <c r="AP84">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ84">
         <v>2.21</v>
@@ -19108,7 +19111,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19314,7 +19317,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19601,7 +19604,7 @@
         <v>2</v>
       </c>
       <c r="AQ88">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR88">
         <v>1.44</v>
@@ -19932,7 +19935,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -20138,7 +20141,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20219,7 +20222,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ91">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20550,7 +20553,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -21168,7 +21171,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21786,7 +21789,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -22198,7 +22201,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22276,7 +22279,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ101">
         <v>0.5</v>
@@ -22404,7 +22407,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22482,7 +22485,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ102">
         <v>2.29</v>
@@ -22610,7 +22613,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22691,7 +22694,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ103">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -23022,7 +23025,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -23103,7 +23106,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR105">
         <v>1.47</v>
@@ -23228,7 +23231,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23434,7 +23437,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>317</v>
+        <v>254</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -25288,7 +25291,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25987,7 +25990,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ119">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR119">
         <v>1.52</v>
@@ -26190,7 +26193,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ120">
         <v>0.43</v>
@@ -27014,7 +27017,7 @@
         <v>1.86</v>
       </c>
       <c r="AP124">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ124">
         <v>1.64</v>
@@ -27348,7 +27351,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27554,7 +27557,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27760,7 +27763,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -28665,7 +28668,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR132">
         <v>1.76</v>
@@ -29901,7 +29904,7 @@
         <v>1</v>
       </c>
       <c r="AQ138">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR138">
         <v>1.83</v>
@@ -30722,7 +30725,7 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ142">
         <v>1.5</v>
@@ -31262,7 +31265,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31961,7 +31964,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ148">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR148">
         <v>1.3</v>
@@ -33194,7 +33197,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ154">
         <v>1.21</v>
@@ -34433,7 +34436,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ160">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR160">
         <v>2.29</v>
@@ -34558,7 +34561,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34639,7 +34642,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ161">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR161">
         <v>2.2</v>
@@ -34842,7 +34845,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ162">
         <v>1.64</v>
@@ -36902,7 +36905,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP172">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ172">
         <v>1</v>
@@ -37317,7 +37320,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ174">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR174">
         <v>1.91</v>
@@ -38138,7 +38141,7 @@
         <v>0.89</v>
       </c>
       <c r="AP178">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ178">
         <v>1.21</v>
@@ -38344,7 +38347,7 @@
         <v>1.4</v>
       </c>
       <c r="AP179">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ179">
         <v>1.21</v>
@@ -38553,7 +38556,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ180">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR180">
         <v>1.83</v>
@@ -38678,7 +38681,7 @@
         <v>219</v>
       </c>
       <c r="P181" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q181">
         <v>1.62</v>
@@ -40120,7 +40123,7 @@
         <v>222</v>
       </c>
       <c r="P188" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -41025,7 +41028,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ192">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR192">
         <v>1.88</v>
@@ -41228,10 +41231,10 @@
         <v>1.1</v>
       </c>
       <c r="AP193">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ193">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR193">
         <v>1.45</v>
@@ -41640,7 +41643,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ195">
         <v>1.14</v>
@@ -44733,7 +44736,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ210">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR210">
         <v>1.38</v>
@@ -44936,7 +44939,7 @@
         <v>0.73</v>
       </c>
       <c r="AP211">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ211">
         <v>1</v>
@@ -45351,7 +45354,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ213">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR213">
         <v>1.38</v>
@@ -45966,7 +45969,7 @@
         <v>0.27</v>
       </c>
       <c r="AP216">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ216">
         <v>0.5</v>
@@ -47948,7 +47951,7 @@
         <v>97</v>
       </c>
       <c r="P226" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q226">
         <v>2.3</v>
@@ -48232,7 +48235,7 @@
         <v>1.08</v>
       </c>
       <c r="AP227">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ227">
         <v>0.93</v>
@@ -48647,7 +48650,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ229">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR229">
         <v>1.55</v>
@@ -48850,7 +48853,7 @@
         <v>2.25</v>
       </c>
       <c r="AP230">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ230">
         <v>2.21</v>
@@ -49059,7 +49062,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ231">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR231">
         <v>1.44</v>
@@ -50626,7 +50629,7 @@
         <v>96</v>
       </c>
       <c r="P239" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q239">
         <v>2.2</v>
@@ -52274,7 +52277,7 @@
         <v>96</v>
       </c>
       <c r="P247" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q247">
         <v>6.5</v>
@@ -53255,6 +53258,418 @@
       </c>
       <c r="BP251">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7492065</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45753.4375</v>
+      </c>
+      <c r="F252">
+        <v>28</v>
+      </c>
+      <c r="G252" t="s">
+        <v>78</v>
+      </c>
+      <c r="H252" t="s">
+        <v>70</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>1</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+      <c r="L252">
+        <v>1</v>
+      </c>
+      <c r="M252">
+        <v>1</v>
+      </c>
+      <c r="N252">
+        <v>2</v>
+      </c>
+      <c r="O252" t="s">
+        <v>254</v>
+      </c>
+      <c r="P252" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q252">
+        <v>3.2</v>
+      </c>
+      <c r="R252">
+        <v>2.2</v>
+      </c>
+      <c r="S252">
+        <v>3.25</v>
+      </c>
+      <c r="T252">
+        <v>1.36</v>
+      </c>
+      <c r="U252">
+        <v>3</v>
+      </c>
+      <c r="V252">
+        <v>2.75</v>
+      </c>
+      <c r="W252">
+        <v>1.4</v>
+      </c>
+      <c r="X252">
+        <v>8</v>
+      </c>
+      <c r="Y252">
+        <v>1.08</v>
+      </c>
+      <c r="Z252">
+        <v>2.6</v>
+      </c>
+      <c r="AA252">
+        <v>3.45</v>
+      </c>
+      <c r="AB252">
+        <v>2.77</v>
+      </c>
+      <c r="AC252">
+        <v>1.05</v>
+      </c>
+      <c r="AD252">
+        <v>9</v>
+      </c>
+      <c r="AE252">
+        <v>1.28</v>
+      </c>
+      <c r="AF252">
+        <v>3.65</v>
+      </c>
+      <c r="AG252">
+        <v>1.81</v>
+      </c>
+      <c r="AH252">
+        <v>2.01</v>
+      </c>
+      <c r="AI252">
+        <v>1.67</v>
+      </c>
+      <c r="AJ252">
+        <v>2.1</v>
+      </c>
+      <c r="AK252">
+        <v>1.44</v>
+      </c>
+      <c r="AL252">
+        <v>1.3</v>
+      </c>
+      <c r="AM252">
+        <v>1.51</v>
+      </c>
+      <c r="AN252">
+        <v>0.92</v>
+      </c>
+      <c r="AO252">
+        <v>1.54</v>
+      </c>
+      <c r="AP252">
+        <v>0.93</v>
+      </c>
+      <c r="AQ252">
+        <v>1.5</v>
+      </c>
+      <c r="AR252">
+        <v>1.26</v>
+      </c>
+      <c r="AS252">
+        <v>1.4</v>
+      </c>
+      <c r="AT252">
+        <v>2.66</v>
+      </c>
+      <c r="AU252">
+        <v>10</v>
+      </c>
+      <c r="AV252">
+        <v>4</v>
+      </c>
+      <c r="AW252">
+        <v>17</v>
+      </c>
+      <c r="AX252">
+        <v>2</v>
+      </c>
+      <c r="AY252">
+        <v>37</v>
+      </c>
+      <c r="AZ252">
+        <v>6</v>
+      </c>
+      <c r="BA252">
+        <v>11</v>
+      </c>
+      <c r="BB252">
+        <v>2</v>
+      </c>
+      <c r="BC252">
+        <v>13</v>
+      </c>
+      <c r="BD252">
+        <v>1.73</v>
+      </c>
+      <c r="BE252">
+        <v>6.65</v>
+      </c>
+      <c r="BF252">
+        <v>2.79</v>
+      </c>
+      <c r="BG252">
+        <v>1.26</v>
+      </c>
+      <c r="BH252">
+        <v>3.22</v>
+      </c>
+      <c r="BI252">
+        <v>1.51</v>
+      </c>
+      <c r="BJ252">
+        <v>2.32</v>
+      </c>
+      <c r="BK252">
+        <v>1.9</v>
+      </c>
+      <c r="BL252">
+        <v>1.8</v>
+      </c>
+      <c r="BM252">
+        <v>2.45</v>
+      </c>
+      <c r="BN252">
+        <v>1.46</v>
+      </c>
+      <c r="BO252">
+        <v>3.28</v>
+      </c>
+      <c r="BP252">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7492063</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45753.52083333334</v>
+      </c>
+      <c r="F253">
+        <v>28</v>
+      </c>
+      <c r="G253" t="s">
+        <v>79</v>
+      </c>
+      <c r="H253" t="s">
+        <v>77</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>1</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>1</v>
+      </c>
+      <c r="O253" t="s">
+        <v>224</v>
+      </c>
+      <c r="P253" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q253">
+        <v>3.1</v>
+      </c>
+      <c r="R253">
+        <v>2.1</v>
+      </c>
+      <c r="S253">
+        <v>3.5</v>
+      </c>
+      <c r="T253">
+        <v>1.4</v>
+      </c>
+      <c r="U253">
+        <v>2.75</v>
+      </c>
+      <c r="V253">
+        <v>3</v>
+      </c>
+      <c r="W253">
+        <v>1.36</v>
+      </c>
+      <c r="X253">
+        <v>8</v>
+      </c>
+      <c r="Y253">
+        <v>1.08</v>
+      </c>
+      <c r="Z253">
+        <v>2.52</v>
+      </c>
+      <c r="AA253">
+        <v>3.3</v>
+      </c>
+      <c r="AB253">
+        <v>2.98</v>
+      </c>
+      <c r="AC253">
+        <v>1.06</v>
+      </c>
+      <c r="AD253">
+        <v>8.5</v>
+      </c>
+      <c r="AE253">
+        <v>1.33</v>
+      </c>
+      <c r="AF253">
+        <v>3.3</v>
+      </c>
+      <c r="AG253">
+        <v>1.93</v>
+      </c>
+      <c r="AH253">
+        <v>1.77</v>
+      </c>
+      <c r="AI253">
+        <v>1.75</v>
+      </c>
+      <c r="AJ253">
+        <v>2</v>
+      </c>
+      <c r="AK253">
+        <v>1.41</v>
+      </c>
+      <c r="AL253">
+        <v>1.31</v>
+      </c>
+      <c r="AM253">
+        <v>1.55</v>
+      </c>
+      <c r="AN253">
+        <v>1.31</v>
+      </c>
+      <c r="AO253">
+        <v>1.77</v>
+      </c>
+      <c r="AP253">
+        <v>1.43</v>
+      </c>
+      <c r="AQ253">
+        <v>1.64</v>
+      </c>
+      <c r="AR253">
+        <v>1.5</v>
+      </c>
+      <c r="AS253">
+        <v>1.27</v>
+      </c>
+      <c r="AT253">
+        <v>2.77</v>
+      </c>
+      <c r="AU253">
+        <v>4</v>
+      </c>
+      <c r="AV253">
+        <v>4</v>
+      </c>
+      <c r="AW253">
+        <v>10</v>
+      </c>
+      <c r="AX253">
+        <v>9</v>
+      </c>
+      <c r="AY253">
+        <v>15</v>
+      </c>
+      <c r="AZ253">
+        <v>18</v>
+      </c>
+      <c r="BA253">
+        <v>6</v>
+      </c>
+      <c r="BB253">
+        <v>4</v>
+      </c>
+      <c r="BC253">
+        <v>10</v>
+      </c>
+      <c r="BD253">
+        <v>1.76</v>
+      </c>
+      <c r="BE253">
+        <v>6.65</v>
+      </c>
+      <c r="BF253">
+        <v>2.71</v>
+      </c>
+      <c r="BG253">
+        <v>1.24</v>
+      </c>
+      <c r="BH253">
+        <v>3.34</v>
+      </c>
+      <c r="BI253">
+        <v>1.48</v>
+      </c>
+      <c r="BJ253">
+        <v>2.4</v>
+      </c>
+      <c r="BK253">
+        <v>1.85</v>
+      </c>
+      <c r="BL253">
+        <v>1.85</v>
+      </c>
+      <c r="BM253">
+        <v>2.38</v>
+      </c>
+      <c r="BN253">
+        <v>1.49</v>
+      </c>
+      <c r="BO253">
+        <v>3.14</v>
+      </c>
+      <c r="BP253">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany Bundesliga_20242025.xlsx
@@ -2092,10 +2092,10 @@
         <v>8</v>
       </c>
       <c r="AY2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BA2">
         <v>2</v>
@@ -2298,10 +2298,10 @@
         <v>0</v>
       </c>
       <c r="AY3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BA3">
         <v>9</v>
@@ -2504,10 +2504,10 @@
         <v>7</v>
       </c>
       <c r="AY4">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA4">
         <v>8</v>
@@ -2710,10 +2710,10 @@
         <v>5</v>
       </c>
       <c r="AY5">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA5">
         <v>6</v>
@@ -2916,10 +2916,10 @@
         <v>4</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA6">
         <v>4</v>
@@ -3122,10 +3122,10 @@
         <v>6</v>
       </c>
       <c r="AY7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA7">
         <v>8</v>
@@ -3328,10 +3328,10 @@
         <v>4</v>
       </c>
       <c r="AY8">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AZ8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA8">
         <v>7</v>
@@ -3534,10 +3534,10 @@
         <v>2</v>
       </c>
       <c r="AY9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA9">
         <v>1</v>
@@ -3740,10 +3740,10 @@
         <v>2</v>
       </c>
       <c r="AY10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA10">
         <v>4</v>
@@ -3946,10 +3946,10 @@
         <v>4</v>
       </c>
       <c r="AY11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -4152,10 +4152,10 @@
         <v>1</v>
       </c>
       <c r="AY12">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AZ12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA12">
         <v>11</v>
@@ -4358,10 +4358,10 @@
         <v>4</v>
       </c>
       <c r="AY13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA13">
         <v>1</v>
@@ -4564,10 +4564,10 @@
         <v>4</v>
       </c>
       <c r="AY14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA14">
         <v>1</v>
@@ -4770,10 +4770,10 @@
         <v>5</v>
       </c>
       <c r="AY15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ15">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA15">
         <v>3</v>
@@ -4976,10 +4976,10 @@
         <v>3</v>
       </c>
       <c r="AY16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AZ16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -5182,10 +5182,10 @@
         <v>3</v>
       </c>
       <c r="AY17">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AZ17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA17">
         <v>18</v>
@@ -5388,10 +5388,10 @@
         <v>11</v>
       </c>
       <c r="AY18">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ18">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA18">
         <v>5</v>
@@ -5594,10 +5594,10 @@
         <v>4</v>
       </c>
       <c r="AY19">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA19">
         <v>2</v>
@@ -5800,10 +5800,10 @@
         <v>2</v>
       </c>
       <c r="AY20">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ20">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA20">
         <v>8</v>
@@ -6006,10 +6006,10 @@
         <v>4</v>
       </c>
       <c r="AY21">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ21">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA21">
         <v>6</v>
@@ -6212,10 +6212,10 @@
         <v>6</v>
       </c>
       <c r="AY22">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ22">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA22">
         <v>4</v>
@@ -6418,10 +6418,10 @@
         <v>6</v>
       </c>
       <c r="AY23">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AZ23">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA23">
         <v>5</v>
@@ -6624,10 +6624,10 @@
         <v>4</v>
       </c>
       <c r="AY24">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AZ24">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA24">
         <v>5</v>
@@ -6830,10 +6830,10 @@
         <v>2</v>
       </c>
       <c r="AY25">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ25">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA25">
         <v>6</v>
@@ -7036,10 +7036,10 @@
         <v>6</v>
       </c>
       <c r="AY26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ26">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA26">
         <v>2</v>
@@ -7242,10 +7242,10 @@
         <v>4</v>
       </c>
       <c r="AY27">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ27">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA27">
         <v>7</v>
@@ -7448,10 +7448,10 @@
         <v>6</v>
       </c>
       <c r="AY28">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ28">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA28">
         <v>10</v>
@@ -7654,7 +7654,7 @@
         <v>2</v>
       </c>
       <c r="AY29">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AZ29">
         <v>6</v>
@@ -7860,10 +7860,10 @@
         <v>6</v>
       </c>
       <c r="AY30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ30">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA30">
         <v>3</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="AZ31">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="BA31">
         <v>1</v>
@@ -8272,10 +8272,10 @@
         <v>2</v>
       </c>
       <c r="AY32">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AZ32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA32">
         <v>5</v>
@@ -8478,10 +8478,10 @@
         <v>8</v>
       </c>
       <c r="AY33">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA33">
         <v>2</v>
@@ -8684,10 +8684,10 @@
         <v>6</v>
       </c>
       <c r="AY34">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ34">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="BA34">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>5</v>
       </c>
       <c r="AY35">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ35">
         <v>10</v>
@@ -9096,10 +9096,10 @@
         <v>2</v>
       </c>
       <c r="AY36">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA36">
         <v>6</v>
@@ -9302,10 +9302,10 @@
         <v>4</v>
       </c>
       <c r="AY37">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ37">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA37">
         <v>3</v>
@@ -9508,10 +9508,10 @@
         <v>3</v>
       </c>
       <c r="AY38">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AZ38">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA38">
         <v>11</v>
@@ -9714,10 +9714,10 @@
         <v>6</v>
       </c>
       <c r="AY39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AZ39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA39">
         <v>2</v>
@@ -9920,10 +9920,10 @@
         <v>6</v>
       </c>
       <c r="AY40">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ40">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA40">
         <v>7</v>
@@ -10126,10 +10126,10 @@
         <v>6</v>
       </c>
       <c r="AY41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ41">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BA41">
         <v>1</v>
@@ -10332,10 +10332,10 @@
         <v>4</v>
       </c>
       <c r="AY42">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA42">
         <v>4</v>
@@ -10538,10 +10538,10 @@
         <v>3</v>
       </c>
       <c r="AY43">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA43">
         <v>8</v>
@@ -10744,7 +10744,7 @@
         <v>1</v>
       </c>
       <c r="AY44">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ44">
         <v>4</v>
@@ -10950,10 +10950,10 @@
         <v>3</v>
       </c>
       <c r="AY45">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ45">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BA45">
         <v>4</v>
@@ -11156,10 +11156,10 @@
         <v>4</v>
       </c>
       <c r="AY46">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ46">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="BA46">
         <v>2</v>
@@ -11362,10 +11362,10 @@
         <v>6</v>
       </c>
       <c r="AY47">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ47">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA47">
         <v>6</v>
@@ -11568,10 +11568,10 @@
         <v>2</v>
       </c>
       <c r="AY48">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AZ48">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA48">
         <v>12</v>
@@ -11774,10 +11774,10 @@
         <v>6</v>
       </c>
       <c r="AY49">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ49">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA49">
         <v>7</v>
@@ -11980,10 +11980,10 @@
         <v>3</v>
       </c>
       <c r="AY50">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ50">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA50">
         <v>3</v>
@@ -12186,10 +12186,10 @@
         <v>5</v>
       </c>
       <c r="AY51">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AZ51">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA51">
         <v>7</v>
@@ -12392,10 +12392,10 @@
         <v>3</v>
       </c>
       <c r="AY52">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AZ52">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA52">
         <v>2</v>
@@ -12598,10 +12598,10 @@
         <v>6</v>
       </c>
       <c r="AY53">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ53">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA53">
         <v>3</v>
@@ -12807,7 +12807,7 @@
         <v>7</v>
       </c>
       <c r="AZ54">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BA54">
         <v>0</v>
@@ -13010,7 +13010,7 @@
         <v>2</v>
       </c>
       <c r="AY55">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ55">
         <v>8</v>
@@ -13422,10 +13422,10 @@
         <v>4</v>
       </c>
       <c r="AY57">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AZ57">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA57">
         <v>8</v>
@@ -13628,10 +13628,10 @@
         <v>5</v>
       </c>
       <c r="AY58">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ58">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA58">
         <v>4</v>
@@ -13834,7 +13834,7 @@
         <v>6</v>
       </c>
       <c r="AY59">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ59">
         <v>10</v>
@@ -14040,10 +14040,10 @@
         <v>3</v>
       </c>
       <c r="AY60">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AZ60">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA60">
         <v>5</v>
@@ -14246,10 +14246,10 @@
         <v>6</v>
       </c>
       <c r="AY61">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ61">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA61">
         <v>6</v>
@@ -14452,10 +14452,10 @@
         <v>2</v>
       </c>
       <c r="AY62">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA62">
         <v>7</v>
@@ -15070,10 +15070,10 @@
         <v>4</v>
       </c>
       <c r="AY65">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AZ65">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA65">
         <v>2</v>
@@ -15276,10 +15276,10 @@
         <v>4</v>
       </c>
       <c r="AY66">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ66">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA66">
         <v>3</v>
@@ -15482,7 +15482,7 @@
         <v>6</v>
       </c>
       <c r="AY67">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ67">
         <v>11</v>
@@ -15688,10 +15688,10 @@
         <v>8</v>
       </c>
       <c r="AY68">
+        <v>13</v>
+      </c>
+      <c r="AZ68">
         <v>14</v>
-      </c>
-      <c r="AZ68">
-        <v>16</v>
       </c>
       <c r="BA68">
         <v>3</v>
@@ -15894,10 +15894,10 @@
         <v>3</v>
       </c>
       <c r="AY69">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ69">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA69">
         <v>9</v>
@@ -16103,7 +16103,7 @@
         <v>14</v>
       </c>
       <c r="AZ70">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA70">
         <v>3</v>
@@ -16306,10 +16306,10 @@
         <v>7</v>
       </c>
       <c r="AY71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ71">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA71">
         <v>2</v>
@@ -16512,10 +16512,10 @@
         <v>6</v>
       </c>
       <c r="AY72">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ72">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA72">
         <v>4</v>
@@ -16718,10 +16718,10 @@
         <v>3</v>
       </c>
       <c r="AY73">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ73">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA73">
         <v>7</v>
@@ -16924,10 +16924,10 @@
         <v>2</v>
       </c>
       <c r="AY74">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA74">
         <v>10</v>
@@ -17130,10 +17130,10 @@
         <v>3</v>
       </c>
       <c r="AY75">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ75">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA75">
         <v>7</v>
@@ -17336,7 +17336,7 @@
         <v>3</v>
       </c>
       <c r="AY76">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ76">
         <v>12</v>
@@ -17542,10 +17542,10 @@
         <v>2</v>
       </c>
       <c r="AY77">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ77">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA77">
         <v>7</v>
@@ -17748,10 +17748,10 @@
         <v>9</v>
       </c>
       <c r="AY78">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ78">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA78">
         <v>5</v>
@@ -17954,7 +17954,7 @@
         <v>2</v>
       </c>
       <c r="AY79">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ79">
         <v>4</v>
@@ -18160,10 +18160,10 @@
         <v>1</v>
       </c>
       <c r="AY80">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ80">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA80">
         <v>4</v>
@@ -18366,10 +18366,10 @@
         <v>5</v>
       </c>
       <c r="AY81">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ81">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA81">
         <v>8</v>
@@ -18572,10 +18572,10 @@
         <v>5</v>
       </c>
       <c r="AY82">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ82">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA82">
         <v>7</v>
@@ -18778,10 +18778,10 @@
         <v>7</v>
       </c>
       <c r="AY83">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ83">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA83">
         <v>4</v>
@@ -18984,10 +18984,10 @@
         <v>4</v>
       </c>
       <c r="AY84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ84">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA84">
         <v>5</v>
@@ -19190,10 +19190,10 @@
         <v>3</v>
       </c>
       <c r="AY85">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ85">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA85">
         <v>6</v>
@@ -19396,7 +19396,7 @@
         <v>1</v>
       </c>
       <c r="AY86">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ86">
         <v>3</v>
@@ -19602,10 +19602,10 @@
         <v>4</v>
       </c>
       <c r="AY87">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ87">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA87">
         <v>6</v>
@@ -19808,10 +19808,10 @@
         <v>4</v>
       </c>
       <c r="AY88">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ88">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA88">
         <v>8</v>
@@ -20014,10 +20014,10 @@
         <v>4</v>
       </c>
       <c r="AY89">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ89">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA89">
         <v>10</v>
@@ -20220,10 +20220,10 @@
         <v>3</v>
       </c>
       <c r="AY90">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ90">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA90">
         <v>8</v>
@@ -20426,10 +20426,10 @@
         <v>3</v>
       </c>
       <c r="AY91">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ91">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA91">
         <v>5</v>
@@ -20838,7 +20838,7 @@
         <v>3</v>
       </c>
       <c r="AY93">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ93">
         <v>7</v>
@@ -21044,10 +21044,10 @@
         <v>6</v>
       </c>
       <c r="AY94">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ94">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA94">
         <v>7</v>
@@ -21868,10 +21868,10 @@
         <v>4</v>
       </c>
       <c r="AY98">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ98">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA98">
         <v>5</v>
@@ -22074,10 +22074,10 @@
         <v>5</v>
       </c>
       <c r="AY99">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ99">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA99">
         <v>2</v>
@@ -22486,10 +22486,10 @@
         <v>5</v>
       </c>
       <c r="AY101">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ101">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA101">
         <v>4</v>
@@ -22692,10 +22692,10 @@
         <v>4</v>
       </c>
       <c r="AY102">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ102">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA102">
         <v>1</v>
@@ -22898,10 +22898,10 @@
         <v>5</v>
       </c>
       <c r="AY103">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ103">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA103">
         <v>4</v>
@@ -23104,10 +23104,10 @@
         <v>5</v>
       </c>
       <c r="AY104">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ104">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA104">
         <v>6</v>
@@ -23310,10 +23310,10 @@
         <v>3</v>
       </c>
       <c r="AY105">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ105">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA105">
         <v>7</v>
@@ -23516,10 +23516,10 @@
         <v>4</v>
       </c>
       <c r="AY106">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ106">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA106">
         <v>11</v>
@@ -23722,10 +23722,10 @@
         <v>3</v>
       </c>
       <c r="AY107">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AZ107">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA107">
         <v>2</v>
@@ -23928,10 +23928,10 @@
         <v>5</v>
       </c>
       <c r="AY108">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ108">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA108">
         <v>8</v>
@@ -24134,10 +24134,10 @@
         <v>5</v>
       </c>
       <c r="AY109">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ109">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA109">
         <v>6</v>
@@ -24343,7 +24343,7 @@
         <v>8</v>
       </c>
       <c r="AZ110">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA110">
         <v>1</v>
@@ -24546,10 +24546,10 @@
         <v>1</v>
       </c>
       <c r="AY111">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ111">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA111">
         <v>6</v>
@@ -24752,10 +24752,10 @@
         <v>4</v>
       </c>
       <c r="AY112">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ112">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA112">
         <v>9</v>
@@ -24958,10 +24958,10 @@
         <v>4</v>
       </c>
       <c r="AY113">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ113">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA113">
         <v>4</v>
@@ -25164,7 +25164,7 @@
         <v>0</v>
       </c>
       <c r="AY114">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ114">
         <v>3</v>
@@ -25370,10 +25370,10 @@
         <v>6</v>
       </c>
       <c r="AY115">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ115">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA115">
         <v>7</v>
@@ -25576,10 +25576,10 @@
         <v>8</v>
       </c>
       <c r="AY116">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ116">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA116">
         <v>7</v>
@@ -25782,10 +25782,10 @@
         <v>6</v>
       </c>
       <c r="AY117">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ117">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA117">
         <v>3</v>
@@ -26194,10 +26194,10 @@
         <v>10</v>
       </c>
       <c r="AY119">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ119">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA119">
         <v>5</v>
@@ -26400,10 +26400,10 @@
         <v>4</v>
       </c>
       <c r="AY120">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ120">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA120">
         <v>7</v>
@@ -26609,7 +26609,7 @@
         <v>9</v>
       </c>
       <c r="AZ121">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA121">
         <v>3</v>
@@ -26812,10 +26812,10 @@
         <v>6</v>
       </c>
       <c r="AY122">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ122">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA122">
         <v>4</v>
@@ -27018,10 +27018,10 @@
         <v>3</v>
       </c>
       <c r="AY123">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ123">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA123">
         <v>5</v>
@@ -27224,10 +27224,10 @@
         <v>2</v>
       </c>
       <c r="AY124">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ124">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA124">
         <v>4</v>
@@ -27430,10 +27430,10 @@
         <v>4</v>
       </c>
       <c r="AY125">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AZ125">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA125">
         <v>9</v>
@@ -27636,10 +27636,10 @@
         <v>9</v>
       </c>
       <c r="AY126">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ126">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA126">
         <v>3</v>
@@ -27842,10 +27842,10 @@
         <v>8</v>
       </c>
       <c r="AY127">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ127">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA127">
         <v>6</v>
@@ -28048,10 +28048,10 @@
         <v>2</v>
       </c>
       <c r="AY128">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA128">
         <v>8</v>
@@ -28254,10 +28254,10 @@
         <v>6</v>
       </c>
       <c r="AY129">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ129">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA129">
         <v>3</v>
@@ -28460,10 +28460,10 @@
         <v>5</v>
       </c>
       <c r="AY130">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AZ130">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA130">
         <v>9</v>
@@ -28666,10 +28666,10 @@
         <v>2</v>
       </c>
       <c r="AY131">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AZ131">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA131">
         <v>17</v>
@@ -28872,10 +28872,10 @@
         <v>1</v>
       </c>
       <c r="AY132">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ132">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA132">
         <v>8</v>
@@ -29078,10 +29078,10 @@
         <v>4</v>
       </c>
       <c r="AY133">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ133">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="BA133">
         <v>4</v>
@@ -29284,10 +29284,10 @@
         <v>4</v>
       </c>
       <c r="AY134">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ134">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA134">
         <v>4</v>
@@ -29490,10 +29490,10 @@
         <v>3</v>
       </c>
       <c r="AY135">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ135">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA135">
         <v>5</v>
@@ -29696,10 +29696,10 @@
         <v>6</v>
       </c>
       <c r="AY136">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ136">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA136">
         <v>10</v>
@@ -29902,7 +29902,7 @@
         <v>2</v>
       </c>
       <c r="AY137">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ137">
         <v>8</v>
@@ -30108,10 +30108,10 @@
         <v>6</v>
       </c>
       <c r="AY138">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AZ138">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA138">
         <v>4</v>
@@ -30314,10 +30314,10 @@
         <v>2</v>
       </c>
       <c r="AY139">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ139">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA139">
         <v>5</v>
@@ -30520,10 +30520,10 @@
         <v>3</v>
       </c>
       <c r="AY140">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ140">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA140">
         <v>7</v>
@@ -30726,10 +30726,10 @@
         <v>3</v>
       </c>
       <c r="AY141">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ141">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA141">
         <v>5</v>
@@ -30932,10 +30932,10 @@
         <v>6</v>
       </c>
       <c r="AY142">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ142">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA142">
         <v>3</v>
@@ -31138,10 +31138,10 @@
         <v>5</v>
       </c>
       <c r="AY143">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ143">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BA143">
         <v>4</v>
@@ -31344,10 +31344,10 @@
         <v>1</v>
       </c>
       <c r="AY144">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ144">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA144">
         <v>4</v>
@@ -31553,7 +31553,7 @@
         <v>9</v>
       </c>
       <c r="AZ145">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA145">
         <v>3</v>
@@ -31759,7 +31759,7 @@
         <v>12</v>
       </c>
       <c r="AZ146">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="BA146">
         <v>1</v>
@@ -31962,10 +31962,10 @@
         <v>2</v>
       </c>
       <c r="AY147">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AZ147">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA147">
         <v>8</v>
@@ -32168,10 +32168,10 @@
         <v>4</v>
       </c>
       <c r="AY148">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ148">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA148">
         <v>4</v>
@@ -32374,10 +32374,10 @@
         <v>3</v>
       </c>
       <c r="AY149">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AZ149">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA149">
         <v>8</v>
@@ -32580,10 +32580,10 @@
         <v>11</v>
       </c>
       <c r="AY150">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ150">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA150">
         <v>6</v>
@@ -32786,10 +32786,10 @@
         <v>3</v>
       </c>
       <c r="AY151">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ151">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA151">
         <v>5</v>
@@ -32992,7 +32992,7 @@
         <v>3</v>
       </c>
       <c r="AY152">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="AZ152">
         <v>6</v>
@@ -33198,10 +33198,10 @@
         <v>9</v>
       </c>
       <c r="AY153">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ153">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA153">
         <v>4</v>
@@ -33404,10 +33404,10 @@
         <v>6</v>
       </c>
       <c r="AY154">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ154">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA154">
         <v>7</v>
@@ -33610,10 +33610,10 @@
         <v>9</v>
       </c>
       <c r="AY155">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ155">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA155">
         <v>5</v>
@@ -33816,10 +33816,10 @@
         <v>5</v>
       </c>
       <c r="AY156">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ156">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA156">
         <v>4</v>
@@ -34022,10 +34022,10 @@
         <v>7</v>
       </c>
       <c r="AY157">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ157">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA157">
         <v>6</v>
@@ -34231,7 +34231,7 @@
         <v>10</v>
       </c>
       <c r="AZ158">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA158">
         <v>4</v>
@@ -34434,10 +34434,10 @@
         <v>5</v>
       </c>
       <c r="AY159">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ159">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA159">
         <v>4</v>
@@ -34640,10 +34640,10 @@
         <v>4</v>
       </c>
       <c r="AY160">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ160">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA160">
         <v>6</v>
@@ -35052,10 +35052,10 @@
         <v>8</v>
       </c>
       <c r="AY162">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ162">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA162">
         <v>2</v>
@@ -35258,7 +35258,7 @@
         <v>5</v>
       </c>
       <c r="AY163">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AZ163">
         <v>10</v>
@@ -35464,10 +35464,10 @@
         <v>3</v>
       </c>
       <c r="AY164">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AZ164">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA164">
         <v>10</v>
@@ -35670,10 +35670,10 @@
         <v>5</v>
       </c>
       <c r="AY165">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ165">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA165">
         <v>9</v>
@@ -35876,7 +35876,7 @@
         <v>5</v>
       </c>
       <c r="AY166">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ166">
         <v>12</v>
@@ -36082,10 +36082,10 @@
         <v>4</v>
       </c>
       <c r="AY167">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ167">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA167">
         <v>2</v>
@@ -36288,7 +36288,7 @@
         <v>9</v>
       </c>
       <c r="AY168">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ168">
         <v>14</v>
@@ -36494,10 +36494,10 @@
         <v>4</v>
       </c>
       <c r="AY169">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ169">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA169">
         <v>7</v>
@@ -36700,10 +36700,10 @@
         <v>7</v>
       </c>
       <c r="AY170">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ170">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA170">
         <v>8</v>
@@ -36906,10 +36906,10 @@
         <v>5</v>
       </c>
       <c r="AY171">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AZ171">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA171">
         <v>9</v>
@@ -37112,10 +37112,10 @@
         <v>12</v>
       </c>
       <c r="AY172">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ172">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA172">
         <v>5</v>
@@ -37318,10 +37318,10 @@
         <v>6</v>
       </c>
       <c r="AY173">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ173">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA173">
         <v>3</v>
@@ -37524,10 +37524,10 @@
         <v>6</v>
       </c>
       <c r="AY174">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ174">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA174">
         <v>2</v>
@@ -37730,7 +37730,7 @@
         <v>4</v>
       </c>
       <c r="AY175">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AZ175">
         <v>11</v>
@@ -37936,10 +37936,10 @@
         <v>11</v>
       </c>
       <c r="AY176">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ176">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA176">
         <v>4</v>
@@ -38142,10 +38142,10 @@
         <v>8</v>
       </c>
       <c r="AY177">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AZ177">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA177">
         <v>9</v>
@@ -38348,10 +38348,10 @@
         <v>2</v>
       </c>
       <c r="AY178">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA178">
         <v>3</v>
@@ -38554,10 +38554,10 @@
         <v>2</v>
       </c>
       <c r="AY179">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AZ179">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA179">
         <v>4</v>
@@ -38760,10 +38760,10 @@
         <v>9</v>
       </c>
       <c r="AY180">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ180">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA180">
         <v>9</v>
@@ -38966,7 +38966,7 @@
         <v>9</v>
       </c>
       <c r="AY181">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ181">
         <v>17</v>
@@ -39172,7 +39172,7 @@
         <v>3</v>
       </c>
       <c r="AY182">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ182">
         <v>3</v>
@@ -39378,10 +39378,10 @@
         <v>14</v>
       </c>
       <c r="AY183">
+        <v>14</v>
+      </c>
+      <c r="AZ183">
         <v>16</v>
-      </c>
-      <c r="AZ183">
-        <v>18</v>
       </c>
       <c r="BA183">
         <v>3</v>
@@ -39584,10 +39584,10 @@
         <v>2</v>
       </c>
       <c r="AY184">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ184">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA184">
         <v>9</v>
@@ -39790,10 +39790,10 @@
         <v>15</v>
       </c>
       <c r="AY185">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ185">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BA185">
         <v>8</v>
@@ -39999,7 +39999,7 @@
         <v>10</v>
       </c>
       <c r="AZ186">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA186">
         <v>6</v>
@@ -40202,10 +40202,10 @@
         <v>6</v>
       </c>
       <c r="AY187">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ187">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA187">
         <v>1</v>
@@ -40408,10 +40408,10 @@
         <v>8</v>
       </c>
       <c r="AY188">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ188">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA188">
         <v>6</v>
@@ -40614,10 +40614,10 @@
         <v>15</v>
       </c>
       <c r="AY189">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ189">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA189">
         <v>3</v>
@@ -41026,10 +41026,10 @@
         <v>10</v>
       </c>
       <c r="AY191">
+        <v>12</v>
+      </c>
+      <c r="AZ191">
         <v>15</v>
-      </c>
-      <c r="AZ191">
-        <v>19</v>
       </c>
       <c r="BA191">
         <v>8</v>
@@ -41232,10 +41232,10 @@
         <v>4</v>
       </c>
       <c r="AY192">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ192">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA192">
         <v>7</v>
@@ -41438,7 +41438,7 @@
         <v>4</v>
       </c>
       <c r="AY193">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ193">
         <v>10</v>
@@ -41644,10 +41644,10 @@
         <v>15</v>
       </c>
       <c r="AY194">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ194">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA194">
         <v>2</v>
@@ -41850,7 +41850,7 @@
         <v>2</v>
       </c>
       <c r="AY195">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ195">
         <v>6</v>
@@ -42056,10 +42056,10 @@
         <v>3</v>
       </c>
       <c r="AY196">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA196">
         <v>6</v>
@@ -42262,10 +42262,10 @@
         <v>9</v>
       </c>
       <c r="AY197">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ197">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BA197">
         <v>6</v>
@@ -42468,10 +42468,10 @@
         <v>6</v>
       </c>
       <c r="AY198">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ198">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA198">
         <v>4</v>
@@ -42674,10 +42674,10 @@
         <v>1</v>
       </c>
       <c r="AY199">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ199">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA199">
         <v>8</v>
@@ -42880,10 +42880,10 @@
         <v>7</v>
       </c>
       <c r="AY200">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ200">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA200">
         <v>3</v>
@@ -43089,7 +43089,7 @@
         <v>5</v>
       </c>
       <c r="AZ201">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA201">
         <v>5</v>
@@ -43292,10 +43292,10 @@
         <v>13</v>
       </c>
       <c r="AY202">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ202">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA202">
         <v>2</v>
@@ -43498,10 +43498,10 @@
         <v>13</v>
       </c>
       <c r="AY203">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ203">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA203">
         <v>6</v>
@@ -43704,10 +43704,10 @@
         <v>6</v>
       </c>
       <c r="AY204">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ204">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA204">
         <v>3</v>
@@ -43913,7 +43913,7 @@
         <v>25</v>
       </c>
       <c r="AZ205">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA205">
         <v>5</v>
@@ -44116,7 +44116,7 @@
         <v>2</v>
       </c>
       <c r="AY206">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ206">
         <v>5</v>
@@ -44322,10 +44322,10 @@
         <v>5</v>
       </c>
       <c r="AY207">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ207">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA207">
         <v>4</v>
@@ -44528,10 +44528,10 @@
         <v>7</v>
       </c>
       <c r="AY208">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ208">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA208">
         <v>4</v>
@@ -44734,10 +44734,10 @@
         <v>9</v>
       </c>
       <c r="AY209">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ209">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA209">
         <v>4</v>
@@ -44940,10 +44940,10 @@
         <v>6</v>
       </c>
       <c r="AY210">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ210">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA210">
         <v>8</v>
@@ -45146,10 +45146,10 @@
         <v>11</v>
       </c>
       <c r="AY211">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ211">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA211">
         <v>7</v>
@@ -45352,10 +45352,10 @@
         <v>8</v>
       </c>
       <c r="AY212">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ212">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA212">
         <v>8</v>
@@ -45558,10 +45558,10 @@
         <v>8</v>
       </c>
       <c r="AY213">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AZ213">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA213">
         <v>6</v>
@@ -45764,10 +45764,10 @@
         <v>13</v>
       </c>
       <c r="AY214">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ214">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA214">
         <v>7</v>
@@ -45970,10 +45970,10 @@
         <v>10</v>
       </c>
       <c r="AY215">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ215">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA215">
         <v>2</v>
@@ -46176,10 +46176,10 @@
         <v>7</v>
       </c>
       <c r="AY216">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ216">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA216">
         <v>11</v>
@@ -46382,10 +46382,10 @@
         <v>4</v>
       </c>
       <c r="AY217">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ217">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA217">
         <v>5</v>
@@ -46588,10 +46588,10 @@
         <v>8</v>
       </c>
       <c r="AY218">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ218">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA218">
         <v>4</v>
@@ -46794,7 +46794,7 @@
         <v>4</v>
       </c>
       <c r="AY219">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ219">
         <v>12</v>
@@ -47000,7 +47000,7 @@
         <v>3</v>
       </c>
       <c r="AY220">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ220">
         <v>9</v>
@@ -47206,10 +47206,10 @@
         <v>3</v>
       </c>
       <c r="AY221">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ221">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA221">
         <v>12</v>
@@ -47412,10 +47412,10 @@
         <v>10</v>
       </c>
       <c r="AY222">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ222">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA222">
         <v>6</v>
@@ -47618,7 +47618,7 @@
         <v>3</v>
       </c>
       <c r="AY223">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ223">
         <v>6</v>
@@ -47824,10 +47824,10 @@
         <v>15</v>
       </c>
       <c r="AY224">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ224">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA224">
         <v>2</v>
@@ -48030,10 +48030,10 @@
         <v>8</v>
       </c>
       <c r="AY225">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ225">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA225">
         <v>1</v>
@@ -48236,10 +48236,10 @@
         <v>18</v>
       </c>
       <c r="AY226">
+        <v>17</v>
+      </c>
+      <c r="AZ226">
         <v>24</v>
-      </c>
-      <c r="AZ226">
-        <v>30</v>
       </c>
       <c r="BA226">
         <v>6</v>
@@ -48442,10 +48442,10 @@
         <v>5</v>
       </c>
       <c r="AY227">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ227">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA227">
         <v>11</v>
@@ -48648,10 +48648,10 @@
         <v>8</v>
       </c>
       <c r="AY228">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ228">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA228">
         <v>1</v>
@@ -48854,10 +48854,10 @@
         <v>6</v>
       </c>
       <c r="AY229">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ229">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA229">
         <v>1</v>
@@ -49063,7 +49063,7 @@
         <v>8</v>
       </c>
       <c r="AZ230">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA230">
         <v>2</v>
@@ -49266,7 +49266,7 @@
         <v>6</v>
       </c>
       <c r="AY231">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ231">
         <v>14</v>
@@ -49472,10 +49472,10 @@
         <v>16</v>
       </c>
       <c r="AY232">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ232">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BA232">
         <v>3</v>
@@ -49678,10 +49678,10 @@
         <v>11</v>
       </c>
       <c r="AY233">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ233">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BA233">
         <v>8</v>
@@ -49884,10 +49884,10 @@
         <v>12</v>
       </c>
       <c r="AY234">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ234">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA234">
         <v>3</v>
@@ -50090,10 +50090,10 @@
         <v>10</v>
       </c>
       <c r="AY235">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ235">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA235">
         <v>1</v>
@@ -50296,10 +50296,10 @@
         <v>5</v>
       </c>
       <c r="AY236">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ236">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA236">
         <v>3</v>
@@ -50502,7 +50502,7 @@
         <v>6</v>
       </c>
       <c r="AY237">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ237">
         <v>11</v>
@@ -50708,10 +50708,10 @@
         <v>7</v>
       </c>
       <c r="AY238">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ238">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA238">
         <v>2</v>
@@ -50914,7 +50914,7 @@
         <v>7</v>
       </c>
       <c r="AY239">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ239">
         <v>12</v>
@@ -51120,10 +51120,10 @@
         <v>16</v>
       </c>
       <c r="AY240">
+        <v>17</v>
+      </c>
+      <c r="AZ240">
         <v>20</v>
-      </c>
-      <c r="AZ240">
-        <v>22</v>
       </c>
       <c r="BA240">
         <v>5</v>
@@ -51326,10 +51326,10 @@
         <v>7</v>
       </c>
       <c r="AY241">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ241">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA241">
         <v>3</v>
@@ -51532,19 +51532,19 @@
         <v>6</v>
       </c>
       <c r="AY242">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ242">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA242">
         <v>6</v>
       </c>
       <c r="BB242">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC242">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD242">
         <v>1.99</v>
@@ -51738,10 +51738,10 @@
         <v>4</v>
       </c>
       <c r="AY243">
+        <v>10</v>
+      </c>
+      <c r="AZ243">
         <v>11</v>
-      </c>
-      <c r="AZ243">
-        <v>12</v>
       </c>
       <c r="BA243">
         <v>3</v>
@@ -51944,10 +51944,10 @@
         <v>8</v>
       </c>
       <c r="AY244">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ244">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA244">
         <v>6</v>
@@ -52150,10 +52150,10 @@
         <v>12</v>
       </c>
       <c r="AY245">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ245">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA245">
         <v>2</v>
@@ -52356,10 +52356,10 @@
         <v>4</v>
       </c>
       <c r="AY246">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ246">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA246">
         <v>8</v>
@@ -52768,10 +52768,10 @@
         <v>11</v>
       </c>
       <c r="AY248">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ248">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BA248">
         <v>3</v>
@@ -52974,7 +52974,7 @@
         <v>4</v>
       </c>
       <c r="AY249">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ249">
         <v>10</v>
@@ -53180,10 +53180,10 @@
         <v>8</v>
       </c>
       <c r="AY250">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ250">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA250">
         <v>2</v>
@@ -53386,10 +53386,10 @@
         <v>10</v>
       </c>
       <c r="AY251">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ251">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA251">
         <v>5</v>
@@ -53592,7 +53592,7 @@
         <v>2</v>
       </c>
       <c r="AY252">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="AZ252">
         <v>6</v>
@@ -53798,10 +53798,10 @@
         <v>9</v>
       </c>
       <c r="AY253">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ253">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA253">
         <v>6</v>
@@ -54004,10 +54004,10 @@
         <v>11</v>
       </c>
       <c r="AY254">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ254">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA254">
         <v>8</v>
@@ -54210,10 +54210,10 @@
         <v>3</v>
       </c>
       <c r="AY255">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AZ255">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA255">
         <v>7</v>
@@ -54416,10 +54416,10 @@
         <v>4</v>
       </c>
       <c r="AY256">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ256">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA256">
         <v>7</v>
@@ -54622,10 +54622,10 @@
         <v>13</v>
       </c>
       <c r="AY257">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ257">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA257">
         <v>4</v>
@@ -54828,10 +54828,10 @@
         <v>10</v>
       </c>
       <c r="AY258">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ258">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA258">
         <v>4</v>
@@ -55034,10 +55034,10 @@
         <v>8</v>
       </c>
       <c r="AY259">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ259">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA259">
         <v>3</v>
@@ -55240,10 +55240,10 @@
         <v>8</v>
       </c>
       <c r="AY260">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AZ260">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA260">
         <v>6</v>
@@ -55446,10 +55446,10 @@
         <v>9</v>
       </c>
       <c r="AY261">
+        <v>13</v>
+      </c>
+      <c r="AZ261">
         <v>15</v>
-      </c>
-      <c r="AZ261">
-        <v>19</v>
       </c>
       <c r="BA261">
         <v>3</v>
@@ -55655,7 +55655,7 @@
         <v>20</v>
       </c>
       <c r="AZ262">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA262">
         <v>5</v>
@@ -55858,10 +55858,10 @@
         <v>13</v>
       </c>
       <c r="AY263">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ263">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BA263">
         <v>2</v>
@@ -56064,10 +56064,10 @@
         <v>12</v>
       </c>
       <c r="AY264">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ264">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BA264">
         <v>2</v>
@@ -56270,7 +56270,7 @@
         <v>12</v>
       </c>
       <c r="AY265">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ265">
         <v>17</v>
@@ -56476,10 +56476,10 @@
         <v>10</v>
       </c>
       <c r="AY266">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ266">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA266">
         <v>9</v>
@@ -56685,7 +56685,7 @@
         <v>5</v>
       </c>
       <c r="AZ267">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA267">
         <v>4</v>
@@ -56888,10 +56888,10 @@
         <v>7</v>
       </c>
       <c r="AY268">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ268">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA268">
         <v>3</v>
@@ -57094,10 +57094,10 @@
         <v>3</v>
       </c>
       <c r="AY269">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ269">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA269">
         <v>3</v>
@@ -57300,10 +57300,10 @@
         <v>3</v>
       </c>
       <c r="AY270">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ270">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA270">
         <v>6</v>
@@ -57506,7 +57506,7 @@
         <v>2</v>
       </c>
       <c r="AY271">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ271">
         <v>7</v>
@@ -57712,7 +57712,7 @@
         <v>4</v>
       </c>
       <c r="AY272">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ272">
         <v>7</v>
@@ -57918,10 +57918,10 @@
         <v>9</v>
       </c>
       <c r="AY273">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ273">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA273">
         <v>3</v>
@@ -58124,7 +58124,7 @@
         <v>5</v>
       </c>
       <c r="AY274">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ274">
         <v>9</v>
@@ -58330,10 +58330,10 @@
         <v>8</v>
       </c>
       <c r="AY275">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ275">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA275">
         <v>2</v>
@@ -58536,10 +58536,10 @@
         <v>12</v>
       </c>
       <c r="AY276">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ276">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA276">
         <v>3</v>
@@ -58742,10 +58742,10 @@
         <v>9</v>
       </c>
       <c r="AY277">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ277">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA277">
         <v>7</v>
@@ -58948,7 +58948,7 @@
         <v>4</v>
       </c>
       <c r="AY278">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ278">
         <v>8</v>
@@ -59154,7 +59154,7 @@
         <v>4</v>
       </c>
       <c r="AY279">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ279">
         <v>6</v>
@@ -59360,10 +59360,10 @@
         <v>6</v>
       </c>
       <c r="AY280">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ280">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA280">
         <v>1</v>
@@ -59566,10 +59566,10 @@
         <v>10</v>
       </c>
       <c r="AY281">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ281">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA281">
         <v>6</v>
@@ -59772,10 +59772,10 @@
         <v>7</v>
       </c>
       <c r="AY282">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ282">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA282">
         <v>5</v>
@@ -59978,10 +59978,10 @@
         <v>18</v>
       </c>
       <c r="AY283">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ283">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="BA283">
         <v>4</v>
@@ -60184,10 +60184,10 @@
         <v>13</v>
       </c>
       <c r="AY284">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ284">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BA284">
         <v>4</v>
@@ -60390,10 +60390,10 @@
         <v>7</v>
       </c>
       <c r="AY285">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ285">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BA285">
         <v>2</v>
@@ -60596,10 +60596,10 @@
         <v>9</v>
       </c>
       <c r="AY286">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ286">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA286">
         <v>4</v>
@@ -60802,19 +60802,19 @@
         <v>2</v>
       </c>
       <c r="AY287">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AZ287">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA287">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB287">
         <v>0</v>
       </c>
       <c r="BC287">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD287">
         <v>1.5</v>
@@ -61008,10 +61008,10 @@
         <v>3</v>
       </c>
       <c r="AY288">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ288">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA288">
         <v>4</v>
@@ -61214,10 +61214,10 @@
         <v>6</v>
       </c>
       <c r="AY289">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ289">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA289">
         <v>8</v>
@@ -61420,10 +61420,10 @@
         <v>10</v>
       </c>
       <c r="AY290">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ290">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA290">
         <v>5</v>
@@ -61626,10 +61626,10 @@
         <v>3</v>
       </c>
       <c r="AY291">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ291">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA291">
         <v>2</v>
@@ -61832,10 +61832,10 @@
         <v>14</v>
       </c>
       <c r="AY292">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ292">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BA292">
         <v>6</v>
@@ -62038,10 +62038,10 @@
         <v>6</v>
       </c>
       <c r="AY293">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AZ293">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA293">
         <v>11</v>
@@ -62244,10 +62244,10 @@
         <v>4</v>
       </c>
       <c r="AY294">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ294">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA294">
         <v>1</v>
@@ -62450,10 +62450,10 @@
         <v>10</v>
       </c>
       <c r="AY295">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AZ295">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA295">
         <v>4</v>
@@ -62656,10 +62656,10 @@
         <v>2</v>
       </c>
       <c r="AY296">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ296">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA296">
         <v>12</v>
@@ -62865,7 +62865,7 @@
         <v>14</v>
       </c>
       <c r="AZ297">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA297">
         <v>3</v>
@@ -63068,10 +63068,10 @@
         <v>8</v>
       </c>
       <c r="AY298">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AZ298">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA298">
         <v>11</v>
@@ -63274,7 +63274,7 @@
         <v>11</v>
       </c>
       <c r="AY299">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ299">
         <v>18</v>
@@ -63480,7 +63480,7 @@
         <v>8</v>
       </c>
       <c r="AY300">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ300">
         <v>15</v>
@@ -63686,10 +63686,10 @@
         <v>2</v>
       </c>
       <c r="AY301">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ301">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA301">
         <v>7</v>
@@ -63892,10 +63892,10 @@
         <v>9</v>
       </c>
       <c r="AY302">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ302">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA302">
         <v>1</v>
@@ -64098,10 +64098,10 @@
         <v>6</v>
       </c>
       <c r="AY303">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ303">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA303">
         <v>6</v>
@@ -64307,7 +64307,7 @@
         <v>9</v>
       </c>
       <c r="AZ304">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA304">
         <v>4</v>
@@ -64510,7 +64510,7 @@
         <v>2</v>
       </c>
       <c r="AY305">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ305">
         <v>6</v>
@@ -64716,10 +64716,10 @@
         <v>3</v>
       </c>
       <c r="AY306">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ306">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA306">
         <v>8</v>
@@ -64922,7 +64922,7 @@
         <v>3</v>
       </c>
       <c r="AY307">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ307">
         <v>10</v>
